--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W24" headerRowCount="1">
-  <autoFilter ref="A17:W24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W25" headerRowCount="1">
+  <autoFilter ref="A17:W25"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -574,20 +574,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -750,55 +750,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MA, QCOM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>171.5996493346816</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>113.6563462979866</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J3" t="n">
-        <v>35.68969575771241</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.149758387444024e-06</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L3" t="n">
-        <v>14.790546875</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M3" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>38.7</v>
+        <v>58.5</v>
       </c>
       <c r="O3" t="n">
-        <v>43.6</v>
+        <v>47</v>
       </c>
       <c r="P3" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>18.504</v>
+        <v>26.042</v>
       </c>
       <c r="T3" t="n">
-        <v>18.504</v>
+        <v>26.042</v>
       </c>
       <c r="U3" t="n">
-        <v>233.534</v>
+        <v>54.396</v>
       </c>
       <c r="V3" t="n">
-        <v>91.316</v>
+        <v>17.882</v>
       </c>
       <c r="W3" t="n">
-        <v>-75.729</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +824,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -825,55 +837,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MA, QCOM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>113.2621681239148</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>113.6563462979866</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J4" t="n">
-        <v>46.8880700793348</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K4" t="n">
-        <v>4.401493125527622e-06</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L4" t="n">
-        <v>13.586640625</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M4" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>40.2</v>
+        <v>58.5</v>
       </c>
       <c r="O4" t="n">
-        <v>38.3</v>
+        <v>47</v>
       </c>
       <c r="P4" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>14.097</v>
+        <v>26.042</v>
       </c>
       <c r="T4" t="n">
-        <v>14.097</v>
+        <v>26.042</v>
       </c>
       <c r="U4" t="n">
-        <v>139.517</v>
+        <v>54.396</v>
       </c>
       <c r="V4" t="n">
-        <v>41.038</v>
+        <v>17.882</v>
       </c>
       <c r="W4" t="n">
-        <v>-36.124</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="5">
@@ -887,7 +911,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -900,55 +924,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MA, UBER</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>113.2621681239148</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>109.1576910033877</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>46.8880700793348</v>
+        <v>56.3945828368037</v>
       </c>
       <c r="K5" t="n">
-        <v>4.401493125527622e-06</v>
+        <v>-9.732791971605792</v>
       </c>
       <c r="L5" t="n">
-        <v>13.586640625</v>
+        <v>17.75079464956312</v>
       </c>
       <c r="M5" t="n">
-        <v>77.77777777777779</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>40.2</v>
+        <v>57</v>
       </c>
       <c r="O5" t="n">
-        <v>38.3</v>
+        <v>48.2</v>
       </c>
       <c r="P5" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>14.097</v>
+        <v>23.526</v>
       </c>
       <c r="T5" t="n">
-        <v>14.097</v>
+        <v>23.526</v>
       </c>
       <c r="U5" t="n">
-        <v>139.517</v>
+        <v>76.224</v>
       </c>
       <c r="V5" t="n">
-        <v>41.038</v>
+        <v>31.024</v>
       </c>
       <c r="W5" t="n">
-        <v>-36.124</v>
+        <v>-51.779</v>
       </c>
     </row>
     <row r="6">
@@ -962,7 +998,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -975,55 +1011,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MA, UBER</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>113.2621681239148</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>109.1576910033877</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
-        <v>46.8880700793348</v>
+        <v>56.3945828368037</v>
       </c>
       <c r="K6" t="n">
-        <v>4.401493125527622e-06</v>
+        <v>-9.732791971605792</v>
       </c>
       <c r="L6" t="n">
-        <v>13.586640625</v>
+        <v>17.75079464956312</v>
       </c>
       <c r="M6" t="n">
-        <v>77.77777777777779</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>40.2</v>
+        <v>57</v>
       </c>
       <c r="O6" t="n">
-        <v>38.3</v>
+        <v>48.2</v>
       </c>
       <c r="P6" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>14.097</v>
+        <v>23.526</v>
       </c>
       <c r="T6" t="n">
-        <v>14.097</v>
+        <v>23.526</v>
       </c>
       <c r="U6" t="n">
-        <v>139.517</v>
+        <v>76.224</v>
       </c>
       <c r="V6" t="n">
-        <v>41.038</v>
+        <v>31.024</v>
       </c>
       <c r="W6" t="n">
-        <v>-36.124</v>
+        <v>-51.779</v>
       </c>
     </row>
     <row r="7">
@@ -1037,7 +1085,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1050,55 +1098,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MA, QCOM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>113.2621681239148</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>113.6563462979866</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J7" t="n">
-        <v>46.8880700793348</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K7" t="n">
-        <v>4.401493125527622e-06</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L7" t="n">
-        <v>13.586640625</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M7" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>40.2</v>
+        <v>58.5</v>
       </c>
       <c r="O7" t="n">
-        <v>38.3</v>
+        <v>47</v>
       </c>
       <c r="P7" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>14.097</v>
+        <v>26.042</v>
       </c>
       <c r="T7" t="n">
-        <v>14.097</v>
+        <v>26.042</v>
       </c>
       <c r="U7" t="n">
-        <v>139.517</v>
+        <v>54.396</v>
       </c>
       <c r="V7" t="n">
-        <v>41.038</v>
+        <v>17.882</v>
       </c>
       <c r="W7" t="n">
-        <v>-36.124</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="8">
@@ -1112,7 +1172,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1127,42 +1187,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
+          <t>MA, QCOM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>80.17424573033163</v>
+        <v>113.6563462979866</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.72% / +1.48% / -1.82% | AKSA.IS: +1.26% / +2.48% / -0.40% | ENJSA.IS: +0.24% / +1.50% / -1.32%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>43.73509800338018</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.511675968566685</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L8" t="n">
-        <v>11.8265388733645</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>226.7</v>
+        <v>58.5</v>
       </c>
       <c r="O8" t="n">
-        <v>52.3</v>
+        <v>47</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1170,22 +1230,22 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>12.925</v>
+        <v>26.042</v>
       </c>
       <c r="T8" t="n">
-        <v>12.925</v>
+        <v>26.042</v>
       </c>
       <c r="U8" t="n">
-        <v>53.841</v>
+        <v>54.396</v>
       </c>
       <c r="V8" t="n">
-        <v>9.707000000000001</v>
+        <v>17.882</v>
       </c>
       <c r="W8" t="n">
-        <v>-20.102</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="9">
@@ -1199,7 +1259,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1212,67 +1272,55 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>80.17424573033163</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: +0.72% / +1.48% / -1.82% | AKSA.IS: +1.26% / +2.48% / -0.40% | ENJSA.IS: +0.24% / +1.50% / -1.32%</t>
-        </is>
-      </c>
+        <v>72.31384487281905</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>43.73509800338018</v>
+        <v>37.12403533357597</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.511675968566685</v>
+        <v>-8.315892014704573</v>
       </c>
       <c r="L9" t="n">
-        <v>11.8265388733645</v>
+        <v>10.17804573632176</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>226.7</v>
+        <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>52.3</v>
+        <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>12.925</v>
+        <v>15.963</v>
       </c>
       <c r="T9" t="n">
-        <v>12.925</v>
+        <v>15.963</v>
       </c>
       <c r="U9" t="n">
-        <v>53.841</v>
+        <v>97.226</v>
       </c>
       <c r="V9" t="n">
-        <v>9.707000000000001</v>
+        <v>42.441</v>
       </c>
       <c r="W9" t="n">
-        <v>-20.102</v>
+        <v>-37.258</v>
       </c>
     </row>
     <row r="10">
@@ -1286,7 +1334,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1299,55 +1347,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MA, UBER</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>113.2621681239148</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>109.1576910033877</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
-        <v>46.8880700793348</v>
+        <v>56.3945828368037</v>
       </c>
       <c r="K10" t="n">
-        <v>4.401493125527622e-06</v>
+        <v>-9.732791971605792</v>
       </c>
       <c r="L10" t="n">
-        <v>13.586640625</v>
+        <v>17.75079464956312</v>
       </c>
       <c r="M10" t="n">
-        <v>77.77777777777779</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>40.2</v>
+        <v>57</v>
       </c>
       <c r="O10" t="n">
-        <v>38.3</v>
+        <v>48.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>14.097</v>
+        <v>23.526</v>
       </c>
       <c r="T10" t="n">
-        <v>14.097</v>
+        <v>23.526</v>
       </c>
       <c r="U10" t="n">
-        <v>139.517</v>
+        <v>76.224</v>
       </c>
       <c r="V10" t="n">
-        <v>41.038</v>
+        <v>31.024</v>
       </c>
       <c r="W10" t="n">
-        <v>-36.124</v>
+        <v>-51.779</v>
       </c>
     </row>
     <row r="11">
@@ -1361,7 +1421,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T6_skor_momentum|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1377,29 +1437,29 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>113.2621681239148</v>
+        <v>48.57758565083525</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>46.8880700793348</v>
+        <v>17.11799836124088</v>
       </c>
       <c r="K11" t="n">
-        <v>4.401493125527622e-06</v>
+        <v>3.774295015995599</v>
       </c>
       <c r="L11" t="n">
-        <v>13.586640625</v>
+        <v>6.042022560264638</v>
       </c>
       <c r="M11" t="n">
-        <v>77.77777777777779</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>40.2</v>
+        <v>67.5</v>
       </c>
       <c r="O11" t="n">
-        <v>38.3</v>
+        <v>54.1</v>
       </c>
       <c r="P11" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1410,19 +1470,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>14.097</v>
+        <v>9.996</v>
       </c>
       <c r="T11" t="n">
-        <v>14.097</v>
+        <v>9.996</v>
       </c>
       <c r="U11" t="n">
-        <v>139.517</v>
+        <v>25.286</v>
       </c>
       <c r="V11" t="n">
-        <v>41.038</v>
+        <v>16.612</v>
       </c>
       <c r="W11" t="n">
-        <v>-36.124</v>
+        <v>-9.667999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1436,7 +1496,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1451,42 +1511,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>COP, CRM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-06 | AKSA.IS: 2026-08-04</t>
+          <t>COP: 2026-08-04 | CRM: 2026-08-10</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>38.79610818915162</v>
+        <v>27.11464560790875</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +1.94% / +2.71% / -0.63% | AKSA.IS: +0.86% / +2.07% / -1.44%</t>
+          <t>COP: +4.29% / +4.51% / -2.74% | CRM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10.65583600136224</v>
+        <v>-2.309006217040011</v>
       </c>
       <c r="K12" t="n">
-        <v>14.91587802615928</v>
+        <v>11.54869430340402</v>
       </c>
       <c r="L12" t="n">
-        <v>21.02029443204582</v>
+        <v>22.59144779746576</v>
       </c>
       <c r="M12" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>91.3</v>
+        <v>125.5</v>
       </c>
       <c r="O12" t="n">
-        <v>52.2</v>
+        <v>48.6</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1497,19 +1557,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>9.993</v>
+        <v>30.091</v>
       </c>
       <c r="T12" t="n">
-        <v>9.993</v>
+        <v>30.091</v>
       </c>
       <c r="U12" t="n">
-        <v>41.157</v>
+        <v>28.397</v>
       </c>
       <c r="V12" t="n">
-        <v>42.994</v>
+        <v>6.208</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.513</v>
+        <v>-7.938</v>
       </c>
     </row>
     <row r="13">
@@ -1523,7 +1583,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1538,42 +1598,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ARCLK.IS, BRSAN.IS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ARCLK.IS: 2026-07-24 | BRSAN.IS: 2026-07-31</t>
+          <t>NVDA: 2026-08-10</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>30.99517004611927</v>
+        <v>-4.689076643110512</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.68% / +2.83% / -3.03% | BRSAN.IS: +19.82% / +20.33% / -0.48%</t>
+          <t>NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7.259269402849022</v>
+        <v>-17.09172083657013</v>
       </c>
       <c r="K13" t="n">
-        <v>14.88866647603475</v>
+        <v>8.208683344692979</v>
       </c>
       <c r="L13" t="n">
-        <v>24.03559217940259</v>
+        <v>18.18815965327731</v>
       </c>
       <c r="M13" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>46.1</v>
+        <v>102.5</v>
       </c>
       <c r="O13" t="n">
-        <v>57</v>
+        <v>41.5</v>
       </c>
       <c r="P13" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1581,22 +1641,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>17.472</v>
+        <v>15.14</v>
       </c>
       <c r="T13" t="n">
-        <v>17.472</v>
+        <v>15.14</v>
       </c>
       <c r="U13" t="n">
-        <v>45.6</v>
+        <v>13.066</v>
       </c>
       <c r="V13" t="n">
-        <v>30.08</v>
+        <v>22.102</v>
       </c>
       <c r="W13" t="n">
-        <v>-14.546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1610,7 +1670,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1625,42 +1685,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CWENE.IS</t>
+          <t>BA, COP</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-10</t>
+          <t>BA: 2026-08-04 | COP: 2026-08-04</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>33.13356088880439</v>
+        <v>10.58832141844577</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BA: -1.86% / +1.66% / -2.66% | COP: +4.29% / +4.51% / -2.74%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4.049930944539293</v>
+        <v>-12.02765652684768</v>
       </c>
       <c r="K14" t="n">
-        <v>14.72494894775047</v>
+        <v>6.882657541326065</v>
       </c>
       <c r="L14" t="n">
-        <v>20.21913622593121</v>
+        <v>24.55026647095465</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>98.7</v>
+        <v>180.5</v>
       </c>
       <c r="O14" t="n">
-        <v>47.7</v>
+        <v>46</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1668,22 +1728,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>20.219</v>
+        <v>27.59</v>
       </c>
       <c r="T14" t="n">
-        <v>14.279</v>
+        <v>27.33</v>
       </c>
       <c r="U14" t="n">
-        <v>36.794</v>
+        <v>-4.274</v>
       </c>
       <c r="V14" t="n">
-        <v>30.572</v>
+        <v>-4.916</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.221</v>
+        <v>-10.362</v>
       </c>
     </row>
     <row r="16">
@@ -1813,17 +1873,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 | 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1836,71 +1896,83 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MA, QCOM</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H18" t="n">
-        <v>171.5996493346816</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>113.6563462979866</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J18" t="n">
-        <v>35.68969575771241</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.149758387444024e-06</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L18" t="n">
-        <v>14.790546875</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M18" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>38.7</v>
+        <v>58.5</v>
       </c>
       <c r="O18" t="n">
-        <v>43.6</v>
+        <v>47</v>
       </c>
       <c r="P18" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>18.504</v>
+        <v>26.042</v>
       </c>
       <c r="T18" t="n">
-        <v>18.504</v>
+        <v>26.042</v>
       </c>
       <c r="U18" t="n">
-        <v>233.534</v>
+        <v>54.396</v>
       </c>
       <c r="V18" t="n">
-        <v>91.316</v>
+        <v>17.882</v>
       </c>
       <c r="W18" t="n">
-        <v>-75.729</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 | 1</t>
+          <t>2 | 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1913,55 +1985,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MA, QCOM</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H19" t="n">
-        <v>113.2621681239148</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>113.6563462979866</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J19" t="n">
-        <v>46.8880700793348</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K19" t="n">
-        <v>4.401493125527622e-06</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L19" t="n">
-        <v>13.586640625</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M19" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>40.2</v>
+        <v>58.5</v>
       </c>
       <c r="O19" t="n">
-        <v>38.3</v>
+        <v>47</v>
       </c>
       <c r="P19" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>14.097</v>
+        <v>26.042</v>
       </c>
       <c r="T19" t="n">
-        <v>14.097</v>
+        <v>26.042</v>
       </c>
       <c r="U19" t="n">
-        <v>139.517</v>
+        <v>54.396</v>
       </c>
       <c r="V19" t="n">
-        <v>41.038</v>
+        <v>17.882</v>
       </c>
       <c r="W19" t="n">
-        <v>-36.124</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="20">
@@ -1972,12 +2056,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 | 2</t>
+          <t>3 | 1 | 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1990,71 +2074,83 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MA, UBER</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H20" t="n">
-        <v>113.2621681239148</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>109.1576910033877</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
-        <v>46.8880700793348</v>
+        <v>56.3945828368037</v>
       </c>
       <c r="K20" t="n">
-        <v>4.401493125527622e-06</v>
+        <v>-9.732791971605792</v>
       </c>
       <c r="L20" t="n">
-        <v>13.586640625</v>
+        <v>17.75079464956312</v>
       </c>
       <c r="M20" t="n">
-        <v>77.77777777777779</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>40.2</v>
+        <v>57</v>
       </c>
       <c r="O20" t="n">
-        <v>38.3</v>
+        <v>48.2</v>
       </c>
       <c r="P20" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>14.097</v>
+        <v>23.526</v>
       </c>
       <c r="T20" t="n">
-        <v>14.097</v>
+        <v>23.526</v>
       </c>
       <c r="U20" t="n">
-        <v>139.517</v>
+        <v>76.224</v>
       </c>
       <c r="V20" t="n">
-        <v>41.038</v>
+        <v>31.024</v>
       </c>
       <c r="W20" t="n">
-        <v>-36.124</v>
+        <v>-51.779</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3 | 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2067,83 +2163,71 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>80.17424573033163</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: +0.72% / +1.48% / -1.82% | AKSA.IS: +1.26% / +2.48% / -0.40% | ENJSA.IS: +0.24% / +1.50% / -1.32%</t>
-        </is>
-      </c>
+        <v>72.31384487281905</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>43.73509800338018</v>
+        <v>37.12403533357597</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.511675968566685</v>
+        <v>-8.315892014704573</v>
       </c>
       <c r="L21" t="n">
-        <v>11.8265388733645</v>
+        <v>10.17804573632176</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N21" t="n">
-        <v>226.7</v>
+        <v>44</v>
       </c>
       <c r="O21" t="n">
-        <v>52.3</v>
+        <v>50</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>12.925</v>
+        <v>15.963</v>
       </c>
       <c r="T21" t="n">
-        <v>12.925</v>
+        <v>15.963</v>
       </c>
       <c r="U21" t="n">
-        <v>53.841</v>
+        <v>97.226</v>
       </c>
       <c r="V21" t="n">
-        <v>9.707000000000001</v>
+        <v>42.441</v>
       </c>
       <c r="W21" t="n">
-        <v>-20.102</v>
+        <v>-37.258</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor</t>
+          <t>T6_skor_momentum|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2156,67 +2240,55 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-06 | AKSA.IS: 2026-08-04</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>38.79610818915162</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: +1.94% / +2.71% / -0.63% | AKSA.IS: +0.86% / +2.07% / -1.44%</t>
-        </is>
-      </c>
+        <v>48.57758565083525</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>10.65583600136224</v>
+        <v>17.11799836124088</v>
       </c>
       <c r="K22" t="n">
-        <v>14.91587802615928</v>
+        <v>3.774295015995599</v>
       </c>
       <c r="L22" t="n">
-        <v>21.02029443204582</v>
+        <v>6.042022560264638</v>
       </c>
       <c r="M22" t="n">
-        <v>72.22222222222221</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>91.3</v>
+        <v>67.5</v>
       </c>
       <c r="O22" t="n">
-        <v>52.2</v>
+        <v>54.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>9.993</v>
+        <v>9.996</v>
       </c>
       <c r="T22" t="n">
-        <v>9.993</v>
+        <v>9.996</v>
       </c>
       <c r="U22" t="n">
-        <v>41.157</v>
+        <v>25.286</v>
       </c>
       <c r="V22" t="n">
-        <v>42.994</v>
+        <v>16.612</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.513</v>
+        <v>-9.667999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2227,12 +2299,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2247,42 +2319,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CWENE.IS</t>
+          <t>COP, CRM</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-10</t>
+          <t>COP: 2026-08-04 | CRM: 2026-08-10</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>33.13356088880439</v>
+        <v>27.11464560790875</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +4.29% / +4.51% / -2.74% | CRM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4.049930944539293</v>
+        <v>-2.309006217040011</v>
       </c>
       <c r="K23" t="n">
-        <v>14.72494894775047</v>
+        <v>11.54869430340402</v>
       </c>
       <c r="L23" t="n">
-        <v>20.21913622593121</v>
+        <v>22.59144779746576</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>98.7</v>
+        <v>125.5</v>
       </c>
       <c r="O23" t="n">
-        <v>47.7</v>
+        <v>48.6</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2290,22 +2362,22 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>20.219</v>
+        <v>30.091</v>
       </c>
       <c r="T23" t="n">
-        <v>14.279</v>
+        <v>30.091</v>
       </c>
       <c r="U23" t="n">
-        <v>36.794</v>
+        <v>28.397</v>
       </c>
       <c r="V23" t="n">
-        <v>30.572</v>
+        <v>6.208</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.221</v>
+        <v>-7.938</v>
       </c>
     </row>
     <row r="24">
@@ -2316,12 +2388,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2336,42 +2408,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ARCLK.IS, BRSAN.IS</t>
+          <t>BA, COP</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ARCLK.IS: 2026-07-24 | BRSAN.IS: 2026-07-31</t>
+          <t>BA: 2026-08-04 | COP: 2026-08-04</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>30.99517004611927</v>
+        <v>10.58832141844577</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.68% / +2.83% / -3.03% | BRSAN.IS: +19.82% / +20.33% / -0.48%</t>
+          <t>BA: -1.86% / +1.66% / -2.66% | COP: +4.29% / +4.51% / -2.74%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7.259269402849022</v>
+        <v>-12.02765652684768</v>
       </c>
       <c r="K24" t="n">
-        <v>14.88866647603475</v>
+        <v>6.882657541326065</v>
       </c>
       <c r="L24" t="n">
-        <v>24.03559217940259</v>
+        <v>24.55026647095465</v>
       </c>
       <c r="M24" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>46.1</v>
+        <v>180.5</v>
       </c>
       <c r="O24" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="P24" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2382,19 +2454,108 @@
         <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>17.472</v>
+        <v>27.59</v>
       </c>
       <c r="T24" t="n">
-        <v>17.472</v>
+        <v>27.33</v>
       </c>
       <c r="U24" t="n">
-        <v>45.6</v>
+        <v>-4.274</v>
       </c>
       <c r="V24" t="n">
-        <v>30.08</v>
+        <v>-4.916</v>
       </c>
       <c r="W24" t="n">
-        <v>-14.546</v>
+        <v>-10.362</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NVDA: 2026-08-10</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>-4.689076643110512</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NVDA: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>-17.09172083657013</v>
+      </c>
+      <c r="K25" t="n">
+        <v>8.208683344692979</v>
+      </c>
+      <c r="L25" t="n">
+        <v>18.18815965327731</v>
+      </c>
+      <c r="M25" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="T25" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="U25" t="n">
+        <v>13.066</v>
+      </c>
+      <c r="V25" t="n">
+        <v>22.102</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2420,16 +2581,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2579,7 +2740,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2594,42 +2755,42 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ENJSA.IS, TRMET.IS</t>
+          <t>MA, QCOM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ENJSA.IS: 2026-08-06 | TRMET.IS: 2026-08-07</t>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>179.0736396556865</v>
+        <v>113.6563462979866</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENJSA.IS: -0.03% / +1.27% / -1.55% | TRMET.IS: +0.30% / +2.32% / -0.40%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>72.80188037535802</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K3" t="n">
-        <v>5.847055796308021</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L3" t="n">
-        <v>20.4127000486159</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>96.2</v>
+        <v>58.5</v>
       </c>
       <c r="O3" t="n">
-        <v>49.5</v>
+        <v>47</v>
       </c>
       <c r="P3" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -2640,19 +2801,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>20.308</v>
+        <v>26.042</v>
       </c>
       <c r="T3" t="n">
-        <v>20.308</v>
+        <v>26.042</v>
       </c>
       <c r="U3" t="n">
-        <v>141.236</v>
+        <v>54.396</v>
       </c>
       <c r="V3" t="n">
-        <v>84.559</v>
+        <v>17.882</v>
       </c>
       <c r="W3" t="n">
-        <v>-31.446</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="4">
@@ -2666,7 +2827,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2681,42 +2842,42 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>MA, QCOM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>101.3283755439263</v>
+        <v>113.6563462979866</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.48% / +1.24% / -2.01% | AKSA.IS: +1.02% / +2.51% / -0.60%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>39.69695362938111</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.048784637331682</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L4" t="n">
-        <v>18.97088964134962</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>115.6</v>
+        <v>58.5</v>
       </c>
       <c r="O4" t="n">
-        <v>45.9</v>
+        <v>47</v>
       </c>
       <c r="P4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -2727,19 +2888,19 @@
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>18.891</v>
+        <v>26.042</v>
       </c>
       <c r="T4" t="n">
-        <v>18.891</v>
+        <v>26.042</v>
       </c>
       <c r="U4" t="n">
-        <v>68.158</v>
+        <v>54.396</v>
       </c>
       <c r="V4" t="n">
-        <v>28.779</v>
+        <v>17.882</v>
       </c>
       <c r="W4" t="n">
-        <v>-28.08</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="5">
@@ -2753,7 +2914,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2768,42 +2929,42 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>MA, UBER</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>93.08073673391458</v>
+        <v>109.1576910033877</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.48% / +1.24% / -2.01% | AKSA.IS: +1.02% / +2.51% / -0.60%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.486427433317534</v>
+        <v>56.3945828368037</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.301997273337168</v>
+        <v>-9.732791971605792</v>
       </c>
       <c r="L5" t="n">
-        <v>24.28294305525478</v>
+        <v>17.75079464956312</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>84.3</v>
+        <v>57</v>
       </c>
       <c r="O5" t="n">
-        <v>44.7</v>
+        <v>48.2</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -2814,19 +2975,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>29.43</v>
+        <v>23.526</v>
       </c>
       <c r="T5" t="n">
-        <v>29.43</v>
+        <v>23.526</v>
       </c>
       <c r="U5" t="n">
-        <v>29.106</v>
+        <v>76.224</v>
       </c>
       <c r="V5" t="n">
-        <v>34.43</v>
+        <v>31.024</v>
       </c>
       <c r="W5" t="n">
-        <v>-44.058</v>
+        <v>-51.779</v>
       </c>
     </row>
     <row r="6">
@@ -2840,7 +3001,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2855,42 +3016,42 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENJSA.IS, TRMET.IS</t>
+          <t>MA, UBER</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ENJSA.IS: 2026-08-06 | TRMET.IS: 2026-08-07</t>
+          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>179.0736396556865</v>
+        <v>109.1576910033877</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ENJSA.IS: -0.03% / +1.27% / -1.55% | TRMET.IS: +0.30% / +2.32% / -0.40%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>72.80188037535802</v>
+        <v>56.3945828368037</v>
       </c>
       <c r="K6" t="n">
-        <v>5.847055796308021</v>
+        <v>-9.732791971605792</v>
       </c>
       <c r="L6" t="n">
-        <v>20.4127000486159</v>
+        <v>17.75079464956312</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>96.2</v>
+        <v>57</v>
       </c>
       <c r="O6" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="P6" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -2901,19 +3062,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>20.308</v>
+        <v>23.526</v>
       </c>
       <c r="T6" t="n">
-        <v>20.308</v>
+        <v>23.526</v>
       </c>
       <c r="U6" t="n">
-        <v>141.236</v>
+        <v>76.224</v>
       </c>
       <c r="V6" t="n">
-        <v>84.559</v>
+        <v>31.024</v>
       </c>
       <c r="W6" t="n">
-        <v>-31.446</v>
+        <v>-51.779</v>
       </c>
     </row>
     <row r="7">
@@ -2927,7 +3088,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2942,42 +3103,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>MA, QCOM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>101.3283755439263</v>
+        <v>113.6563462979866</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.48% / +1.24% / -2.01% | AKSA.IS: +1.02% / +2.51% / -0.60%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.69695362938111</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.048784637331682</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L7" t="n">
-        <v>18.97088964134962</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>115.6</v>
+        <v>58.5</v>
       </c>
       <c r="O7" t="n">
-        <v>45.9</v>
+        <v>47</v>
       </c>
       <c r="P7" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -2988,19 +3149,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>18.891</v>
+        <v>26.042</v>
       </c>
       <c r="T7" t="n">
-        <v>18.891</v>
+        <v>26.042</v>
       </c>
       <c r="U7" t="n">
-        <v>68.158</v>
+        <v>54.396</v>
       </c>
       <c r="V7" t="n">
-        <v>28.779</v>
+        <v>17.882</v>
       </c>
       <c r="W7" t="n">
-        <v>-28.08</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="8">
@@ -3014,7 +3175,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3029,42 +3190,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>MA, QCOM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>83.15828479391203</v>
+        <v>113.6563462979866</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.48% / +1.24% / -2.01% | AKSA.IS: +1.02% / +2.51% / -0.60%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>25.84311170265405</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.278608679814164</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L8" t="n">
-        <v>19.40037281355067</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>85.3</v>
+        <v>58.5</v>
       </c>
       <c r="O8" t="n">
-        <v>45.3</v>
+        <v>47</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -3075,19 +3236,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>28.754</v>
+        <v>26.042</v>
       </c>
       <c r="T8" t="n">
-        <v>28.754</v>
+        <v>26.042</v>
       </c>
       <c r="U8" t="n">
-        <v>37.48</v>
+        <v>54.396</v>
       </c>
       <c r="V8" t="n">
-        <v>17.678</v>
+        <v>17.882</v>
       </c>
       <c r="W8" t="n">
-        <v>-35.665</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="9">
@@ -3101,7 +3262,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3114,67 +3275,55 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ENJSA.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ENJSA.IS: 2026-08-06 | TRMET.IS: 2026-08-07</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>179.0736396556865</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ENJSA.IS: -0.03% / +1.27% / -1.55% | TRMET.IS: +0.30% / +2.32% / -0.40%</t>
-        </is>
-      </c>
+        <v>72.31384487281905</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>72.80188037535802</v>
+        <v>37.12403533357597</v>
       </c>
       <c r="K9" t="n">
-        <v>5.847055796308021</v>
+        <v>-8.315892014704573</v>
       </c>
       <c r="L9" t="n">
-        <v>20.4127000486159</v>
+        <v>10.17804573632176</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>96.2</v>
+        <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="P9" t="n">
         <v>4.1</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>20.308</v>
+        <v>15.963</v>
       </c>
       <c r="T9" t="n">
-        <v>20.308</v>
+        <v>15.963</v>
       </c>
       <c r="U9" t="n">
-        <v>141.236</v>
+        <v>97.226</v>
       </c>
       <c r="V9" t="n">
-        <v>84.559</v>
+        <v>42.441</v>
       </c>
       <c r="W9" t="n">
-        <v>-31.446</v>
+        <v>-37.258</v>
       </c>
     </row>
     <row r="10">
@@ -3188,7 +3337,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E70|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3201,55 +3350,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MA, UBER</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>34.02891348587347</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>109.1576910033877</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
-        <v>16.01327176822664</v>
+        <v>56.3945828368037</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.509191405180133e-06</v>
+        <v>-9.732791971605792</v>
       </c>
       <c r="L10" t="n">
-        <v>5.795310567919277</v>
+        <v>17.75079464956312</v>
       </c>
       <c r="M10" t="n">
-        <v>50</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>20.8</v>
+        <v>57</v>
       </c>
       <c r="O10" t="n">
-        <v>66.7</v>
+        <v>48.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>5.795</v>
+        <v>23.526</v>
       </c>
       <c r="T10" t="n">
-        <v>5.795</v>
+        <v>23.526</v>
       </c>
       <c r="U10" t="n">
-        <v>17.81</v>
+        <v>76.224</v>
       </c>
       <c r="V10" t="n">
-        <v>7.498</v>
+        <v>31.024</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.958</v>
+        <v>-51.779</v>
       </c>
     </row>
     <row r="11">
@@ -3263,7 +3424,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3276,67 +3437,55 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>101.3283755439263</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: +0.48% / +1.24% / -2.01% | AKSA.IS: +1.02% / +2.51% / -0.60%</t>
-        </is>
-      </c>
+        <v>48.57758565083525</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>39.69695362938111</v>
+        <v>17.11799836124088</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.048784637331682</v>
+        <v>3.774295015995599</v>
       </c>
       <c r="L11" t="n">
-        <v>18.97088964134962</v>
+        <v>6.042022560264638</v>
       </c>
       <c r="M11" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>115.6</v>
+        <v>67.5</v>
       </c>
       <c r="O11" t="n">
-        <v>45.9</v>
+        <v>54.1</v>
       </c>
       <c r="P11" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>18.891</v>
+        <v>9.996</v>
       </c>
       <c r="T11" t="n">
-        <v>18.891</v>
+        <v>9.996</v>
       </c>
       <c r="U11" t="n">
-        <v>68.158</v>
+        <v>25.286</v>
       </c>
       <c r="V11" t="n">
-        <v>28.779</v>
+        <v>16.612</v>
       </c>
       <c r="W11" t="n">
-        <v>-28.08</v>
+        <v>-9.667999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -3350,7 +3499,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3365,42 +3514,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CWENE.IS, ENJSA.IS</t>
+          <t>COP, CRM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-10 | ENJSA.IS: 2026-08-10</t>
+          <t>COP: 2026-08-04 | CRM: 2026-08-10</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.866628370507507</v>
+        <v>27.11464560790875</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +4.29% / +4.51% / -2.74% | CRM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-16.25722513630928</v>
+        <v>-2.309006217040011</v>
       </c>
       <c r="K12" t="n">
-        <v>12.89801256516083</v>
+        <v>11.54869430340402</v>
       </c>
       <c r="L12" t="n">
-        <v>24.35983167178696</v>
+        <v>22.59144779746576</v>
       </c>
       <c r="M12" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>102.2</v>
+        <v>125.5</v>
       </c>
       <c r="O12" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3411,19 +3560,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>11.929</v>
+        <v>30.091</v>
       </c>
       <c r="T12" t="n">
-        <v>11.929</v>
+        <v>30.091</v>
       </c>
       <c r="U12" t="n">
-        <v>64.499</v>
+        <v>28.397</v>
       </c>
       <c r="V12" t="n">
-        <v>53.116</v>
+        <v>6.208</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.581</v>
+        <v>-7.938</v>
       </c>
     </row>
     <row r="13">
@@ -3437,7 +3586,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3452,42 +3601,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HEKTS.IS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HEKTS.IS: 2026-08-05</t>
+          <t>NVDA: 2026-08-10</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>17.98915589052719</v>
+        <v>-4.689076643110512</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HEKTS.IS: -1.96% / +1.84% / -2.28%</t>
+          <t>NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-12.03534131276881</v>
+        <v>-17.09172083657013</v>
       </c>
       <c r="K13" t="n">
-        <v>9.815318132471674</v>
+        <v>8.208683344692979</v>
       </c>
       <c r="L13" t="n">
-        <v>19.66917122048275</v>
+        <v>18.18815965327731</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>73.90000000000001</v>
+        <v>102.5</v>
       </c>
       <c r="O13" t="n">
-        <v>45.6</v>
+        <v>41.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3498,19 +3647,19 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>14.477</v>
+        <v>15.14</v>
       </c>
       <c r="T13" t="n">
-        <v>10.484</v>
+        <v>15.14</v>
       </c>
       <c r="U13" t="n">
-        <v>47.824</v>
+        <v>13.066</v>
       </c>
       <c r="V13" t="n">
-        <v>42.922</v>
+        <v>22.102</v>
       </c>
       <c r="W13" t="n">
-        <v>-8.308999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3524,7 +3673,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
+          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3537,55 +3686,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BA, COP</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BA: 2026-08-04 | COP: 2026-08-04</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>5.300307555342831</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>10.58832141844577</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BA: -1.86% / +1.66% / -2.66% | COP: +4.29% / +4.51% / -2.74%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>-3.850913578828841</v>
+        <v>-12.02765652684768</v>
       </c>
       <c r="K14" t="n">
-        <v>8.219882416031998</v>
+        <v>6.882657541326065</v>
       </c>
       <c r="L14" t="n">
-        <v>20.55470960248356</v>
+        <v>24.55026647095465</v>
       </c>
       <c r="M14" t="n">
-        <v>44.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>38.7</v>
+        <v>180.5</v>
       </c>
       <c r="O14" t="n">
-        <v>48.7</v>
+        <v>46</v>
       </c>
       <c r="P14" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>10.695</v>
+        <v>27.59</v>
       </c>
       <c r="T14" t="n">
-        <v>9.141</v>
+        <v>27.33</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.154</v>
+        <v>-4.274</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5659999999999999</v>
+        <v>-4.916</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.38</v>
+        <v>-10.362</v>
       </c>
     </row>
     <row r="16">
@@ -3715,17 +3876,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 | 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3740,42 +3901,42 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENJSA.IS, TRMET.IS</t>
+          <t>MA, QCOM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ENJSA.IS: 2026-08-06 | TRMET.IS: 2026-08-07</t>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>179.0736396556865</v>
+        <v>113.6563462979866</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENJSA.IS: -0.03% / +1.27% / -1.55% | TRMET.IS: +0.30% / +2.32% / -0.40%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>72.80188037535802</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K18" t="n">
-        <v>5.847055796308021</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L18" t="n">
-        <v>20.4127000486159</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>96.2</v>
+        <v>58.5</v>
       </c>
       <c r="O18" t="n">
-        <v>49.5</v>
+        <v>47</v>
       </c>
       <c r="P18" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3786,25 +3947,25 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>20.308</v>
+        <v>26.042</v>
       </c>
       <c r="T18" t="n">
-        <v>20.308</v>
+        <v>26.042</v>
       </c>
       <c r="U18" t="n">
-        <v>141.236</v>
+        <v>54.396</v>
       </c>
       <c r="V18" t="n">
-        <v>84.559</v>
+        <v>17.882</v>
       </c>
       <c r="W18" t="n">
-        <v>-31.446</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3814,7 +3975,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3829,42 +3990,42 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>MA, QCOM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>101.3283755439263</v>
+        <v>113.6563462979866</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.48% / +1.24% / -2.01% | AKSA.IS: +1.02% / +2.51% / -0.60%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>39.69695362938111</v>
+        <v>49.84731201091597</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.048784637331682</v>
+        <v>-13.62426524891165</v>
       </c>
       <c r="L19" t="n">
-        <v>18.97088964134962</v>
+        <v>17.73807655877185</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>115.6</v>
+        <v>58.5</v>
       </c>
       <c r="O19" t="n">
-        <v>45.9</v>
+        <v>47</v>
       </c>
       <c r="P19" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3875,35 +4036,35 @@
         <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>18.891</v>
+        <v>26.042</v>
       </c>
       <c r="T19" t="n">
-        <v>18.891</v>
+        <v>26.042</v>
       </c>
       <c r="U19" t="n">
-        <v>68.158</v>
+        <v>54.396</v>
       </c>
       <c r="V19" t="n">
-        <v>28.779</v>
+        <v>17.882</v>
       </c>
       <c r="W19" t="n">
-        <v>-28.08</v>
+        <v>-54.365</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 | 1 | 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3918,42 +4079,42 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>MA, UBER</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>93.08073673391458</v>
+        <v>109.1576910033877</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.48% / +1.24% / -2.01% | AKSA.IS: +1.02% / +2.51% / -0.60%</t>
+          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>9.486427433317534</v>
+        <v>56.3945828368037</v>
       </c>
       <c r="K20" t="n">
-        <v>-7.301997273337168</v>
+        <v>-9.732791971605792</v>
       </c>
       <c r="L20" t="n">
-        <v>24.28294305525478</v>
+        <v>17.75079464956312</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>84.3</v>
+        <v>57</v>
       </c>
       <c r="O20" t="n">
-        <v>44.7</v>
+        <v>48.2</v>
       </c>
       <c r="P20" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3964,35 +4125,35 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>29.43</v>
+        <v>23.526</v>
       </c>
       <c r="T20" t="n">
-        <v>29.43</v>
+        <v>23.526</v>
       </c>
       <c r="U20" t="n">
-        <v>29.106</v>
+        <v>76.224</v>
       </c>
       <c r="V20" t="n">
-        <v>34.43</v>
+        <v>31.024</v>
       </c>
       <c r="W20" t="n">
-        <v>-44.058</v>
+        <v>-51.779</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4005,67 +4166,55 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>83.15828479391203</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: +0.48% / +1.24% / -2.01% | AKSA.IS: +1.02% / +2.51% / -0.60%</t>
-        </is>
-      </c>
+        <v>72.31384487281905</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>25.84311170265405</v>
+        <v>37.12403533357597</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.278608679814164</v>
+        <v>-8.315892014704573</v>
       </c>
       <c r="L21" t="n">
-        <v>19.40037281355067</v>
+        <v>10.17804573632176</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N21" t="n">
-        <v>85.3</v>
+        <v>44</v>
       </c>
       <c r="O21" t="n">
-        <v>45.3</v>
+        <v>50</v>
       </c>
       <c r="P21" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>28.754</v>
+        <v>15.963</v>
       </c>
       <c r="T21" t="n">
-        <v>28.754</v>
+        <v>15.963</v>
       </c>
       <c r="U21" t="n">
-        <v>37.48</v>
+        <v>97.226</v>
       </c>
       <c r="V21" t="n">
-        <v>17.678</v>
+        <v>42.441</v>
       </c>
       <c r="W21" t="n">
-        <v>-35.665</v>
+        <v>-37.258</v>
       </c>
     </row>
     <row r="22">
@@ -4076,12 +4225,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E70|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T6_skor_momentum|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4097,29 +4246,29 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>34.02891348587347</v>
+        <v>48.57758565083525</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>16.01327176822664</v>
+        <v>17.11799836124088</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.509191405180133e-06</v>
+        <v>3.774295015995599</v>
       </c>
       <c r="L22" t="n">
-        <v>5.795310567919277</v>
+        <v>6.042022560264638</v>
       </c>
       <c r="M22" t="n">
-        <v>50</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>20.8</v>
+        <v>67.5</v>
       </c>
       <c r="O22" t="n">
-        <v>66.7</v>
+        <v>54.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4130,19 +4279,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>5.795</v>
+        <v>9.996</v>
       </c>
       <c r="T22" t="n">
-        <v>5.795</v>
+        <v>9.996</v>
       </c>
       <c r="U22" t="n">
-        <v>17.81</v>
+        <v>25.286</v>
       </c>
       <c r="V22" t="n">
-        <v>7.498</v>
+        <v>16.612</v>
       </c>
       <c r="W22" t="n">
-        <v>-4.958</v>
+        <v>-9.667999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -4153,12 +4302,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4173,42 +4322,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HEKTS.IS</t>
+          <t>COP, CRM</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HEKTS.IS: 2026-08-05</t>
+          <t>COP: 2026-08-04 | CRM: 2026-08-10</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>17.98915589052719</v>
+        <v>27.11464560790875</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>HEKTS.IS: -1.96% / +1.84% / -2.28%</t>
+          <t>COP: +4.29% / +4.51% / -2.74% | CRM: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>-12.03534131276881</v>
+        <v>-2.309006217040011</v>
       </c>
       <c r="K23" t="n">
-        <v>9.815318132471674</v>
+        <v>11.54869430340402</v>
       </c>
       <c r="L23" t="n">
-        <v>19.66917122048275</v>
+        <v>22.59144779746576</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>73.90000000000001</v>
+        <v>125.5</v>
       </c>
       <c r="O23" t="n">
-        <v>45.6</v>
+        <v>48.6</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -4216,22 +4365,22 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>14.477</v>
+        <v>30.091</v>
       </c>
       <c r="T23" t="n">
-        <v>10.484</v>
+        <v>30.091</v>
       </c>
       <c r="U23" t="n">
-        <v>47.824</v>
+        <v>28.397</v>
       </c>
       <c r="V23" t="n">
-        <v>42.922</v>
+        <v>6.208</v>
       </c>
       <c r="W23" t="n">
-        <v>-8.308999999999999</v>
+        <v>-7.938</v>
       </c>
     </row>
     <row r="24">
@@ -4247,7 +4396,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
+          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4260,55 +4409,67 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BA, COP</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>BA: 2026-08-04 | COP: 2026-08-04</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>5.300307555342831</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>10.58832141844577</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BA: -1.86% / +1.66% / -2.66% | COP: +4.29% / +4.51% / -2.74%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>-3.850913578828841</v>
+        <v>-12.02765652684768</v>
       </c>
       <c r="K24" t="n">
-        <v>8.219882416031998</v>
+        <v>6.882657541326065</v>
       </c>
       <c r="L24" t="n">
-        <v>20.55470960248356</v>
+        <v>24.55026647095465</v>
       </c>
       <c r="M24" t="n">
-        <v>44.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>38.7</v>
+        <v>180.5</v>
       </c>
       <c r="O24" t="n">
-        <v>48.7</v>
+        <v>46</v>
       </c>
       <c r="P24" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>10.695</v>
+        <v>27.59</v>
       </c>
       <c r="T24" t="n">
-        <v>9.141</v>
+        <v>27.33</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.154</v>
+        <v>-4.274</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5659999999999999</v>
+        <v>-4.916</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.38</v>
+        <v>-10.362</v>
       </c>
     </row>
     <row r="25">
@@ -4319,12 +4480,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4339,42 +4500,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CWENE.IS, ENJSA.IS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-10 | ENJSA.IS: 2026-08-10</t>
+          <t>NVDA: 2026-08-10</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.866628370507507</v>
+        <v>-4.689076643110512</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-16.25722513630928</v>
+        <v>-17.09172083657013</v>
       </c>
       <c r="K25" t="n">
-        <v>12.89801256516083</v>
+        <v>8.208683344692979</v>
       </c>
       <c r="L25" t="n">
-        <v>24.35983167178696</v>
+        <v>18.18815965327731</v>
       </c>
       <c r="M25" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>102.2</v>
+        <v>102.5</v>
       </c>
       <c r="O25" t="n">
-        <v>48.1</v>
+        <v>41.5</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4382,22 +4543,22 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>11.929</v>
+        <v>15.14</v>
       </c>
       <c r="T25" t="n">
-        <v>11.929</v>
+        <v>15.14</v>
       </c>
       <c r="U25" t="n">
-        <v>64.499</v>
+        <v>13.066</v>
       </c>
       <c r="V25" t="n">
-        <v>53.116</v>
+        <v>22.102</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.581</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W25" headerRowCount="1">
-  <autoFilter ref="A17:W25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W27" headerRowCount="1">
+  <autoFilter ref="A17:W27"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -254,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W25" headerRowCount="1">
-  <autoFilter ref="A17:W25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W27" headerRowCount="1">
+  <autoFilter ref="A17:W27"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -574,16 +574,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -737,57 +737,57 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AGHOL.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-11 | KCHOL.IS: 2026-08-10</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>113.6563462979866</v>
+        <v>196.0145500782185</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.51% / +0.24% / -0.83%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>49.84731201091597</v>
+        <v>63.34899933726425</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.62426524891165</v>
+        <v>-21.81265060949008</v>
       </c>
       <c r="L3" t="n">
-        <v>17.73807655877185</v>
+        <v>15.29584799816456</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N3" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="O3" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="P3" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -798,19 +798,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>26.042</v>
+        <v>31.712</v>
       </c>
       <c r="T3" t="n">
-        <v>26.042</v>
+        <v>31.712</v>
       </c>
       <c r="U3" t="n">
-        <v>54.396</v>
+        <v>75.562</v>
       </c>
       <c r="V3" t="n">
-        <v>17.882</v>
+        <v>36.809</v>
       </c>
       <c r="W3" t="n">
-        <v>-54.365</v>
+        <v>-81.52800000000001</v>
       </c>
     </row>
     <row r="4">
@@ -824,57 +824,57 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>113.6563462979866</v>
+        <v>146.7734767245263</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72% | ENJSA.IS: +2.36% / +3.53% / -1.32%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>49.84731201091597</v>
+        <v>47.22954892038405</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.62426524891165</v>
+        <v>-19.20830486844693</v>
       </c>
       <c r="L4" t="n">
-        <v>17.73807655877185</v>
+        <v>15.35053030132546</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>58.5</v>
+        <v>103.2</v>
       </c>
       <c r="O4" t="n">
-        <v>47</v>
+        <v>45.2</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -882,22 +882,22 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>26.042</v>
+        <v>40.769</v>
       </c>
       <c r="T4" t="n">
-        <v>26.042</v>
+        <v>40.769</v>
       </c>
       <c r="U4" t="n">
-        <v>54.396</v>
+        <v>33.75</v>
       </c>
       <c r="V4" t="n">
-        <v>17.882</v>
+        <v>11.03</v>
       </c>
       <c r="W4" t="n">
-        <v>-54.365</v>
+        <v>-91.593</v>
       </c>
     </row>
     <row r="5">
@@ -911,57 +911,57 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MA, UBER</t>
+          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>109.1576910033877</v>
+        <v>146.7734767245263</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72% | ENJSA.IS: +2.36% / +3.53% / -1.32%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>56.3945828368037</v>
+        <v>47.22954892038405</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.732791971605792</v>
+        <v>-19.20830486844693</v>
       </c>
       <c r="L5" t="n">
-        <v>17.75079464956312</v>
+        <v>15.35053030132546</v>
       </c>
       <c r="M5" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>57</v>
+        <v>103.2</v>
       </c>
       <c r="O5" t="n">
-        <v>48.2</v>
+        <v>45.2</v>
       </c>
       <c r="P5" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>23.526</v>
+        <v>40.769</v>
       </c>
       <c r="T5" t="n">
-        <v>23.526</v>
+        <v>40.769</v>
       </c>
       <c r="U5" t="n">
-        <v>76.224</v>
+        <v>33.75</v>
       </c>
       <c r="V5" t="n">
-        <v>31.024</v>
+        <v>11.03</v>
       </c>
       <c r="W5" t="n">
-        <v>-51.779</v>
+        <v>-91.593</v>
       </c>
     </row>
     <row r="6">
@@ -998,80 +998,68 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>MA, UBER</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>109.1576910033877</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>126.2206153952506</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>56.3945828368037</v>
+        <v>64.25814715116636</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.732791971605792</v>
+        <v>-16.40003330398215</v>
       </c>
       <c r="L6" t="n">
-        <v>17.75079464956312</v>
+        <v>18.07106570176042</v>
       </c>
       <c r="M6" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>57</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>48.2</v>
+        <v>41.5</v>
       </c>
       <c r="P6" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>23.526</v>
+        <v>26.83</v>
       </c>
       <c r="T6" t="n">
-        <v>23.526</v>
+        <v>26.83</v>
       </c>
       <c r="U6" t="n">
-        <v>76.224</v>
+        <v>95.631</v>
       </c>
       <c r="V6" t="n">
-        <v>31.024</v>
+        <v>5.112</v>
       </c>
       <c r="W6" t="n">
-        <v>-51.779</v>
+        <v>-71.735</v>
       </c>
     </row>
     <row r="7">
@@ -1085,57 +1073,57 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AGHOL.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-11 | KCHOL.IS: 2026-08-10</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>113.6563462979866</v>
+        <v>196.0145500782185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.51% / +0.24% / -0.83%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49.84731201091597</v>
+        <v>63.34899933726425</v>
       </c>
       <c r="K7" t="n">
-        <v>-13.62426524891165</v>
+        <v>-21.81265060949008</v>
       </c>
       <c r="L7" t="n">
-        <v>17.73807655877185</v>
+        <v>15.29584799816456</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="O7" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="P7" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1146,19 +1134,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>26.042</v>
+        <v>31.712</v>
       </c>
       <c r="T7" t="n">
-        <v>26.042</v>
+        <v>31.712</v>
       </c>
       <c r="U7" t="n">
-        <v>54.396</v>
+        <v>75.562</v>
       </c>
       <c r="V7" t="n">
-        <v>17.882</v>
+        <v>36.809</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.365</v>
+        <v>-81.52800000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1172,57 +1160,57 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AGHOL.IS, AKSA.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>113.6563462979866</v>
+        <v>93.60033703739212</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49.84731201091597</v>
+        <v>47.53227287837143</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.62426524891165</v>
+        <v>-17.1588592206241</v>
       </c>
       <c r="L8" t="n">
-        <v>17.73807655877185</v>
+        <v>9.119528181849423</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>58.5</v>
+        <v>238.1</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>50.8</v>
       </c>
       <c r="P8" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1233,19 +1221,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>26.042</v>
+        <v>33.389</v>
       </c>
       <c r="T8" t="n">
-        <v>26.042</v>
+        <v>33.389</v>
       </c>
       <c r="U8" t="n">
-        <v>54.396</v>
+        <v>24.685</v>
       </c>
       <c r="V8" t="n">
-        <v>17.882</v>
+        <v>-8.041</v>
       </c>
       <c r="W8" t="n">
-        <v>-54.365</v>
+        <v>-60.117</v>
       </c>
     </row>
     <row r="9">
@@ -1259,45 +1247,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T2_rotasyon|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>72.31384487281905</v>
+        <v>54.76877819482784</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>37.12403533357597</v>
+        <v>27.20988524839496</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.315892014704573</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>10.17804573632176</v>
+        <v>5.126628442603421</v>
       </c>
       <c r="M9" t="n">
-        <v>83.33333333333334</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>44</v>
+        <v>55.1</v>
       </c>
       <c r="O9" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1308,19 +1296,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>15.963</v>
+        <v>6.126</v>
       </c>
       <c r="T9" t="n">
-        <v>15.963</v>
+        <v>6.126</v>
       </c>
       <c r="U9" t="n">
-        <v>97.226</v>
+        <v>39.296</v>
       </c>
       <c r="V9" t="n">
-        <v>42.441</v>
+        <v>20.698</v>
       </c>
       <c r="W9" t="n">
-        <v>-37.258</v>
+        <v>-7.427</v>
       </c>
     </row>
     <row r="10">
@@ -1334,57 +1322,57 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MA, UBER</t>
+          <t>AGHOL.IS, AKSA.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>109.1576910033877</v>
+        <v>93.60033703739212</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>56.3945828368037</v>
+        <v>47.53227287837143</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.732791971605792</v>
+        <v>-17.1588592206241</v>
       </c>
       <c r="L10" t="n">
-        <v>17.75079464956312</v>
+        <v>9.119528181849423</v>
       </c>
       <c r="M10" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>57</v>
+        <v>238.1</v>
       </c>
       <c r="O10" t="n">
-        <v>48.2</v>
+        <v>50.8</v>
       </c>
       <c r="P10" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1395,19 +1383,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>23.526</v>
+        <v>33.389</v>
       </c>
       <c r="T10" t="n">
-        <v>23.526</v>
+        <v>33.389</v>
       </c>
       <c r="U10" t="n">
-        <v>76.224</v>
+        <v>24.685</v>
       </c>
       <c r="V10" t="n">
-        <v>31.024</v>
+        <v>-8.041</v>
       </c>
       <c r="W10" t="n">
-        <v>-51.779</v>
+        <v>-60.117</v>
       </c>
     </row>
     <row r="11">
@@ -1421,68 +1409,80 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-07-29 | ENJSA.IS: 2026-08-04</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>48.57758565083525</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>125.8329115571189</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: +1.02% / +4.09% / -0.81% | ENJSA.IS: +7.38% / +8.60% / 0.00%</t>
+        </is>
+      </c>
       <c r="J11" t="n">
-        <v>17.11799836124088</v>
+        <v>46.52344373225456</v>
       </c>
       <c r="K11" t="n">
-        <v>3.774295015995599</v>
+        <v>-11.00158045293973</v>
       </c>
       <c r="L11" t="n">
-        <v>6.042022560264638</v>
+        <v>9.28497945193878</v>
       </c>
       <c r="M11" t="n">
-        <v>94.44444444444444</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>67.5</v>
+        <v>43.7</v>
       </c>
       <c r="O11" t="n">
-        <v>54.1</v>
+        <v>50</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>9.996</v>
+        <v>24.438</v>
       </c>
       <c r="T11" t="n">
-        <v>9.996</v>
+        <v>24.438</v>
       </c>
       <c r="U11" t="n">
-        <v>25.286</v>
+        <v>39.76</v>
       </c>
       <c r="V11" t="n">
-        <v>16.612</v>
+        <v>25.436</v>
       </c>
       <c r="W11" t="n">
-        <v>-9.667999999999999</v>
+        <v>-37.491</v>
       </c>
     </row>
     <row r="12">
@@ -1496,57 +1496,57 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COP, CRM</t>
+          <t>ARCLK.IS, ASELS.IS, BSOKE.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>COP: 2026-08-04 | CRM: 2026-08-10</t>
+          <t>ARCLK.IS: 2026-08-05 | ASELS.IS: 2026-08-07 | BSOKE.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>27.11464560790875</v>
+        <v>36.17882492656488</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COP: +4.29% / +4.51% / -2.74% | CRM: -0.02% / +0.00% / 0.00%</t>
+          <t>ARCLK.IS: -0.79% / +3.12% / -0.97% | ASELS.IS: -0.87% / +2.47% / -1.27% | BSOKE.IS: +2.96% / +4.50% / -0.51%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-2.309006217040011</v>
+        <v>12.13985438046492</v>
       </c>
       <c r="K12" t="n">
-        <v>11.54869430340402</v>
+        <v>19.46689160117285</v>
       </c>
       <c r="L12" t="n">
-        <v>22.59144779746576</v>
+        <v>17.59856907346148</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>125.5</v>
+        <v>100.2</v>
       </c>
       <c r="O12" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>30.091</v>
+        <v>17.599</v>
       </c>
       <c r="T12" t="n">
-        <v>30.091</v>
+        <v>15.841</v>
       </c>
       <c r="U12" t="n">
-        <v>28.397</v>
+        <v>36.227</v>
       </c>
       <c r="V12" t="n">
-        <v>6.208</v>
+        <v>46.429</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.938</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="13">
@@ -1583,57 +1583,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AGHOL.IS, AKSA.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NVDA: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-4.689076643110512</v>
+        <v>20.72341894805065</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-17.09172083657013</v>
+        <v>-11.44224702348308</v>
       </c>
       <c r="K13" t="n">
-        <v>8.208683344692979</v>
+        <v>15.7607063609839</v>
       </c>
       <c r="L13" t="n">
-        <v>18.18815965327731</v>
+        <v>36.6634557592222</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>102.5</v>
+        <v>212.3</v>
       </c>
       <c r="O13" t="n">
-        <v>41.5</v>
+        <v>49.8</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1641,22 +1641,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>15.14</v>
+        <v>19.486</v>
       </c>
       <c r="T13" t="n">
-        <v>15.14</v>
+        <v>19.486</v>
       </c>
       <c r="U13" t="n">
-        <v>13.066</v>
+        <v>51.535</v>
       </c>
       <c r="V13" t="n">
-        <v>22.102</v>
+        <v>30.523</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-4.673</v>
       </c>
     </row>
     <row r="14">
@@ -1670,57 +1670,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T2_rotasyon|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BA, COP</t>
+          <t>AGHOL.IS, AKSA.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BA: 2026-08-04 | COP: 2026-08-04</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>10.58832141844577</v>
+        <v>39.96325520115791</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BA: -1.86% / +1.66% / -2.66% | COP: +4.29% / +4.51% / -2.74%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-12.02765652684768</v>
+        <v>-1.54670412835074</v>
       </c>
       <c r="K14" t="n">
-        <v>6.882657541326065</v>
+        <v>14.73077373382976</v>
       </c>
       <c r="L14" t="n">
-        <v>24.55026647095465</v>
+        <v>21.31957528357794</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>180.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>46</v>
+        <v>51.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1731,19 +1731,19 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>27.59</v>
+        <v>20.511</v>
       </c>
       <c r="T14" t="n">
-        <v>27.33</v>
+        <v>20.511</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.274</v>
+        <v>36.035</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.916</v>
+        <v>14.423</v>
       </c>
       <c r="W14" t="n">
-        <v>-10.362</v>
+        <v>-6.644</v>
       </c>
     </row>
     <row r="16">
@@ -1883,57 +1883,57 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AGHOL.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-11 | KCHOL.IS: 2026-08-10</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>113.6563462979866</v>
+        <v>196.0145500782185</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.51% / +0.24% / -0.83%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>49.84731201091597</v>
+        <v>63.34899933726425</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.62426524891165</v>
+        <v>-21.81265060949008</v>
       </c>
       <c r="L18" t="n">
-        <v>17.73807655877185</v>
+        <v>15.29584799816456</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N18" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="O18" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="P18" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1944,85 +1944,85 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>26.042</v>
+        <v>31.712</v>
       </c>
       <c r="T18" t="n">
-        <v>26.042</v>
+        <v>31.712</v>
       </c>
       <c r="U18" t="n">
-        <v>54.396</v>
+        <v>75.562</v>
       </c>
       <c r="V18" t="n">
-        <v>17.882</v>
+        <v>36.809</v>
       </c>
       <c r="W18" t="n">
-        <v>-54.365</v>
+        <v>-81.52800000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 | 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>113.6563462979866</v>
+        <v>146.7734767245263</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72% | ENJSA.IS: +2.36% / +3.53% / -1.32%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>49.84731201091597</v>
+        <v>47.22954892038405</v>
       </c>
       <c r="K19" t="n">
-        <v>-13.62426524891165</v>
+        <v>-19.20830486844693</v>
       </c>
       <c r="L19" t="n">
-        <v>17.73807655877185</v>
+        <v>15.35053030132546</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>58.5</v>
+        <v>103.2</v>
       </c>
       <c r="O19" t="n">
-        <v>47</v>
+        <v>45.2</v>
       </c>
       <c r="P19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2030,88 +2030,88 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>26.042</v>
+        <v>40.769</v>
       </c>
       <c r="T19" t="n">
-        <v>26.042</v>
+        <v>40.769</v>
       </c>
       <c r="U19" t="n">
-        <v>54.396</v>
+        <v>33.75</v>
       </c>
       <c r="V19" t="n">
-        <v>17.882</v>
+        <v>11.03</v>
       </c>
       <c r="W19" t="n">
-        <v>-54.365</v>
+        <v>-91.593</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 | 1 | 2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MA, UBER</t>
+          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>109.1576910033877</v>
+        <v>146.7734767245263</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72% | ENJSA.IS: +2.36% / +3.53% / -1.32%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>56.3945828368037</v>
+        <v>47.22954892038405</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.732791971605792</v>
+        <v>-19.20830486844693</v>
       </c>
       <c r="L20" t="n">
-        <v>17.75079464956312</v>
+        <v>15.35053030132546</v>
       </c>
       <c r="M20" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>57</v>
+        <v>103.2</v>
       </c>
       <c r="O20" t="n">
-        <v>48.2</v>
+        <v>45.2</v>
       </c>
       <c r="P20" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2119,28 +2119,28 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>23.526</v>
+        <v>40.769</v>
       </c>
       <c r="T20" t="n">
-        <v>23.526</v>
+        <v>40.769</v>
       </c>
       <c r="U20" t="n">
-        <v>76.224</v>
+        <v>33.75</v>
       </c>
       <c r="V20" t="n">
-        <v>31.024</v>
+        <v>11.03</v>
       </c>
       <c r="W20" t="n">
-        <v>-51.779</v>
+        <v>-91.593</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2150,45 +2150,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>72.31384487281905</v>
+        <v>126.2206153952506</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>37.12403533357597</v>
+        <v>64.25814715116636</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.315892014704573</v>
+        <v>-16.40003330398215</v>
       </c>
       <c r="L21" t="n">
-        <v>10.17804573632176</v>
+        <v>18.07106570176042</v>
       </c>
       <c r="M21" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>44</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>50</v>
+        <v>41.5</v>
       </c>
       <c r="P21" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2199,19 +2199,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>15.963</v>
+        <v>26.83</v>
       </c>
       <c r="T21" t="n">
-        <v>15.963</v>
+        <v>26.83</v>
       </c>
       <c r="U21" t="n">
-        <v>97.226</v>
+        <v>95.631</v>
       </c>
       <c r="V21" t="n">
-        <v>42.441</v>
+        <v>5.112</v>
       </c>
       <c r="W21" t="n">
-        <v>-37.258</v>
+        <v>-71.735</v>
       </c>
     </row>
     <row r="22">
@@ -2227,134 +2227,146 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-07-29 | ENJSA.IS: 2026-08-04</t>
+        </is>
+      </c>
       <c r="H22" t="n">
-        <v>48.57758565083525</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>125.8329115571189</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: +1.02% / +4.09% / -0.81% | ENJSA.IS: +7.38% / +8.60% / 0.00%</t>
+        </is>
+      </c>
       <c r="J22" t="n">
-        <v>17.11799836124088</v>
+        <v>46.52344373225456</v>
       </c>
       <c r="K22" t="n">
-        <v>3.774295015995599</v>
+        <v>-11.00158045293973</v>
       </c>
       <c r="L22" t="n">
-        <v>6.042022560264638</v>
+        <v>9.28497945193878</v>
       </c>
       <c r="M22" t="n">
-        <v>94.44444444444444</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>67.5</v>
+        <v>43.7</v>
       </c>
       <c r="O22" t="n">
-        <v>54.1</v>
+        <v>50</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>9.996</v>
+        <v>24.438</v>
       </c>
       <c r="T22" t="n">
-        <v>9.996</v>
+        <v>24.438</v>
       </c>
       <c r="U22" t="n">
-        <v>25.286</v>
+        <v>39.76</v>
       </c>
       <c r="V22" t="n">
-        <v>16.612</v>
+        <v>25.436</v>
       </c>
       <c r="W22" t="n">
-        <v>-9.667999999999999</v>
+        <v>-37.491</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3 | 2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COP, CRM</t>
+          <t>AGHOL.IS, AKSA.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>COP: 2026-08-04 | CRM: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>27.11464560790875</v>
+        <v>93.60033703739212</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COP: +4.29% / +4.51% / -2.74% | CRM: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>-2.309006217040011</v>
+        <v>47.53227287837143</v>
       </c>
       <c r="K23" t="n">
-        <v>11.54869430340402</v>
+        <v>-17.1588592206241</v>
       </c>
       <c r="L23" t="n">
-        <v>22.59144779746576</v>
+        <v>9.119528181849423</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>125.5</v>
+        <v>238.1</v>
       </c>
       <c r="O23" t="n">
-        <v>48.6</v>
+        <v>50.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2365,108 +2377,96 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>30.091</v>
+        <v>33.389</v>
       </c>
       <c r="T23" t="n">
-        <v>30.091</v>
+        <v>33.389</v>
       </c>
       <c r="U23" t="n">
-        <v>28.397</v>
+        <v>24.685</v>
       </c>
       <c r="V23" t="n">
-        <v>6.208</v>
+        <v>-8.041</v>
       </c>
       <c r="W23" t="n">
-        <v>-7.938</v>
+        <v>-60.117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T2_rotasyon|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>BA, COP</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>BA: 2026-08-04 | COP: 2026-08-04</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>10.58832141844577</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>BA: -1.86% / +1.66% / -2.66% | COP: +4.29% / +4.51% / -2.74%</t>
-        </is>
-      </c>
+        <v>54.76877819482784</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-12.02765652684768</v>
+        <v>27.20988524839496</v>
       </c>
       <c r="K24" t="n">
-        <v>6.882657541326065</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>24.55026647095465</v>
+        <v>5.126628442603421</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N24" t="n">
-        <v>180.5</v>
+        <v>55.1</v>
       </c>
       <c r="O24" t="n">
-        <v>46</v>
+        <v>48.6</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>27.59</v>
+        <v>6.126</v>
       </c>
       <c r="T24" t="n">
-        <v>27.33</v>
+        <v>6.126</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.274</v>
+        <v>39.296</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.916</v>
+        <v>20.698</v>
       </c>
       <c r="W24" t="n">
-        <v>-10.362</v>
+        <v>-7.427</v>
       </c>
     </row>
     <row r="25">
@@ -2477,62 +2477,62 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AGHOL.IS, AKSA.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NVDA: 2026-08-10</t>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-4.689076643110512</v>
+        <v>39.96325520115791</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-17.09172083657013</v>
+        <v>-1.54670412835074</v>
       </c>
       <c r="K25" t="n">
-        <v>8.208683344692979</v>
+        <v>14.73077373382976</v>
       </c>
       <c r="L25" t="n">
-        <v>18.18815965327731</v>
+        <v>21.31957528357794</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>102.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>41.5</v>
+        <v>51.1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2540,22 +2540,200 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>15.14</v>
+        <v>20.511</v>
       </c>
       <c r="T25" t="n">
-        <v>15.14</v>
+        <v>20.511</v>
       </c>
       <c r="U25" t="n">
-        <v>13.066</v>
+        <v>36.035</v>
       </c>
       <c r="V25" t="n">
-        <v>22.102</v>
+        <v>14.423</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-6.644</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ARCLK.IS, ASELS.IS, BSOKE.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ARCLK.IS: 2026-08-05 | ASELS.IS: 2026-08-07 | BSOKE.IS: 2026-08-05</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>36.17882492656488</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ARCLK.IS: -0.79% / +3.12% / -0.97% | ASELS.IS: -0.87% / +2.47% / -1.27% | BSOKE.IS: +2.96% / +4.50% / -0.51%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>12.13985438046492</v>
+      </c>
+      <c r="K26" t="n">
+        <v>19.46689160117285</v>
+      </c>
+      <c r="L26" t="n">
+        <v>17.59856907346148</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>49</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>17.599</v>
+      </c>
+      <c r="T26" t="n">
+        <v>15.841</v>
+      </c>
+      <c r="U26" t="n">
+        <v>36.227</v>
+      </c>
+      <c r="V26" t="n">
+        <v>46.429</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-4.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, AKSA.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>20.72341894805065</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>-11.44224702348308</v>
+      </c>
+      <c r="K27" t="n">
+        <v>15.7607063609839</v>
+      </c>
+      <c r="L27" t="n">
+        <v>36.6634557592222</v>
+      </c>
+      <c r="M27" t="n">
+        <v>100</v>
+      </c>
+      <c r="N27" t="n">
+        <v>212.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>19.486</v>
+      </c>
+      <c r="T27" t="n">
+        <v>19.486</v>
+      </c>
+      <c r="U27" t="n">
+        <v>51.535</v>
+      </c>
+      <c r="V27" t="n">
+        <v>30.523</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-4.673</v>
       </c>
     </row>
   </sheetData>
@@ -2577,16 +2755,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -2740,57 +2918,57 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AEFES.IS, AGHOL.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>113.6563462979866</v>
+        <v>142.9866408823153</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>49.84731201091597</v>
+        <v>65.19165962041819</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.62426524891165</v>
+        <v>-11.3190314802712</v>
       </c>
       <c r="L3" t="n">
-        <v>17.73807655877185</v>
+        <v>17.81201575904778</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>58.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="P3" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -2801,19 +2979,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="T3" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="U3" t="n">
-        <v>54.396</v>
+        <v>58.083</v>
       </c>
       <c r="V3" t="n">
-        <v>17.882</v>
+        <v>6.64</v>
       </c>
       <c r="W3" t="n">
-        <v>-54.365</v>
+        <v>-53.623</v>
       </c>
     </row>
     <row r="4">
@@ -2827,57 +3005,57 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AEFES.IS, AGHOL.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>113.6563462979866</v>
+        <v>142.9866408823153</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>49.84731201091597</v>
+        <v>65.19165962041819</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.62426524891165</v>
+        <v>-11.3190314802712</v>
       </c>
       <c r="L4" t="n">
-        <v>17.73807655877185</v>
+        <v>17.81201575904778</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>58.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -2888,19 +3066,19 @@
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="T4" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="U4" t="n">
-        <v>54.396</v>
+        <v>58.083</v>
       </c>
       <c r="V4" t="n">
-        <v>17.882</v>
+        <v>6.64</v>
       </c>
       <c r="W4" t="n">
-        <v>-54.365</v>
+        <v>-53.623</v>
       </c>
     </row>
     <row r="5">
@@ -2914,57 +3092,57 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T3_kademeli_slot|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MA, UBER</t>
+          <t>AEFES.IS, AGHOL.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>109.1576910033877</v>
+        <v>124.0849320677873</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>56.3945828368037</v>
+        <v>52.92070323228515</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.732791971605792</v>
+        <v>-29.40155890265139</v>
       </c>
       <c r="L5" t="n">
-        <v>17.75079464956312</v>
+        <v>21.28997122934656</v>
       </c>
       <c r="M5" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="O5" t="n">
-        <v>48.2</v>
+        <v>41.7</v>
       </c>
       <c r="P5" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -2975,19 +3153,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>23.526</v>
+        <v>36.284</v>
       </c>
       <c r="T5" t="n">
-        <v>23.526</v>
+        <v>36.284</v>
       </c>
       <c r="U5" t="n">
-        <v>76.224</v>
+        <v>36.191</v>
       </c>
       <c r="V5" t="n">
-        <v>31.024</v>
+        <v>-10.159</v>
       </c>
       <c r="W5" t="n">
-        <v>-51.779</v>
+        <v>-77.556</v>
       </c>
     </row>
     <row r="6">
@@ -3001,57 +3179,57 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MA, UBER</t>
+          <t>AEFES.IS, AGHOL.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>109.1576910033877</v>
+        <v>142.9866408823153</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>56.3945828368037</v>
+        <v>65.19165962041819</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.732791971605792</v>
+        <v>-11.3190314802712</v>
       </c>
       <c r="L6" t="n">
-        <v>17.75079464956312</v>
+        <v>17.81201575904778</v>
       </c>
       <c r="M6" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>57</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>48.2</v>
+        <v>47.1</v>
       </c>
       <c r="P6" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -3062,19 +3240,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>23.526</v>
+        <v>28.525</v>
       </c>
       <c r="T6" t="n">
-        <v>23.526</v>
+        <v>28.525</v>
       </c>
       <c r="U6" t="n">
-        <v>76.224</v>
+        <v>58.083</v>
       </c>
       <c r="V6" t="n">
-        <v>31.024</v>
+        <v>6.64</v>
       </c>
       <c r="W6" t="n">
-        <v>-51.779</v>
+        <v>-53.623</v>
       </c>
     </row>
     <row r="7">
@@ -3088,57 +3266,57 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AEFES.IS, AGHOL.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>113.6563462979866</v>
+        <v>142.9866408823153</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49.84731201091597</v>
+        <v>65.19165962041819</v>
       </c>
       <c r="K7" t="n">
-        <v>-13.62426524891165</v>
+        <v>-11.3190314802712</v>
       </c>
       <c r="L7" t="n">
-        <v>17.73807655877185</v>
+        <v>17.81201575904778</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>58.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="P7" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -3149,19 +3327,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="T7" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="U7" t="n">
-        <v>54.396</v>
+        <v>58.083</v>
       </c>
       <c r="V7" t="n">
-        <v>17.882</v>
+        <v>6.64</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.365</v>
+        <v>-53.623</v>
       </c>
     </row>
     <row r="8">
@@ -3175,57 +3353,57 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AEFES.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | ENJSA.IS: 2026-08-06</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>113.6563462979866</v>
+        <v>101.1085282252811</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.96% / +3.13% / -1.55%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49.84731201091597</v>
+        <v>54.14354947497561</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.62426524891165</v>
+        <v>-16.42514448231509</v>
       </c>
       <c r="L8" t="n">
-        <v>17.73807655877185</v>
+        <v>14.8067531783691</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>58.5</v>
+        <v>99.2</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>45.5</v>
       </c>
       <c r="P8" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -3236,19 +3414,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>26.042</v>
+        <v>33.244</v>
       </c>
       <c r="T8" t="n">
-        <v>26.042</v>
+        <v>33.244</v>
       </c>
       <c r="U8" t="n">
-        <v>54.396</v>
+        <v>5.697</v>
       </c>
       <c r="V8" t="n">
-        <v>17.882</v>
+        <v>-13.977</v>
       </c>
       <c r="W8" t="n">
-        <v>-54.365</v>
+        <v>-50.178</v>
       </c>
     </row>
     <row r="9">
@@ -3262,45 +3440,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>72.31384487281905</v>
+        <v>47.83080759857017</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>37.12403533357597</v>
+        <v>25.16275776739663</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.315892014704573</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>10.17804573632176</v>
+        <v>3.614619346743542</v>
       </c>
       <c r="M9" t="n">
-        <v>83.33333333333334</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N9" t="n">
-        <v>44</v>
+        <v>18.4</v>
       </c>
       <c r="O9" t="n">
-        <v>50</v>
+        <v>62.2</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -3311,19 +3489,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>15.963</v>
+        <v>6.293</v>
       </c>
       <c r="T9" t="n">
-        <v>15.963</v>
+        <v>6.293</v>
       </c>
       <c r="U9" t="n">
-        <v>97.226</v>
+        <v>33.654</v>
       </c>
       <c r="V9" t="n">
-        <v>42.441</v>
+        <v>14.787</v>
       </c>
       <c r="W9" t="n">
-        <v>-37.258</v>
+        <v>-8.975</v>
       </c>
     </row>
     <row r="10">
@@ -3337,80 +3515,68 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T2_rotasyon|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>MA, UBER</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>109.1576910033877</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>55.35821059962866</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>56.3945828368037</v>
+        <v>24.87579530471873</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.732791971605792</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>17.75079464956312</v>
+        <v>5.722314490411828</v>
       </c>
       <c r="M10" t="n">
-        <v>94.44444444444444</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N10" t="n">
-        <v>57</v>
+        <v>27.3</v>
       </c>
       <c r="O10" t="n">
-        <v>48.2</v>
+        <v>67.3</v>
       </c>
       <c r="P10" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>23.526</v>
+        <v>5.722</v>
       </c>
       <c r="T10" t="n">
-        <v>23.526</v>
+        <v>5.722</v>
       </c>
       <c r="U10" t="n">
-        <v>76.224</v>
+        <v>43.47</v>
       </c>
       <c r="V10" t="n">
-        <v>31.024</v>
+        <v>22.875</v>
       </c>
       <c r="W10" t="n">
-        <v>-51.779</v>
+        <v>-4.271</v>
       </c>
     </row>
     <row r="11">
@@ -3424,45 +3590,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>48.57758565083525</v>
+        <v>54.89485286492015</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>17.11799836124088</v>
+        <v>24.50335174084792</v>
       </c>
       <c r="K11" t="n">
-        <v>3.774295015995599</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6.042022560264638</v>
+        <v>5.722314490411828</v>
       </c>
       <c r="M11" t="n">
-        <v>94.44444444444444</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N11" t="n">
-        <v>67.5</v>
+        <v>26.8</v>
       </c>
       <c r="O11" t="n">
-        <v>54.1</v>
+        <v>68.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -3473,19 +3639,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>9.996</v>
+        <v>5.722</v>
       </c>
       <c r="T11" t="n">
-        <v>9.996</v>
+        <v>5.722</v>
       </c>
       <c r="U11" t="n">
-        <v>25.286</v>
+        <v>42.828</v>
       </c>
       <c r="V11" t="n">
-        <v>16.612</v>
+        <v>22.326</v>
       </c>
       <c r="W11" t="n">
-        <v>-9.667999999999999</v>
+        <v>-4.336</v>
       </c>
     </row>
     <row r="12">
@@ -3499,57 +3665,57 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COP, CRM</t>
+          <t>TRENJ.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>COP: 2026-08-04 | CRM: 2026-08-10</t>
+          <t>TRENJ.IS: 2026-08-11 | TUPRS.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>27.11464560790875</v>
+        <v>32.85505973212863</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COP: +4.29% / +4.51% / -2.74% | CRM: -0.02% / +0.00% / 0.00%</t>
+          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +12.79% / +13.47% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-2.309006217040011</v>
+        <v>4.084120214350562</v>
       </c>
       <c r="K12" t="n">
-        <v>11.54869430340402</v>
+        <v>18.96421883109429</v>
       </c>
       <c r="L12" t="n">
-        <v>22.59144779746576</v>
+        <v>14.21663032630368</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>125.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>48.6</v>
+        <v>50.3</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3560,19 +3726,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>30.091</v>
+        <v>13.97</v>
       </c>
       <c r="T12" t="n">
-        <v>30.091</v>
+        <v>12.828</v>
       </c>
       <c r="U12" t="n">
-        <v>28.397</v>
+        <v>89.71899999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>6.208</v>
+        <v>75.795</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.938</v>
+        <v>-1.631</v>
       </c>
     </row>
     <row r="13">
@@ -3586,57 +3752,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ENJSA.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NVDA: 2026-08-10</t>
+          <t>ENJSA.IS: 2026-08-06 | TUPRS.IS: 2026-08-10</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-4.689076643110512</v>
+        <v>43.27571901061749</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>ENJSA.IS: +1.96% / +3.13% / -1.55% | TUPRS.IS: +0.40% / +1.01% / -0.75%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-17.09172083657013</v>
+        <v>17.15699621331257</v>
       </c>
       <c r="K13" t="n">
-        <v>8.208683344692979</v>
+        <v>17.38568208693025</v>
       </c>
       <c r="L13" t="n">
-        <v>18.18815965327731</v>
+        <v>18.48670982489935</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>102.5</v>
+        <v>197.9</v>
       </c>
       <c r="O13" t="n">
-        <v>41.5</v>
+        <v>48.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3644,22 +3810,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>15.14</v>
+        <v>19.604</v>
       </c>
       <c r="T13" t="n">
-        <v>15.14</v>
+        <v>19.604</v>
       </c>
       <c r="U13" t="n">
-        <v>13.066</v>
+        <v>66.898</v>
       </c>
       <c r="V13" t="n">
-        <v>22.102</v>
+        <v>35.864</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-3.609</v>
       </c>
     </row>
     <row r="14">
@@ -3673,57 +3839,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T6_skor_momentum|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BA, COP</t>
+          <t>BRSAN.IS, MGROS.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BA: 2026-08-04 | COP: 2026-08-04</t>
+          <t>BRSAN.IS: 2026-08-11 | MGROS.IS: 2026-08-11</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>10.58832141844577</v>
+        <v>4.985786278494286</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BA: -1.86% / +1.66% / -2.66% | COP: +4.29% / +4.51% / -2.74%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | MGROS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-12.02765652684768</v>
+        <v>-0.8807538058383857</v>
       </c>
       <c r="K14" t="n">
-        <v>6.882657541326065</v>
+        <v>10.86132436418468</v>
       </c>
       <c r="L14" t="n">
-        <v>24.55026647095465</v>
+        <v>8.252478196531154</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N14" t="n">
-        <v>180.5</v>
+        <v>26.3</v>
       </c>
       <c r="O14" t="n">
-        <v>46</v>
+        <v>45.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3734,19 +3900,19 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>27.59</v>
+        <v>4.228</v>
       </c>
       <c r="T14" t="n">
-        <v>27.33</v>
+        <v>4.228</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.274</v>
+        <v>7.025</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.916</v>
+        <v>6.195</v>
       </c>
       <c r="W14" t="n">
-        <v>-10.362</v>
+        <v>-1.429</v>
       </c>
     </row>
     <row r="16">
@@ -3881,62 +4047,62 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 | 2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AEFES.IS, AGHOL.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>113.6563462979866</v>
+        <v>142.9866408823153</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>49.84731201091597</v>
+        <v>65.19165962041819</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.62426524891165</v>
+        <v>-11.3190314802712</v>
       </c>
       <c r="L18" t="n">
-        <v>17.73807655877185</v>
+        <v>17.81201575904778</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>58.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="P18" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3947,19 +4113,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="T18" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="U18" t="n">
-        <v>54.396</v>
+        <v>58.083</v>
       </c>
       <c r="V18" t="n">
-        <v>17.882</v>
+        <v>6.64</v>
       </c>
       <c r="W18" t="n">
-        <v>-54.365</v>
+        <v>-53.623</v>
       </c>
     </row>
     <row r="19">
@@ -3970,62 +4136,62 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 | 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MA, QCOM</t>
+          <t>AEFES.IS, AGHOL.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | QCOM: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>113.6563462979866</v>
+        <v>142.9866408823153</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | QCOM: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>49.84731201091597</v>
+        <v>65.19165962041819</v>
       </c>
       <c r="K19" t="n">
-        <v>-13.62426524891165</v>
+        <v>-11.3190314802712</v>
       </c>
       <c r="L19" t="n">
-        <v>17.73807655877185</v>
+        <v>17.81201575904778</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>58.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="P19" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -4036,85 +4202,85 @@
         <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="T19" t="n">
-        <v>26.042</v>
+        <v>28.525</v>
       </c>
       <c r="U19" t="n">
-        <v>54.396</v>
+        <v>58.083</v>
       </c>
       <c r="V19" t="n">
-        <v>17.882</v>
+        <v>6.64</v>
       </c>
       <c r="W19" t="n">
-        <v>-54.365</v>
+        <v>-53.623</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 | 1 | 2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T3_kademeli_slot|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MA, UBER</t>
+          <t>AEFES.IS, AGHOL.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MA: 2026-08-04 | UBER: 2026-08-10</t>
+          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>109.1576910033877</v>
+        <v>124.0849320677873</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MA: -1.41% / +1.25% / -2.06% | UBER: -0.02% / +0.00% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>56.3945828368037</v>
+        <v>52.92070323228515</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.732791971605792</v>
+        <v>-29.40155890265139</v>
       </c>
       <c r="L20" t="n">
-        <v>17.75079464956312</v>
+        <v>21.28997122934656</v>
       </c>
       <c r="M20" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="O20" t="n">
-        <v>48.2</v>
+        <v>41.7</v>
       </c>
       <c r="P20" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -4125,96 +4291,108 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>23.526</v>
+        <v>36.284</v>
       </c>
       <c r="T20" t="n">
-        <v>23.526</v>
+        <v>36.284</v>
       </c>
       <c r="U20" t="n">
-        <v>76.224</v>
+        <v>36.191</v>
       </c>
       <c r="V20" t="n">
-        <v>31.024</v>
+        <v>-10.159</v>
       </c>
       <c r="W20" t="n">
-        <v>-51.779</v>
+        <v>-77.556</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AEFES.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AEFES.IS: 2026-08-11 | ENJSA.IS: 2026-08-06</t>
+        </is>
+      </c>
       <c r="H21" t="n">
-        <v>72.31384487281905</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>101.1085282252811</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.96% / +3.13% / -1.55%</t>
+        </is>
+      </c>
       <c r="J21" t="n">
-        <v>37.12403533357597</v>
+        <v>54.14354947497561</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.315892014704573</v>
+        <v>-16.42514448231509</v>
       </c>
       <c r="L21" t="n">
-        <v>10.17804573632176</v>
+        <v>14.8067531783691</v>
       </c>
       <c r="M21" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>44</v>
+        <v>99.2</v>
       </c>
       <c r="O21" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="P21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>15.963</v>
+        <v>33.244</v>
       </c>
       <c r="T21" t="n">
-        <v>15.963</v>
+        <v>33.244</v>
       </c>
       <c r="U21" t="n">
-        <v>97.226</v>
+        <v>5.697</v>
       </c>
       <c r="V21" t="n">
-        <v>42.441</v>
+        <v>-13.977</v>
       </c>
       <c r="W21" t="n">
-        <v>-37.258</v>
+        <v>-50.178</v>
       </c>
     </row>
     <row r="22">
@@ -4225,50 +4403,50 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>48.57758565083525</v>
+        <v>55.35821059962866</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>17.11799836124088</v>
+        <v>24.87579530471873</v>
       </c>
       <c r="K22" t="n">
-        <v>3.774295015995599</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6.042022560264638</v>
+        <v>5.722314490411828</v>
       </c>
       <c r="M22" t="n">
-        <v>94.44444444444444</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N22" t="n">
-        <v>67.5</v>
+        <v>27.3</v>
       </c>
       <c r="O22" t="n">
-        <v>54.1</v>
+        <v>67.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4279,197 +4457,173 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>9.996</v>
+        <v>5.722</v>
       </c>
       <c r="T22" t="n">
-        <v>9.996</v>
+        <v>5.722</v>
       </c>
       <c r="U22" t="n">
-        <v>25.286</v>
+        <v>43.47</v>
       </c>
       <c r="V22" t="n">
-        <v>16.612</v>
+        <v>22.875</v>
       </c>
       <c r="W22" t="n">
-        <v>-9.667999999999999</v>
+        <v>-4.271</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T1_genislik_skor|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>COP, CRM</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>COP: 2026-08-04 | CRM: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>27.11464560790875</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>COP: +4.29% / +4.51% / -2.74% | CRM: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>54.89485286492015</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>-2.309006217040011</v>
+        <v>24.50335174084792</v>
       </c>
       <c r="K23" t="n">
-        <v>11.54869430340402</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>22.59144779746576</v>
+        <v>5.722314490411828</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N23" t="n">
-        <v>125.5</v>
+        <v>26.8</v>
       </c>
       <c r="O23" t="n">
-        <v>48.6</v>
+        <v>68.5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>30.091</v>
+        <v>5.722</v>
       </c>
       <c r="T23" t="n">
-        <v>30.091</v>
+        <v>5.722</v>
       </c>
       <c r="U23" t="n">
-        <v>28.397</v>
+        <v>42.828</v>
       </c>
       <c r="V23" t="n">
-        <v>6.208</v>
+        <v>22.326</v>
       </c>
       <c r="W23" t="n">
-        <v>-7.938</v>
+        <v>-4.336</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>BA, COP</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>BA: 2026-08-04 | COP: 2026-08-04</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>10.58832141844577</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>BA: -1.86% / +1.66% / -2.66% | COP: +4.29% / +4.51% / -2.74%</t>
-        </is>
-      </c>
+        <v>47.83080759857017</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-12.02765652684768</v>
+        <v>25.16275776739663</v>
       </c>
       <c r="K24" t="n">
-        <v>6.882657541326065</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>24.55026647095465</v>
+        <v>3.614619346743542</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N24" t="n">
-        <v>180.5</v>
+        <v>18.4</v>
       </c>
       <c r="O24" t="n">
-        <v>46</v>
+        <v>62.2</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>27.59</v>
+        <v>6.293</v>
       </c>
       <c r="T24" t="n">
-        <v>27.33</v>
+        <v>6.293</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.274</v>
+        <v>33.654</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.916</v>
+        <v>14.787</v>
       </c>
       <c r="W24" t="n">
-        <v>-10.362</v>
+        <v>-8.975</v>
       </c>
     </row>
     <row r="25">
@@ -4485,57 +4639,57 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ENJSA.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NVDA: 2026-08-10</t>
+          <t>ENJSA.IS: 2026-08-06 | TUPRS.IS: 2026-08-10</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-4.689076643110512</v>
+        <v>43.27571901061749</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>ENJSA.IS: +1.96% / +3.13% / -1.55% | TUPRS.IS: +0.40% / +1.01% / -0.75%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-17.09172083657013</v>
+        <v>17.15699621331257</v>
       </c>
       <c r="K25" t="n">
-        <v>8.208683344692979</v>
+        <v>17.38568208693025</v>
       </c>
       <c r="L25" t="n">
-        <v>18.18815965327731</v>
+        <v>18.48670982489935</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>102.5</v>
+        <v>197.9</v>
       </c>
       <c r="O25" t="n">
-        <v>41.5</v>
+        <v>48.1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4543,22 +4697,200 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>15.14</v>
+        <v>19.604</v>
       </c>
       <c r="T25" t="n">
-        <v>15.14</v>
+        <v>19.604</v>
       </c>
       <c r="U25" t="n">
-        <v>13.066</v>
+        <v>66.898</v>
       </c>
       <c r="V25" t="n">
-        <v>22.102</v>
+        <v>35.864</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-3.609</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TRENJ.IS, TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>TRENJ.IS: 2026-08-11 | TUPRS.IS: 2026-08-05</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>32.85505973212863</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +12.79% / +13.47% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>4.084120214350562</v>
+      </c>
+      <c r="K26" t="n">
+        <v>18.96421883109429</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14.21663032630368</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="O26" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="T26" t="n">
+        <v>12.828</v>
+      </c>
+      <c r="U26" t="n">
+        <v>89.71899999999999</v>
+      </c>
+      <c r="V26" t="n">
+        <v>75.795</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1.631</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T6_skor_momentum|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, MGROS.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-11 | MGROS.IS: 2026-08-11</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>4.985786278494286</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | MGROS.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.8807538058383857</v>
+      </c>
+      <c r="K27" t="n">
+        <v>10.86132436418468</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8.252478196531154</v>
+      </c>
+      <c r="M27" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="N27" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.228</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4.228</v>
+      </c>
+      <c r="U27" t="n">
+        <v>7.025</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.195</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-1.429</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -587,7 +587,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -761,21 +761,21 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>196.0145500782185</v>
+        <v>196.0145460497629</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.51% / +0.24% / -0.83%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -3.35% / +0.24% / -3.48%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>63.34899933726425</v>
+        <v>63.34898599832736</v>
       </c>
       <c r="K3" t="n">
-        <v>-21.81265060949008</v>
+        <v>-22.93357048073267</v>
       </c>
       <c r="L3" t="n">
-        <v>15.29584799816456</v>
+        <v>15.29584021689743</v>
       </c>
       <c r="M3" t="n">
         <v>77.77777777777779</v>
@@ -798,19 +798,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>31.712</v>
+        <v>32.691</v>
       </c>
       <c r="T3" t="n">
-        <v>31.712</v>
+        <v>32.691</v>
       </c>
       <c r="U3" t="n">
-        <v>75.562</v>
+        <v>73.045</v>
       </c>
       <c r="V3" t="n">
-        <v>36.809</v>
+        <v>34.847</v>
       </c>
       <c r="W3" t="n">
-        <v>-81.52800000000001</v>
+        <v>-84.045</v>
       </c>
     </row>
     <row r="4">
@@ -848,21 +848,21 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>146.7734767245263</v>
+        <v>146.7734767607337</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72% | ENJSA.IS: +2.36% / +3.53% / -1.32%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28% | ENJSA.IS: -0.20% / +3.53% / -3.44%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>47.22954892038405</v>
+        <v>47.22954822730454</v>
       </c>
       <c r="K4" t="n">
-        <v>-19.20830486844693</v>
+        <v>-19.69020065949884</v>
       </c>
       <c r="L4" t="n">
-        <v>15.35053030132546</v>
+        <v>15.35053097522994</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
@@ -871,7 +871,7 @@
         <v>103.2</v>
       </c>
       <c r="O4" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
       <c r="P4" t="n">
         <v>5.7</v>
@@ -885,19 +885,19 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>40.769</v>
+        <v>41</v>
       </c>
       <c r="T4" t="n">
-        <v>40.769</v>
+        <v>41</v>
       </c>
       <c r="U4" t="n">
-        <v>33.75</v>
+        <v>32.952</v>
       </c>
       <c r="V4" t="n">
-        <v>11.03</v>
+        <v>10.368</v>
       </c>
       <c r="W4" t="n">
-        <v>-91.593</v>
+        <v>-92.39100000000001</v>
       </c>
     </row>
     <row r="5">
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>146.7734767245263</v>
+        <v>146.7734767607337</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72% | ENJSA.IS: +2.36% / +3.53% / -1.32%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28% | ENJSA.IS: -0.20% / +3.53% / -3.44%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>47.22954892038405</v>
+        <v>47.22954822730454</v>
       </c>
       <c r="K5" t="n">
-        <v>-19.20830486844693</v>
+        <v>-19.69020065949884</v>
       </c>
       <c r="L5" t="n">
-        <v>15.35053030132546</v>
+        <v>15.35053097522994</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
@@ -958,7 +958,7 @@
         <v>103.2</v>
       </c>
       <c r="O5" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
       <c r="P5" t="n">
         <v>5.7</v>
@@ -972,19 +972,19 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>40.769</v>
+        <v>41</v>
       </c>
       <c r="T5" t="n">
-        <v>40.769</v>
+        <v>41</v>
       </c>
       <c r="U5" t="n">
-        <v>33.75</v>
+        <v>32.952</v>
       </c>
       <c r="V5" t="n">
-        <v>11.03</v>
+        <v>10.368</v>
       </c>
       <c r="W5" t="n">
-        <v>-91.593</v>
+        <v>-92.39100000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1014,17 +1014,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>126.2206153952506</v>
+        <v>126.2206233289701</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>64.25814715116636</v>
+        <v>64.25815959292049</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.40003330398215</v>
+        <v>-16.40003301706789</v>
       </c>
       <c r="L6" t="n">
-        <v>18.07106570176042</v>
+        <v>18.07106661977934</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
@@ -1097,21 +1097,21 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>196.0145500782185</v>
+        <v>196.0145460497629</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.51% / +0.24% / -0.83%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -3.35% / +0.24% / -3.48%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>63.34899933726425</v>
+        <v>63.34898599832736</v>
       </c>
       <c r="K7" t="n">
-        <v>-21.81265060949008</v>
+        <v>-22.93357048073267</v>
       </c>
       <c r="L7" t="n">
-        <v>15.29584799816456</v>
+        <v>15.29584021689743</v>
       </c>
       <c r="M7" t="n">
         <v>77.77777777777779</v>
@@ -1134,19 +1134,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>31.712</v>
+        <v>32.691</v>
       </c>
       <c r="T7" t="n">
-        <v>31.712</v>
+        <v>32.691</v>
       </c>
       <c r="U7" t="n">
-        <v>75.562</v>
+        <v>73.045</v>
       </c>
       <c r="V7" t="n">
-        <v>36.809</v>
+        <v>34.847</v>
       </c>
       <c r="W7" t="n">
-        <v>-81.52800000000001</v>
+        <v>-84.045</v>
       </c>
     </row>
     <row r="8">
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>93.60033703739212</v>
+        <v>93.60033341861605</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.53227287837143</v>
+        <v>47.53226786131737</v>
       </c>
       <c r="K8" t="n">
-        <v>-17.1588592206241</v>
+        <v>-16.87141671872388</v>
       </c>
       <c r="L8" t="n">
-        <v>9.119528181849423</v>
+        <v>9.11952761462077</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -1227,13 +1227,13 @@
         <v>33.389</v>
       </c>
       <c r="U8" t="n">
-        <v>24.685</v>
+        <v>25.117</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.041</v>
+        <v>-7.722</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.117</v>
+        <v>-59.684</v>
       </c>
     </row>
     <row r="9">
@@ -1263,17 +1263,17 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>54.76877819482784</v>
+        <v>54.76877565958047</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>27.20988524839496</v>
+        <v>27.20988295234317</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2.366463069947145e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>5.126628442603421</v>
+        <v>5.126631971735584</v>
       </c>
       <c r="M9" t="n">
         <v>88.88888888888889</v>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>93.60033703739212</v>
+        <v>93.60033341861605</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.53227287837143</v>
+        <v>47.53226786131737</v>
       </c>
       <c r="K10" t="n">
-        <v>-17.1588592206241</v>
+        <v>-16.87141671872388</v>
       </c>
       <c r="L10" t="n">
-        <v>9.119528181849423</v>
+        <v>9.11952761462077</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
@@ -1389,13 +1389,13 @@
         <v>33.389</v>
       </c>
       <c r="U10" t="n">
-        <v>24.685</v>
+        <v>25.117</v>
       </c>
       <c r="V10" t="n">
-        <v>-8.041</v>
+        <v>-7.722</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.117</v>
+        <v>-59.684</v>
       </c>
     </row>
     <row r="11">
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>125.8329115571189</v>
+        <v>125.8329117087326</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +1.02% / +4.09% / -0.81% | ENJSA.IS: +7.38% / +8.60% / 0.00%</t>
+          <t>AGHOL.IS: +0.90% / +4.09% / -0.81% | ENJSA.IS: +4.70% / +8.60% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>46.52344373225456</v>
+        <v>46.52344570180613</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.00158045293973</v>
+        <v>-12.18772864242025</v>
       </c>
       <c r="L11" t="n">
-        <v>9.28497945193878</v>
+        <v>9.284980112588903</v>
       </c>
       <c r="M11" t="n">
         <v>77.77777777777779</v>
@@ -1476,13 +1476,13 @@
         <v>24.438</v>
       </c>
       <c r="U11" t="n">
-        <v>39.76</v>
+        <v>37.898</v>
       </c>
       <c r="V11" t="n">
-        <v>25.436</v>
+        <v>23.764</v>
       </c>
       <c r="W11" t="n">
-        <v>-37.491</v>
+        <v>-39.354</v>
       </c>
     </row>
     <row r="12">
@@ -1520,21 +1520,21 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>36.17882492656488</v>
+        <v>36.17882212689536</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.79% / +3.12% / -0.97% | ASELS.IS: -0.87% / +2.47% / -1.27% | BSOKE.IS: +2.96% / +4.50% / -0.51%</t>
+          <t>ARCLK.IS: -0.74% / +3.12% / -1.43% | ASELS.IS: -0.80% / +2.47% / -1.98% | BSOKE.IS: +3.30% / +4.50% / -0.51%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12.13985438046492</v>
+        <v>12.13985059364762</v>
       </c>
       <c r="K12" t="n">
-        <v>19.46689160117285</v>
+        <v>19.64714705999398</v>
       </c>
       <c r="L12" t="n">
-        <v>17.59856907346148</v>
+        <v>17.59856804976424</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
@@ -1563,13 +1563,13 @@
         <v>15.841</v>
       </c>
       <c r="U12" t="n">
-        <v>36.227</v>
+        <v>36.433</v>
       </c>
       <c r="V12" t="n">
-        <v>46.429</v>
+        <v>46.65</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.12</v>
+        <v>-3.914</v>
       </c>
     </row>
     <row r="13">
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>20.72341894805065</v>
+        <v>20.7234228693673</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-11.44224702348308</v>
+        <v>-11.44224900467197</v>
       </c>
       <c r="K13" t="n">
-        <v>15.7607063609839</v>
+        <v>16.1623698481679</v>
       </c>
       <c r="L13" t="n">
-        <v>36.6634557592222</v>
+        <v>36.66344986553255</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
@@ -1650,13 +1650,13 @@
         <v>19.486</v>
       </c>
       <c r="U13" t="n">
-        <v>51.535</v>
+        <v>52.061</v>
       </c>
       <c r="V13" t="n">
-        <v>30.523</v>
+        <v>30.976</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.673</v>
+        <v>-4.147</v>
       </c>
     </row>
     <row r="14">
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>39.96325520115791</v>
+        <v>39.96325775756866</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-1.54670412835074</v>
+        <v>-1.546706160761147</v>
       </c>
       <c r="K14" t="n">
-        <v>14.73077373382976</v>
+        <v>15.12886155472652</v>
       </c>
       <c r="L14" t="n">
-        <v>21.31957528357794</v>
+        <v>21.31957361714377</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -1737,13 +1737,13 @@
         <v>20.511</v>
       </c>
       <c r="U14" t="n">
-        <v>36.035</v>
+        <v>36.507</v>
       </c>
       <c r="V14" t="n">
-        <v>14.423</v>
+        <v>14.82</v>
       </c>
       <c r="W14" t="n">
-        <v>-6.644</v>
+        <v>-6.172</v>
       </c>
     </row>
     <row r="16">
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>196.0145500782185</v>
+        <v>196.0145460497629</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.51% / +0.24% / -0.83%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -3.35% / +0.24% / -3.48%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>63.34899933726425</v>
+        <v>63.34898599832736</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.81265060949008</v>
+        <v>-22.93357048073267</v>
       </c>
       <c r="L18" t="n">
-        <v>15.29584799816456</v>
+        <v>15.29584021689743</v>
       </c>
       <c r="M18" t="n">
         <v>77.77777777777779</v>
@@ -1944,19 +1944,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>31.712</v>
+        <v>32.691</v>
       </c>
       <c r="T18" t="n">
-        <v>31.712</v>
+        <v>32.691</v>
       </c>
       <c r="U18" t="n">
-        <v>75.562</v>
+        <v>73.045</v>
       </c>
       <c r="V18" t="n">
-        <v>36.809</v>
+        <v>34.847</v>
       </c>
       <c r="W18" t="n">
-        <v>-81.52800000000001</v>
+        <v>-84.045</v>
       </c>
     </row>
     <row r="19">
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>146.7734767245263</v>
+        <v>146.7734767607337</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72% | ENJSA.IS: +2.36% / +3.53% / -1.32%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28% | ENJSA.IS: -0.20% / +3.53% / -3.44%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47.22954892038405</v>
+        <v>47.22954822730454</v>
       </c>
       <c r="K19" t="n">
-        <v>-19.20830486844693</v>
+        <v>-19.69020065949884</v>
       </c>
       <c r="L19" t="n">
-        <v>15.35053030132546</v>
+        <v>15.35053097522994</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
@@ -2019,7 +2019,7 @@
         <v>103.2</v>
       </c>
       <c r="O19" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
       <c r="P19" t="n">
         <v>5.7</v>
@@ -2033,19 +2033,19 @@
         <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>40.769</v>
+        <v>41</v>
       </c>
       <c r="T19" t="n">
-        <v>40.769</v>
+        <v>41</v>
       </c>
       <c r="U19" t="n">
-        <v>33.75</v>
+        <v>32.952</v>
       </c>
       <c r="V19" t="n">
-        <v>11.03</v>
+        <v>10.368</v>
       </c>
       <c r="W19" t="n">
-        <v>-91.593</v>
+        <v>-92.39100000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>146.7734767245263</v>
+        <v>146.7734767607337</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72% | ENJSA.IS: +2.36% / +3.53% / -1.32%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28% | ENJSA.IS: -0.20% / +3.53% / -3.44%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>47.22954892038405</v>
+        <v>47.22954822730454</v>
       </c>
       <c r="K20" t="n">
-        <v>-19.20830486844693</v>
+        <v>-19.69020065949884</v>
       </c>
       <c r="L20" t="n">
-        <v>15.35053030132546</v>
+        <v>15.35053097522994</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
@@ -2108,7 +2108,7 @@
         <v>103.2</v>
       </c>
       <c r="O20" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
       <c r="P20" t="n">
         <v>5.7</v>
@@ -2122,19 +2122,19 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>40.769</v>
+        <v>41</v>
       </c>
       <c r="T20" t="n">
-        <v>40.769</v>
+        <v>41</v>
       </c>
       <c r="U20" t="n">
-        <v>33.75</v>
+        <v>32.952</v>
       </c>
       <c r="V20" t="n">
-        <v>11.03</v>
+        <v>10.368</v>
       </c>
       <c r="W20" t="n">
-        <v>-91.593</v>
+        <v>-92.39100000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2166,17 +2166,17 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>126.2206153952506</v>
+        <v>126.2206233289701</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>64.25814715116636</v>
+        <v>64.25815959292049</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.40003330398215</v>
+        <v>-16.40003301706789</v>
       </c>
       <c r="L21" t="n">
-        <v>18.07106570176042</v>
+        <v>18.07106661977934</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>125.8329115571189</v>
+        <v>125.8329117087326</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +1.02% / +4.09% / -0.81% | ENJSA.IS: +7.38% / +8.60% / 0.00%</t>
+          <t>AGHOL.IS: +0.90% / +4.09% / -0.81% | ENJSA.IS: +4.70% / +8.60% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>46.52344373225456</v>
+        <v>46.52344570180613</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.00158045293973</v>
+        <v>-12.18772864242025</v>
       </c>
       <c r="L22" t="n">
-        <v>9.28497945193878</v>
+        <v>9.284980112588903</v>
       </c>
       <c r="M22" t="n">
         <v>77.77777777777779</v>
@@ -2294,13 +2294,13 @@
         <v>24.438</v>
       </c>
       <c r="U22" t="n">
-        <v>39.76</v>
+        <v>37.898</v>
       </c>
       <c r="V22" t="n">
-        <v>25.436</v>
+        <v>23.764</v>
       </c>
       <c r="W22" t="n">
-        <v>-37.491</v>
+        <v>-39.354</v>
       </c>
     </row>
     <row r="23">
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>93.60033703739212</v>
+        <v>93.60033341861605</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>47.53227287837143</v>
+        <v>47.53226786131737</v>
       </c>
       <c r="K23" t="n">
-        <v>-17.1588592206241</v>
+        <v>-16.87141671872388</v>
       </c>
       <c r="L23" t="n">
-        <v>9.119528181849423</v>
+        <v>9.11952761462077</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
@@ -2383,13 +2383,13 @@
         <v>33.389</v>
       </c>
       <c r="U23" t="n">
-        <v>24.685</v>
+        <v>25.117</v>
       </c>
       <c r="V23" t="n">
-        <v>-8.041</v>
+        <v>-7.722</v>
       </c>
       <c r="W23" t="n">
-        <v>-60.117</v>
+        <v>-59.684</v>
       </c>
     </row>
     <row r="24">
@@ -2421,17 +2421,17 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>54.76877819482784</v>
+        <v>54.76877565958047</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>27.20988524839496</v>
+        <v>27.20988295234317</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2.366463069947145e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>5.126628442603421</v>
+        <v>5.126631971735584</v>
       </c>
       <c r="M24" t="n">
         <v>88.88888888888889</v>
@@ -2506,21 +2506,21 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>39.96325520115791</v>
+        <v>39.96325775756866</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-1.54670412835074</v>
+        <v>-1.546706160761147</v>
       </c>
       <c r="K25" t="n">
-        <v>14.73077373382976</v>
+        <v>15.12886155472652</v>
       </c>
       <c r="L25" t="n">
-        <v>21.31957528357794</v>
+        <v>21.31957361714377</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
@@ -2549,13 +2549,13 @@
         <v>20.511</v>
       </c>
       <c r="U25" t="n">
-        <v>36.035</v>
+        <v>36.507</v>
       </c>
       <c r="V25" t="n">
-        <v>14.423</v>
+        <v>14.82</v>
       </c>
       <c r="W25" t="n">
-        <v>-6.644</v>
+        <v>-6.172</v>
       </c>
     </row>
     <row r="26">
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>36.17882492656488</v>
+        <v>36.17882212689536</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.79% / +3.12% / -0.97% | ASELS.IS: -0.87% / +2.47% / -1.27% | BSOKE.IS: +2.96% / +4.50% / -0.51%</t>
+          <t>ARCLK.IS: -0.74% / +3.12% / -1.43% | ASELS.IS: -0.80% / +2.47% / -1.98% | BSOKE.IS: +3.30% / +4.50% / -0.51%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12.13985438046492</v>
+        <v>12.13985059364762</v>
       </c>
       <c r="K26" t="n">
-        <v>19.46689160117285</v>
+        <v>19.64714705999398</v>
       </c>
       <c r="L26" t="n">
-        <v>17.59856907346148</v>
+        <v>17.59856804976424</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
@@ -2638,13 +2638,13 @@
         <v>15.841</v>
       </c>
       <c r="U26" t="n">
-        <v>36.227</v>
+        <v>36.433</v>
       </c>
       <c r="V26" t="n">
-        <v>46.429</v>
+        <v>46.65</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.12</v>
+        <v>-3.914</v>
       </c>
     </row>
     <row r="27">
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>20.72341894805065</v>
+        <v>20.7234228693673</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.25% / +2.22% / -1.82% | AKSA.IS: -1.86% / +2.48% / -2.72%</t>
+          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-11.44224702348308</v>
+        <v>-11.44224900467197</v>
       </c>
       <c r="K27" t="n">
-        <v>15.7607063609839</v>
+        <v>16.1623698481679</v>
       </c>
       <c r="L27" t="n">
-        <v>36.6634557592222</v>
+        <v>36.66344986553255</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
@@ -2727,13 +2727,13 @@
         <v>19.486</v>
       </c>
       <c r="U27" t="n">
-        <v>51.535</v>
+        <v>52.061</v>
       </c>
       <c r="V27" t="n">
-        <v>30.523</v>
+        <v>30.976</v>
       </c>
       <c r="W27" t="n">
-        <v>-4.673</v>
+        <v>-4.147</v>
       </c>
     </row>
   </sheetData>
@@ -2768,7 +2768,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>142.9866408823153</v>
+        <v>142.9866459109618</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>65.19165962041819</v>
+        <v>65.1916625269281</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.3190314802712</v>
+        <v>-11.01420062825922</v>
       </c>
       <c r="L3" t="n">
-        <v>17.81201575904778</v>
+        <v>17.81201875402705</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
@@ -2985,13 +2985,13 @@
         <v>28.525</v>
       </c>
       <c r="U3" t="n">
-        <v>58.083</v>
+        <v>58.626</v>
       </c>
       <c r="V3" t="n">
-        <v>6.64</v>
+        <v>7.007</v>
       </c>
       <c r="W3" t="n">
-        <v>-53.623</v>
+        <v>-53.079</v>
       </c>
     </row>
     <row r="4">
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>142.9866408823153</v>
+        <v>142.9866459109618</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>65.19165962041819</v>
+        <v>65.1916625269281</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.3190314802712</v>
+        <v>-11.01420062825922</v>
       </c>
       <c r="L4" t="n">
-        <v>17.81201575904778</v>
+        <v>17.81201875402705</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
@@ -3072,13 +3072,13 @@
         <v>28.525</v>
       </c>
       <c r="U4" t="n">
-        <v>58.083</v>
+        <v>58.626</v>
       </c>
       <c r="V4" t="n">
-        <v>6.64</v>
+        <v>7.007</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.623</v>
+        <v>-53.079</v>
       </c>
     </row>
     <row r="5">
@@ -3116,21 +3116,21 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>124.0849320677873</v>
+        <v>124.0849306185654</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>52.92070323228515</v>
+        <v>52.92070673367628</v>
       </c>
       <c r="K5" t="n">
-        <v>-29.40155890265139</v>
+        <v>-29.15888906262061</v>
       </c>
       <c r="L5" t="n">
-        <v>21.28997122934656</v>
+        <v>21.28996887664675</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
@@ -3153,19 +3153,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>36.284</v>
+        <v>36.065</v>
       </c>
       <c r="T5" t="n">
-        <v>36.284</v>
+        <v>36.065</v>
       </c>
       <c r="U5" t="n">
-        <v>36.191</v>
+        <v>36.659</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.159</v>
+        <v>-9.85</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.556</v>
+        <v>-77.08799999999999</v>
       </c>
     </row>
     <row r="6">
@@ -3203,21 +3203,21 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>142.9866408823153</v>
+        <v>142.9866459109618</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>65.19165962041819</v>
+        <v>65.1916625269281</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.3190314802712</v>
+        <v>-11.01420062825922</v>
       </c>
       <c r="L6" t="n">
-        <v>17.81201575904778</v>
+        <v>17.81201875402705</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
@@ -3246,13 +3246,13 @@
         <v>28.525</v>
       </c>
       <c r="U6" t="n">
-        <v>58.083</v>
+        <v>58.626</v>
       </c>
       <c r="V6" t="n">
-        <v>6.64</v>
+        <v>7.007</v>
       </c>
       <c r="W6" t="n">
-        <v>-53.623</v>
+        <v>-53.079</v>
       </c>
     </row>
     <row r="7">
@@ -3290,21 +3290,21 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>142.9866408823153</v>
+        <v>142.9866459109618</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>65.19165962041819</v>
+        <v>65.1916625269281</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.3190314802712</v>
+        <v>-11.01420062825922</v>
       </c>
       <c r="L7" t="n">
-        <v>17.81201575904778</v>
+        <v>17.81201875402705</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
@@ -3333,13 +3333,13 @@
         <v>28.525</v>
       </c>
       <c r="U7" t="n">
-        <v>58.083</v>
+        <v>58.626</v>
       </c>
       <c r="V7" t="n">
-        <v>6.64</v>
+        <v>7.007</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.623</v>
+        <v>-53.079</v>
       </c>
     </row>
     <row r="8">
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>101.1085282252811</v>
+        <v>101.1085328114334</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.96% / +3.13% / -1.55%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.59% / +3.12% / -3.81%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>54.14354947497561</v>
+        <v>54.14356002865899</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.42514448231509</v>
+        <v>-17.49536511186779</v>
       </c>
       <c r="L8" t="n">
-        <v>14.8067531783691</v>
+        <v>14.80675251389611</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -3400,7 +3400,7 @@
         <v>99.2</v>
       </c>
       <c r="O8" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -3420,13 +3420,13 @@
         <v>33.244</v>
       </c>
       <c r="U8" t="n">
-        <v>5.697</v>
+        <v>4.343</v>
       </c>
       <c r="V8" t="n">
-        <v>-13.977</v>
+        <v>-15.079</v>
       </c>
       <c r="W8" t="n">
-        <v>-50.178</v>
+        <v>-51.532</v>
       </c>
     </row>
     <row r="9">
@@ -3456,17 +3456,17 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>47.83080759857017</v>
+        <v>47.8308061630879</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>25.16275776739663</v>
+        <v>25.16275546523637</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6.946340391777994e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>3.614619346743542</v>
+        <v>3.614626786018349</v>
       </c>
       <c r="M9" t="n">
         <v>61.11111111111111</v>
@@ -3531,17 +3531,17 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>55.35821059962866</v>
+        <v>55.35820965628533</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>24.87579530471873</v>
+        <v>24.87578844692908</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>9.144514923065117e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>5.722314490411828</v>
+        <v>5.722319728450575</v>
       </c>
       <c r="M10" t="n">
         <v>61.11111111111111</v>
@@ -3606,17 +3606,17 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>54.89485286492015</v>
+        <v>54.89484911121498</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>24.50335174084792</v>
+        <v>24.50334264230198</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-1.620916922906446e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>5.722314490411828</v>
+        <v>5.722319728450575</v>
       </c>
       <c r="M11" t="n">
         <v>61.11111111111111</v>
@@ -3689,21 +3689,21 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>32.85505973212863</v>
+        <v>32.85505614492337</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +12.79% / +13.47% / 0.00%</t>
+          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +9.17% / +13.47% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4.084120214350562</v>
+        <v>4.084117806506127</v>
       </c>
       <c r="K12" t="n">
-        <v>18.96421883109429</v>
+        <v>17.35301880123166</v>
       </c>
       <c r="L12" t="n">
-        <v>14.21663032630368</v>
+        <v>14.21663509452158</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
@@ -3712,7 +3712,7 @@
         <v>71.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>50.3</v>
+        <v>49.7</v>
       </c>
       <c r="P12" t="n">
         <v>4.2</v>
@@ -3732,13 +3732,13 @@
         <v>12.828</v>
       </c>
       <c r="U12" t="n">
-        <v>89.71899999999999</v>
+        <v>87.149</v>
       </c>
       <c r="V12" t="n">
-        <v>75.795</v>
+        <v>73.414</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.631</v>
+        <v>-4.201</v>
       </c>
     </row>
     <row r="13">
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>43.27571901061749</v>
+        <v>43.27572142553255</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENJSA.IS: +1.96% / +3.13% / -1.55% | TUPRS.IS: +0.40% / +1.01% / -0.75%</t>
+          <t>ENJSA.IS: -0.59% / +3.12% / -3.81% | TUPRS.IS: -2.82% / +1.00% / -2.80%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17.15699621331257</v>
+        <v>17.15699452443811</v>
       </c>
       <c r="K13" t="n">
-        <v>17.38568208693025</v>
+        <v>15.16136074010526</v>
       </c>
       <c r="L13" t="n">
-        <v>18.48670982489935</v>
+        <v>18.48670658660864</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
@@ -3799,7 +3799,7 @@
         <v>197.9</v>
       </c>
       <c r="O13" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="P13" t="n">
         <v>2.7</v>
@@ -3819,13 +3819,13 @@
         <v>19.604</v>
       </c>
       <c r="U13" t="n">
-        <v>66.898</v>
+        <v>63.735</v>
       </c>
       <c r="V13" t="n">
-        <v>35.864</v>
+        <v>33.289</v>
       </c>
       <c r="W13" t="n">
-        <v>-3.609</v>
+        <v>-6.772</v>
       </c>
     </row>
     <row r="14">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.985786278494286</v>
+        <v>4.985783758045081</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3871,13 +3871,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-0.8807538058383857</v>
+        <v>-0.880754364333225</v>
       </c>
       <c r="K14" t="n">
-        <v>10.86132436418468</v>
+        <v>9.52888287634217</v>
       </c>
       <c r="L14" t="n">
-        <v>8.252478196531154</v>
+        <v>8.252476290495281</v>
       </c>
       <c r="M14" t="n">
         <v>33.33333333333333</v>
@@ -3886,7 +3886,7 @@
         <v>26.3</v>
       </c>
       <c r="O14" t="n">
-        <v>45.3</v>
+        <v>43.4</v>
       </c>
       <c r="P14" t="n">
         <v>1.9</v>
@@ -3906,13 +3906,13 @@
         <v>4.228</v>
       </c>
       <c r="U14" t="n">
-        <v>7.025</v>
+        <v>5.739</v>
       </c>
       <c r="V14" t="n">
-        <v>6.195</v>
+        <v>4.919</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.429</v>
+        <v>-2.716</v>
       </c>
     </row>
     <row r="16">
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>142.9866408823153</v>
+        <v>142.9866459109618</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>65.19165962041819</v>
+        <v>65.1916625269281</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.3190314802712</v>
+        <v>-11.01420062825922</v>
       </c>
       <c r="L18" t="n">
-        <v>17.81201575904778</v>
+        <v>17.81201875402705</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
@@ -4119,13 +4119,13 @@
         <v>28.525</v>
       </c>
       <c r="U18" t="n">
-        <v>58.083</v>
+        <v>58.626</v>
       </c>
       <c r="V18" t="n">
-        <v>6.64</v>
+        <v>7.007</v>
       </c>
       <c r="W18" t="n">
-        <v>-53.623</v>
+        <v>-53.079</v>
       </c>
     </row>
     <row r="19">
@@ -4165,21 +4165,21 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>142.9866408823153</v>
+        <v>142.9866459109618</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>65.19165962041819</v>
+        <v>65.1916625269281</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.3190314802712</v>
+        <v>-11.01420062825922</v>
       </c>
       <c r="L19" t="n">
-        <v>17.81201575904778</v>
+        <v>17.81201875402705</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
@@ -4208,13 +4208,13 @@
         <v>28.525</v>
       </c>
       <c r="U19" t="n">
-        <v>58.083</v>
+        <v>58.626</v>
       </c>
       <c r="V19" t="n">
-        <v>6.64</v>
+        <v>7.007</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.623</v>
+        <v>-53.079</v>
       </c>
     </row>
     <row r="20">
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>124.0849320677873</v>
+        <v>124.0849306185654</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.60% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>52.92070323228515</v>
+        <v>52.92070673367628</v>
       </c>
       <c r="K20" t="n">
-        <v>-29.40155890265139</v>
+        <v>-29.15888906262061</v>
       </c>
       <c r="L20" t="n">
-        <v>21.28997122934656</v>
+        <v>21.28996887664675</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
@@ -4291,19 +4291,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>36.284</v>
+        <v>36.065</v>
       </c>
       <c r="T20" t="n">
-        <v>36.284</v>
+        <v>36.065</v>
       </c>
       <c r="U20" t="n">
-        <v>36.191</v>
+        <v>36.659</v>
       </c>
       <c r="V20" t="n">
-        <v>-10.159</v>
+        <v>-9.85</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.556</v>
+        <v>-77.08799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>101.1085282252811</v>
+        <v>101.1085328114334</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.96% / +3.13% / -1.55%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.59% / +3.12% / -3.81%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>54.14354947497561</v>
+        <v>54.14356002865899</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.42514448231509</v>
+        <v>-17.49536511186779</v>
       </c>
       <c r="L21" t="n">
-        <v>14.8067531783691</v>
+        <v>14.80675251389611</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -4366,7 +4366,7 @@
         <v>99.2</v>
       </c>
       <c r="O21" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="P21" t="n">
         <v>4</v>
@@ -4386,13 +4386,13 @@
         <v>33.244</v>
       </c>
       <c r="U21" t="n">
-        <v>5.697</v>
+        <v>4.343</v>
       </c>
       <c r="V21" t="n">
-        <v>-13.977</v>
+        <v>-15.079</v>
       </c>
       <c r="W21" t="n">
-        <v>-50.178</v>
+        <v>-51.532</v>
       </c>
     </row>
     <row r="22">
@@ -4424,17 +4424,17 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>55.35821059962866</v>
+        <v>55.35820965628533</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>24.87579530471873</v>
+        <v>24.87578844692908</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>9.144514923065117e-07</v>
       </c>
       <c r="L22" t="n">
-        <v>5.722314490411828</v>
+        <v>5.722319728450575</v>
       </c>
       <c r="M22" t="n">
         <v>61.11111111111111</v>
@@ -4501,17 +4501,17 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>54.89485286492015</v>
+        <v>54.89484911121498</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>24.50335174084792</v>
+        <v>24.50334264230198</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-1.620916922906446e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>5.722314490411828</v>
+        <v>5.722319728450575</v>
       </c>
       <c r="M23" t="n">
         <v>61.11111111111111</v>
@@ -4578,17 +4578,17 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>47.83080759857017</v>
+        <v>47.8308061630879</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>25.16275776739663</v>
+        <v>25.16275546523637</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>6.946340391777994e-07</v>
       </c>
       <c r="L24" t="n">
-        <v>3.614619346743542</v>
+        <v>3.614626786018349</v>
       </c>
       <c r="M24" t="n">
         <v>61.11111111111111</v>
@@ -4663,21 +4663,21 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>43.27571901061749</v>
+        <v>43.27572142553255</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ENJSA.IS: +1.96% / +3.13% / -1.55% | TUPRS.IS: +0.40% / +1.01% / -0.75%</t>
+          <t>ENJSA.IS: -0.59% / +3.12% / -3.81% | TUPRS.IS: -2.82% / +1.00% / -2.80%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17.15699621331257</v>
+        <v>17.15699452443811</v>
       </c>
       <c r="K25" t="n">
-        <v>17.38568208693025</v>
+        <v>15.16136074010526</v>
       </c>
       <c r="L25" t="n">
-        <v>18.48670982489935</v>
+        <v>18.48670658660864</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
@@ -4686,7 +4686,7 @@
         <v>197.9</v>
       </c>
       <c r="O25" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="P25" t="n">
         <v>2.7</v>
@@ -4706,13 +4706,13 @@
         <v>19.604</v>
       </c>
       <c r="U25" t="n">
-        <v>66.898</v>
+        <v>63.735</v>
       </c>
       <c r="V25" t="n">
-        <v>35.864</v>
+        <v>33.289</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.609</v>
+        <v>-6.772</v>
       </c>
     </row>
     <row r="26">
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>32.85505973212863</v>
+        <v>32.85505614492337</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +12.79% / +13.47% / 0.00%</t>
+          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +9.17% / +13.47% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4.084120214350562</v>
+        <v>4.084117806506127</v>
       </c>
       <c r="K26" t="n">
-        <v>18.96421883109429</v>
+        <v>17.35301880123166</v>
       </c>
       <c r="L26" t="n">
-        <v>14.21663032630368</v>
+        <v>14.21663509452158</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
@@ -4775,7 +4775,7 @@
         <v>71.90000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>50.3</v>
+        <v>49.7</v>
       </c>
       <c r="P26" t="n">
         <v>4.2</v>
@@ -4795,13 +4795,13 @@
         <v>12.828</v>
       </c>
       <c r="U26" t="n">
-        <v>89.71899999999999</v>
+        <v>87.149</v>
       </c>
       <c r="V26" t="n">
-        <v>75.795</v>
+        <v>73.414</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.631</v>
+        <v>-4.201</v>
       </c>
     </row>
     <row r="27">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.985786278494286</v>
+        <v>4.985783758045081</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4849,13 +4849,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-0.8807538058383857</v>
+        <v>-0.880754364333225</v>
       </c>
       <c r="K27" t="n">
-        <v>10.86132436418468</v>
+        <v>9.52888287634217</v>
       </c>
       <c r="L27" t="n">
-        <v>8.252478196531154</v>
+        <v>8.252476290495281</v>
       </c>
       <c r="M27" t="n">
         <v>33.33333333333333</v>
@@ -4864,7 +4864,7 @@
         <v>26.3</v>
       </c>
       <c r="O27" t="n">
-        <v>45.3</v>
+        <v>43.4</v>
       </c>
       <c r="P27" t="n">
         <v>1.9</v>
@@ -4884,13 +4884,13 @@
         <v>4.228</v>
       </c>
       <c r="U27" t="n">
-        <v>7.025</v>
+        <v>5.739</v>
       </c>
       <c r="V27" t="n">
-        <v>6.195</v>
+        <v>4.919</v>
       </c>
       <c r="W27" t="n">
-        <v>-1.429</v>
+        <v>-2.716</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -765,14 +765,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -3.35% / +0.24% / -3.48%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -2.17% / +0.24% / -3.48%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>63.34898599832736</v>
       </c>
       <c r="K3" t="n">
-        <v>-22.93357048073267</v>
+        <v>-22.46977726967703</v>
       </c>
       <c r="L3" t="n">
         <v>15.29584021689743</v>
@@ -798,19 +798,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>32.691</v>
+        <v>32.286</v>
       </c>
       <c r="T3" t="n">
-        <v>32.691</v>
+        <v>32.286</v>
       </c>
       <c r="U3" t="n">
-        <v>73.045</v>
+        <v>74.087</v>
       </c>
       <c r="V3" t="n">
-        <v>34.847</v>
+        <v>35.659</v>
       </c>
       <c r="W3" t="n">
-        <v>-84.045</v>
+        <v>-83.004</v>
       </c>
     </row>
     <row r="4">
@@ -852,14 +852,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28% | ENJSA.IS: -0.20% / +3.53% / -3.44%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28% | ENJSA.IS: -1.61% / +3.53% / -3.44%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>47.22954822730454</v>
       </c>
       <c r="K4" t="n">
-        <v>-19.69020065949884</v>
+        <v>-19.66730433335175</v>
       </c>
       <c r="L4" t="n">
         <v>15.35053097522994</v>
@@ -871,7 +871,7 @@
         <v>103.2</v>
       </c>
       <c r="O4" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="P4" t="n">
         <v>5.7</v>
@@ -885,19 +885,19 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>41</v>
+        <v>40.983</v>
       </c>
       <c r="T4" t="n">
-        <v>41</v>
+        <v>40.983</v>
       </c>
       <c r="U4" t="n">
-        <v>32.952</v>
+        <v>32.99</v>
       </c>
       <c r="V4" t="n">
-        <v>10.368</v>
+        <v>10.399</v>
       </c>
       <c r="W4" t="n">
-        <v>-92.39100000000001</v>
+        <v>-92.35299999999999</v>
       </c>
     </row>
     <row r="5">
@@ -939,14 +939,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28% | ENJSA.IS: -0.20% / +3.53% / -3.44%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28% | ENJSA.IS: -1.61% / +3.53% / -3.44%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>47.22954822730454</v>
       </c>
       <c r="K5" t="n">
-        <v>-19.69020065949884</v>
+        <v>-19.66730433335175</v>
       </c>
       <c r="L5" t="n">
         <v>15.35053097522994</v>
@@ -958,7 +958,7 @@
         <v>103.2</v>
       </c>
       <c r="O5" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="P5" t="n">
         <v>5.7</v>
@@ -972,19 +972,19 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>41</v>
+        <v>40.983</v>
       </c>
       <c r="T5" t="n">
-        <v>41</v>
+        <v>40.983</v>
       </c>
       <c r="U5" t="n">
-        <v>32.952</v>
+        <v>32.99</v>
       </c>
       <c r="V5" t="n">
-        <v>10.368</v>
+        <v>10.399</v>
       </c>
       <c r="W5" t="n">
-        <v>-92.39100000000001</v>
+        <v>-92.35299999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -3.35% / +0.24% / -3.48%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -2.17% / +0.24% / -3.48%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>63.34898599832736</v>
       </c>
       <c r="K7" t="n">
-        <v>-22.93357048073267</v>
+        <v>-22.46977726967703</v>
       </c>
       <c r="L7" t="n">
         <v>15.29584021689743</v>
@@ -1134,19 +1134,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>32.691</v>
+        <v>32.286</v>
       </c>
       <c r="T7" t="n">
-        <v>32.691</v>
+        <v>32.286</v>
       </c>
       <c r="U7" t="n">
-        <v>73.045</v>
+        <v>74.087</v>
       </c>
       <c r="V7" t="n">
-        <v>34.847</v>
+        <v>35.659</v>
       </c>
       <c r="W7" t="n">
-        <v>-84.045</v>
+        <v>-83.004</v>
       </c>
     </row>
     <row r="8">
@@ -1188,14 +1188,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>47.53226786131737</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.87141671872388</v>
+        <v>-16.26977966026103</v>
       </c>
       <c r="L8" t="n">
         <v>9.11952761462077</v>
@@ -1207,7 +1207,7 @@
         <v>238.1</v>
       </c>
       <c r="O8" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="P8" t="n">
         <v>3.4</v>
@@ -1227,13 +1227,13 @@
         <v>33.389</v>
       </c>
       <c r="U8" t="n">
-        <v>25.117</v>
+        <v>26.023</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.722</v>
+        <v>-7.054</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.684</v>
+        <v>-58.779</v>
       </c>
     </row>
     <row r="9">
@@ -1350,14 +1350,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>47.53226786131737</v>
       </c>
       <c r="K10" t="n">
-        <v>-16.87141671872388</v>
+        <v>-16.26977966026103</v>
       </c>
       <c r="L10" t="n">
         <v>9.11952761462077</v>
@@ -1369,7 +1369,7 @@
         <v>238.1</v>
       </c>
       <c r="O10" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="P10" t="n">
         <v>3.4</v>
@@ -1389,13 +1389,13 @@
         <v>33.389</v>
       </c>
       <c r="U10" t="n">
-        <v>25.117</v>
+        <v>26.023</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.722</v>
+        <v>-7.054</v>
       </c>
       <c r="W10" t="n">
-        <v>-59.684</v>
+        <v>-58.779</v>
       </c>
     </row>
     <row r="11">
@@ -1437,14 +1437,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.90% / +4.09% / -0.81% | ENJSA.IS: +4.70% / +8.60% / 0.00%</t>
+          <t>AGHOL.IS: +1.71% / +4.09% / -0.81% | ENJSA.IS: +3.22% / +8.60% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>46.52344570180613</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.18772864242025</v>
+        <v>-12.46730594284595</v>
       </c>
       <c r="L11" t="n">
         <v>9.284980112588903</v>
@@ -1476,13 +1476,13 @@
         <v>24.438</v>
       </c>
       <c r="U11" t="n">
-        <v>37.898</v>
+        <v>37.459</v>
       </c>
       <c r="V11" t="n">
-        <v>23.764</v>
+        <v>23.37</v>
       </c>
       <c r="W11" t="n">
-        <v>-39.354</v>
+        <v>-39.793</v>
       </c>
     </row>
     <row r="12">
@@ -1524,14 +1524,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.74% / +3.12% / -1.43% | ASELS.IS: -0.80% / +2.47% / -1.98% | BSOKE.IS: +3.30% / +4.50% / -0.51%</t>
+          <t>ARCLK.IS: -0.84% / +3.12% / -1.64% | ASELS.IS: +0.26% / +2.47% / -1.98% | BSOKE.IS: +2.23% / +4.50% / -0.51%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>12.13985059364762</v>
       </c>
       <c r="K12" t="n">
-        <v>19.64714705999398</v>
+        <v>19.61050606302861</v>
       </c>
       <c r="L12" t="n">
         <v>17.59856804976424</v>
@@ -1543,7 +1543,7 @@
         <v>100.2</v>
       </c>
       <c r="O12" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="P12" t="n">
         <v>6.1</v>
@@ -1563,13 +1563,13 @@
         <v>15.841</v>
       </c>
       <c r="U12" t="n">
-        <v>36.433</v>
+        <v>36.391</v>
       </c>
       <c r="V12" t="n">
-        <v>46.65</v>
+        <v>46.605</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.914</v>
+        <v>-3.956</v>
       </c>
     </row>
     <row r="13">
@@ -1611,14 +1611,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-11.44224900467197</v>
       </c>
       <c r="K13" t="n">
-        <v>16.1623698481679</v>
+        <v>17.00308652756868</v>
       </c>
       <c r="L13" t="n">
         <v>36.66344986553255</v>
@@ -1630,7 +1630,7 @@
         <v>212.3</v>
       </c>
       <c r="O13" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
         <v>3.6</v>
@@ -1650,13 +1650,13 @@
         <v>19.486</v>
       </c>
       <c r="U13" t="n">
-        <v>52.061</v>
+        <v>53.162</v>
       </c>
       <c r="V13" t="n">
-        <v>30.976</v>
+        <v>31.924</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.147</v>
+        <v>-3.046</v>
       </c>
     </row>
     <row r="14">
@@ -1698,14 +1698,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-1.546706160761147</v>
       </c>
       <c r="K14" t="n">
-        <v>15.12886155472652</v>
+        <v>15.96209829323305</v>
       </c>
       <c r="L14" t="n">
         <v>21.31957361714377</v>
@@ -1717,7 +1717,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>51.1</v>
+        <v>51.8</v>
       </c>
       <c r="P14" t="n">
         <v>5.6</v>
@@ -1737,13 +1737,13 @@
         <v>20.511</v>
       </c>
       <c r="U14" t="n">
-        <v>36.507</v>
+        <v>37.495</v>
       </c>
       <c r="V14" t="n">
-        <v>14.82</v>
+        <v>15.651</v>
       </c>
       <c r="W14" t="n">
-        <v>-6.172</v>
+        <v>-5.184</v>
       </c>
     </row>
     <row r="16">
@@ -1911,14 +1911,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -3.35% / +0.24% / -3.48%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -2.17% / +0.24% / -3.48%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>63.34898599832736</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.93357048073267</v>
+        <v>-22.46977726967703</v>
       </c>
       <c r="L18" t="n">
         <v>15.29584021689743</v>
@@ -1944,19 +1944,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>32.691</v>
+        <v>32.286</v>
       </c>
       <c r="T18" t="n">
-        <v>32.691</v>
+        <v>32.286</v>
       </c>
       <c r="U18" t="n">
-        <v>73.045</v>
+        <v>74.087</v>
       </c>
       <c r="V18" t="n">
-        <v>34.847</v>
+        <v>35.659</v>
       </c>
       <c r="W18" t="n">
-        <v>-84.045</v>
+        <v>-83.004</v>
       </c>
     </row>
     <row r="19">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28% | ENJSA.IS: -0.20% / +3.53% / -3.44%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28% | ENJSA.IS: -1.61% / +3.53% / -3.44%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>47.22954822730454</v>
       </c>
       <c r="K19" t="n">
-        <v>-19.69020065949884</v>
+        <v>-19.66730433335175</v>
       </c>
       <c r="L19" t="n">
         <v>15.35053097522994</v>
@@ -2019,7 +2019,7 @@
         <v>103.2</v>
       </c>
       <c r="O19" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="P19" t="n">
         <v>5.7</v>
@@ -2033,19 +2033,19 @@
         <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>41</v>
+        <v>40.983</v>
       </c>
       <c r="T19" t="n">
-        <v>41</v>
+        <v>40.983</v>
       </c>
       <c r="U19" t="n">
-        <v>32.952</v>
+        <v>32.99</v>
       </c>
       <c r="V19" t="n">
-        <v>10.368</v>
+        <v>10.399</v>
       </c>
       <c r="W19" t="n">
-        <v>-92.39100000000001</v>
+        <v>-92.35299999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2089,14 +2089,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28% | ENJSA.IS: -0.20% / +3.53% / -3.44%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28% | ENJSA.IS: -1.61% / +3.53% / -3.44%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>47.22954822730454</v>
       </c>
       <c r="K20" t="n">
-        <v>-19.69020065949884</v>
+        <v>-19.66730433335175</v>
       </c>
       <c r="L20" t="n">
         <v>15.35053097522994</v>
@@ -2108,7 +2108,7 @@
         <v>103.2</v>
       </c>
       <c r="O20" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="P20" t="n">
         <v>5.7</v>
@@ -2122,19 +2122,19 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>41</v>
+        <v>40.983</v>
       </c>
       <c r="T20" t="n">
-        <v>41</v>
+        <v>40.983</v>
       </c>
       <c r="U20" t="n">
-        <v>32.952</v>
+        <v>32.99</v>
       </c>
       <c r="V20" t="n">
-        <v>10.368</v>
+        <v>10.399</v>
       </c>
       <c r="W20" t="n">
-        <v>-92.39100000000001</v>
+        <v>-92.35299999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.90% / +4.09% / -0.81% | ENJSA.IS: +4.70% / +8.60% / 0.00%</t>
+          <t>AGHOL.IS: +1.71% / +4.09% / -0.81% | ENJSA.IS: +3.22% / +8.60% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>46.52344570180613</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.18772864242025</v>
+        <v>-12.46730594284595</v>
       </c>
       <c r="L22" t="n">
         <v>9.284980112588903</v>
@@ -2294,13 +2294,13 @@
         <v>24.438</v>
       </c>
       <c r="U22" t="n">
-        <v>37.898</v>
+        <v>37.459</v>
       </c>
       <c r="V22" t="n">
-        <v>23.764</v>
+        <v>23.37</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.354</v>
+        <v>-39.793</v>
       </c>
     </row>
     <row r="23">
@@ -2344,14 +2344,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>47.53226786131737</v>
       </c>
       <c r="K23" t="n">
-        <v>-16.87141671872388</v>
+        <v>-16.26977966026103</v>
       </c>
       <c r="L23" t="n">
         <v>9.11952761462077</v>
@@ -2363,7 +2363,7 @@
         <v>238.1</v>
       </c>
       <c r="O23" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="P23" t="n">
         <v>3.4</v>
@@ -2383,13 +2383,13 @@
         <v>33.389</v>
       </c>
       <c r="U23" t="n">
-        <v>25.117</v>
+        <v>26.023</v>
       </c>
       <c r="V23" t="n">
-        <v>-7.722</v>
+        <v>-7.054</v>
       </c>
       <c r="W23" t="n">
-        <v>-59.684</v>
+        <v>-58.779</v>
       </c>
     </row>
     <row r="24">
@@ -2510,14 +2510,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.546706160761147</v>
       </c>
       <c r="K25" t="n">
-        <v>15.12886155472652</v>
+        <v>15.96209829323305</v>
       </c>
       <c r="L25" t="n">
         <v>21.31957361714377</v>
@@ -2529,7 +2529,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>51.1</v>
+        <v>51.8</v>
       </c>
       <c r="P25" t="n">
         <v>5.6</v>
@@ -2549,13 +2549,13 @@
         <v>20.511</v>
       </c>
       <c r="U25" t="n">
-        <v>36.507</v>
+        <v>37.495</v>
       </c>
       <c r="V25" t="n">
-        <v>14.82</v>
+        <v>15.651</v>
       </c>
       <c r="W25" t="n">
-        <v>-6.172</v>
+        <v>-5.184</v>
       </c>
     </row>
     <row r="26">
@@ -2599,14 +2599,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.74% / +3.12% / -1.43% | ASELS.IS: -0.80% / +2.47% / -1.98% | BSOKE.IS: +3.30% / +4.50% / -0.51%</t>
+          <t>ARCLK.IS: -0.84% / +3.12% / -1.64% | ASELS.IS: +0.26% / +2.47% / -1.98% | BSOKE.IS: +2.23% / +4.50% / -0.51%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.13985059364762</v>
       </c>
       <c r="K26" t="n">
-        <v>19.64714705999398</v>
+        <v>19.61050606302861</v>
       </c>
       <c r="L26" t="n">
         <v>17.59856804976424</v>
@@ -2618,7 +2618,7 @@
         <v>100.2</v>
       </c>
       <c r="O26" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="P26" t="n">
         <v>6.1</v>
@@ -2638,13 +2638,13 @@
         <v>15.841</v>
       </c>
       <c r="U26" t="n">
-        <v>36.433</v>
+        <v>36.391</v>
       </c>
       <c r="V26" t="n">
-        <v>46.65</v>
+        <v>46.605</v>
       </c>
       <c r="W26" t="n">
-        <v>-3.914</v>
+        <v>-3.956</v>
       </c>
     </row>
     <row r="27">
@@ -2688,14 +2688,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.36% / +2.22% / -1.82% | AKSA.IS: -1.06% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-11.44224900467197</v>
       </c>
       <c r="K27" t="n">
-        <v>16.1623698481679</v>
+        <v>17.00308652756868</v>
       </c>
       <c r="L27" t="n">
         <v>36.66344986553255</v>
@@ -2707,7 +2707,7 @@
         <v>212.3</v>
       </c>
       <c r="O27" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
         <v>3.6</v>
@@ -2727,13 +2727,13 @@
         <v>19.486</v>
       </c>
       <c r="U27" t="n">
-        <v>52.061</v>
+        <v>53.162</v>
       </c>
       <c r="V27" t="n">
-        <v>30.976</v>
+        <v>31.924</v>
       </c>
       <c r="W27" t="n">
-        <v>-4.147</v>
+        <v>-3.046</v>
       </c>
     </row>
   </sheetData>
@@ -2946,14 +2946,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.01420062825922</v>
+        <v>-10.36640499489124</v>
       </c>
       <c r="L3" t="n">
         <v>17.81201875402705</v>
@@ -2965,7 +2965,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -2985,13 +2985,13 @@
         <v>28.525</v>
       </c>
       <c r="U3" t="n">
-        <v>58.626</v>
+        <v>59.781</v>
       </c>
       <c r="V3" t="n">
-        <v>7.007</v>
+        <v>7.786</v>
       </c>
       <c r="W3" t="n">
-        <v>-53.079</v>
+        <v>-51.924</v>
       </c>
     </row>
     <row r="4">
@@ -3033,14 +3033,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.01420062825922</v>
+        <v>-10.36640499489124</v>
       </c>
       <c r="L4" t="n">
         <v>17.81201875402705</v>
@@ -3052,7 +3052,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="P4" t="n">
         <v>5</v>
@@ -3072,13 +3072,13 @@
         <v>28.525</v>
       </c>
       <c r="U4" t="n">
-        <v>58.626</v>
+        <v>59.781</v>
       </c>
       <c r="V4" t="n">
-        <v>7.007</v>
+        <v>7.786</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.079</v>
+        <v>-51.924</v>
       </c>
     </row>
     <row r="5">
@@ -3120,14 +3120,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>52.92070673367628</v>
       </c>
       <c r="K5" t="n">
-        <v>-29.15888906262061</v>
+        <v>-28.64318248188337</v>
       </c>
       <c r="L5" t="n">
         <v>21.28996887664675</v>
@@ -3139,7 +3139,7 @@
         <v>120</v>
       </c>
       <c r="O5" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="P5" t="n">
         <v>5.2</v>
@@ -3153,19 +3153,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>36.065</v>
+        <v>35.94</v>
       </c>
       <c r="T5" t="n">
-        <v>36.065</v>
+        <v>35.94</v>
       </c>
       <c r="U5" t="n">
-        <v>36.659</v>
+        <v>37.654</v>
       </c>
       <c r="V5" t="n">
-        <v>-9.85</v>
+        <v>-9.194000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.08799999999999</v>
+        <v>-76.093</v>
       </c>
     </row>
     <row r="6">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.01420062825922</v>
+        <v>-10.36640499489124</v>
       </c>
       <c r="L6" t="n">
         <v>17.81201875402705</v>
@@ -3226,7 +3226,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -3246,13 +3246,13 @@
         <v>28.525</v>
       </c>
       <c r="U6" t="n">
-        <v>58.626</v>
+        <v>59.781</v>
       </c>
       <c r="V6" t="n">
-        <v>7.007</v>
+        <v>7.786</v>
       </c>
       <c r="W6" t="n">
-        <v>-53.079</v>
+        <v>-51.924</v>
       </c>
     </row>
     <row r="7">
@@ -3294,14 +3294,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.01420062825922</v>
+        <v>-10.36640499489124</v>
       </c>
       <c r="L7" t="n">
         <v>17.81201875402705</v>
@@ -3313,7 +3313,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="P7" t="n">
         <v>5</v>
@@ -3333,13 +3333,13 @@
         <v>28.525</v>
       </c>
       <c r="U7" t="n">
-        <v>58.626</v>
+        <v>59.781</v>
       </c>
       <c r="V7" t="n">
-        <v>7.007</v>
+        <v>7.786</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.079</v>
+        <v>-51.924</v>
       </c>
     </row>
     <row r="8">
@@ -3381,14 +3381,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.59% / +3.12% / -3.81%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -1.99% / +3.13% / -3.81%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>54.14356002865899</v>
       </c>
       <c r="K8" t="n">
-        <v>-17.49536511186779</v>
+        <v>-18.08336659282025</v>
       </c>
       <c r="L8" t="n">
         <v>14.80675251389611</v>
@@ -3414,19 +3414,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>33.244</v>
+        <v>33.537</v>
       </c>
       <c r="T8" t="n">
-        <v>33.244</v>
+        <v>33.537</v>
       </c>
       <c r="U8" t="n">
-        <v>4.343</v>
+        <v>3.6</v>
       </c>
       <c r="V8" t="n">
-        <v>-15.079</v>
+        <v>-15.684</v>
       </c>
       <c r="W8" t="n">
-        <v>-51.532</v>
+        <v>-52.276</v>
       </c>
     </row>
     <row r="9">
@@ -3693,14 +3693,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +9.17% / +13.47% / 0.00%</t>
+          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +10.49% / +13.48% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>4.084117806506127</v>
       </c>
       <c r="K12" t="n">
-        <v>17.35301880123166</v>
+        <v>17.34102688518859</v>
       </c>
       <c r="L12" t="n">
         <v>14.21663509452158</v>
@@ -3732,13 +3732,13 @@
         <v>12.828</v>
       </c>
       <c r="U12" t="n">
-        <v>87.149</v>
+        <v>87.13</v>
       </c>
       <c r="V12" t="n">
-        <v>73.414</v>
+        <v>73.39700000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.201</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="13">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3767,42 +3767,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENJSA.IS, TUPRS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENJSA.IS: 2026-08-06 | TUPRS.IS: 2026-08-10</t>
+          <t>TUPRS.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>43.27572142553255</v>
+        <v>49.20349509572279</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ENJSA.IS: -0.59% / +3.12% / -3.81% | TUPRS.IS: -2.82% / +1.00% / -2.80%</t>
+          <t>TUPRS.IS: +10.49% / +13.48% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17.15699452443811</v>
+        <v>5.871595897009474</v>
       </c>
       <c r="K13" t="n">
-        <v>15.16136074010526</v>
+        <v>15.19036530457831</v>
       </c>
       <c r="L13" t="n">
-        <v>18.48670658660864</v>
+        <v>19.92682085509051</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>197.9</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3810,22 +3810,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>19.604</v>
+        <v>17.263</v>
       </c>
       <c r="T13" t="n">
-        <v>19.604</v>
+        <v>15.567</v>
       </c>
       <c r="U13" t="n">
-        <v>63.735</v>
+        <v>111.008</v>
       </c>
       <c r="V13" t="n">
-        <v>33.289</v>
+        <v>111.157</v>
       </c>
       <c r="W13" t="n">
-        <v>-6.772</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="14">
@@ -3874,7 +3874,7 @@
         <v>-0.880754364333225</v>
       </c>
       <c r="K14" t="n">
-        <v>9.52888287634217</v>
+        <v>8.857985453728556</v>
       </c>
       <c r="L14" t="n">
         <v>8.252476290495281</v>
@@ -3906,13 +3906,13 @@
         <v>4.228</v>
       </c>
       <c r="U14" t="n">
-        <v>5.739</v>
+        <v>5.091</v>
       </c>
       <c r="V14" t="n">
-        <v>4.919</v>
+        <v>4.276</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.716</v>
+        <v>-3.363</v>
       </c>
     </row>
     <row r="16">
@@ -4080,14 +4080,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.01420062825922</v>
+        <v>-10.36640499489124</v>
       </c>
       <c r="L18" t="n">
         <v>17.81201875402705</v>
@@ -4099,7 +4099,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="P18" t="n">
         <v>5</v>
@@ -4119,13 +4119,13 @@
         <v>28.525</v>
       </c>
       <c r="U18" t="n">
-        <v>58.626</v>
+        <v>59.781</v>
       </c>
       <c r="V18" t="n">
-        <v>7.007</v>
+        <v>7.786</v>
       </c>
       <c r="W18" t="n">
-        <v>-53.079</v>
+        <v>-51.924</v>
       </c>
     </row>
     <row r="19">
@@ -4169,14 +4169,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.01420062825922</v>
+        <v>-10.36640499489124</v>
       </c>
       <c r="L19" t="n">
         <v>17.81201875402705</v>
@@ -4188,7 +4188,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="P19" t="n">
         <v>5</v>
@@ -4208,13 +4208,13 @@
         <v>28.525</v>
       </c>
       <c r="U19" t="n">
-        <v>58.626</v>
+        <v>59.781</v>
       </c>
       <c r="V19" t="n">
-        <v>7.007</v>
+        <v>7.786</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.079</v>
+        <v>-51.924</v>
       </c>
     </row>
     <row r="20">
@@ -4258,14 +4258,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: -0.71% / +1.96% / -2.01%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>52.92070673367628</v>
       </c>
       <c r="K20" t="n">
-        <v>-29.15888906262061</v>
+        <v>-28.64318248188337</v>
       </c>
       <c r="L20" t="n">
         <v>21.28996887664675</v>
@@ -4277,7 +4277,7 @@
         <v>120</v>
       </c>
       <c r="O20" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="P20" t="n">
         <v>5.2</v>
@@ -4291,19 +4291,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>36.065</v>
+        <v>35.94</v>
       </c>
       <c r="T20" t="n">
-        <v>36.065</v>
+        <v>35.94</v>
       </c>
       <c r="U20" t="n">
-        <v>36.659</v>
+        <v>37.654</v>
       </c>
       <c r="V20" t="n">
-        <v>-9.85</v>
+        <v>-9.194000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.08799999999999</v>
+        <v>-76.093</v>
       </c>
     </row>
     <row r="21">
@@ -4347,14 +4347,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.59% / +3.12% / -3.81%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -1.99% / +3.13% / -3.81%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>54.14356002865899</v>
       </c>
       <c r="K21" t="n">
-        <v>-17.49536511186779</v>
+        <v>-18.08336659282025</v>
       </c>
       <c r="L21" t="n">
         <v>14.80675251389611</v>
@@ -4380,19 +4380,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>33.244</v>
+        <v>33.537</v>
       </c>
       <c r="T21" t="n">
-        <v>33.244</v>
+        <v>33.537</v>
       </c>
       <c r="U21" t="n">
-        <v>4.343</v>
+        <v>3.6</v>
       </c>
       <c r="V21" t="n">
-        <v>-15.079</v>
+        <v>-15.684</v>
       </c>
       <c r="W21" t="n">
-        <v>-51.532</v>
+        <v>-52.276</v>
       </c>
     </row>
     <row r="22">
@@ -4552,17 +4552,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4575,71 +4575,83 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TUPRS.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>47.8308061630879</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>49.20349509572279</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TUPRS.IS: +10.49% / +13.48% / 0.00%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>25.16275546523637</v>
+        <v>5.871595897009474</v>
       </c>
       <c r="K24" t="n">
-        <v>6.946340391777994e-07</v>
+        <v>15.19036530457831</v>
       </c>
       <c r="L24" t="n">
-        <v>3.614626786018349</v>
+        <v>19.92682085509051</v>
       </c>
       <c r="M24" t="n">
-        <v>61.11111111111111</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>18.4</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>62.2</v>
+        <v>48.3</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>6.293</v>
+        <v>17.263</v>
       </c>
       <c r="T24" t="n">
-        <v>6.293</v>
+        <v>15.567</v>
       </c>
       <c r="U24" t="n">
-        <v>33.654</v>
+        <v>111.008</v>
       </c>
       <c r="V24" t="n">
-        <v>14.787</v>
+        <v>111.157</v>
       </c>
       <c r="W24" t="n">
-        <v>-8.975</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4652,67 +4664,55 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ENJSA.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ENJSA.IS: 2026-08-06 | TUPRS.IS: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>43.27572142553255</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ENJSA.IS: -0.59% / +3.12% / -3.81% | TUPRS.IS: -2.82% / +1.00% / -2.80%</t>
-        </is>
-      </c>
+        <v>47.8308061630879</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>17.15699452443811</v>
+        <v>25.16275546523637</v>
       </c>
       <c r="K25" t="n">
-        <v>15.16136074010526</v>
+        <v>6.946340391777994e-07</v>
       </c>
       <c r="L25" t="n">
-        <v>18.48670658660864</v>
+        <v>3.614626786018349</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N25" t="n">
-        <v>197.9</v>
+        <v>18.4</v>
       </c>
       <c r="O25" t="n">
-        <v>47.6</v>
+        <v>62.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>19.604</v>
+        <v>6.293</v>
       </c>
       <c r="T25" t="n">
-        <v>19.604</v>
+        <v>6.293</v>
       </c>
       <c r="U25" t="n">
-        <v>63.735</v>
+        <v>33.654</v>
       </c>
       <c r="V25" t="n">
-        <v>33.289</v>
+        <v>14.787</v>
       </c>
       <c r="W25" t="n">
-        <v>-6.772</v>
+        <v>-8.975</v>
       </c>
     </row>
     <row r="26">
@@ -4756,14 +4756,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +9.17% / +13.47% / 0.00%</t>
+          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +10.49% / +13.48% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>4.084117806506127</v>
       </c>
       <c r="K26" t="n">
-        <v>17.35301880123166</v>
+        <v>17.34102688518859</v>
       </c>
       <c r="L26" t="n">
         <v>14.21663509452158</v>
@@ -4795,13 +4795,13 @@
         <v>12.828</v>
       </c>
       <c r="U26" t="n">
-        <v>87.149</v>
+        <v>87.13</v>
       </c>
       <c r="V26" t="n">
-        <v>73.414</v>
+        <v>73.39700000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.201</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="27">
@@ -4852,7 +4852,7 @@
         <v>-0.880754364333225</v>
       </c>
       <c r="K27" t="n">
-        <v>9.52888287634217</v>
+        <v>8.857985453728556</v>
       </c>
       <c r="L27" t="n">
         <v>8.252476290495281</v>
@@ -4884,13 +4884,13 @@
         <v>4.228</v>
       </c>
       <c r="U27" t="n">
-        <v>5.739</v>
+        <v>5.091</v>
       </c>
       <c r="V27" t="n">
-        <v>4.919</v>
+        <v>4.276</v>
       </c>
       <c r="W27" t="n">
-        <v>-2.716</v>
+        <v>-3.363</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -582,7 +582,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -742,37 +742,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-11 | KCHOL.IS: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>196.0145460497629</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -2.17% / +0.24% / -3.48%</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>63.34898599832736</v>
       </c>
       <c r="K3" t="n">
-        <v>-22.46977726967703</v>
+        <v>-24.74012475534331</v>
       </c>
       <c r="L3" t="n">
         <v>15.29584021689743</v>
@@ -781,7 +769,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N3" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O3" t="n">
         <v>46.7</v>
@@ -791,26 +779,26 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>32.286</v>
+        <v>34.269</v>
       </c>
       <c r="T3" t="n">
-        <v>32.286</v>
+        <v>34.269</v>
       </c>
       <c r="U3" t="n">
-        <v>74.087</v>
+        <v>67.491</v>
       </c>
       <c r="V3" t="n">
-        <v>35.659</v>
+        <v>31.686</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.004</v>
+        <v>-87.31999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -829,22 +817,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
+          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -852,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28% | ENJSA.IS: -1.61% / +3.53% / -3.44%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>47.22954822730454</v>
       </c>
       <c r="K4" t="n">
-        <v>-19.66730433335175</v>
+        <v>-21.90618105639208</v>
       </c>
       <c r="L4" t="n">
         <v>15.35053097522994</v>
@@ -868,10 +856,10 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>103.2</v>
+        <v>104</v>
       </c>
       <c r="O4" t="n">
-        <v>45.2</v>
+        <v>44.3</v>
       </c>
       <c r="P4" t="n">
         <v>5.7</v>
@@ -885,19 +873,19 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>40.983</v>
+        <v>42.628</v>
       </c>
       <c r="T4" t="n">
-        <v>40.983</v>
+        <v>42.628</v>
       </c>
       <c r="U4" t="n">
-        <v>32.99</v>
+        <v>30.051</v>
       </c>
       <c r="V4" t="n">
-        <v>10.399</v>
+        <v>7.323</v>
       </c>
       <c r="W4" t="n">
-        <v>-92.35299999999999</v>
+        <v>-96.63</v>
       </c>
     </row>
     <row r="5">
@@ -916,22 +904,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
+          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -939,14 +927,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28% | ENJSA.IS: -1.61% / +3.53% / -3.44%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>47.22954822730454</v>
       </c>
       <c r="K5" t="n">
-        <v>-19.66730433335175</v>
+        <v>-21.90618105639208</v>
       </c>
       <c r="L5" t="n">
         <v>15.35053097522994</v>
@@ -955,10 +943,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>103.2</v>
+        <v>104</v>
       </c>
       <c r="O5" t="n">
-        <v>45.2</v>
+        <v>44.3</v>
       </c>
       <c r="P5" t="n">
         <v>5.7</v>
@@ -972,19 +960,19 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>40.983</v>
+        <v>42.628</v>
       </c>
       <c r="T5" t="n">
-        <v>40.983</v>
+        <v>42.628</v>
       </c>
       <c r="U5" t="n">
-        <v>32.99</v>
+        <v>30.051</v>
       </c>
       <c r="V5" t="n">
-        <v>10.399</v>
+        <v>7.323</v>
       </c>
       <c r="W5" t="n">
-        <v>-92.35299999999999</v>
+        <v>-96.63</v>
       </c>
     </row>
     <row r="6">
@@ -1003,12 +991,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1030,7 +1018,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="O6" t="n">
         <v>41.5</v>
@@ -1053,13 +1041,13 @@
         <v>26.83</v>
       </c>
       <c r="U6" t="n">
-        <v>95.631</v>
+        <v>86.158</v>
       </c>
       <c r="V6" t="n">
         <v>5.112</v>
       </c>
       <c r="W6" t="n">
-        <v>-71.735</v>
+        <v>-68.262</v>
       </c>
     </row>
     <row r="7">
@@ -1078,37 +1066,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-11 | KCHOL.IS: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>196.0145460497629</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -2.17% / +0.24% / -3.48%</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>63.34898599832736</v>
       </c>
       <c r="K7" t="n">
-        <v>-22.46977726967703</v>
+        <v>-24.74012475534331</v>
       </c>
       <c r="L7" t="n">
         <v>15.29584021689743</v>
@@ -1117,7 +1093,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -1127,26 +1103,26 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>32.286</v>
+        <v>34.269</v>
       </c>
       <c r="T7" t="n">
-        <v>32.286</v>
+        <v>34.269</v>
       </c>
       <c r="U7" t="n">
-        <v>74.087</v>
+        <v>67.491</v>
       </c>
       <c r="V7" t="n">
-        <v>35.659</v>
+        <v>31.686</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.004</v>
+        <v>-87.31999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1165,22 +1141,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1188,14 +1164,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
+          <t>AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>47.53226786131737</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.26977966026103</v>
+        <v>-18.72059728988012</v>
       </c>
       <c r="L8" t="n">
         <v>9.11952761462077</v>
@@ -1207,7 +1183,7 @@
         <v>238.1</v>
       </c>
       <c r="O8" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="P8" t="n">
         <v>3.4</v>
@@ -1221,19 +1197,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>33.389</v>
+        <v>33.802</v>
       </c>
       <c r="T8" t="n">
-        <v>33.389</v>
+        <v>33.802</v>
       </c>
       <c r="U8" t="n">
-        <v>26.023</v>
+        <v>23.219</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.054</v>
+        <v>-9.775</v>
       </c>
       <c r="W8" t="n">
-        <v>-58.779</v>
+        <v>-62.919</v>
       </c>
     </row>
     <row r="9">
@@ -1252,12 +1228,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1279,7 +1255,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
       <c r="O9" t="n">
         <v>48.6</v>
@@ -1302,13 +1278,13 @@
         <v>6.126</v>
       </c>
       <c r="U9" t="n">
-        <v>39.296</v>
+        <v>39.565</v>
       </c>
       <c r="V9" t="n">
         <v>20.698</v>
       </c>
       <c r="W9" t="n">
-        <v>-7.427</v>
+        <v>-7.441</v>
       </c>
     </row>
     <row r="10">
@@ -1327,22 +1303,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1350,14 +1326,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
+          <t>AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>47.53226786131737</v>
       </c>
       <c r="K10" t="n">
-        <v>-16.26977966026103</v>
+        <v>-18.72059728988012</v>
       </c>
       <c r="L10" t="n">
         <v>9.11952761462077</v>
@@ -1369,7 +1345,7 @@
         <v>238.1</v>
       </c>
       <c r="O10" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="P10" t="n">
         <v>3.4</v>
@@ -1383,19 +1359,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>33.389</v>
+        <v>33.802</v>
       </c>
       <c r="T10" t="n">
-        <v>33.389</v>
+        <v>33.802</v>
       </c>
       <c r="U10" t="n">
-        <v>26.023</v>
+        <v>23.219</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.054</v>
+        <v>-9.775</v>
       </c>
       <c r="W10" t="n">
-        <v>-58.779</v>
+        <v>-62.919</v>
       </c>
     </row>
     <row r="11">
@@ -1414,22 +1390,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGHOL.IS, ENJSA.IS</t>
+          <t>AGHOL.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-07-29 | ENJSA.IS: 2026-08-04</t>
+          <t>AGHOL.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1437,14 +1413,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +1.71% / +4.09% / -0.81% | ENJSA.IS: +3.22% / +8.60% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>46.52344570180613</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.46730594284595</v>
+        <v>-16.14354363893605</v>
       </c>
       <c r="L11" t="n">
         <v>9.284980112588903</v>
@@ -1453,13 +1429,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>43.7</v>
+        <v>44.6</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="P11" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1470,19 +1446,19 @@
         <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>24.438</v>
+        <v>25.707</v>
       </c>
       <c r="T11" t="n">
-        <v>24.438</v>
+        <v>25.707</v>
       </c>
       <c r="U11" t="n">
-        <v>37.459</v>
+        <v>31.079</v>
       </c>
       <c r="V11" t="n">
-        <v>23.37</v>
+        <v>18.189</v>
       </c>
       <c r="W11" t="n">
-        <v>-39.793</v>
+        <v>-45.356</v>
       </c>
     </row>
     <row r="12">
@@ -1496,57 +1472,57 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ARCLK.IS, ASELS.IS, BSOKE.IS</t>
+          <t>ARCLK.IS, ASELS.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: 2026-08-05 | ASELS.IS: 2026-08-07 | BSOKE.IS: 2026-08-05</t>
+          <t>ARCLK.IS: 2026-07-14 | ASELS.IS: 2026-08-07</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>36.17882212689536</v>
+        <v>27.75558345657336</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.84% / +3.12% / -1.64% | ASELS.IS: +0.26% / +2.47% / -1.98% | BSOKE.IS: +2.23% / +4.50% / -0.51%</t>
+          <t>ARCLK.IS: -1.40% / +3.93% / -1.99% | ASELS.IS: +2.81% / +3.60% / -1.98%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12.13985059364762</v>
+        <v>4.386506377662958</v>
       </c>
       <c r="K12" t="n">
-        <v>19.61050606302861</v>
+        <v>19.80823695935388</v>
       </c>
       <c r="L12" t="n">
-        <v>17.59856804976424</v>
+        <v>29.34479286819045</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>100.2</v>
+        <v>47</v>
       </c>
       <c r="O12" t="n">
-        <v>49.5</v>
+        <v>54.7</v>
       </c>
       <c r="P12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1554,22 +1530,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>17.599</v>
+        <v>10.345</v>
       </c>
       <c r="T12" t="n">
-        <v>15.841</v>
+        <v>10.345</v>
       </c>
       <c r="U12" t="n">
-        <v>36.391</v>
+        <v>68.96599999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>46.605</v>
+        <v>52.724</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.956</v>
+        <v>-10.882</v>
       </c>
     </row>
     <row r="13">
@@ -1588,14 +1564,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>AGHOL.IS, AKSA.IS</t>
@@ -1603,7 +1579,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1611,14 +1587,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-11.44224900467197</v>
       </c>
       <c r="K13" t="n">
-        <v>17.00308652756868</v>
+        <v>13.5783585617506</v>
       </c>
       <c r="L13" t="n">
         <v>36.66344986553255</v>
@@ -1627,10 +1603,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>212.3</v>
+        <v>212.4</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="P13" t="n">
         <v>3.6</v>
@@ -1650,13 +1626,13 @@
         <v>19.486</v>
       </c>
       <c r="U13" t="n">
-        <v>53.162</v>
+        <v>50.058</v>
       </c>
       <c r="V13" t="n">
-        <v>31.924</v>
+        <v>28.062</v>
       </c>
       <c r="W13" t="n">
-        <v>-3.046</v>
+        <v>-7.599</v>
       </c>
     </row>
     <row r="14">
@@ -1675,14 +1651,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>AGHOL.IS, AKSA.IS</t>
@@ -1690,7 +1666,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1698,14 +1674,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-1.546706160761147</v>
       </c>
       <c r="K14" t="n">
-        <v>15.96209829323305</v>
+        <v>12.56784047674202</v>
       </c>
       <c r="L14" t="n">
         <v>21.31957361714377</v>
@@ -1714,10 +1690,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>69.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="O14" t="n">
-        <v>51.8</v>
+        <v>50.7</v>
       </c>
       <c r="P14" t="n">
         <v>5.6</v>
@@ -1737,13 +1713,13 @@
         <v>20.511</v>
       </c>
       <c r="U14" t="n">
-        <v>37.495</v>
+        <v>33.956</v>
       </c>
       <c r="V14" t="n">
-        <v>15.651</v>
+        <v>12.266</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.184</v>
+        <v>-9.242000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1888,37 +1864,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-11 | KCHOL.IS: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>196.0145460497629</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -2.17% / +0.24% / -3.48%</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>63.34898599832736</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.46977726967703</v>
+        <v>-24.74012475534331</v>
       </c>
       <c r="L18" t="n">
         <v>15.29584021689743</v>
@@ -1927,7 +1891,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N18" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O18" t="n">
         <v>46.7</v>
@@ -1937,26 +1901,26 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>32.286</v>
+        <v>34.269</v>
       </c>
       <c r="T18" t="n">
-        <v>32.286</v>
+        <v>34.269</v>
       </c>
       <c r="U18" t="n">
-        <v>74.087</v>
+        <v>67.491</v>
       </c>
       <c r="V18" t="n">
-        <v>35.659</v>
+        <v>31.686</v>
       </c>
       <c r="W18" t="n">
-        <v>-83.004</v>
+        <v>-87.31999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1977,22 +1941,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
+          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2000,14 +1964,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28% | ENJSA.IS: -1.61% / +3.53% / -3.44%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>47.22954822730454</v>
       </c>
       <c r="K19" t="n">
-        <v>-19.66730433335175</v>
+        <v>-21.90618105639208</v>
       </c>
       <c r="L19" t="n">
         <v>15.35053097522994</v>
@@ -2016,10 +1980,10 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>103.2</v>
+        <v>104</v>
       </c>
       <c r="O19" t="n">
-        <v>45.2</v>
+        <v>44.3</v>
       </c>
       <c r="P19" t="n">
         <v>5.7</v>
@@ -2033,19 +1997,19 @@
         <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>40.983</v>
+        <v>42.628</v>
       </c>
       <c r="T19" t="n">
-        <v>40.983</v>
+        <v>42.628</v>
       </c>
       <c r="U19" t="n">
-        <v>32.99</v>
+        <v>30.051</v>
       </c>
       <c r="V19" t="n">
-        <v>10.399</v>
+        <v>7.323</v>
       </c>
       <c r="W19" t="n">
-        <v>-92.35299999999999</v>
+        <v>-96.63</v>
       </c>
     </row>
     <row r="20">
@@ -2066,22 +2030,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS, ENJSA.IS</t>
+          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05 | ENJSA.IS: 2026-08-06</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2089,14 +2053,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28% | ENJSA.IS: -1.61% / +3.53% / -3.44%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>47.22954822730454</v>
       </c>
       <c r="K20" t="n">
-        <v>-19.66730433335175</v>
+        <v>-21.90618105639208</v>
       </c>
       <c r="L20" t="n">
         <v>15.35053097522994</v>
@@ -2105,10 +2069,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>103.2</v>
+        <v>104</v>
       </c>
       <c r="O20" t="n">
-        <v>45.2</v>
+        <v>44.3</v>
       </c>
       <c r="P20" t="n">
         <v>5.7</v>
@@ -2122,19 +2086,19 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>40.983</v>
+        <v>42.628</v>
       </c>
       <c r="T20" t="n">
-        <v>40.983</v>
+        <v>42.628</v>
       </c>
       <c r="U20" t="n">
-        <v>32.99</v>
+        <v>30.051</v>
       </c>
       <c r="V20" t="n">
-        <v>10.399</v>
+        <v>7.323</v>
       </c>
       <c r="W20" t="n">
-        <v>-92.35299999999999</v>
+        <v>-96.63</v>
       </c>
     </row>
     <row r="21">
@@ -2155,12 +2119,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2182,7 +2146,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="O21" t="n">
         <v>41.5</v>
@@ -2205,13 +2169,13 @@
         <v>26.83</v>
       </c>
       <c r="U21" t="n">
-        <v>95.631</v>
+        <v>86.158</v>
       </c>
       <c r="V21" t="n">
         <v>5.112</v>
       </c>
       <c r="W21" t="n">
-        <v>-71.735</v>
+        <v>-68.262</v>
       </c>
     </row>
     <row r="22">
@@ -2232,22 +2196,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGHOL.IS, ENJSA.IS</t>
+          <t>AGHOL.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-07-29 | ENJSA.IS: 2026-08-04</t>
+          <t>AGHOL.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2255,14 +2219,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +1.71% / +4.09% / -0.81% | ENJSA.IS: +3.22% / +8.60% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>46.52344570180613</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.46730594284595</v>
+        <v>-16.14354363893605</v>
       </c>
       <c r="L22" t="n">
         <v>9.284980112588903</v>
@@ -2271,13 +2235,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>43.7</v>
+        <v>44.6</v>
       </c>
       <c r="O22" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="P22" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2288,19 +2252,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>24.438</v>
+        <v>25.707</v>
       </c>
       <c r="T22" t="n">
-        <v>24.438</v>
+        <v>25.707</v>
       </c>
       <c r="U22" t="n">
-        <v>37.459</v>
+        <v>31.079</v>
       </c>
       <c r="V22" t="n">
-        <v>23.37</v>
+        <v>18.189</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.793</v>
+        <v>-45.356</v>
       </c>
     </row>
     <row r="23">
@@ -2321,22 +2285,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2344,14 +2308,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
+          <t>AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>47.53226786131737</v>
       </c>
       <c r="K23" t="n">
-        <v>-16.26977966026103</v>
+        <v>-18.72059728988012</v>
       </c>
       <c r="L23" t="n">
         <v>9.11952761462077</v>
@@ -2363,7 +2327,7 @@
         <v>238.1</v>
       </c>
       <c r="O23" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="P23" t="n">
         <v>3.4</v>
@@ -2377,19 +2341,19 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>33.389</v>
+        <v>33.802</v>
       </c>
       <c r="T23" t="n">
-        <v>33.389</v>
+        <v>33.802</v>
       </c>
       <c r="U23" t="n">
-        <v>26.023</v>
+        <v>23.219</v>
       </c>
       <c r="V23" t="n">
-        <v>-7.054</v>
+        <v>-9.775</v>
       </c>
       <c r="W23" t="n">
-        <v>-58.779</v>
+        <v>-62.919</v>
       </c>
     </row>
     <row r="24">
@@ -2410,12 +2374,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2437,7 +2401,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N24" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
       <c r="O24" t="n">
         <v>48.6</v>
@@ -2460,13 +2424,13 @@
         <v>6.126</v>
       </c>
       <c r="U24" t="n">
-        <v>39.296</v>
+        <v>39.565</v>
       </c>
       <c r="V24" t="n">
         <v>20.698</v>
       </c>
       <c r="W24" t="n">
-        <v>-7.427</v>
+        <v>-7.441</v>
       </c>
     </row>
     <row r="25">
@@ -2487,14 +2451,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>AGHOL.IS, AKSA.IS</t>
@@ -2502,7 +2466,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2510,14 +2474,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.546706160761147</v>
       </c>
       <c r="K25" t="n">
-        <v>15.96209829323305</v>
+        <v>12.56784047674202</v>
       </c>
       <c r="L25" t="n">
         <v>21.31957361714377</v>
@@ -2526,10 +2490,10 @@
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>69.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="O25" t="n">
-        <v>51.8</v>
+        <v>50.7</v>
       </c>
       <c r="P25" t="n">
         <v>5.6</v>
@@ -2549,13 +2513,13 @@
         <v>20.511</v>
       </c>
       <c r="U25" t="n">
-        <v>37.495</v>
+        <v>33.956</v>
       </c>
       <c r="V25" t="n">
-        <v>15.651</v>
+        <v>12.266</v>
       </c>
       <c r="W25" t="n">
-        <v>-5.184</v>
+        <v>-9.242000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2571,57 +2535,57 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ARCLK.IS, ASELS.IS, BSOKE.IS</t>
+          <t>ARCLK.IS, ASELS.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ARCLK.IS: 2026-08-05 | ASELS.IS: 2026-08-07 | BSOKE.IS: 2026-08-05</t>
+          <t>ARCLK.IS: 2026-07-14 | ASELS.IS: 2026-08-07</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>36.17882212689536</v>
+        <v>27.75558345657336</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.84% / +3.12% / -1.64% | ASELS.IS: +0.26% / +2.47% / -1.98% | BSOKE.IS: +2.23% / +4.50% / -0.51%</t>
+          <t>ARCLK.IS: -1.40% / +3.93% / -1.99% | ASELS.IS: +2.81% / +3.60% / -1.98%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12.13985059364762</v>
+        <v>4.386506377662958</v>
       </c>
       <c r="K26" t="n">
-        <v>19.61050606302861</v>
+        <v>19.80823695935388</v>
       </c>
       <c r="L26" t="n">
-        <v>17.59856804976424</v>
+        <v>29.34479286819045</v>
       </c>
       <c r="M26" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>100.2</v>
+        <v>47</v>
       </c>
       <c r="O26" t="n">
-        <v>49.5</v>
+        <v>54.7</v>
       </c>
       <c r="P26" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2629,22 +2593,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>17.599</v>
+        <v>10.345</v>
       </c>
       <c r="T26" t="n">
-        <v>15.841</v>
+        <v>10.345</v>
       </c>
       <c r="U26" t="n">
-        <v>36.391</v>
+        <v>68.96599999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>46.605</v>
+        <v>52.724</v>
       </c>
       <c r="W26" t="n">
-        <v>-3.956</v>
+        <v>-10.882</v>
       </c>
     </row>
     <row r="27">
@@ -2665,14 +2629,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>AGHOL.IS, AKSA.IS</t>
@@ -2680,7 +2644,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-05 | AKSA.IS: 2026-08-05</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2688,14 +2652,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.44% / +2.22% / -1.82% | AKSA.IS: -0.42% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-11.44224900467197</v>
       </c>
       <c r="K27" t="n">
-        <v>17.00308652756868</v>
+        <v>13.5783585617506</v>
       </c>
       <c r="L27" t="n">
         <v>36.66344986553255</v>
@@ -2704,10 +2668,10 @@
         <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>212.3</v>
+        <v>212.4</v>
       </c>
       <c r="O27" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="P27" t="n">
         <v>3.6</v>
@@ -2727,13 +2691,13 @@
         <v>19.486</v>
       </c>
       <c r="U27" t="n">
-        <v>53.162</v>
+        <v>50.058</v>
       </c>
       <c r="V27" t="n">
-        <v>31.924</v>
+        <v>28.062</v>
       </c>
       <c r="W27" t="n">
-        <v>-3.046</v>
+        <v>-7.599</v>
       </c>
     </row>
   </sheetData>
@@ -2763,7 +2727,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -2923,22 +2887,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AEFES.IS, AGHOL.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2946,14 +2910,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.36640499489124</v>
+        <v>-14.50640349607323</v>
       </c>
       <c r="L3" t="n">
         <v>17.81201875402705</v>
@@ -2962,10 +2926,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="O3" t="n">
-        <v>47.7</v>
+        <v>46.5</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -2985,13 +2949,13 @@
         <v>28.525</v>
       </c>
       <c r="U3" t="n">
-        <v>59.781</v>
+        <v>52.666</v>
       </c>
       <c r="V3" t="n">
-        <v>7.786</v>
+        <v>2.807</v>
       </c>
       <c r="W3" t="n">
-        <v>-51.924</v>
+        <v>-59.407</v>
       </c>
     </row>
     <row r="4">
@@ -3010,22 +2974,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AEFES.IS, AGHOL.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3033,14 +2997,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.36640499489124</v>
+        <v>-14.50640349607323</v>
       </c>
       <c r="L4" t="n">
         <v>17.81201875402705</v>
@@ -3049,10 +3013,10 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="O4" t="n">
-        <v>47.7</v>
+        <v>46.5</v>
       </c>
       <c r="P4" t="n">
         <v>5</v>
@@ -3072,13 +3036,13 @@
         <v>28.525</v>
       </c>
       <c r="U4" t="n">
-        <v>59.781</v>
+        <v>52.666</v>
       </c>
       <c r="V4" t="n">
-        <v>7.786</v>
+        <v>2.807</v>
       </c>
       <c r="W4" t="n">
-        <v>-51.924</v>
+        <v>-59.407</v>
       </c>
     </row>
     <row r="5">
@@ -3097,22 +3061,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AEFES.IS, AGHOL.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3120,14 +3084,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>52.92070673367628</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.64318248188337</v>
+        <v>-31.93901277360915</v>
       </c>
       <c r="L5" t="n">
         <v>21.28996887664675</v>
@@ -3136,10 +3100,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>120</v>
+        <v>120.8</v>
       </c>
       <c r="O5" t="n">
-        <v>42.1</v>
+        <v>41.4</v>
       </c>
       <c r="P5" t="n">
         <v>5.2</v>
@@ -3153,19 +3117,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>35.94</v>
+        <v>38.574</v>
       </c>
       <c r="T5" t="n">
-        <v>35.94</v>
+        <v>38.574</v>
       </c>
       <c r="U5" t="n">
-        <v>37.654</v>
+        <v>31.542</v>
       </c>
       <c r="V5" t="n">
-        <v>-9.194000000000001</v>
+        <v>-13.388</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.093</v>
+        <v>-82.605</v>
       </c>
     </row>
     <row r="6">
@@ -3184,22 +3148,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AEFES.IS, AGHOL.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3207,14 +3171,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.36640499489124</v>
+        <v>-14.50640349607323</v>
       </c>
       <c r="L6" t="n">
         <v>17.81201875402705</v>
@@ -3223,10 +3187,10 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="O6" t="n">
-        <v>47.7</v>
+        <v>46.5</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -3246,13 +3210,13 @@
         <v>28.525</v>
       </c>
       <c r="U6" t="n">
-        <v>59.781</v>
+        <v>52.666</v>
       </c>
       <c r="V6" t="n">
-        <v>7.786</v>
+        <v>2.807</v>
       </c>
       <c r="W6" t="n">
-        <v>-51.924</v>
+        <v>-59.407</v>
       </c>
     </row>
     <row r="7">
@@ -3271,22 +3235,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEFES.IS, AGHOL.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3294,14 +3258,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.36640499489124</v>
+        <v>-14.50640349607323</v>
       </c>
       <c r="L7" t="n">
         <v>17.81201875402705</v>
@@ -3310,10 +3274,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="O7" t="n">
-        <v>47.7</v>
+        <v>46.5</v>
       </c>
       <c r="P7" t="n">
         <v>5</v>
@@ -3333,13 +3297,13 @@
         <v>28.525</v>
       </c>
       <c r="U7" t="n">
-        <v>59.781</v>
+        <v>52.666</v>
       </c>
       <c r="V7" t="n">
-        <v>7.786</v>
+        <v>2.807</v>
       </c>
       <c r="W7" t="n">
-        <v>-51.924</v>
+        <v>-59.407</v>
       </c>
     </row>
     <row r="8">
@@ -3358,22 +3322,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEFES.IS, ENJSA.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | ENJSA.IS: 2026-08-06</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3381,14 +3345,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -1.99% / +3.13% / -3.81%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>54.14356002865899</v>
       </c>
       <c r="K8" t="n">
-        <v>-18.08336659282025</v>
+        <v>-21.04314354246713</v>
       </c>
       <c r="L8" t="n">
         <v>14.80675251389611</v>
@@ -3397,10 +3361,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>45</v>
+        <v>44.6</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -3414,19 +3378,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>33.537</v>
+        <v>35.938</v>
       </c>
       <c r="T8" t="n">
-        <v>33.537</v>
+        <v>35.938</v>
       </c>
       <c r="U8" t="n">
-        <v>3.6</v>
+        <v>0.004</v>
       </c>
       <c r="V8" t="n">
-        <v>-15.684</v>
+        <v>-18.73</v>
       </c>
       <c r="W8" t="n">
-        <v>-52.276</v>
+        <v>-56.102</v>
       </c>
     </row>
     <row r="9">
@@ -3445,12 +3409,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3472,7 +3436,7 @@
         <v>61.11111111111111</v>
       </c>
       <c r="N9" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="O9" t="n">
         <v>62.2</v>
@@ -3495,13 +3459,13 @@
         <v>6.293</v>
       </c>
       <c r="U9" t="n">
-        <v>33.654</v>
+        <v>33.681</v>
       </c>
       <c r="V9" t="n">
         <v>14.787</v>
       </c>
       <c r="W9" t="n">
-        <v>-8.975</v>
+        <v>-8.977</v>
       </c>
     </row>
     <row r="10">
@@ -3520,12 +3484,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3547,7 +3511,7 @@
         <v>61.11111111111111</v>
       </c>
       <c r="N10" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="O10" t="n">
         <v>67.3</v>
@@ -3570,13 +3534,13 @@
         <v>5.722</v>
       </c>
       <c r="U10" t="n">
-        <v>43.47</v>
+        <v>43.498</v>
       </c>
       <c r="V10" t="n">
         <v>22.875</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.271</v>
+        <v>-4.272</v>
       </c>
     </row>
     <row r="11">
@@ -3595,12 +3559,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3622,7 +3586,7 @@
         <v>61.11111111111111</v>
       </c>
       <c r="N11" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="O11" t="n">
         <v>68.5</v>
@@ -3645,13 +3609,13 @@
         <v>5.722</v>
       </c>
       <c r="U11" t="n">
-        <v>42.828</v>
+        <v>42.857</v>
       </c>
       <c r="V11" t="n">
         <v>22.326</v>
       </c>
       <c r="W11" t="n">
-        <v>-4.336</v>
+        <v>-4.337</v>
       </c>
     </row>
     <row r="12">
@@ -3670,12 +3634,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3693,14 +3657,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +10.49% / +13.48% / 0.00%</t>
+          <t>TRENJ.IS: -0.19% / +0.36% / -0.74% | TUPRS.IS: +13.00% / +13.50% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>4.084117806506127</v>
       </c>
       <c r="K12" t="n">
-        <v>17.34102688518859</v>
+        <v>17.95202756543382</v>
       </c>
       <c r="L12" t="n">
         <v>14.21663509452158</v>
@@ -3709,7 +3673,7 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="O12" t="n">
         <v>49.7</v>
@@ -3732,13 +3696,13 @@
         <v>12.828</v>
       </c>
       <c r="U12" t="n">
-        <v>87.13</v>
+        <v>87.133</v>
       </c>
       <c r="V12" t="n">
-        <v>73.39700000000001</v>
+        <v>74.3</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.22</v>
+        <v>-3.229</v>
       </c>
     </row>
     <row r="13">
@@ -3757,12 +3721,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3780,14 +3744,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TUPRS.IS: +10.49% / +13.48% / 0.00%</t>
+          <t>TUPRS.IS: +13.00% / +13.50% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>5.871595897009474</v>
       </c>
       <c r="K13" t="n">
-        <v>15.19036530457831</v>
+        <v>16.56269116367324</v>
       </c>
       <c r="L13" t="n">
         <v>19.92682085509051</v>
@@ -3796,7 +3760,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="O13" t="n">
         <v>48.3</v>
@@ -3819,13 +3783,13 @@
         <v>15.567</v>
       </c>
       <c r="U13" t="n">
-        <v>111.008</v>
+        <v>113.42</v>
       </c>
       <c r="V13" t="n">
-        <v>111.157</v>
+        <v>113.672</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.31</v>
+        <v>-4.793</v>
       </c>
     </row>
     <row r="14">
@@ -3839,57 +3803,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BRSAN.IS, MGROS.IS</t>
+          <t>ASTOR.IS, TKFEN.IS, TRENJ.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-11 | MGROS.IS: 2026-08-11</t>
+          <t>ASTOR.IS: 2026-08-05 | TKFEN.IS: 2026-08-12 | TRENJ.IS: 2026-08-11 | TUPRS.IS: 2026-08-10</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.985783758045081</v>
+        <v>27.17808701479216</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | MGROS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -1.29% / +4.46% / -3.93% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.19% / +0.36% / -0.74% | TUPRS.IS: +0.58% / +1.03% / -3.36%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-0.880754364333225</v>
+        <v>0.7994491519249358</v>
       </c>
       <c r="K14" t="n">
-        <v>8.857985453728556</v>
+        <v>9.455141646681685</v>
       </c>
       <c r="L14" t="n">
-        <v>8.252476290495281</v>
+        <v>11.00674698777365</v>
       </c>
       <c r="M14" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>26.3</v>
+        <v>291.6</v>
       </c>
       <c r="O14" t="n">
-        <v>43.4</v>
+        <v>47</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3897,22 +3861,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>4.228</v>
+        <v>10.148</v>
       </c>
       <c r="T14" t="n">
-        <v>4.228</v>
+        <v>10.148</v>
       </c>
       <c r="U14" t="n">
-        <v>5.091</v>
+        <v>63.561</v>
       </c>
       <c r="V14" t="n">
-        <v>4.276</v>
+        <v>47.081</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.363</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="16">
@@ -4057,22 +4021,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEFES.IS, AGHOL.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4080,14 +4044,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.36640499489124</v>
+        <v>-14.50640349607323</v>
       </c>
       <c r="L18" t="n">
         <v>17.81201875402705</v>
@@ -4096,10 +4060,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="O18" t="n">
-        <v>47.7</v>
+        <v>46.5</v>
       </c>
       <c r="P18" t="n">
         <v>5</v>
@@ -4119,13 +4083,13 @@
         <v>28.525</v>
       </c>
       <c r="U18" t="n">
-        <v>59.781</v>
+        <v>52.666</v>
       </c>
       <c r="V18" t="n">
-        <v>7.786</v>
+        <v>2.807</v>
       </c>
       <c r="W18" t="n">
-        <v>-51.924</v>
+        <v>-59.407</v>
       </c>
     </row>
     <row r="19">
@@ -4146,22 +4110,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEFES.IS, AGHOL.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4169,14 +4133,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>65.1916625269281</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.36640499489124</v>
+        <v>-14.50640349607323</v>
       </c>
       <c r="L19" t="n">
         <v>17.81201875402705</v>
@@ -4185,10 +4149,10 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="O19" t="n">
-        <v>47.7</v>
+        <v>46.5</v>
       </c>
       <c r="P19" t="n">
         <v>5</v>
@@ -4208,13 +4172,13 @@
         <v>28.525</v>
       </c>
       <c r="U19" t="n">
-        <v>59.781</v>
+        <v>52.666</v>
       </c>
       <c r="V19" t="n">
-        <v>7.786</v>
+        <v>2.807</v>
       </c>
       <c r="W19" t="n">
-        <v>-51.924</v>
+        <v>-59.407</v>
       </c>
     </row>
     <row r="20">
@@ -4235,22 +4199,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEFES.IS, AGHOL.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | AGHOL.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4258,14 +4222,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | AGHOL.IS: +0.08% / +1.96% / -2.01%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>52.92070673367628</v>
       </c>
       <c r="K20" t="n">
-        <v>-28.64318248188337</v>
+        <v>-31.93901277360915</v>
       </c>
       <c r="L20" t="n">
         <v>21.28996887664675</v>
@@ -4274,10 +4238,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>120</v>
+        <v>120.8</v>
       </c>
       <c r="O20" t="n">
-        <v>42.1</v>
+        <v>41.4</v>
       </c>
       <c r="P20" t="n">
         <v>5.2</v>
@@ -4291,19 +4255,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>35.94</v>
+        <v>38.574</v>
       </c>
       <c r="T20" t="n">
-        <v>35.94</v>
+        <v>38.574</v>
       </c>
       <c r="U20" t="n">
-        <v>37.654</v>
+        <v>31.542</v>
       </c>
       <c r="V20" t="n">
-        <v>-9.194000000000001</v>
+        <v>-13.388</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.093</v>
+        <v>-82.605</v>
       </c>
     </row>
     <row r="21">
@@ -4324,22 +4288,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEFES.IS, ENJSA.IS</t>
+          <t>TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-11 | ENJSA.IS: 2026-08-06</t>
+          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4347,14 +4311,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -1.99% / +3.13% / -3.81%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>54.14356002865899</v>
       </c>
       <c r="K21" t="n">
-        <v>-18.08336659282025</v>
+        <v>-21.04314354246713</v>
       </c>
       <c r="L21" t="n">
         <v>14.80675251389611</v>
@@ -4363,10 +4327,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="O21" t="n">
-        <v>45</v>
+        <v>44.6</v>
       </c>
       <c r="P21" t="n">
         <v>4</v>
@@ -4380,19 +4344,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>33.537</v>
+        <v>35.938</v>
       </c>
       <c r="T21" t="n">
-        <v>33.537</v>
+        <v>35.938</v>
       </c>
       <c r="U21" t="n">
-        <v>3.6</v>
+        <v>0.004</v>
       </c>
       <c r="V21" t="n">
-        <v>-15.684</v>
+        <v>-18.73</v>
       </c>
       <c r="W21" t="n">
-        <v>-52.276</v>
+        <v>-56.102</v>
       </c>
     </row>
     <row r="22">
@@ -4413,12 +4377,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4440,7 +4404,7 @@
         <v>61.11111111111111</v>
       </c>
       <c r="N22" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="O22" t="n">
         <v>67.3</v>
@@ -4463,13 +4427,13 @@
         <v>5.722</v>
       </c>
       <c r="U22" t="n">
-        <v>43.47</v>
+        <v>43.498</v>
       </c>
       <c r="V22" t="n">
         <v>22.875</v>
       </c>
       <c r="W22" t="n">
-        <v>-4.271</v>
+        <v>-4.272</v>
       </c>
     </row>
     <row r="23">
@@ -4490,12 +4454,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4517,7 +4481,7 @@
         <v>61.11111111111111</v>
       </c>
       <c r="N23" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="O23" t="n">
         <v>68.5</v>
@@ -4540,13 +4504,13 @@
         <v>5.722</v>
       </c>
       <c r="U23" t="n">
-        <v>42.828</v>
+        <v>42.857</v>
       </c>
       <c r="V23" t="n">
         <v>22.326</v>
       </c>
       <c r="W23" t="n">
-        <v>-4.336</v>
+        <v>-4.337</v>
       </c>
     </row>
     <row r="24">
@@ -4567,12 +4531,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4590,14 +4554,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TUPRS.IS: +10.49% / +13.48% / 0.00%</t>
+          <t>TUPRS.IS: +13.00% / +13.50% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>5.871595897009474</v>
       </c>
       <c r="K24" t="n">
-        <v>15.19036530457831</v>
+        <v>16.56269116367324</v>
       </c>
       <c r="L24" t="n">
         <v>19.92682085509051</v>
@@ -4606,7 +4570,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="O24" t="n">
         <v>48.3</v>
@@ -4629,13 +4593,13 @@
         <v>15.567</v>
       </c>
       <c r="U24" t="n">
-        <v>111.008</v>
+        <v>113.42</v>
       </c>
       <c r="V24" t="n">
-        <v>111.157</v>
+        <v>113.672</v>
       </c>
       <c r="W24" t="n">
-        <v>-7.31</v>
+        <v>-4.793</v>
       </c>
     </row>
     <row r="25">
@@ -4656,12 +4620,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4683,7 +4647,7 @@
         <v>61.11111111111111</v>
       </c>
       <c r="N25" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="O25" t="n">
         <v>62.2</v>
@@ -4706,13 +4670,13 @@
         <v>6.293</v>
       </c>
       <c r="U25" t="n">
-        <v>33.654</v>
+        <v>33.681</v>
       </c>
       <c r="V25" t="n">
         <v>14.787</v>
       </c>
       <c r="W25" t="n">
-        <v>-8.975</v>
+        <v>-8.977</v>
       </c>
     </row>
     <row r="26">
@@ -4733,12 +4697,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4756,14 +4720,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRENJ.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +10.49% / +13.48% / 0.00%</t>
+          <t>TRENJ.IS: -0.19% / +0.36% / -0.74% | TUPRS.IS: +13.00% / +13.50% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>4.084117806506127</v>
       </c>
       <c r="K26" t="n">
-        <v>17.34102688518859</v>
+        <v>17.95202756543382</v>
       </c>
       <c r="L26" t="n">
         <v>14.21663509452158</v>
@@ -4772,7 +4736,7 @@
         <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="O26" t="n">
         <v>49.7</v>
@@ -4795,13 +4759,13 @@
         <v>12.828</v>
       </c>
       <c r="U26" t="n">
-        <v>87.13</v>
+        <v>87.133</v>
       </c>
       <c r="V26" t="n">
-        <v>73.39700000000001</v>
+        <v>74.3</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.22</v>
+        <v>-3.229</v>
       </c>
     </row>
     <row r="27">
@@ -4817,57 +4781,57 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BRSAN.IS, MGROS.IS</t>
+          <t>ASTOR.IS, TKFEN.IS, TRENJ.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-11 | MGROS.IS: 2026-08-11</t>
+          <t>ASTOR.IS: 2026-08-05 | TKFEN.IS: 2026-08-12 | TRENJ.IS: 2026-08-11 | TUPRS.IS: 2026-08-10</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.985783758045081</v>
+        <v>27.17808701479216</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | MGROS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -1.29% / +4.46% / -3.93% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.19% / +0.36% / -0.74% | TUPRS.IS: +0.58% / +1.03% / -3.36%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-0.880754364333225</v>
+        <v>0.7994491519249358</v>
       </c>
       <c r="K27" t="n">
-        <v>8.857985453728556</v>
+        <v>9.455141646681685</v>
       </c>
       <c r="L27" t="n">
-        <v>8.252476290495281</v>
+        <v>11.00674698777365</v>
       </c>
       <c r="M27" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>26.3</v>
+        <v>291.6</v>
       </c>
       <c r="O27" t="n">
-        <v>43.4</v>
+        <v>47</v>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4875,22 +4839,22 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>4.228</v>
+        <v>10.148</v>
       </c>
       <c r="T27" t="n">
-        <v>4.228</v>
+        <v>10.148</v>
       </c>
       <c r="U27" t="n">
-        <v>5.091</v>
+        <v>63.561</v>
       </c>
       <c r="V27" t="n">
-        <v>4.276</v>
+        <v>47.081</v>
       </c>
       <c r="W27" t="n">
-        <v>-3.363</v>
+        <v>-5.22</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -577,7 +577,7 @@
   <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -587,7 +587,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -750,26 +750,38 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KCHOL.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>196.0145460497629</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>200.7847581010547</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>KCHOL.IS: -1.49% / +0.24% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J3" t="n">
-        <v>63.34898599832736</v>
+        <v>60.44543523268126</v>
       </c>
       <c r="K3" t="n">
-        <v>-24.74012475534331</v>
+        <v>-23.6398853472563</v>
       </c>
       <c r="L3" t="n">
         <v>15.29584021689743</v>
       </c>
       <c r="M3" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N3" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="O3" t="n">
         <v>46.7</v>
@@ -779,26 +791,26 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>34.269</v>
+        <v>33.308</v>
       </c>
       <c r="T3" t="n">
-        <v>34.269</v>
+        <v>33.308</v>
       </c>
       <c r="U3" t="n">
-        <v>67.491</v>
+        <v>71.459</v>
       </c>
       <c r="V3" t="n">
-        <v>31.686</v>
+        <v>32.793</v>
       </c>
       <c r="W3" t="n">
-        <v>-87.31999999999999</v>
+        <v>-85.631</v>
       </c>
     </row>
     <row r="4">
@@ -836,18 +848,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>146.7734767607337</v>
+        <v>162.016721807671</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>47.22954822730454</v>
+        <v>51.6858649523811</v>
       </c>
       <c r="K4" t="n">
-        <v>-21.90618105639208</v>
+        <v>-22.32122527611138</v>
       </c>
       <c r="L4" t="n">
         <v>15.35053097522994</v>
@@ -856,13 +868,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>104</v>
+        <v>104.2</v>
       </c>
       <c r="O4" t="n">
         <v>44.3</v>
       </c>
       <c r="P4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -873,19 +885,19 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>42.628</v>
+        <v>42.933</v>
       </c>
       <c r="T4" t="n">
-        <v>42.628</v>
+        <v>42.933</v>
       </c>
       <c r="U4" t="n">
-        <v>30.051</v>
+        <v>28.597</v>
       </c>
       <c r="V4" t="n">
-        <v>7.323</v>
+        <v>5.824</v>
       </c>
       <c r="W4" t="n">
-        <v>-96.63</v>
+        <v>-96.747</v>
       </c>
     </row>
     <row r="5">
@@ -923,18 +935,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>146.7734767607337</v>
+        <v>162.016721807671</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>47.22954822730454</v>
+        <v>51.6858649523811</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.90618105639208</v>
+        <v>-22.32122527611138</v>
       </c>
       <c r="L5" t="n">
         <v>15.35053097522994</v>
@@ -943,13 +955,13 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>104</v>
+        <v>104.2</v>
       </c>
       <c r="O5" t="n">
         <v>44.3</v>
       </c>
       <c r="P5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -960,19 +972,19 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>42.628</v>
+        <v>42.933</v>
       </c>
       <c r="T5" t="n">
-        <v>42.628</v>
+        <v>42.933</v>
       </c>
       <c r="U5" t="n">
-        <v>30.051</v>
+        <v>28.597</v>
       </c>
       <c r="V5" t="n">
-        <v>7.323</v>
+        <v>5.824</v>
       </c>
       <c r="W5" t="n">
-        <v>-96.63</v>
+        <v>-96.747</v>
       </c>
     </row>
     <row r="6">
@@ -1002,11 +1014,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>126.2206233289701</v>
+        <v>128.7435625153324</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>64.25815959292049</v>
+        <v>71.62036832824464</v>
       </c>
       <c r="K6" t="n">
         <v>-16.40003301706789</v>
@@ -1018,7 +1030,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>41.5</v>
@@ -1041,13 +1053,13 @@
         <v>26.83</v>
       </c>
       <c r="U6" t="n">
-        <v>86.158</v>
+        <v>95.631</v>
       </c>
       <c r="V6" t="n">
-        <v>5.112</v>
+        <v>4.807</v>
       </c>
       <c r="W6" t="n">
-        <v>-68.262</v>
+        <v>-71.735</v>
       </c>
     </row>
     <row r="7">
@@ -1074,26 +1086,38 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KCHOL.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>196.0145460497629</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>200.7847581010547</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>KCHOL.IS: -1.49% / +0.24% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J7" t="n">
-        <v>63.34898599832736</v>
+        <v>60.44543523268126</v>
       </c>
       <c r="K7" t="n">
-        <v>-24.74012475534331</v>
+        <v>-23.6398853472563</v>
       </c>
       <c r="L7" t="n">
         <v>15.29584021689743</v>
       </c>
       <c r="M7" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -1103,26 +1127,26 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>34.269</v>
+        <v>33.308</v>
       </c>
       <c r="T7" t="n">
-        <v>34.269</v>
+        <v>33.308</v>
       </c>
       <c r="U7" t="n">
-        <v>67.491</v>
+        <v>71.459</v>
       </c>
       <c r="V7" t="n">
-        <v>31.686</v>
+        <v>32.793</v>
       </c>
       <c r="W7" t="n">
-        <v>-87.31999999999999</v>
+        <v>-85.631</v>
       </c>
     </row>
     <row r="8">
@@ -1136,7 +1160,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1151,42 +1175,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AKSA.IS, TKFEN.IS</t>
+          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>93.60033341861605</v>
+        <v>162.016721807671</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.53226786131737</v>
+        <v>51.6858649523811</v>
       </c>
       <c r="K8" t="n">
-        <v>-18.72059728988012</v>
+        <v>-22.32122527611138</v>
       </c>
       <c r="L8" t="n">
-        <v>9.11952761462077</v>
+        <v>15.35053097522994</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>238.1</v>
+        <v>104.2</v>
       </c>
       <c r="O8" t="n">
-        <v>50.7</v>
+        <v>44.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1194,22 +1218,22 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>33.802</v>
+        <v>42.933</v>
       </c>
       <c r="T8" t="n">
-        <v>33.802</v>
+        <v>42.933</v>
       </c>
       <c r="U8" t="n">
-        <v>23.219</v>
+        <v>28.597</v>
       </c>
       <c r="V8" t="n">
-        <v>-9.775</v>
+        <v>5.824</v>
       </c>
       <c r="W8" t="n">
-        <v>-62.919</v>
+        <v>-96.747</v>
       </c>
     </row>
     <row r="9">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1236,55 +1260,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AKSA.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>54.76877565958047</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>99.0327377189677</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>27.20988295234317</v>
+        <v>49.78061960916962</v>
       </c>
       <c r="K9" t="n">
-        <v>2.366463069947145e-06</v>
+        <v>-19.35728289705845</v>
       </c>
       <c r="L9" t="n">
-        <v>5.126631971735584</v>
+        <v>9.11952761462077</v>
       </c>
       <c r="M9" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>55</v>
+        <v>238.6</v>
       </c>
       <c r="O9" t="n">
-        <v>48.6</v>
+        <v>50.7</v>
       </c>
       <c r="P9" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>6.126</v>
+        <v>34.321</v>
       </c>
       <c r="T9" t="n">
-        <v>6.126</v>
+        <v>34.321</v>
       </c>
       <c r="U9" t="n">
-        <v>39.565</v>
+        <v>21.376</v>
       </c>
       <c r="V9" t="n">
-        <v>20.698</v>
+        <v>-10.534</v>
       </c>
       <c r="W9" t="n">
-        <v>-7.441</v>
+        <v>-63.426</v>
       </c>
     </row>
     <row r="10">
@@ -1298,7 +1334,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1313,42 +1349,42 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AKSA.IS, TKFEN.IS</t>
+          <t>AGHOL.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>93.60033341861605</v>
+        <v>126.4280989095678</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.53226786131737</v>
+        <v>50.27876005534335</v>
       </c>
       <c r="K10" t="n">
-        <v>-18.72059728988012</v>
+        <v>-16.61363394689339</v>
       </c>
       <c r="L10" t="n">
-        <v>9.11952761462077</v>
+        <v>9.284980112588903</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>238.1</v>
+        <v>44.6</v>
       </c>
       <c r="O10" t="n">
-        <v>50.7</v>
+        <v>46.7</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1359,19 +1395,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>33.802</v>
+        <v>26.123</v>
       </c>
       <c r="T10" t="n">
-        <v>33.802</v>
+        <v>26.123</v>
       </c>
       <c r="U10" t="n">
-        <v>23.219</v>
+        <v>30.947</v>
       </c>
       <c r="V10" t="n">
-        <v>-9.775</v>
+        <v>17.063</v>
       </c>
       <c r="W10" t="n">
-        <v>-62.919</v>
+        <v>-46.304</v>
       </c>
     </row>
     <row r="11">
@@ -1385,7 +1421,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1409,7 +1445,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>125.8329117087326</v>
+        <v>126.4280989095678</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1417,22 +1453,22 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>46.52344570180613</v>
+        <v>50.27876005534335</v>
       </c>
       <c r="K11" t="n">
-        <v>-16.14354363893605</v>
+        <v>-16.61363394689339</v>
       </c>
       <c r="L11" t="n">
         <v>9.284980112588903</v>
       </c>
       <c r="M11" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N11" t="n">
         <v>44.6</v>
       </c>
       <c r="O11" t="n">
-        <v>47.8</v>
+        <v>46.7</v>
       </c>
       <c r="P11" t="n">
         <v>6.3</v>
@@ -1446,19 +1482,19 @@
         <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>25.707</v>
+        <v>26.123</v>
       </c>
       <c r="T11" t="n">
-        <v>25.707</v>
+        <v>26.123</v>
       </c>
       <c r="U11" t="n">
-        <v>31.079</v>
+        <v>30.947</v>
       </c>
       <c r="V11" t="n">
-        <v>18.189</v>
+        <v>17.063</v>
       </c>
       <c r="W11" t="n">
-        <v>-45.356</v>
+        <v>-46.304</v>
       </c>
     </row>
     <row r="12">
@@ -1496,27 +1532,27 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>27.75558345657336</v>
+        <v>30.92002035237105</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -1.40% / +3.93% / -1.99% | ASELS.IS: +2.81% / +3.60% / -1.98%</t>
+          <t>ARCLK.IS: -1.30% / +3.93% / -1.99% | ASELS.IS: +4.43% / +5.51% / -1.98%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4.386506377662958</v>
+        <v>2.22726845475778</v>
       </c>
       <c r="K12" t="n">
-        <v>19.80823695935388</v>
+        <v>20.83344757852008</v>
       </c>
       <c r="L12" t="n">
         <v>29.34479286819045</v>
       </c>
       <c r="M12" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="O12" t="n">
         <v>54.7</v>
@@ -1539,13 +1575,13 @@
         <v>10.345</v>
       </c>
       <c r="U12" t="n">
-        <v>68.96599999999999</v>
+        <v>69.879</v>
       </c>
       <c r="V12" t="n">
-        <v>52.724</v>
+        <v>53.686</v>
       </c>
       <c r="W12" t="n">
-        <v>-10.882</v>
+        <v>-9.407</v>
       </c>
     </row>
     <row r="13">
@@ -1583,18 +1619,18 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>20.7234228693673</v>
+        <v>27.13445809277037</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-11.44224900467197</v>
+        <v>-10.97009491799502</v>
       </c>
       <c r="K13" t="n">
-        <v>13.5783585617506</v>
+        <v>12.68866567804288</v>
       </c>
       <c r="L13" t="n">
         <v>36.66344986553255</v>
@@ -1603,7 +1639,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>212.4</v>
+        <v>212.8</v>
       </c>
       <c r="O13" t="n">
         <v>49.7</v>
@@ -1626,13 +1662,13 @@
         <v>19.486</v>
       </c>
       <c r="U13" t="n">
-        <v>50.058</v>
+        <v>47.514</v>
       </c>
       <c r="V13" t="n">
-        <v>28.062</v>
+        <v>27.434</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.599</v>
+        <v>-8.694000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1670,18 +1706,18 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>39.96325775756866</v>
+        <v>50.63929346397487</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-1.546706160761147</v>
+        <v>2.414581191190335</v>
       </c>
       <c r="K14" t="n">
-        <v>12.56784047674202</v>
+        <v>11.68606328014647</v>
       </c>
       <c r="L14" t="n">
         <v>21.31957361714377</v>
@@ -1690,7 +1726,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>50.7</v>
@@ -1713,13 +1749,13 @@
         <v>20.511</v>
       </c>
       <c r="U14" t="n">
-        <v>33.956</v>
+        <v>32.425</v>
       </c>
       <c r="V14" t="n">
-        <v>12.266</v>
+        <v>11.159</v>
       </c>
       <c r="W14" t="n">
-        <v>-9.242000000000001</v>
+        <v>-10.254</v>
       </c>
     </row>
     <row r="16">
@@ -1872,26 +1908,38 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KCHOL.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H18" t="n">
-        <v>196.0145460497629</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>200.7847581010547</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>KCHOL.IS: -1.49% / +0.24% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J18" t="n">
-        <v>63.34898599832736</v>
+        <v>60.44543523268126</v>
       </c>
       <c r="K18" t="n">
-        <v>-24.74012475534331</v>
+        <v>-23.6398853472563</v>
       </c>
       <c r="L18" t="n">
         <v>15.29584021689743</v>
       </c>
       <c r="M18" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="O18" t="n">
         <v>46.7</v>
@@ -1901,37 +1949,37 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>34.269</v>
+        <v>33.308</v>
       </c>
       <c r="T18" t="n">
-        <v>34.269</v>
+        <v>33.308</v>
       </c>
       <c r="U18" t="n">
-        <v>67.491</v>
+        <v>71.459</v>
       </c>
       <c r="V18" t="n">
-        <v>31.686</v>
+        <v>32.793</v>
       </c>
       <c r="W18" t="n">
-        <v>-87.31999999999999</v>
+        <v>-85.631</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 | 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1960,18 +2008,18 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>146.7734767607337</v>
+        <v>162.016721807671</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47.22954822730454</v>
+        <v>51.6858649523811</v>
       </c>
       <c r="K19" t="n">
-        <v>-21.90618105639208</v>
+        <v>-22.32122527611138</v>
       </c>
       <c r="L19" t="n">
         <v>15.35053097522994</v>
@@ -1980,13 +2028,13 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>104</v>
+        <v>104.2</v>
       </c>
       <c r="O19" t="n">
         <v>44.3</v>
       </c>
       <c r="P19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1997,19 +2045,19 @@
         <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>42.628</v>
+        <v>42.933</v>
       </c>
       <c r="T19" t="n">
-        <v>42.628</v>
+        <v>42.933</v>
       </c>
       <c r="U19" t="n">
-        <v>30.051</v>
+        <v>28.597</v>
       </c>
       <c r="V19" t="n">
-        <v>7.323</v>
+        <v>5.824</v>
       </c>
       <c r="W19" t="n">
-        <v>-96.63</v>
+        <v>-96.747</v>
       </c>
     </row>
     <row r="20">
@@ -2049,18 +2097,18 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>146.7734767607337</v>
+        <v>162.016721807671</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>47.22954822730454</v>
+        <v>51.6858649523811</v>
       </c>
       <c r="K20" t="n">
-        <v>-21.90618105639208</v>
+        <v>-22.32122527611138</v>
       </c>
       <c r="L20" t="n">
         <v>15.35053097522994</v>
@@ -2069,13 +2117,13 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>104</v>
+        <v>104.2</v>
       </c>
       <c r="O20" t="n">
         <v>44.3</v>
       </c>
       <c r="P20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2086,19 +2134,19 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>42.628</v>
+        <v>42.933</v>
       </c>
       <c r="T20" t="n">
-        <v>42.628</v>
+        <v>42.933</v>
       </c>
       <c r="U20" t="n">
-        <v>30.051</v>
+        <v>28.597</v>
       </c>
       <c r="V20" t="n">
-        <v>7.323</v>
+        <v>5.824</v>
       </c>
       <c r="W20" t="n">
-        <v>-96.63</v>
+        <v>-96.747</v>
       </c>
     </row>
     <row r="21">
@@ -2130,11 +2178,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>126.2206233289701</v>
+        <v>128.7435625153324</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>64.25815959292049</v>
+        <v>71.62036832824464</v>
       </c>
       <c r="K21" t="n">
         <v>-16.40003301706789</v>
@@ -2146,7 +2194,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O21" t="n">
         <v>41.5</v>
@@ -2169,13 +2217,13 @@
         <v>26.83</v>
       </c>
       <c r="U21" t="n">
-        <v>86.158</v>
+        <v>95.631</v>
       </c>
       <c r="V21" t="n">
-        <v>5.112</v>
+        <v>4.807</v>
       </c>
       <c r="W21" t="n">
-        <v>-68.262</v>
+        <v>-71.735</v>
       </c>
     </row>
     <row r="22">
@@ -2186,7 +2234,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2215,7 +2263,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>125.8329117087326</v>
+        <v>126.4280989095678</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2223,22 +2271,22 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>46.52344570180613</v>
+        <v>50.27876005534335</v>
       </c>
       <c r="K22" t="n">
-        <v>-16.14354363893605</v>
+        <v>-16.61363394689339</v>
       </c>
       <c r="L22" t="n">
         <v>9.284980112588903</v>
       </c>
       <c r="M22" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N22" t="n">
         <v>44.6</v>
       </c>
       <c r="O22" t="n">
-        <v>47.8</v>
+        <v>46.7</v>
       </c>
       <c r="P22" t="n">
         <v>6.3</v>
@@ -2252,35 +2300,35 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>25.707</v>
+        <v>26.123</v>
       </c>
       <c r="T22" t="n">
-        <v>25.707</v>
+        <v>26.123</v>
       </c>
       <c r="U22" t="n">
-        <v>31.079</v>
+        <v>30.947</v>
       </c>
       <c r="V22" t="n">
-        <v>18.189</v>
+        <v>17.063</v>
       </c>
       <c r="W22" t="n">
-        <v>-45.356</v>
+        <v>-46.304</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3 | 2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2295,42 +2343,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AKSA.IS, TKFEN.IS</t>
+          <t>AGHOL.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>93.60033341861605</v>
+        <v>126.4280989095678</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AKSA.IS: -1.78% / +2.48% / -3.28% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>47.53226786131737</v>
+        <v>50.27876005534335</v>
       </c>
       <c r="K23" t="n">
-        <v>-18.72059728988012</v>
+        <v>-16.61363394689339</v>
       </c>
       <c r="L23" t="n">
-        <v>9.11952761462077</v>
+        <v>9.284980112588903</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N23" t="n">
-        <v>238.1</v>
+        <v>44.6</v>
       </c>
       <c r="O23" t="n">
-        <v>50.7</v>
+        <v>46.7</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2341,19 +2389,19 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>33.802</v>
+        <v>26.123</v>
       </c>
       <c r="T23" t="n">
-        <v>33.802</v>
+        <v>26.123</v>
       </c>
       <c r="U23" t="n">
-        <v>23.219</v>
+        <v>30.947</v>
       </c>
       <c r="V23" t="n">
-        <v>-9.775</v>
+        <v>17.063</v>
       </c>
       <c r="W23" t="n">
-        <v>-62.919</v>
+        <v>-46.304</v>
       </c>
     </row>
     <row r="24">
@@ -2369,7 +2417,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2382,55 +2430,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AKSA.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>54.76877565958047</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>99.0327377189677</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>27.20988295234317</v>
+        <v>49.78061960916962</v>
       </c>
       <c r="K24" t="n">
-        <v>2.366463069947145e-06</v>
+        <v>-19.35728289705845</v>
       </c>
       <c r="L24" t="n">
-        <v>5.126631971735584</v>
+        <v>9.11952761462077</v>
       </c>
       <c r="M24" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>55</v>
+        <v>238.6</v>
       </c>
       <c r="O24" t="n">
-        <v>48.6</v>
+        <v>50.7</v>
       </c>
       <c r="P24" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>6.126</v>
+        <v>34.321</v>
       </c>
       <c r="T24" t="n">
-        <v>6.126</v>
+        <v>34.321</v>
       </c>
       <c r="U24" t="n">
-        <v>39.565</v>
+        <v>21.376</v>
       </c>
       <c r="V24" t="n">
-        <v>20.698</v>
+        <v>-10.534</v>
       </c>
       <c r="W24" t="n">
-        <v>-7.441</v>
+        <v>-63.426</v>
       </c>
     </row>
     <row r="25">
@@ -2470,18 +2530,18 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>39.96325775756866</v>
+        <v>50.63929346397487</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-1.546706160761147</v>
+        <v>2.414581191190335</v>
       </c>
       <c r="K25" t="n">
-        <v>12.56784047674202</v>
+        <v>11.68606328014647</v>
       </c>
       <c r="L25" t="n">
         <v>21.31957361714377</v>
@@ -2490,7 +2550,7 @@
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="O25" t="n">
         <v>50.7</v>
@@ -2513,13 +2573,13 @@
         <v>20.511</v>
       </c>
       <c r="U25" t="n">
-        <v>33.956</v>
+        <v>32.425</v>
       </c>
       <c r="V25" t="n">
-        <v>12.266</v>
+        <v>11.159</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.242000000000001</v>
+        <v>-10.254</v>
       </c>
     </row>
     <row r="26">
@@ -2559,27 +2619,27 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>27.75558345657336</v>
+        <v>30.92002035237105</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -1.40% / +3.93% / -1.99% | ASELS.IS: +2.81% / +3.60% / -1.98%</t>
+          <t>ARCLK.IS: -1.30% / +3.93% / -1.99% | ASELS.IS: +4.43% / +5.51% / -1.98%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4.386506377662958</v>
+        <v>2.22726845475778</v>
       </c>
       <c r="K26" t="n">
-        <v>19.80823695935388</v>
+        <v>20.83344757852008</v>
       </c>
       <c r="L26" t="n">
         <v>29.34479286819045</v>
       </c>
       <c r="M26" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N26" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="O26" t="n">
         <v>54.7</v>
@@ -2602,13 +2662,13 @@
         <v>10.345</v>
       </c>
       <c r="U26" t="n">
-        <v>68.96599999999999</v>
+        <v>69.879</v>
       </c>
       <c r="V26" t="n">
-        <v>52.724</v>
+        <v>53.686</v>
       </c>
       <c r="W26" t="n">
-        <v>-10.882</v>
+        <v>-9.407</v>
       </c>
     </row>
     <row r="27">
@@ -2648,18 +2708,18 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>20.7234228693673</v>
+        <v>27.13445809277037</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -1.78% / +2.48% / -3.28%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-11.44224900467197</v>
+        <v>-10.97009491799502</v>
       </c>
       <c r="K27" t="n">
-        <v>13.5783585617506</v>
+        <v>12.68866567804288</v>
       </c>
       <c r="L27" t="n">
         <v>36.66344986553255</v>
@@ -2668,7 +2728,7 @@
         <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>212.4</v>
+        <v>212.8</v>
       </c>
       <c r="O27" t="n">
         <v>49.7</v>
@@ -2691,13 +2751,13 @@
         <v>19.486</v>
       </c>
       <c r="U27" t="n">
-        <v>50.058</v>
+        <v>47.514</v>
       </c>
       <c r="V27" t="n">
-        <v>28.062</v>
+        <v>27.434</v>
       </c>
       <c r="W27" t="n">
-        <v>-7.599</v>
+        <v>-8.694000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2727,7 +2787,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -2906,7 +2966,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>142.9866459109618</v>
+        <v>151.2943298428036</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2914,10 +2974,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>65.1916625269281</v>
+        <v>72.08955528364842</v>
       </c>
       <c r="K3" t="n">
-        <v>-14.50640349607323</v>
+        <v>-13.53796403385184</v>
       </c>
       <c r="L3" t="n">
         <v>17.81201875402705</v>
@@ -2926,10 +2986,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -2949,13 +3009,13 @@
         <v>28.525</v>
       </c>
       <c r="U3" t="n">
-        <v>52.666</v>
+        <v>54.127</v>
       </c>
       <c r="V3" t="n">
-        <v>2.807</v>
+        <v>3.974</v>
       </c>
       <c r="W3" t="n">
-        <v>-59.407</v>
+        <v>-57.578</v>
       </c>
     </row>
     <row r="4">
@@ -2993,7 +3053,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>142.9866459109618</v>
+        <v>151.2943298428036</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3001,10 +3061,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>65.1916625269281</v>
+        <v>72.08955528364842</v>
       </c>
       <c r="K4" t="n">
-        <v>-14.50640349607323</v>
+        <v>-13.53796403385184</v>
       </c>
       <c r="L4" t="n">
         <v>17.81201875402705</v>
@@ -3013,10 +3073,10 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="P4" t="n">
         <v>5</v>
@@ -3036,13 +3096,13 @@
         <v>28.525</v>
       </c>
       <c r="U4" t="n">
-        <v>52.666</v>
+        <v>54.127</v>
       </c>
       <c r="V4" t="n">
-        <v>2.807</v>
+        <v>3.974</v>
       </c>
       <c r="W4" t="n">
-        <v>-59.407</v>
+        <v>-57.578</v>
       </c>
     </row>
     <row r="5">
@@ -3080,7 +3140,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>124.0849306185654</v>
+        <v>128.4755933807431</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3088,10 +3148,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>52.92070673367628</v>
+        <v>56.20016752408367</v>
       </c>
       <c r="K5" t="n">
-        <v>-31.93901277360915</v>
+        <v>-31.16688936762892</v>
       </c>
       <c r="L5" t="n">
         <v>21.28996887664675</v>
@@ -3100,10 +3160,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>120.8</v>
+        <v>120.5</v>
       </c>
       <c r="O5" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="P5" t="n">
         <v>5.2</v>
@@ -3117,19 +3177,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>38.574</v>
+        <v>37.878</v>
       </c>
       <c r="T5" t="n">
-        <v>38.574</v>
+        <v>37.878</v>
       </c>
       <c r="U5" t="n">
-        <v>31.542</v>
+        <v>32.784</v>
       </c>
       <c r="V5" t="n">
-        <v>-13.388</v>
+        <v>-13.067</v>
       </c>
       <c r="W5" t="n">
-        <v>-82.605</v>
+        <v>-80.964</v>
       </c>
     </row>
     <row r="6">
@@ -3167,7 +3227,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>142.9866459109618</v>
+        <v>151.2943298428036</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3175,10 +3235,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>65.1916625269281</v>
+        <v>72.08955528364842</v>
       </c>
       <c r="K6" t="n">
-        <v>-14.50640349607323</v>
+        <v>-13.53796403385184</v>
       </c>
       <c r="L6" t="n">
         <v>17.81201875402705</v>
@@ -3187,10 +3247,10 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -3210,13 +3270,13 @@
         <v>28.525</v>
       </c>
       <c r="U6" t="n">
-        <v>52.666</v>
+        <v>54.127</v>
       </c>
       <c r="V6" t="n">
-        <v>2.807</v>
+        <v>3.974</v>
       </c>
       <c r="W6" t="n">
-        <v>-59.407</v>
+        <v>-57.578</v>
       </c>
     </row>
     <row r="7">
@@ -3254,7 +3314,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>142.9866459109618</v>
+        <v>151.2943298428036</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3262,10 +3322,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>65.1916625269281</v>
+        <v>72.08955528364842</v>
       </c>
       <c r="K7" t="n">
-        <v>-14.50640349607323</v>
+        <v>-13.53796403385184</v>
       </c>
       <c r="L7" t="n">
         <v>17.81201875402705</v>
@@ -3274,10 +3334,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="P7" t="n">
         <v>5</v>
@@ -3297,13 +3357,13 @@
         <v>28.525</v>
       </c>
       <c r="U7" t="n">
-        <v>52.666</v>
+        <v>54.127</v>
       </c>
       <c r="V7" t="n">
-        <v>2.807</v>
+        <v>3.974</v>
       </c>
       <c r="W7" t="n">
-        <v>-59.407</v>
+        <v>-57.578</v>
       </c>
     </row>
     <row r="8">
@@ -3341,7 +3401,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>101.1085328114334</v>
+        <v>107.8169721165111</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3349,10 +3409,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>54.14356002865899</v>
+        <v>60.80342782086534</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.04314354246713</v>
+        <v>-20.45434535687304</v>
       </c>
       <c r="L8" t="n">
         <v>14.80675251389611</v>
@@ -3361,10 +3421,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="O8" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -3378,19 +3438,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>35.938</v>
+        <v>35.46</v>
       </c>
       <c r="T8" t="n">
-        <v>35.938</v>
+        <v>35.46</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004</v>
+        <v>0.601</v>
       </c>
       <c r="V8" t="n">
-        <v>-18.73</v>
+        <v>-18.124</v>
       </c>
       <c r="W8" t="n">
-        <v>-56.102</v>
+        <v>-55.274</v>
       </c>
     </row>
     <row r="9">
@@ -3404,7 +3464,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3420,29 +3480,29 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>47.8308061630879</v>
+        <v>58.80428923934629</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>25.16275546523637</v>
+        <v>30.07596445029146</v>
       </c>
       <c r="K9" t="n">
-        <v>6.946340391777994e-07</v>
+        <v>3.396171499581158e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>3.614626786018349</v>
+        <v>5.722322668094826</v>
       </c>
       <c r="M9" t="n">
-        <v>61.11111111111111</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>18.3</v>
+        <v>28.8</v>
       </c>
       <c r="O9" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -3459,13 +3519,13 @@
         <v>6.293</v>
       </c>
       <c r="U9" t="n">
-        <v>33.681</v>
+        <v>42.915</v>
       </c>
       <c r="V9" t="n">
-        <v>14.787</v>
+        <v>18.438</v>
       </c>
       <c r="W9" t="n">
-        <v>-8.977</v>
+        <v>-9.597</v>
       </c>
     </row>
     <row r="10">
@@ -3495,11 +3555,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>55.35820965628533</v>
+        <v>55.35820965628528</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>24.87578844692908</v>
+        <v>27.2532961310044</v>
       </c>
       <c r="K10" t="n">
         <v>9.144514923065117e-07</v>
@@ -3508,10 +3568,10 @@
         <v>5.722319728450575</v>
       </c>
       <c r="M10" t="n">
-        <v>61.11111111111111</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N10" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="O10" t="n">
         <v>67.3</v>
@@ -3534,13 +3594,13 @@
         <v>5.722</v>
       </c>
       <c r="U10" t="n">
-        <v>43.498</v>
+        <v>43.47</v>
       </c>
       <c r="V10" t="n">
         <v>22.875</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.272</v>
+        <v>-4.271</v>
       </c>
     </row>
     <row r="11">
@@ -3570,11 +3630,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>54.89484911121498</v>
+        <v>54.89484911121494</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>24.50334264230198</v>
+        <v>26.87375933801668</v>
       </c>
       <c r="K11" t="n">
         <v>-1.620916922906446e-06</v>
@@ -3583,10 +3643,10 @@
         <v>5.722319728450575</v>
       </c>
       <c r="M11" t="n">
-        <v>61.11111111111111</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N11" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="O11" t="n">
         <v>68.5</v>
@@ -3609,13 +3669,13 @@
         <v>5.722</v>
       </c>
       <c r="U11" t="n">
-        <v>42.857</v>
+        <v>42.828</v>
       </c>
       <c r="V11" t="n">
         <v>22.326</v>
       </c>
       <c r="W11" t="n">
-        <v>-4.337</v>
+        <v>-4.336</v>
       </c>
     </row>
     <row r="12">
@@ -3644,12 +3704,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRENJ.IS, TUPRS.IS</t>
+          <t>ASTOR.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TRENJ.IS: 2026-08-11 | TUPRS.IS: 2026-08-05</t>
+          <t>ASTOR.IS: 2026-08-12 | TUPRS.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -3657,14 +3717,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRENJ.IS: -0.19% / +0.36% / -0.74% | TUPRS.IS: +13.00% / +13.50% / 0.00%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4.084117806506127</v>
+        <v>3.648278064592536</v>
       </c>
       <c r="K12" t="n">
-        <v>17.95202756543382</v>
+        <v>17.84271452630865</v>
       </c>
       <c r="L12" t="n">
         <v>14.21663509452158</v>
@@ -3673,7 +3733,7 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>49.7</v>
@@ -3696,13 +3756,13 @@
         <v>12.828</v>
       </c>
       <c r="U12" t="n">
-        <v>87.133</v>
+        <v>87.928</v>
       </c>
       <c r="V12" t="n">
-        <v>74.3</v>
+        <v>76.92100000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.229</v>
+        <v>-3.422</v>
       </c>
     </row>
     <row r="13">
@@ -3740,18 +3800,18 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>49.20349509572279</v>
+        <v>49.32520312773359</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TUPRS.IS: +13.00% / +13.50% / 0.00%</t>
+          <t>TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5.871595897009474</v>
+        <v>8.710579729266543</v>
       </c>
       <c r="K13" t="n">
-        <v>16.56269116367324</v>
+        <v>16.69700824862934</v>
       </c>
       <c r="L13" t="n">
         <v>19.92682085509051</v>
@@ -3760,7 +3820,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>48.3</v>
@@ -3783,13 +3843,13 @@
         <v>15.567</v>
       </c>
       <c r="U13" t="n">
-        <v>113.42</v>
+        <v>113.768</v>
       </c>
       <c r="V13" t="n">
-        <v>113.672</v>
+        <v>112.198</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.793</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="14">
@@ -3803,7 +3863,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T2_rotasyon|E30|S3|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3818,42 +3878,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TKFEN.IS, TRENJ.IS, TUPRS.IS</t>
+          <t>ASTOR.IS, TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-08-05 | TKFEN.IS: 2026-08-12 | TRENJ.IS: 2026-08-11 | TUPRS.IS: 2026-08-10</t>
+          <t>ASTOR.IS: 2026-08-07 | TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>27.17808701479216</v>
+        <v>33.88781788770123</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -1.29% / +4.46% / -3.93% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.19% / +0.36% / -0.74% | TUPRS.IS: +0.58% / +1.03% / -3.36%</t>
+          <t>ASTOR.IS: +2.69% / +4.49% / -2.97% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.7994491519249358</v>
+        <v>3.397049184484535</v>
       </c>
       <c r="K14" t="n">
-        <v>9.455141646681685</v>
+        <v>10.12341466288347</v>
       </c>
       <c r="L14" t="n">
-        <v>11.00674698777365</v>
+        <v>16.88858078470971</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>291.6</v>
+        <v>128.5</v>
       </c>
       <c r="O14" t="n">
-        <v>47</v>
+        <v>45.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3861,22 +3921,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>10.148</v>
+        <v>13.827</v>
       </c>
       <c r="T14" t="n">
-        <v>10.148</v>
+        <v>11.093</v>
       </c>
       <c r="U14" t="n">
-        <v>63.561</v>
+        <v>87.521</v>
       </c>
       <c r="V14" t="n">
-        <v>47.081</v>
+        <v>87.063</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.22</v>
+        <v>-9.086</v>
       </c>
     </row>
     <row r="16">
@@ -4040,7 +4100,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>142.9866459109618</v>
+        <v>151.2943298428036</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4048,10 +4108,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>65.1916625269281</v>
+        <v>72.08955528364842</v>
       </c>
       <c r="K18" t="n">
-        <v>-14.50640349607323</v>
+        <v>-13.53796403385184</v>
       </c>
       <c r="L18" t="n">
         <v>17.81201875402705</v>
@@ -4060,10 +4120,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="P18" t="n">
         <v>5</v>
@@ -4083,13 +4143,13 @@
         <v>28.525</v>
       </c>
       <c r="U18" t="n">
-        <v>52.666</v>
+        <v>54.127</v>
       </c>
       <c r="V18" t="n">
-        <v>2.807</v>
+        <v>3.974</v>
       </c>
       <c r="W18" t="n">
-        <v>-59.407</v>
+        <v>-57.578</v>
       </c>
     </row>
     <row r="19">
@@ -4129,7 +4189,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>142.9866459109618</v>
+        <v>151.2943298428036</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4137,10 +4197,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>65.1916625269281</v>
+        <v>72.08955528364842</v>
       </c>
       <c r="K19" t="n">
-        <v>-14.50640349607323</v>
+        <v>-13.53796403385184</v>
       </c>
       <c r="L19" t="n">
         <v>17.81201875402705</v>
@@ -4149,10 +4209,10 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="P19" t="n">
         <v>5</v>
@@ -4172,13 +4232,13 @@
         <v>28.525</v>
       </c>
       <c r="U19" t="n">
-        <v>52.666</v>
+        <v>54.127</v>
       </c>
       <c r="V19" t="n">
-        <v>2.807</v>
+        <v>3.974</v>
       </c>
       <c r="W19" t="n">
-        <v>-59.407</v>
+        <v>-57.578</v>
       </c>
     </row>
     <row r="20">
@@ -4218,7 +4278,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>124.0849306185654</v>
+        <v>128.4755933807431</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -4226,10 +4286,10 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>52.92070673367628</v>
+        <v>56.20016752408367</v>
       </c>
       <c r="K20" t="n">
-        <v>-31.93901277360915</v>
+        <v>-31.16688936762892</v>
       </c>
       <c r="L20" t="n">
         <v>21.28996887664675</v>
@@ -4238,10 +4298,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>120.8</v>
+        <v>120.5</v>
       </c>
       <c r="O20" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="P20" t="n">
         <v>5.2</v>
@@ -4255,19 +4315,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>38.574</v>
+        <v>37.878</v>
       </c>
       <c r="T20" t="n">
-        <v>38.574</v>
+        <v>37.878</v>
       </c>
       <c r="U20" t="n">
-        <v>31.542</v>
+        <v>32.784</v>
       </c>
       <c r="V20" t="n">
-        <v>-13.388</v>
+        <v>-13.067</v>
       </c>
       <c r="W20" t="n">
-        <v>-82.605</v>
+        <v>-80.964</v>
       </c>
     </row>
     <row r="21">
@@ -4307,7 +4367,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>101.1085328114334</v>
+        <v>107.8169721165111</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4315,10 +4375,10 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>54.14356002865899</v>
+        <v>60.80342782086534</v>
       </c>
       <c r="K21" t="n">
-        <v>-21.04314354246713</v>
+        <v>-20.45434535687304</v>
       </c>
       <c r="L21" t="n">
         <v>14.80675251389611</v>
@@ -4327,10 +4387,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="O21" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="P21" t="n">
         <v>4</v>
@@ -4344,19 +4404,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>35.938</v>
+        <v>35.46</v>
       </c>
       <c r="T21" t="n">
-        <v>35.938</v>
+        <v>35.46</v>
       </c>
       <c r="U21" t="n">
-        <v>0.004</v>
+        <v>0.601</v>
       </c>
       <c r="V21" t="n">
-        <v>-18.73</v>
+        <v>-18.124</v>
       </c>
       <c r="W21" t="n">
-        <v>-56.102</v>
+        <v>-55.274</v>
       </c>
     </row>
     <row r="22">
@@ -4367,12 +4427,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4388,29 +4448,29 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>55.35820965628533</v>
+        <v>58.80428923934629</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>24.87578844692908</v>
+        <v>30.07596445029146</v>
       </c>
       <c r="K22" t="n">
-        <v>9.144514923065117e-07</v>
+        <v>3.396171499581158e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>5.722319728450575</v>
+        <v>5.722322668094826</v>
       </c>
       <c r="M22" t="n">
-        <v>61.11111111111111</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N22" t="n">
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
       <c r="O22" t="n">
-        <v>67.3</v>
+        <v>62.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4421,19 +4481,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>5.722</v>
+        <v>6.293</v>
       </c>
       <c r="T22" t="n">
-        <v>5.722</v>
+        <v>6.293</v>
       </c>
       <c r="U22" t="n">
-        <v>43.498</v>
+        <v>42.915</v>
       </c>
       <c r="V22" t="n">
-        <v>22.875</v>
+        <v>18.438</v>
       </c>
       <c r="W22" t="n">
-        <v>-4.272</v>
+        <v>-9.597</v>
       </c>
     </row>
     <row r="23">
@@ -4444,12 +4504,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4465,29 +4525,29 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>54.89484911121498</v>
+        <v>55.35820965628528</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>24.50334264230198</v>
+        <v>27.2532961310044</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.620916922906446e-06</v>
+        <v>9.144514923065117e-07</v>
       </c>
       <c r="L23" t="n">
         <v>5.722319728450575</v>
       </c>
       <c r="M23" t="n">
-        <v>61.11111111111111</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N23" t="n">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="O23" t="n">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -4504,29 +4564,29 @@
         <v>5.722</v>
       </c>
       <c r="U23" t="n">
-        <v>42.857</v>
+        <v>43.47</v>
       </c>
       <c r="V23" t="n">
-        <v>22.326</v>
+        <v>22.875</v>
       </c>
       <c r="W23" t="n">
-        <v>-4.337</v>
+        <v>-4.271</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T1_genislik_skor|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4539,83 +4599,71 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>TUPRS.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>49.20349509572279</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>TUPRS.IS: +13.00% / +13.50% / 0.00%</t>
-        </is>
-      </c>
+        <v>54.89484911121494</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>5.871595897009474</v>
+        <v>26.87375933801668</v>
       </c>
       <c r="K24" t="n">
-        <v>16.56269116367324</v>
+        <v>-1.620916922906446e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>19.92682085509051</v>
+        <v>5.722319728450575</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>73.8</v>
+        <v>26.8</v>
       </c>
       <c r="O24" t="n">
-        <v>48.3</v>
+        <v>68.5</v>
       </c>
       <c r="P24" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>17.263</v>
+        <v>5.722</v>
       </c>
       <c r="T24" t="n">
-        <v>15.567</v>
+        <v>5.722</v>
       </c>
       <c r="U24" t="n">
-        <v>113.42</v>
+        <v>42.828</v>
       </c>
       <c r="V24" t="n">
-        <v>113.672</v>
+        <v>22.326</v>
       </c>
       <c r="W24" t="n">
-        <v>-4.793</v>
+        <v>-4.336</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4628,55 +4676,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TUPRS.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>47.8308061630879</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>49.32520312773359</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>25.16275546523637</v>
+        <v>8.710579729266543</v>
       </c>
       <c r="K25" t="n">
-        <v>6.946340391777994e-07</v>
+        <v>16.69700824862934</v>
       </c>
       <c r="L25" t="n">
-        <v>3.614626786018349</v>
+        <v>19.92682085509051</v>
       </c>
       <c r="M25" t="n">
-        <v>61.11111111111111</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>18.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>62.2</v>
+        <v>48.3</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>6.293</v>
+        <v>17.263</v>
       </c>
       <c r="T25" t="n">
-        <v>6.293</v>
+        <v>15.567</v>
       </c>
       <c r="U25" t="n">
-        <v>33.681</v>
+        <v>113.768</v>
       </c>
       <c r="V25" t="n">
-        <v>14.787</v>
+        <v>112.198</v>
       </c>
       <c r="W25" t="n">
-        <v>-8.977</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="26">
@@ -4687,12 +4747,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T2_rotasyon|E30|S3|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4707,39 +4767,39 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRENJ.IS, TUPRS.IS</t>
+          <t>ASTOR.IS, TKFEN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TRENJ.IS: 2026-08-11 | TUPRS.IS: 2026-08-05</t>
+          <t>ASTOR.IS: 2026-08-07 | TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>32.85505614492337</v>
+        <v>33.88781788770123</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRENJ.IS: -0.19% / +0.36% / -0.74% | TUPRS.IS: +13.00% / +13.50% / 0.00%</t>
+          <t>ASTOR.IS: +2.69% / +4.49% / -2.97% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4.084117806506127</v>
+        <v>3.397049184484535</v>
       </c>
       <c r="K26" t="n">
-        <v>17.95202756543382</v>
+        <v>10.12341466288347</v>
       </c>
       <c r="L26" t="n">
-        <v>14.21663509452158</v>
+        <v>16.88858078470971</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>71.8</v>
+        <v>128.5</v>
       </c>
       <c r="O26" t="n">
-        <v>49.7</v>
+        <v>45.9</v>
       </c>
       <c r="P26" t="n">
         <v>4.2</v>
@@ -4750,22 +4810,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>13.97</v>
+        <v>13.827</v>
       </c>
       <c r="T26" t="n">
-        <v>12.828</v>
+        <v>11.093</v>
       </c>
       <c r="U26" t="n">
-        <v>87.133</v>
+        <v>87.521</v>
       </c>
       <c r="V26" t="n">
-        <v>74.3</v>
+        <v>87.063</v>
       </c>
       <c r="W26" t="n">
-        <v>-3.229</v>
+        <v>-9.086</v>
       </c>
     </row>
     <row r="27">
@@ -4776,12 +4836,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4796,42 +4856,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TKFEN.IS, TRENJ.IS, TUPRS.IS</t>
+          <t>ASTOR.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-08-05 | TKFEN.IS: 2026-08-12 | TRENJ.IS: 2026-08-11 | TUPRS.IS: 2026-08-10</t>
+          <t>ASTOR.IS: 2026-08-12 | TUPRS.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>27.17808701479216</v>
+        <v>32.85505614492337</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -1.29% / +4.46% / -3.93% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRENJ.IS: -0.19% / +0.36% / -0.74% | TUPRS.IS: +0.58% / +1.03% / -3.36%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.7994491519249358</v>
+        <v>3.648278064592536</v>
       </c>
       <c r="K27" t="n">
-        <v>9.455141646681685</v>
+        <v>17.84271452630865</v>
       </c>
       <c r="L27" t="n">
-        <v>11.00674698777365</v>
+        <v>14.21663509452158</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>291.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>47</v>
+        <v>49.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4839,22 +4899,22 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>10.148</v>
+        <v>13.97</v>
       </c>
       <c r="T27" t="n">
-        <v>10.148</v>
+        <v>12.828</v>
       </c>
       <c r="U27" t="n">
-        <v>63.561</v>
+        <v>87.928</v>
       </c>
       <c r="V27" t="n">
-        <v>47.081</v>
+        <v>76.92100000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>-5.22</v>
+        <v>-3.422</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -254,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W27" headerRowCount="1">
-  <autoFilter ref="A17:W27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W28" headerRowCount="1">
+  <autoFilter ref="A17:W28"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -582,7 +582,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,42 +752,42 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KCHOL.IS, TKFEN.IS</t>
+          <t>CWENE.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-12</t>
+          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>200.7847581010547</v>
+        <v>71.34931625087668</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KCHOL.IS: -1.49% / +0.24% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.06% / +1.65% / -2.28%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>60.44543523268126</v>
+        <v>28.90742063531546</v>
       </c>
       <c r="K3" t="n">
-        <v>-23.6398853472563</v>
+        <v>-16.99472687746309</v>
       </c>
       <c r="L3" t="n">
-        <v>15.29584021689743</v>
+        <v>17.11290165300374</v>
       </c>
       <c r="M3" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>59.5</v>
+        <v>162.7</v>
       </c>
       <c r="O3" t="n">
-        <v>46.7</v>
+        <v>43.3</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -798,19 +798,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>33.308</v>
+        <v>36.941</v>
       </c>
       <c r="T3" t="n">
-        <v>33.308</v>
+        <v>36.941</v>
       </c>
       <c r="U3" t="n">
-        <v>71.459</v>
+        <v>24.864</v>
       </c>
       <c r="V3" t="n">
-        <v>32.793</v>
+        <v>-15.956</v>
       </c>
       <c r="W3" t="n">
-        <v>-85.631</v>
+        <v>-70.018</v>
       </c>
     </row>
     <row r="4">
@@ -824,7 +824,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -837,67 +837,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>162.016721807671</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>67.66470042665729</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>51.6858649523811</v>
+        <v>27.23826429058853</v>
       </c>
       <c r="K4" t="n">
-        <v>-22.32122527611138</v>
+        <v>-8.063423115131684</v>
       </c>
       <c r="L4" t="n">
-        <v>15.35053097522994</v>
+        <v>14.41050093817465</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>104.2</v>
+        <v>53.1</v>
       </c>
       <c r="O4" t="n">
-        <v>44.3</v>
+        <v>51.4</v>
       </c>
       <c r="P4" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="T4" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="U4" t="n">
-        <v>28.597</v>
+        <v>8.699</v>
       </c>
       <c r="V4" t="n">
-        <v>5.824</v>
+        <v>2.761</v>
       </c>
       <c r="W4" t="n">
-        <v>-96.747</v>
+        <v>-30.289</v>
       </c>
     </row>
     <row r="5">
@@ -911,7 +899,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -924,67 +912,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>162.016721807671</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>67.66470042665729</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>51.6858649523811</v>
+        <v>27.23826429058853</v>
       </c>
       <c r="K5" t="n">
-        <v>-22.32122527611138</v>
+        <v>-8.063423115131684</v>
       </c>
       <c r="L5" t="n">
-        <v>15.35053097522994</v>
+        <v>14.41050093817465</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>104.2</v>
+        <v>53.1</v>
       </c>
       <c r="O5" t="n">
-        <v>44.3</v>
+        <v>51.4</v>
       </c>
       <c r="P5" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="T5" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="U5" t="n">
-        <v>28.597</v>
+        <v>8.699</v>
       </c>
       <c r="V5" t="n">
-        <v>5.824</v>
+        <v>2.761</v>
       </c>
       <c r="W5" t="n">
-        <v>-96.747</v>
+        <v>-30.289</v>
       </c>
     </row>
     <row r="6">
@@ -998,7 +974,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1011,55 +987,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CWENE.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>128.7435625153324</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>71.34931625087668</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.06% / +1.65% / -2.28%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
-        <v>71.62036832824464</v>
+        <v>28.90742063531546</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.40003301706789</v>
+        <v>-16.99472687746309</v>
       </c>
       <c r="L6" t="n">
-        <v>18.07106661977934</v>
+        <v>17.11290165300374</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>72.90000000000001</v>
+        <v>162.7</v>
       </c>
       <c r="O6" t="n">
-        <v>41.5</v>
+        <v>43.3</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>26.83</v>
+        <v>36.941</v>
       </c>
       <c r="T6" t="n">
-        <v>26.83</v>
+        <v>36.941</v>
       </c>
       <c r="U6" t="n">
-        <v>95.631</v>
+        <v>24.864</v>
       </c>
       <c r="V6" t="n">
-        <v>4.807</v>
+        <v>-15.956</v>
       </c>
       <c r="W6" t="n">
-        <v>-71.735</v>
+        <v>-70.018</v>
       </c>
     </row>
     <row r="7">
@@ -1073,7 +1061,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1086,67 +1074,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>KCHOL.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>200.7847581010547</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>KCHOL.IS: -1.49% / +0.24% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>56.53775570047603</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>60.44543523268126</v>
+        <v>27.61399570060789</v>
       </c>
       <c r="K7" t="n">
-        <v>-23.6398853472563</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15.29584021689743</v>
+        <v>13.7859231192354</v>
       </c>
       <c r="M7" t="n">
-        <v>83.33333333333334</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>59.5</v>
+        <v>24.3</v>
       </c>
       <c r="O7" t="n">
-        <v>46.7</v>
+        <v>63.3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.7</v>
+        <v>6.3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>33.308</v>
+        <v>8.218</v>
       </c>
       <c r="T7" t="n">
-        <v>33.308</v>
+        <v>4.976</v>
       </c>
       <c r="U7" t="n">
-        <v>71.459</v>
+        <v>83.73399999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>32.793</v>
+        <v>13.056</v>
       </c>
       <c r="W7" t="n">
-        <v>-85.631</v>
+        <v>-4.893</v>
       </c>
     </row>
     <row r="8">
@@ -1160,7 +1136,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1173,67 +1149,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>162.016721807671</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>67.66470042665729</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>51.6858649523811</v>
+        <v>27.23826429058853</v>
       </c>
       <c r="K8" t="n">
-        <v>-22.32122527611138</v>
+        <v>-8.063423115131684</v>
       </c>
       <c r="L8" t="n">
-        <v>15.35053097522994</v>
+        <v>14.41050093817465</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N8" t="n">
-        <v>104.2</v>
+        <v>53.1</v>
       </c>
       <c r="O8" t="n">
-        <v>44.3</v>
+        <v>51.4</v>
       </c>
       <c r="P8" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="T8" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="U8" t="n">
-        <v>28.597</v>
+        <v>8.699</v>
       </c>
       <c r="V8" t="n">
-        <v>5.824</v>
+        <v>2.761</v>
       </c>
       <c r="W8" t="n">
-        <v>-96.747</v>
+        <v>-30.289</v>
       </c>
     </row>
     <row r="9">
@@ -1247,7 +1211,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1260,67 +1224,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AKSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>99.0327377189677</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>31.91300386790401</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>49.78061960916962</v>
+        <v>19.31957507327515</v>
       </c>
       <c r="K9" t="n">
-        <v>-19.35728289705845</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9.11952761462077</v>
+        <v>4.846554716272955</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>238.6</v>
+        <v>13.9</v>
       </c>
       <c r="O9" t="n">
-        <v>50.7</v>
+        <v>75</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>34.321</v>
+        <v>4.847</v>
       </c>
       <c r="T9" t="n">
-        <v>34.321</v>
+        <v>3.503</v>
       </c>
       <c r="U9" t="n">
-        <v>21.376</v>
+        <v>46.446</v>
       </c>
       <c r="V9" t="n">
-        <v>-10.534</v>
+        <v>12.887</v>
       </c>
       <c r="W9" t="n">
-        <v>-63.426</v>
+        <v>-2.154</v>
       </c>
     </row>
     <row r="10">
@@ -1334,7 +1286,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1349,42 +1301,42 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGHOL.IS, TKFEN.IS</t>
+          <t>AGHOL.IS, CWENE.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>126.4280989095678</v>
+        <v>44.19317946034131</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>50.27876005534335</v>
+        <v>20.60664571193298</v>
       </c>
       <c r="K10" t="n">
-        <v>-16.61363394689339</v>
+        <v>-12.25021507568633</v>
       </c>
       <c r="L10" t="n">
-        <v>9.284980112588903</v>
+        <v>8.000657065885175</v>
       </c>
       <c r="M10" t="n">
-        <v>83.33333333333334</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>44.6</v>
+        <v>83.8</v>
       </c>
       <c r="O10" t="n">
-        <v>46.7</v>
+        <v>47.3</v>
       </c>
       <c r="P10" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1392,22 +1344,22 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>26.123</v>
+        <v>16.901</v>
       </c>
       <c r="T10" t="n">
-        <v>26.123</v>
+        <v>16.901</v>
       </c>
       <c r="U10" t="n">
-        <v>30.947</v>
+        <v>18.351</v>
       </c>
       <c r="V10" t="n">
-        <v>17.063</v>
+        <v>6.741</v>
       </c>
       <c r="W10" t="n">
-        <v>-46.304</v>
+        <v>-24.071</v>
       </c>
     </row>
     <row r="11">
@@ -1421,7 +1373,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+          <t>T2_rotasyon|E30|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1436,42 +1388,42 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGHOL.IS, TKFEN.IS</t>
+          <t>AGHOL.IS, CWENE.IS, KCHOL.IS, TKFEN.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-11 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>126.4280989095678</v>
+        <v>39.67606784950113</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +2.83% / +3.05% / -0.60% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.11% / +24.59% / -0.43%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>50.27876005534335</v>
+        <v>20.68188472109249</v>
       </c>
       <c r="K11" t="n">
-        <v>-16.61363394689339</v>
+        <v>-14.19085719438359</v>
       </c>
       <c r="L11" t="n">
-        <v>9.284980112588903</v>
+        <v>8.721899168210411</v>
       </c>
       <c r="M11" t="n">
-        <v>83.33333333333334</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>44.6</v>
+        <v>156.3</v>
       </c>
       <c r="O11" t="n">
-        <v>46.7</v>
+        <v>45.7</v>
       </c>
       <c r="P11" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1479,22 +1431,22 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>26.123</v>
+        <v>20.172</v>
       </c>
       <c r="T11" t="n">
-        <v>26.123</v>
+        <v>20.172</v>
       </c>
       <c r="U11" t="n">
-        <v>30.947</v>
+        <v>3.186</v>
       </c>
       <c r="V11" t="n">
-        <v>17.063</v>
+        <v>-2.682</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.304</v>
+        <v>-26.074</v>
       </c>
     </row>
     <row r="12">
@@ -1508,7 +1460,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1523,42 +1475,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ARCLK.IS, ASELS.IS</t>
+          <t>ARCLK.IS, BRSAN.IS, BSOKE.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: 2026-07-14 | ASELS.IS: 2026-08-07</t>
+          <t>ARCLK.IS: 2026-07-29 | BRSAN.IS: 2026-08-07 | BSOKE.IS: 2026-08-03</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30.92002035237105</v>
+        <v>24.12163341352522</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -1.30% / +3.93% / -1.99% | ASELS.IS: +4.43% / +5.51% / -1.98%</t>
+          <t>ARCLK.IS: -0.68% / +3.12% / -1.79% | BRSAN.IS: +9.24% / +12.94% / 0.00% | BSOKE.IS: +7.08% / +8.97% / -0.29%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2.22726845475778</v>
+        <v>5.10035685902106</v>
       </c>
       <c r="K12" t="n">
-        <v>20.83344757852008</v>
+        <v>15.53274306979866</v>
       </c>
       <c r="L12" t="n">
-        <v>29.34479286819045</v>
+        <v>14.82627540363896</v>
       </c>
       <c r="M12" t="n">
-        <v>83.33333333333334</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>47.1</v>
+        <v>64</v>
       </c>
       <c r="O12" t="n">
-        <v>54.7</v>
+        <v>56.6</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1566,22 +1518,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>10.345</v>
+        <v>14.383</v>
       </c>
       <c r="T12" t="n">
-        <v>10.345</v>
+        <v>14.383</v>
       </c>
       <c r="U12" t="n">
-        <v>69.879</v>
+        <v>45.748</v>
       </c>
       <c r="V12" t="n">
-        <v>53.686</v>
+        <v>32.338</v>
       </c>
       <c r="W12" t="n">
-        <v>-9.407</v>
+        <v>-13.427</v>
       </c>
     </row>
     <row r="13">
@@ -1595,7 +1547,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1610,42 +1562,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>TKFEN.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05</t>
+          <t>TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>27.13445809277037</v>
+        <v>8.623921515490141</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-10.97009491799502</v>
+        <v>-8.51698817675388</v>
       </c>
       <c r="K13" t="n">
-        <v>12.68866567804288</v>
+        <v>7.569460837479336</v>
       </c>
       <c r="L13" t="n">
-        <v>36.66344986553255</v>
+        <v>16.53177210390998</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>212.8</v>
+        <v>84.8</v>
       </c>
       <c r="O13" t="n">
-        <v>49.7</v>
+        <v>43.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1653,22 +1605,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>19.486</v>
+        <v>15.149</v>
       </c>
       <c r="T13" t="n">
-        <v>19.486</v>
+        <v>15.149</v>
       </c>
       <c r="U13" t="n">
-        <v>47.514</v>
+        <v>31.508</v>
       </c>
       <c r="V13" t="n">
-        <v>27.434</v>
+        <v>24.09</v>
       </c>
       <c r="W13" t="n">
-        <v>-8.694000000000001</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="14">
@@ -1682,7 +1634,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T6_skor_momentum|E30|S5|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|Bvolatilite</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1697,42 +1649,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>BRYAT.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05</t>
+          <t>BRYAT.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>50.63929346397487</v>
+        <v>5.314242466438723</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60%</t>
+          <t>BRYAT.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2.414581191190335</v>
+        <v>-6.347929995877966</v>
       </c>
       <c r="K14" t="n">
-        <v>11.68606328014647</v>
+        <v>3.239578225065443</v>
       </c>
       <c r="L14" t="n">
-        <v>21.31957361714377</v>
+        <v>13.58292401523599</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>70.40000000000001</v>
+        <v>304.6</v>
       </c>
       <c r="O14" t="n">
-        <v>50.7</v>
+        <v>46.9</v>
       </c>
       <c r="P14" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1743,19 +1695,19 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>20.511</v>
+        <v>10.3</v>
       </c>
       <c r="T14" t="n">
-        <v>20.511</v>
+        <v>10.3</v>
       </c>
       <c r="U14" t="n">
-        <v>32.425</v>
+        <v>17.958</v>
       </c>
       <c r="V14" t="n">
-        <v>11.159</v>
+        <v>6.874</v>
       </c>
       <c r="W14" t="n">
-        <v>-10.254</v>
+        <v>-8.095000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1890,12 +1842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 | 2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1910,42 +1862,42 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KCHOL.IS, TKFEN.IS</t>
+          <t>CWENE.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-12</t>
+          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>200.7847581010547</v>
+        <v>71.34931625087668</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>KCHOL.IS: -1.49% / +0.24% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.06% / +1.65% / -2.28%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>60.44543523268126</v>
+        <v>28.90742063531546</v>
       </c>
       <c r="K18" t="n">
-        <v>-23.6398853472563</v>
+        <v>-16.99472687746309</v>
       </c>
       <c r="L18" t="n">
-        <v>15.29584021689743</v>
+        <v>17.11290165300374</v>
       </c>
       <c r="M18" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>59.5</v>
+        <v>162.7</v>
       </c>
       <c r="O18" t="n">
-        <v>46.7</v>
+        <v>43.3</v>
       </c>
       <c r="P18" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1956,19 +1908,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>33.308</v>
+        <v>36.941</v>
       </c>
       <c r="T18" t="n">
-        <v>33.308</v>
+        <v>36.941</v>
       </c>
       <c r="U18" t="n">
-        <v>71.459</v>
+        <v>24.864</v>
       </c>
       <c r="V18" t="n">
-        <v>32.793</v>
+        <v>-15.956</v>
       </c>
       <c r="W18" t="n">
-        <v>-85.631</v>
+        <v>-70.018</v>
       </c>
     </row>
     <row r="19">
@@ -1984,7 +1936,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1997,67 +1949,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>162.016721807671</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>67.66470042665729</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>51.6858649523811</v>
+        <v>27.23826429058853</v>
       </c>
       <c r="K19" t="n">
-        <v>-22.32122527611138</v>
+        <v>-8.063423115131684</v>
       </c>
       <c r="L19" t="n">
-        <v>15.35053097522994</v>
+        <v>14.41050093817465</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>104.2</v>
+        <v>53.1</v>
       </c>
       <c r="O19" t="n">
-        <v>44.3</v>
+        <v>51.4</v>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="T19" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="U19" t="n">
-        <v>28.597</v>
+        <v>8.699</v>
       </c>
       <c r="V19" t="n">
-        <v>5.824</v>
+        <v>2.761</v>
       </c>
       <c r="W19" t="n">
-        <v>-96.747</v>
+        <v>-30.289</v>
       </c>
     </row>
     <row r="20">
@@ -2073,7 +2013,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2086,67 +2026,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, AKSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>162.016721807671</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>67.66470042665729</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>51.6858649523811</v>
+        <v>27.23826429058853</v>
       </c>
       <c r="K20" t="n">
-        <v>-22.32122527611138</v>
+        <v>-8.063423115131684</v>
       </c>
       <c r="L20" t="n">
-        <v>15.35053097522994</v>
+        <v>14.41050093817465</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>104.2</v>
+        <v>53.1</v>
       </c>
       <c r="O20" t="n">
-        <v>44.3</v>
+        <v>51.4</v>
       </c>
       <c r="P20" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="T20" t="n">
-        <v>42.933</v>
+        <v>23.105</v>
       </c>
       <c r="U20" t="n">
-        <v>28.597</v>
+        <v>8.699</v>
       </c>
       <c r="V20" t="n">
-        <v>5.824</v>
+        <v>2.761</v>
       </c>
       <c r="W20" t="n">
-        <v>-96.747</v>
+        <v>-30.289</v>
       </c>
     </row>
     <row r="21">
@@ -2157,12 +2085,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2178,29 +2106,29 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>128.7435625153324</v>
+        <v>56.53775570047603</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>71.62036832824464</v>
+        <v>27.61399570060789</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.40003301706789</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>18.07106661977934</v>
+        <v>13.7859231192354</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>72.90000000000001</v>
+        <v>24.3</v>
       </c>
       <c r="O21" t="n">
-        <v>41.5</v>
+        <v>63.3</v>
       </c>
       <c r="P21" t="n">
-        <v>5.1</v>
+        <v>6.3</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2211,19 +2139,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>26.83</v>
+        <v>8.218</v>
       </c>
       <c r="T21" t="n">
-        <v>26.83</v>
+        <v>4.976</v>
       </c>
       <c r="U21" t="n">
-        <v>95.631</v>
+        <v>83.73399999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>4.807</v>
+        <v>13.056</v>
       </c>
       <c r="W21" t="n">
-        <v>-71.735</v>
+        <v>-4.893</v>
       </c>
     </row>
     <row r="22">
@@ -2239,7 +2167,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2254,42 +2182,42 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGHOL.IS, TKFEN.IS</t>
+          <t>AGHOL.IS, CWENE.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>126.4280989095678</v>
+        <v>44.19317946034131</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>50.27876005534335</v>
+        <v>20.60664571193298</v>
       </c>
       <c r="K22" t="n">
-        <v>-16.61363394689339</v>
+        <v>-12.25021507568633</v>
       </c>
       <c r="L22" t="n">
-        <v>9.284980112588903</v>
+        <v>8.000657065885175</v>
       </c>
       <c r="M22" t="n">
-        <v>83.33333333333334</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>44.6</v>
+        <v>83.8</v>
       </c>
       <c r="O22" t="n">
-        <v>46.7</v>
+        <v>47.3</v>
       </c>
       <c r="P22" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2297,22 +2225,22 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>26.123</v>
+        <v>16.901</v>
       </c>
       <c r="T22" t="n">
-        <v>26.123</v>
+        <v>16.901</v>
       </c>
       <c r="U22" t="n">
-        <v>30.947</v>
+        <v>18.351</v>
       </c>
       <c r="V22" t="n">
-        <v>17.063</v>
+        <v>6.741</v>
       </c>
       <c r="W22" t="n">
-        <v>-46.304</v>
+        <v>-24.071</v>
       </c>
     </row>
     <row r="23">
@@ -2328,7 +2256,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+          <t>T2_rotasyon|E30|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2343,42 +2271,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AGHOL.IS, TKFEN.IS</t>
+          <t>AGHOL.IS, CWENE.IS, KCHOL.IS, TKFEN.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-11 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>126.4280989095678</v>
+        <v>39.67606784950113</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +2.83% / +3.05% / -0.60% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.11% / +24.59% / -0.43%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>50.27876005534335</v>
+        <v>20.68188472109249</v>
       </c>
       <c r="K23" t="n">
-        <v>-16.61363394689339</v>
+        <v>-14.19085719438359</v>
       </c>
       <c r="L23" t="n">
-        <v>9.284980112588903</v>
+        <v>8.721899168210411</v>
       </c>
       <c r="M23" t="n">
-        <v>83.33333333333334</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>44.6</v>
+        <v>156.3</v>
       </c>
       <c r="O23" t="n">
-        <v>46.7</v>
+        <v>45.7</v>
       </c>
       <c r="P23" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2386,22 +2314,22 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>26.123</v>
+        <v>20.172</v>
       </c>
       <c r="T23" t="n">
-        <v>26.123</v>
+        <v>20.172</v>
       </c>
       <c r="U23" t="n">
-        <v>30.947</v>
+        <v>3.186</v>
       </c>
       <c r="V23" t="n">
-        <v>17.063</v>
+        <v>-2.682</v>
       </c>
       <c r="W23" t="n">
-        <v>-46.304</v>
+        <v>-26.074</v>
       </c>
     </row>
     <row r="24">
@@ -2417,7 +2345,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2430,67 +2358,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>AKSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-05 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>99.0327377189677</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -3.30% / +2.48% / -3.60% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>31.91300386790401</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>49.78061960916962</v>
+        <v>19.31957507327515</v>
       </c>
       <c r="K24" t="n">
-        <v>-19.35728289705845</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>9.11952761462077</v>
+        <v>4.846554716272955</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N24" t="n">
-        <v>238.6</v>
+        <v>13.9</v>
       </c>
       <c r="O24" t="n">
-        <v>50.7</v>
+        <v>75</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>34.321</v>
+        <v>4.847</v>
       </c>
       <c r="T24" t="n">
-        <v>34.321</v>
+        <v>3.503</v>
       </c>
       <c r="U24" t="n">
-        <v>21.376</v>
+        <v>46.446</v>
       </c>
       <c r="V24" t="n">
-        <v>-10.534</v>
+        <v>12.887</v>
       </c>
       <c r="W24" t="n">
-        <v>-63.426</v>
+        <v>-2.154</v>
       </c>
     </row>
     <row r="25">
@@ -2501,12 +2417,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2521,42 +2437,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>ARCLK.IS, BRSAN.IS, BSOKE.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05</t>
+          <t>ARCLK.IS: 2026-07-29 | BRSAN.IS: 2026-08-07 | BSOKE.IS: 2026-08-03</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>50.63929346397487</v>
+        <v>24.12163341352522</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60%</t>
+          <t>ARCLK.IS: -0.68% / +3.12% / -1.79% | BRSAN.IS: +9.24% / +12.94% / 0.00% | BSOKE.IS: +7.08% / +8.97% / -0.29%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2.414581191190335</v>
+        <v>5.10035685902106</v>
       </c>
       <c r="K25" t="n">
-        <v>11.68606328014647</v>
+        <v>15.53274306979866</v>
       </c>
       <c r="L25" t="n">
-        <v>21.31957361714377</v>
+        <v>14.82627540363896</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>70.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="O25" t="n">
-        <v>50.7</v>
+        <v>56.6</v>
       </c>
       <c r="P25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2564,22 +2480,22 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>20.511</v>
+        <v>14.383</v>
       </c>
       <c r="T25" t="n">
-        <v>20.511</v>
+        <v>14.383</v>
       </c>
       <c r="U25" t="n">
-        <v>32.425</v>
+        <v>45.748</v>
       </c>
       <c r="V25" t="n">
-        <v>11.159</v>
+        <v>32.338</v>
       </c>
       <c r="W25" t="n">
-        <v>-10.254</v>
+        <v>-13.427</v>
       </c>
     </row>
     <row r="26">
@@ -2590,12 +2506,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2610,42 +2526,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ARCLK.IS, ASELS.IS</t>
+          <t>TKFEN.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ARCLK.IS: 2026-07-14 | ASELS.IS: 2026-08-07</t>
+          <t>TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>30.92002035237105</v>
+        <v>8.623921515490141</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -1.30% / +3.93% / -1.99% | ASELS.IS: +4.43% / +5.51% / -1.98%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2.22726845475778</v>
+        <v>-8.51698817675388</v>
       </c>
       <c r="K26" t="n">
-        <v>20.83344757852008</v>
+        <v>7.569460837479336</v>
       </c>
       <c r="L26" t="n">
-        <v>29.34479286819045</v>
+        <v>16.53177210390998</v>
       </c>
       <c r="M26" t="n">
-        <v>83.33333333333334</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>47.1</v>
+        <v>84.8</v>
       </c>
       <c r="O26" t="n">
-        <v>54.7</v>
+        <v>43.3</v>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2653,22 +2569,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>10.345</v>
+        <v>15.149</v>
       </c>
       <c r="T26" t="n">
-        <v>10.345</v>
+        <v>15.149</v>
       </c>
       <c r="U26" t="n">
-        <v>69.879</v>
+        <v>31.508</v>
       </c>
       <c r="V26" t="n">
-        <v>53.686</v>
+        <v>24.09</v>
       </c>
       <c r="W26" t="n">
-        <v>-9.407</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="27">
@@ -2679,12 +2595,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T6_skor_momentum|E30|S5|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|Bvolatilite</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2699,42 +2615,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGHOL.IS, AKSA.IS</t>
+          <t>BRYAT.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | AKSA.IS: 2026-08-05</t>
+          <t>BRYAT.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>27.13445809277037</v>
+        <v>5.314242466438723</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | AKSA.IS: -3.30% / +2.48% / -3.60%</t>
+          <t>BRYAT.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-10.97009491799502</v>
+        <v>-6.347929995877966</v>
       </c>
       <c r="K27" t="n">
-        <v>12.68866567804288</v>
+        <v>3.239578225065443</v>
       </c>
       <c r="L27" t="n">
-        <v>36.66344986553255</v>
+        <v>13.58292401523599</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>212.8</v>
+        <v>304.6</v>
       </c>
       <c r="O27" t="n">
-        <v>49.7</v>
+        <v>46.9</v>
       </c>
       <c r="P27" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2745,19 +2661,19 @@
         <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>19.486</v>
+        <v>10.3</v>
       </c>
       <c r="T27" t="n">
-        <v>19.486</v>
+        <v>10.3</v>
       </c>
       <c r="U27" t="n">
-        <v>47.514</v>
+        <v>17.958</v>
       </c>
       <c r="V27" t="n">
-        <v>27.434</v>
+        <v>6.874</v>
       </c>
       <c r="W27" t="n">
-        <v>-8.694000000000001</v>
+        <v>-8.095000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2779,20 +2695,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2942,7 +2858,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2955,67 +2871,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>151.2943298428036</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>91.56479142315331</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>72.08955528364842</v>
+        <v>23.39595791492497</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.53796403385184</v>
+        <v>-13.34044992083334</v>
       </c>
       <c r="L3" t="n">
-        <v>17.81201875402705</v>
+        <v>20.60969316507146</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>77.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>46.8</v>
+        <v>43.7</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>28.525</v>
+        <v>28.897</v>
       </c>
       <c r="T3" t="n">
-        <v>28.525</v>
+        <v>28.897</v>
       </c>
       <c r="U3" t="n">
-        <v>54.127</v>
+        <v>6.931</v>
       </c>
       <c r="V3" t="n">
-        <v>3.974</v>
+        <v>18.912</v>
       </c>
       <c r="W3" t="n">
-        <v>-57.578</v>
+        <v>-33.344</v>
       </c>
     </row>
     <row r="4">
@@ -3029,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3042,67 +2946,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>151.2943298428036</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>91.56479142315331</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>72.08955528364842</v>
+        <v>23.39595791492497</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.53796403385184</v>
+        <v>-13.34044992083334</v>
       </c>
       <c r="L4" t="n">
-        <v>17.81201875402705</v>
+        <v>20.60969316507146</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>77.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>46.8</v>
+        <v>43.7</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>28.525</v>
+        <v>28.897</v>
       </c>
       <c r="T4" t="n">
-        <v>28.525</v>
+        <v>28.897</v>
       </c>
       <c r="U4" t="n">
-        <v>54.127</v>
+        <v>6.931</v>
       </c>
       <c r="V4" t="n">
-        <v>3.974</v>
+        <v>18.912</v>
       </c>
       <c r="W4" t="n">
-        <v>-57.578</v>
+        <v>-33.344</v>
       </c>
     </row>
     <row r="5">
@@ -3116,7 +3008,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3131,42 +3023,42 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>128.4755933807431</v>
+        <v>87.45314000196969</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>56.20016752408367</v>
+        <v>25.04604914606534</v>
       </c>
       <c r="K5" t="n">
-        <v>-31.16688936762892</v>
+        <v>-17.41753659076543</v>
       </c>
       <c r="L5" t="n">
-        <v>21.28996887664675</v>
+        <v>19.87241364643113</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>120.5</v>
+        <v>101.2</v>
       </c>
       <c r="O5" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="P5" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -3177,19 +3069,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>37.878</v>
+        <v>28.429</v>
       </c>
       <c r="T5" t="n">
-        <v>37.878</v>
+        <v>28.429</v>
       </c>
       <c r="U5" t="n">
-        <v>32.784</v>
+        <v>-5.961</v>
       </c>
       <c r="V5" t="n">
-        <v>-13.067</v>
+        <v>2.87</v>
       </c>
       <c r="W5" t="n">
-        <v>-80.964</v>
+        <v>-36.63</v>
       </c>
     </row>
     <row r="6">
@@ -3203,7 +3095,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3216,67 +3108,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>151.2943298428036</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>73.75965029798431</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>72.08955528364842</v>
+        <v>32.17500191033664</v>
       </c>
       <c r="K6" t="n">
-        <v>-13.53796403385184</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>17.81201875402705</v>
+        <v>10.93171461772147</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>77.40000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="O6" t="n">
-        <v>46.8</v>
+        <v>52.4</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>28.525</v>
+        <v>15.232</v>
       </c>
       <c r="T6" t="n">
-        <v>28.525</v>
+        <v>15.232</v>
       </c>
       <c r="U6" t="n">
-        <v>54.127</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>3.974</v>
+        <v>45.816</v>
       </c>
       <c r="W6" t="n">
-        <v>-57.578</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="7">
@@ -3290,7 +3170,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3303,67 +3183,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>151.2943298428036</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>73.75965029798431</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>72.08955528364842</v>
+        <v>32.17500191033664</v>
       </c>
       <c r="K7" t="n">
-        <v>-13.53796403385184</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>17.81201875402705</v>
+        <v>10.93171461772147</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>77.40000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="O7" t="n">
-        <v>46.8</v>
+        <v>52.4</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>28.525</v>
+        <v>15.232</v>
       </c>
       <c r="T7" t="n">
-        <v>28.525</v>
+        <v>15.232</v>
       </c>
       <c r="U7" t="n">
-        <v>54.127</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>3.974</v>
+        <v>45.816</v>
       </c>
       <c r="W7" t="n">
-        <v>-57.578</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="8">
@@ -3392,42 +3260,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>107.8169721165111</v>
+        <v>66.301491594128</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>60.80342782086534</v>
+        <v>30.34761461502702</v>
       </c>
       <c r="K8" t="n">
-        <v>-20.45434535687304</v>
+        <v>-24.73544841530867</v>
       </c>
       <c r="L8" t="n">
-        <v>14.80675251389611</v>
+        <v>14.51092346785601</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>99.7</v>
+        <v>104.2</v>
       </c>
       <c r="O8" t="n">
-        <v>44.8</v>
+        <v>39.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -3438,19 +3306,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>35.46</v>
+        <v>35.389</v>
       </c>
       <c r="T8" t="n">
-        <v>35.46</v>
+        <v>35.389</v>
       </c>
       <c r="U8" t="n">
-        <v>0.601</v>
+        <v>-8.851000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-18.124</v>
+        <v>-15.453</v>
       </c>
       <c r="W8" t="n">
-        <v>-55.274</v>
+        <v>-49.924</v>
       </c>
     </row>
     <row r="9">
@@ -3464,7 +3332,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3477,55 +3345,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BSOKE.IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>58.80428923934629</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>41.94190130252267</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>30.07596445029146</v>
+        <v>19.29474647515033</v>
       </c>
       <c r="K9" t="n">
-        <v>3.396171499581158e-06</v>
+        <v>-3.806499800967666</v>
       </c>
       <c r="L9" t="n">
-        <v>5.722322668094826</v>
+        <v>5.815917056938346</v>
       </c>
       <c r="M9" t="n">
-        <v>55.55555555555556</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N9" t="n">
-        <v>28.8</v>
+        <v>32.2</v>
       </c>
       <c r="O9" t="n">
-        <v>62.1</v>
+        <v>56.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>6.293</v>
+        <v>11.943</v>
       </c>
       <c r="T9" t="n">
-        <v>6.293</v>
+        <v>11.943</v>
       </c>
       <c r="U9" t="n">
-        <v>42.915</v>
+        <v>-7.397</v>
       </c>
       <c r="V9" t="n">
-        <v>18.438</v>
+        <v>-9.045</v>
       </c>
       <c r="W9" t="n">
-        <v>-9.597</v>
+        <v>-12.56</v>
       </c>
     </row>
     <row r="10">
@@ -3539,7 +3419,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3552,55 +3432,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BSOKE.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>55.35820965628528</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>32.22665840648815</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +8.70% / +24.13% / -0.52%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
-        <v>27.2532961310044</v>
+        <v>15.87125249023873</v>
       </c>
       <c r="K10" t="n">
-        <v>9.144514923065117e-07</v>
+        <v>-7.701750553347598</v>
       </c>
       <c r="L10" t="n">
-        <v>5.722319728450575</v>
+        <v>4.152177865701379</v>
       </c>
       <c r="M10" t="n">
-        <v>55.55555555555556</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N10" t="n">
-        <v>27.3</v>
+        <v>61</v>
       </c>
       <c r="O10" t="n">
-        <v>67.3</v>
+        <v>45.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>5.722</v>
+        <v>19.115</v>
       </c>
       <c r="T10" t="n">
-        <v>5.722</v>
+        <v>19.115</v>
       </c>
       <c r="U10" t="n">
-        <v>43.47</v>
+        <v>-14.207</v>
       </c>
       <c r="V10" t="n">
-        <v>22.875</v>
+        <v>-17.014</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.271</v>
+        <v>-20.275</v>
       </c>
     </row>
     <row r="11">
@@ -3614,7 +3506,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3630,29 +3522,29 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>54.89484911121494</v>
+        <v>73.75965029798431</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>26.87375933801668</v>
+        <v>32.17500191033664</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.620916922906446e-06</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5.722319728450575</v>
+        <v>10.93171461772147</v>
       </c>
       <c r="M11" t="n">
-        <v>55.55555555555556</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>26.8</v>
+        <v>41.7</v>
       </c>
       <c r="O11" t="n">
-        <v>68.5</v>
+        <v>52.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -3663,19 +3555,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>5.722</v>
+        <v>15.232</v>
       </c>
       <c r="T11" t="n">
-        <v>5.722</v>
+        <v>15.232</v>
       </c>
       <c r="U11" t="n">
-        <v>42.828</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>22.326</v>
+        <v>45.816</v>
       </c>
       <c r="W11" t="n">
-        <v>-4.336</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="12">
@@ -3689,7 +3581,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3702,67 +3594,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ASTOR.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: 2026-08-12 | TUPRS.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>32.85505614492337</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
-        </is>
-      </c>
+        <v>8.326901382152464</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>3.648278064592536</v>
+        <v>-8.338699492242052</v>
       </c>
       <c r="K12" t="n">
-        <v>17.84271452630865</v>
+        <v>11.24844230268831</v>
       </c>
       <c r="L12" t="n">
-        <v>14.21663509452158</v>
+        <v>15.11937055513065</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N12" t="n">
-        <v>71.90000000000001</v>
+        <v>39.7</v>
       </c>
       <c r="O12" t="n">
-        <v>49.7</v>
+        <v>45</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>13.97</v>
+        <v>12.679</v>
       </c>
       <c r="T12" t="n">
-        <v>12.828</v>
+        <v>10.364</v>
       </c>
       <c r="U12" t="n">
-        <v>87.928</v>
+        <v>32.693</v>
       </c>
       <c r="V12" t="n">
-        <v>76.92100000000001</v>
+        <v>17.594</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.422</v>
+        <v>-5.555</v>
       </c>
     </row>
     <row r="13">
@@ -3776,7 +3656,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3791,42 +3671,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>AEFES.IS, BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TUPRS.IS: 2026-08-05</t>
+          <t>AEFES.IS: 2026-08-12 | BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-12 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>49.32520312773359</v>
+        <v>12.66701959909342</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.32% / +1.93% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +2.28% / +4.22% / -2.41% | ECILC.IS: +8.75% / +9.42% / -1.57%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8.710579729266543</v>
+        <v>-8.680217320764083</v>
       </c>
       <c r="K13" t="n">
-        <v>16.69700824862934</v>
+        <v>6.566662997937844</v>
       </c>
       <c r="L13" t="n">
-        <v>19.92682085509051</v>
+        <v>26.13605589995283</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>73.90000000000001</v>
+        <v>175.1</v>
       </c>
       <c r="O13" t="n">
-        <v>48.3</v>
+        <v>43.6</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3834,22 +3714,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>17.263</v>
+        <v>21.464</v>
       </c>
       <c r="T13" t="n">
-        <v>15.567</v>
+        <v>21.464</v>
       </c>
       <c r="U13" t="n">
-        <v>113.768</v>
+        <v>27.278</v>
       </c>
       <c r="V13" t="n">
-        <v>112.198</v>
+        <v>17.086</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.55</v>
+        <v>-7.865</v>
       </c>
     </row>
     <row r="14">
@@ -3863,7 +3743,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S3|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3876,67 +3756,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ASTOR.IS, TKFEN.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: 2026-08-07 | TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>33.88781788770123</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: +2.69% / +4.49% / -2.97% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
-        </is>
-      </c>
+        <v>41.95416190351076</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>3.397049184484535</v>
+        <v>1.887819455580941</v>
       </c>
       <c r="K14" t="n">
-        <v>10.12341466288347</v>
+        <v>4.97142476951602</v>
       </c>
       <c r="L14" t="n">
-        <v>16.88858078470971</v>
+        <v>28.80374734693901</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>128.5</v>
+        <v>64.5</v>
       </c>
       <c r="O14" t="n">
-        <v>45.9</v>
+        <v>41.5</v>
       </c>
       <c r="P14" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>13.827</v>
+        <v>18.867</v>
       </c>
       <c r="T14" t="n">
-        <v>11.093</v>
+        <v>18.867</v>
       </c>
       <c r="U14" t="n">
-        <v>87.521</v>
+        <v>78.093</v>
       </c>
       <c r="V14" t="n">
-        <v>87.063</v>
+        <v>40.341</v>
       </c>
       <c r="W14" t="n">
-        <v>-9.086</v>
+        <v>-24.086</v>
       </c>
     </row>
     <row r="16">
@@ -4066,7 +3934,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4076,7 +3944,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4089,73 +3957,61 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>151.2943298428036</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>91.56479142315331</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>72.08955528364842</v>
+        <v>23.39595791492497</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.53796403385184</v>
+        <v>-13.34044992083334</v>
       </c>
       <c r="L18" t="n">
-        <v>17.81201875402705</v>
+        <v>20.60969316507146</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>77.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>46.8</v>
+        <v>43.7</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>28.525</v>
+        <v>28.897</v>
       </c>
       <c r="T18" t="n">
-        <v>28.525</v>
+        <v>28.897</v>
       </c>
       <c r="U18" t="n">
-        <v>54.127</v>
+        <v>6.931</v>
       </c>
       <c r="V18" t="n">
-        <v>3.974</v>
+        <v>18.912</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.578</v>
+        <v>-33.344</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4165,7 +4021,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4178,67 +4034,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>151.2943298428036</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>91.56479142315331</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>72.08955528364842</v>
+        <v>23.39595791492497</v>
       </c>
       <c r="K19" t="n">
-        <v>-13.53796403385184</v>
+        <v>-13.34044992083334</v>
       </c>
       <c r="L19" t="n">
-        <v>17.81201875402705</v>
+        <v>20.60969316507146</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>77.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>46.8</v>
+        <v>43.7</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>28.525</v>
+        <v>28.897</v>
       </c>
       <c r="T19" t="n">
-        <v>28.525</v>
+        <v>28.897</v>
       </c>
       <c r="U19" t="n">
-        <v>54.127</v>
+        <v>6.931</v>
       </c>
       <c r="V19" t="n">
-        <v>3.974</v>
+        <v>18.912</v>
       </c>
       <c r="W19" t="n">
-        <v>-57.578</v>
+        <v>-33.344</v>
       </c>
     </row>
     <row r="20">
@@ -4254,7 +4098,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4269,42 +4113,42 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>128.4755933807431</v>
+        <v>87.45314000196969</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>56.20016752408367</v>
+        <v>25.04604914606534</v>
       </c>
       <c r="K20" t="n">
-        <v>-31.16688936762892</v>
+        <v>-17.41753659076543</v>
       </c>
       <c r="L20" t="n">
-        <v>21.28996887664675</v>
+        <v>19.87241364643113</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>120.5</v>
+        <v>101.2</v>
       </c>
       <c r="O20" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -4315,35 +4159,35 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>37.878</v>
+        <v>28.429</v>
       </c>
       <c r="T20" t="n">
-        <v>37.878</v>
+        <v>28.429</v>
       </c>
       <c r="U20" t="n">
-        <v>32.784</v>
+        <v>-5.961</v>
       </c>
       <c r="V20" t="n">
-        <v>-13.067</v>
+        <v>2.87</v>
       </c>
       <c r="W20" t="n">
-        <v>-80.964</v>
+        <v>-36.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 | 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4356,83 +4200,71 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>107.8169721165111</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>73.75965029798431</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>60.80342782086534</v>
+        <v>32.17500191033664</v>
       </c>
       <c r="K21" t="n">
-        <v>-20.45434535687304</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>14.80675251389611</v>
+        <v>10.93171461772147</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>99.7</v>
+        <v>41.7</v>
       </c>
       <c r="O21" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>35.46</v>
+        <v>15.232</v>
       </c>
       <c r="T21" t="n">
-        <v>35.46</v>
+        <v>15.232</v>
       </c>
       <c r="U21" t="n">
-        <v>0.601</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-18.124</v>
+        <v>45.816</v>
       </c>
       <c r="W21" t="n">
-        <v>-55.274</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4448,29 +4280,29 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>58.80428923934629</v>
+        <v>73.75965029798431</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>30.07596445029146</v>
+        <v>32.17500191033664</v>
       </c>
       <c r="K22" t="n">
-        <v>3.396171499581158e-06</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>5.722322668094826</v>
+        <v>10.93171461772147</v>
       </c>
       <c r="M22" t="n">
-        <v>55.55555555555556</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>28.8</v>
+        <v>41.7</v>
       </c>
       <c r="O22" t="n">
-        <v>62.1</v>
+        <v>52.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4481,35 +4313,35 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>6.293</v>
+        <v>15.232</v>
       </c>
       <c r="T22" t="n">
-        <v>6.293</v>
+        <v>15.232</v>
       </c>
       <c r="U22" t="n">
-        <v>42.915</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>18.438</v>
+        <v>45.816</v>
       </c>
       <c r="W22" t="n">
-        <v>-9.597</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4522,61 +4354,73 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>55.35820965628528</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>66.301491594128</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>27.2532961310044</v>
+        <v>30.34761461502702</v>
       </c>
       <c r="K23" t="n">
-        <v>9.144514923065117e-07</v>
+        <v>-24.73544841530867</v>
       </c>
       <c r="L23" t="n">
-        <v>5.722319728450575</v>
+        <v>14.51092346785601</v>
       </c>
       <c r="M23" t="n">
-        <v>55.55555555555556</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>27.3</v>
+        <v>104.2</v>
       </c>
       <c r="O23" t="n">
-        <v>67.3</v>
+        <v>39.5</v>
       </c>
       <c r="P23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="n">
-        <v>5.722</v>
+        <v>35.389</v>
       </c>
       <c r="T23" t="n">
-        <v>5.722</v>
+        <v>35.389</v>
       </c>
       <c r="U23" t="n">
-        <v>43.47</v>
+        <v>-8.851000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>22.875</v>
+        <v>-15.453</v>
       </c>
       <c r="W23" t="n">
-        <v>-4.271</v>
+        <v>-49.924</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4586,7 +4430,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4602,29 +4446,29 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>54.89484911121494</v>
+        <v>41.95416190351076</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>26.87375933801668</v>
+        <v>1.887819455580941</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.620916922906446e-06</v>
+        <v>4.97142476951602</v>
       </c>
       <c r="L24" t="n">
-        <v>5.722319728450575</v>
+        <v>28.80374734693901</v>
       </c>
       <c r="M24" t="n">
-        <v>55.55555555555556</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>26.8</v>
+        <v>64.5</v>
       </c>
       <c r="O24" t="n">
-        <v>68.5</v>
+        <v>41.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4635,35 +4479,35 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.722</v>
+        <v>18.867</v>
       </c>
       <c r="T24" t="n">
-        <v>5.722</v>
+        <v>18.867</v>
       </c>
       <c r="U24" t="n">
-        <v>42.828</v>
+        <v>78.093</v>
       </c>
       <c r="V24" t="n">
-        <v>22.326</v>
+        <v>40.341</v>
       </c>
       <c r="W24" t="n">
-        <v>-4.336</v>
+        <v>-24.086</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4678,42 +4522,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>BRSAN.IS, BSOKE.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TUPRS.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>49.32520312773359</v>
+        <v>41.94190130252267</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>8.710579729266543</v>
+        <v>19.29474647515033</v>
       </c>
       <c r="K25" t="n">
-        <v>16.69700824862934</v>
+        <v>-3.806499800967666</v>
       </c>
       <c r="L25" t="n">
-        <v>19.92682085509051</v>
+        <v>5.815917056938346</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>73.90000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="O25" t="n">
-        <v>48.3</v>
+        <v>56.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4721,38 +4565,38 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>17.263</v>
+        <v>11.943</v>
       </c>
       <c r="T25" t="n">
-        <v>15.567</v>
+        <v>11.943</v>
       </c>
       <c r="U25" t="n">
-        <v>113.768</v>
+        <v>-7.397</v>
       </c>
       <c r="V25" t="n">
-        <v>112.198</v>
+        <v>-9.045</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.55</v>
+        <v>-12.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S3|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T2_rotasyon|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4767,39 +4611,39 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TKFEN.IS, TUPRS.IS</t>
+          <t>BRSAN.IS, BSOKE.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-08-07 | TKFEN.IS: 2026-08-12 | TUPRS.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>33.88781788770123</v>
+        <v>32.22665840648815</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +2.69% / +4.49% / -2.97% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +8.70% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3.397049184484535</v>
+        <v>15.87125249023873</v>
       </c>
       <c r="K26" t="n">
-        <v>10.12341466288347</v>
+        <v>-7.701750553347598</v>
       </c>
       <c r="L26" t="n">
-        <v>16.88858078470971</v>
+        <v>4.152177865701379</v>
       </c>
       <c r="M26" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N26" t="n">
-        <v>128.5</v>
+        <v>61</v>
       </c>
       <c r="O26" t="n">
-        <v>45.9</v>
+        <v>45.5</v>
       </c>
       <c r="P26" t="n">
         <v>4.2</v>
@@ -4810,22 +4654,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
-        <v>13.827</v>
+        <v>19.115</v>
       </c>
       <c r="T26" t="n">
-        <v>11.093</v>
+        <v>19.115</v>
       </c>
       <c r="U26" t="n">
-        <v>87.521</v>
+        <v>-14.207</v>
       </c>
       <c r="V26" t="n">
-        <v>87.063</v>
+        <v>-17.014</v>
       </c>
       <c r="W26" t="n">
-        <v>-9.086</v>
+        <v>-20.275</v>
       </c>
     </row>
     <row r="27">
@@ -4836,12 +4680,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4856,42 +4700,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TUPRS.IS</t>
+          <t>AEFES.IS, BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-08-12 | TUPRS.IS: 2026-08-05</t>
+          <t>AEFES.IS: 2026-08-12 | BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-12 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>32.85505614492337</v>
+        <v>12.66701959909342</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | TUPRS.IS: +13.24% / +14.91% / 0.00%</t>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.32% / +1.93% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +2.28% / +4.22% / -2.41% | ECILC.IS: +8.75% / +9.42% / -1.57%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3.648278064592536</v>
+        <v>-8.680217320764083</v>
       </c>
       <c r="K27" t="n">
-        <v>17.84271452630865</v>
+        <v>6.566662997937844</v>
       </c>
       <c r="L27" t="n">
-        <v>14.21663509452158</v>
+        <v>26.13605589995283</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>71.90000000000001</v>
+        <v>175.1</v>
       </c>
       <c r="O27" t="n">
-        <v>49.7</v>
+        <v>43.6</v>
       </c>
       <c r="P27" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4899,22 +4743,99 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>13.97</v>
+        <v>21.464</v>
       </c>
       <c r="T27" t="n">
-        <v>12.828</v>
+        <v>21.464</v>
       </c>
       <c r="U27" t="n">
-        <v>87.928</v>
+        <v>27.278</v>
       </c>
       <c r="V27" t="n">
-        <v>76.92100000000001</v>
+        <v>17.086</v>
       </c>
       <c r="W27" t="n">
-        <v>-3.422</v>
+        <v>-7.865</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>8.326901382152464</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>-8.338699492242052</v>
+      </c>
+      <c r="K28" t="n">
+        <v>11.24844230268831</v>
+      </c>
+      <c r="L28" t="n">
+        <v>15.11937055513065</v>
+      </c>
+      <c r="M28" t="n">
+        <v>72.22222222222221</v>
+      </c>
+      <c r="N28" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>45</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>12.679</v>
+      </c>
+      <c r="T28" t="n">
+        <v>10.364</v>
+      </c>
+      <c r="U28" t="n">
+        <v>32.693</v>
+      </c>
+      <c r="V28" t="n">
+        <v>17.594</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-5.555</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -158,8 +158,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ATL_1_1" displayName="ATL_1_1" ref="A2:W15" headerRowCount="1">
-  <autoFilter ref="A2:W15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ATL_1_1" displayName="ATL_1_1" ref="A2:W14" headerRowCount="1">
+  <autoFilter ref="A2:W14"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A18:W29" headerRowCount="1">
-  <autoFilter ref="A18:W29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W27" headerRowCount="1">
+  <autoFilter ref="A17:W27"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -222,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ATL_2_1" displayName="ATL_2_1" ref="A2:W15" headerRowCount="1">
-  <autoFilter ref="A2:W15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ATL_2_1" displayName="ATL_2_1" ref="A2:W14" headerRowCount="1">
+  <autoFilter ref="A2:W14"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -254,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A18:W29" headerRowCount="1">
-  <autoFilter ref="A18:W29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W28" headerRowCount="1">
+  <autoFilter ref="A17:W28"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -582,18 +582,18 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -727,37 +727,91 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KAR_TOP3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ÖNCEKİ_ANALİZ_YOK</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CWENE.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>71.34932273384752</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.65% / -2.28%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>28.90742434227913</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-16.69555354433906</v>
+      </c>
+      <c r="L3" t="n">
+        <v>17.11290382444416</v>
+      </c>
+      <c r="M3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N3" t="n">
+        <v>162.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ÖNCEKİ_ANALİZ_YOK</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>36.941</v>
+      </c>
+      <c r="T3" t="n">
+        <v>36.941</v>
+      </c>
+      <c r="U3" t="n">
+        <v>25.314</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-15.653</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-69.568</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -766,11 +820,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -783,67 +837,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CWENE.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>68.47567086069381</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.65% / -2.28%</t>
-        </is>
-      </c>
+        <v>67.66470503641577</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>25.99730926061523</v>
+        <v>27.238264119624</v>
       </c>
       <c r="K4" t="n">
-        <v>-17.4953917208495</v>
+        <v>-8.063423217612653</v>
       </c>
       <c r="L4" t="n">
-        <v>17.11290165300374</v>
+        <v>14.41049705545434</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>162.2</v>
+        <v>53.1</v>
       </c>
       <c r="O4" t="n">
-        <v>42.8</v>
+        <v>51.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>36.973</v>
+        <v>23.105</v>
       </c>
       <c r="T4" t="n">
-        <v>36.973</v>
+        <v>23.105</v>
       </c>
       <c r="U4" t="n">
-        <v>20.912</v>
+        <v>8.699</v>
       </c>
       <c r="V4" t="n">
-        <v>-15.803</v>
+        <v>2.761</v>
       </c>
       <c r="W4" t="n">
-        <v>-69.044</v>
+        <v>-30.289</v>
       </c>
     </row>
     <row r="5">
@@ -853,11 +895,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -873,17 +915,17 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>67.66470042665729</v>
+        <v>67.66470503641577</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>27.23826429058853</v>
+        <v>27.238264119624</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.063423115131684</v>
+        <v>-8.063423217612653</v>
       </c>
       <c r="L5" t="n">
-        <v>14.41050093817465</v>
+        <v>14.41049705545434</v>
       </c>
       <c r="M5" t="n">
         <v>77.77777777777779</v>
@@ -924,15 +966,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -945,55 +987,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CWENE.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>67.66470042665729</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>71.34932273384752</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.65% / -2.28%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
-        <v>27.23826429058853</v>
+        <v>28.90742434227913</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.063423115131684</v>
+        <v>-16.69555354433906</v>
       </c>
       <c r="L6" t="n">
-        <v>14.41050093817465</v>
+        <v>17.11290382444416</v>
       </c>
       <c r="M6" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>53.1</v>
+        <v>162.7</v>
       </c>
       <c r="O6" t="n">
-        <v>51.4</v>
+        <v>43.3</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>23.105</v>
+        <v>36.941</v>
       </c>
       <c r="T6" t="n">
-        <v>23.105</v>
+        <v>36.941</v>
       </c>
       <c r="U6" t="n">
-        <v>8.699</v>
+        <v>25.314</v>
       </c>
       <c r="V6" t="n">
-        <v>2.761</v>
+        <v>-15.653</v>
       </c>
       <c r="W6" t="n">
-        <v>-30.289</v>
+        <v>-69.568</v>
       </c>
     </row>
     <row r="7">
@@ -1003,7 +1057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1023,17 +1077,17 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>56.53775570047603</v>
+        <v>56.53775645557823</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>27.61399570060789</v>
+        <v>27.61399559485631</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.621821921204969e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>13.7859231192354</v>
+        <v>13.78592482270004</v>
       </c>
       <c r="M7" t="n">
         <v>77.77777777777779</v>
@@ -1078,7 +1132,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1098,17 +1152,17 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>67.66470042665729</v>
+        <v>67.66470503641577</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>27.23826429058853</v>
+        <v>27.238264119624</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.063423115131684</v>
+        <v>-8.063423217612653</v>
       </c>
       <c r="L8" t="n">
-        <v>14.41050093817465</v>
+        <v>14.41049705545434</v>
       </c>
       <c r="M8" t="n">
         <v>77.77777777777779</v>
@@ -1149,15 +1203,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1173,29 +1227,29 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>67.66470042665729</v>
+        <v>31.91300080326922</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>27.23826429058853</v>
+        <v>19.31957756950657</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.063423115131684</v>
+        <v>2.302203561121985e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>14.41050093817465</v>
+        <v>4.846554569756845</v>
       </c>
       <c r="M9" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>53.1</v>
+        <v>13.9</v>
       </c>
       <c r="O9" t="n">
-        <v>51.4</v>
+        <v>75</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1206,19 +1260,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>23.105</v>
+        <v>4.847</v>
       </c>
       <c r="T9" t="n">
-        <v>23.105</v>
+        <v>3.503</v>
       </c>
       <c r="U9" t="n">
-        <v>8.699</v>
+        <v>46.446</v>
       </c>
       <c r="V9" t="n">
-        <v>2.761</v>
+        <v>12.887</v>
       </c>
       <c r="W9" t="n">
-        <v>-30.289</v>
+        <v>-2.154</v>
       </c>
     </row>
     <row r="10">
@@ -1228,11 +1282,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1245,55 +1299,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, CWENE.IS, KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>31.91300386790401</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>44.1931793598139</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
-        <v>19.31957507327515</v>
+        <v>20.60664105207755</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-12.39404112492812</v>
       </c>
       <c r="L10" t="n">
-        <v>4.846554716272955</v>
+        <v>8.000657219756324</v>
       </c>
       <c r="M10" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>13.9</v>
+        <v>83.8</v>
       </c>
       <c r="O10" t="n">
-        <v>75</v>
+        <v>47.3</v>
       </c>
       <c r="P10" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>4.847</v>
+        <v>17.037</v>
       </c>
       <c r="T10" t="n">
-        <v>3.503</v>
+        <v>17.037</v>
       </c>
       <c r="U10" t="n">
-        <v>46.446</v>
+        <v>18.157</v>
       </c>
       <c r="V10" t="n">
-        <v>12.887</v>
+        <v>6.566</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.154</v>
+        <v>-24.265</v>
       </c>
     </row>
     <row r="11">
@@ -1303,11 +1369,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T2_rotasyon|E30|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1322,42 +1388,42 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGHOL.IS, CWENE.IS, KCHOL.IS</t>
+          <t>AGHOL.IS, CWENE.IS, KCHOL.IS, TKFEN.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-11 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>44.19317946034131</v>
+        <v>39.6760709590217</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +2.93% / +3.05% / -0.60% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.89% / +24.59% / -0.43%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>20.60664571193298</v>
+        <v>20.68188468299766</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.39404092636683</v>
+        <v>-14.19875003210586</v>
       </c>
       <c r="L11" t="n">
-        <v>8.000657065885175</v>
+        <v>8.721900452178899</v>
       </c>
       <c r="M11" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>83.8</v>
+        <v>156.3</v>
       </c>
       <c r="O11" t="n">
-        <v>47.3</v>
+        <v>45.7</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1365,97 +1431,109 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>17.037</v>
+        <v>20.179</v>
       </c>
       <c r="T11" t="n">
-        <v>17.037</v>
+        <v>20.179</v>
       </c>
       <c r="U11" t="n">
-        <v>18.157</v>
+        <v>3.177</v>
       </c>
       <c r="V11" t="n">
-        <v>6.566</v>
+        <v>-2.691</v>
       </c>
       <c r="W11" t="n">
-        <v>-24.265</v>
+        <v>-26.083</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ARCLK.IS, BRSAN.IS, BSOKE.IS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ARCLK.IS: 2026-07-29 | BRSAN.IS: 2026-08-07 | BSOKE.IS: 2026-08-03</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>24.12162912768729</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ARCLK.IS: -0.63% / +3.12% / -1.79% | BRSAN.IS: +9.94% / +12.94% / 0.00% | BSOKE.IS: +6.66% / +8.97% / -0.29%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>5.100353757880249</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15.66519674594435</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.82627592190883</v>
+      </c>
+      <c r="M12" t="n">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="N12" t="n">
+        <v>64</v>
+      </c>
+      <c r="O12" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>T3_kademeli_slot|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>50.71222513402564</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>21.05459022214706</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>9.327549806218627</v>
-      </c>
-      <c r="M12" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="N12" t="n">
-        <v>129.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="n">
-        <v>12.201</v>
+        <v>14.383</v>
       </c>
       <c r="T12" t="n">
-        <v>12.201</v>
+        <v>14.383</v>
       </c>
       <c r="U12" t="n">
-        <v>45.301</v>
+        <v>45.915</v>
       </c>
       <c r="V12" t="n">
-        <v>38.358</v>
+        <v>32.49</v>
       </c>
       <c r="W12" t="n">
-        <v>-10.494</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="13">
@@ -1465,72 +1543,84 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>8.623920580589118</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>-8.516992429863468</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.569461404868649</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.53177272942414</v>
+      </c>
+      <c r="M13" t="n">
+        <v>72.22222222222221</v>
+      </c>
+      <c r="N13" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>11.62011748225586</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>-5.014656161917919</v>
-      </c>
-      <c r="K13" t="n">
-        <v>14.97783194397475</v>
-      </c>
-      <c r="L13" t="n">
-        <v>26.56377822016731</v>
-      </c>
-      <c r="M13" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="N13" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" t="n">
-        <v>13.274</v>
+        <v>15.149</v>
       </c>
       <c r="T13" t="n">
-        <v>13.274</v>
+        <v>15.149</v>
       </c>
       <c r="U13" t="n">
-        <v>44.285</v>
+        <v>31.508</v>
       </c>
       <c r="V13" t="n">
-        <v>33.438</v>
+        <v>24.09</v>
       </c>
       <c r="W13" t="n">
-        <v>-22.085</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="14">
@@ -1540,329 +1630,375 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>T6_skor_momentum|E30|S5|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|Bvolatilite</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BRYAT.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BRYAT.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5.314240480464827</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BRYAT.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>-6.347935434616581</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.239577297814389</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13.58292314070337</v>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" t="n">
+        <v>304.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="S14" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>17.958</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.874</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-8.095000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>BENZERSIZ SECILEN SISTEMLER</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Grup</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Sira</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Etiket</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Karar_Tarihi</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Onceki_Karar_Tarihi</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Acik_Hisseler</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Pozisyon_Baslangiclari</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Secim_Donemi_CAGR_Pct</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Hisse_Bazli_Aktif_Kar_Pct</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Iki_Ay_Haric_CAGR_Pct</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Son_3_Ay_Getiri_Pct</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Secim_Donemi_Max_DD_Pct</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Aktif_Ay_Orani_Pct</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Yillik_Islem</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Kazanma_Pct</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Ort_Tutma_Bar</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Pozisyon_Durumu</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Acik_Pozisyon_Adedi</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Yillik_Max_DD_Pct</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>YTD_Max_DD_Pct</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Yillik_Kar_Pct</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>YTD_Kar_Pct</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Son_1Y_Tepeden_Suana_DD_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>9.056918277769066</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>-8.866327060107892</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7.569460837479292</v>
-      </c>
-      <c r="L14" t="n">
-        <v>16.92815412482109</v>
-      </c>
-      <c r="M14" t="n">
-        <v>72.22222222222221</v>
-      </c>
-      <c r="N14" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CWENE.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>71.34932273384752</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.65% / -2.28%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>28.90742434227913</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-16.69555354433906</v>
+      </c>
+      <c r="L18" t="n">
+        <v>17.11290382444416</v>
+      </c>
+      <c r="M18" t="n">
+        <v>100</v>
+      </c>
+      <c r="N18" t="n">
+        <v>162.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>15.149</v>
-      </c>
-      <c r="T14" t="n">
-        <v>15.149</v>
-      </c>
-      <c r="U14" t="n">
-        <v>32.295</v>
-      </c>
-      <c r="V14" t="n">
-        <v>24.09</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-4.946</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>T1_genislik_skor|E30|S3|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="S18" t="n">
+        <v>36.941</v>
+      </c>
+      <c r="T18" t="n">
+        <v>36.941</v>
+      </c>
+      <c r="U18" t="n">
+        <v>25.314</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-15.653</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-69.568</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>AKSA.IS, ALARK.IS, BSOKE.IS</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-12 | ALARK.IS: 2026-08-11 | BSOKE.IS: 2026-08-05</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>-12.73766062807727</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | ALARK.IS: -2.80% / +0.10% / -3.16% | BSOKE.IS: +2.29% / +4.50% / -2.02%</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>-24.54927299214288</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.619278208897891</v>
-      </c>
-      <c r="L15" t="n">
-        <v>44.44773885999038</v>
-      </c>
-      <c r="M15" t="n">
-        <v>100</v>
-      </c>
-      <c r="N15" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>17.278</v>
-      </c>
-      <c r="T15" t="n">
-        <v>13.054</v>
-      </c>
-      <c r="U15" t="n">
-        <v>26.029</v>
-      </c>
-      <c r="V15" t="n">
-        <v>23.445</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-15.994</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>BENZERSIZ SECILEN SISTEMLER</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Grup</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Sira</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Etiket</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Karar_Tarihi</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Onceki_Karar_Tarihi</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Acik_Hisseler</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Pozisyon_Baslangiclari</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Secim_Donemi_CAGR_Pct</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Hisse_Bazli_Aktif_Kar_Pct</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Iki_Ay_Haric_CAGR_Pct</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Son_3_Ay_Getiri_Pct</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>Secim_Donemi_Max_DD_Pct</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Aktif_Ay_Orani_Pct</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Yillik_Islem</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Kazanma_Pct</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Ort_Tutma_Bar</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Pozisyon_Durumu</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Acik_Pozisyon_Adedi</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>Yillik_Max_DD_Pct</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>YTD_Max_DD_Pct</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>Yillik_Kar_Pct</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>YTD_Kar_Pct</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>Son_1Y_Tepeden_Suana_DD_Pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ÖNCEKİ_ANALİZ_YOK</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>67.66470503641577</v>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>27.238264119624</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-8.063423217612653</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14.41049705545434</v>
+      </c>
+      <c r="M19" t="n">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="N19" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ÖNCEKİ_ANALİZ_YOK</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>23.105</v>
+      </c>
+      <c r="T19" t="n">
+        <v>23.105</v>
+      </c>
+      <c r="U19" t="n">
+        <v>8.699</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.761</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-30.289</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1872,12 +2008,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1890,73 +2026,61 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>CWENE.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>68.47567086069381</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.65% / -2.28%</t>
-        </is>
-      </c>
+        <v>67.66470503641577</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>25.99730926061523</v>
+        <v>27.238264119624</v>
       </c>
       <c r="K20" t="n">
-        <v>-17.4953917208495</v>
+        <v>-8.063423217612653</v>
       </c>
       <c r="L20" t="n">
-        <v>17.11290165300374</v>
+        <v>14.41049705545434</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>162.2</v>
+        <v>53.1</v>
       </c>
       <c r="O20" t="n">
-        <v>42.8</v>
+        <v>51.4</v>
       </c>
       <c r="P20" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>36.973</v>
+        <v>23.105</v>
       </c>
       <c r="T20" t="n">
-        <v>36.973</v>
+        <v>23.105</v>
       </c>
       <c r="U20" t="n">
-        <v>20.912</v>
+        <v>8.699</v>
       </c>
       <c r="V20" t="n">
-        <v>-15.803</v>
+        <v>2.761</v>
       </c>
       <c r="W20" t="n">
-        <v>-69.044</v>
+        <v>-30.289</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1966,7 +2090,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1982,29 +2106,29 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>67.66470042665729</v>
+        <v>56.53775645557823</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>27.23826429058853</v>
+        <v>27.61399559485631</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.063423115131684</v>
+        <v>1.621821921204969e-06</v>
       </c>
       <c r="L21" t="n">
-        <v>14.41050093817465</v>
+        <v>13.78592482270004</v>
       </c>
       <c r="M21" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>53.1</v>
+        <v>24.3</v>
       </c>
       <c r="O21" t="n">
-        <v>51.4</v>
+        <v>63.3</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2015,35 +2139,35 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>23.105</v>
+        <v>8.218</v>
       </c>
       <c r="T21" t="n">
-        <v>23.105</v>
+        <v>4.976</v>
       </c>
       <c r="U21" t="n">
-        <v>8.699</v>
+        <v>83.73399999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>2.761</v>
+        <v>13.056</v>
       </c>
       <c r="W21" t="n">
-        <v>-30.289</v>
+        <v>-4.893</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2056,71 +2180,83 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, CWENE.IS, KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H22" t="n">
-        <v>67.66470042665729</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>44.1931793598139</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J22" t="n">
-        <v>27.23826429058853</v>
+        <v>20.60664105207755</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.063423115131684</v>
+        <v>-12.39404112492812</v>
       </c>
       <c r="L22" t="n">
-        <v>14.41050093817465</v>
+        <v>8.000657219756324</v>
       </c>
       <c r="M22" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>53.1</v>
+        <v>83.8</v>
       </c>
       <c r="O22" t="n">
-        <v>51.4</v>
+        <v>47.3</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>23.105</v>
+        <v>17.037</v>
       </c>
       <c r="T22" t="n">
-        <v>23.105</v>
+        <v>17.037</v>
       </c>
       <c r="U22" t="n">
-        <v>8.699</v>
+        <v>18.157</v>
       </c>
       <c r="V22" t="n">
-        <v>2.761</v>
+        <v>6.566</v>
       </c>
       <c r="W22" t="n">
-        <v>-30.289</v>
+        <v>-24.265</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
+          <t>T2_rotasyon|E30|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2133,55 +2269,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, CWENE.IS, KCHOL.IS, TKFEN.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-11 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>56.53775570047603</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>39.6760709590217</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +2.93% / +3.05% / -0.60% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.89% / +24.59% / -0.43%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>27.61399570060789</v>
+        <v>20.68188468299766</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-14.19875003210586</v>
       </c>
       <c r="L23" t="n">
-        <v>13.7859231192354</v>
+        <v>8.721900452178899</v>
       </c>
       <c r="M23" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>24.3</v>
+        <v>156.3</v>
       </c>
       <c r="O23" t="n">
-        <v>63.3</v>
+        <v>45.7</v>
       </c>
       <c r="P23" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>8.218</v>
+        <v>20.179</v>
       </c>
       <c r="T23" t="n">
-        <v>4.976</v>
+        <v>20.179</v>
       </c>
       <c r="U23" t="n">
-        <v>83.73399999999999</v>
+        <v>3.177</v>
       </c>
       <c r="V23" t="n">
-        <v>13.056</v>
+        <v>-2.691</v>
       </c>
       <c r="W23" t="n">
-        <v>-4.893</v>
+        <v>-26.083</v>
       </c>
     </row>
     <row r="24">
@@ -2192,12 +2340,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2213,29 +2361,29 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>50.71222513402564</v>
+        <v>31.91300080326922</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>21.05459022214706</v>
+        <v>19.31957756950657</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2.302203561121985e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>9.327549806218627</v>
+        <v>4.846554569756845</v>
       </c>
       <c r="M24" t="n">
-        <v>83.33333333333334</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N24" t="n">
-        <v>129.5</v>
+        <v>13.9</v>
       </c>
       <c r="O24" t="n">
-        <v>47.1</v>
+        <v>75</v>
       </c>
       <c r="P24" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2246,35 +2394,35 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>12.201</v>
+        <v>4.847</v>
       </c>
       <c r="T24" t="n">
-        <v>12.201</v>
+        <v>3.503</v>
       </c>
       <c r="U24" t="n">
-        <v>45.301</v>
+        <v>46.446</v>
       </c>
       <c r="V24" t="n">
-        <v>38.358</v>
+        <v>12.887</v>
       </c>
       <c r="W24" t="n">
-        <v>-10.494</v>
+        <v>-2.154</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2289,42 +2437,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGHOL.IS, CWENE.IS, KCHOL.IS</t>
+          <t>ARCLK.IS, BRSAN.IS, BSOKE.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-12</t>
+          <t>ARCLK.IS: 2026-07-29 | BRSAN.IS: 2026-08-07 | BSOKE.IS: 2026-08-03</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>44.19317946034131</v>
+        <v>24.12162912768729</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ARCLK.IS: -0.63% / +3.12% / -1.79% | BRSAN.IS: +9.94% / +12.94% / 0.00% | BSOKE.IS: +6.66% / +8.97% / -0.29%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>20.60664571193298</v>
+        <v>5.100353757880249</v>
       </c>
       <c r="K25" t="n">
-        <v>-12.39404092636683</v>
+        <v>15.66519674594435</v>
       </c>
       <c r="L25" t="n">
-        <v>8.000657065885175</v>
+        <v>14.82627592190883</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>83.8</v>
+        <v>64</v>
       </c>
       <c r="O25" t="n">
-        <v>47.3</v>
+        <v>56.6</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2335,35 +2483,35 @@
         <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>17.037</v>
+        <v>14.383</v>
       </c>
       <c r="T25" t="n">
-        <v>17.037</v>
+        <v>14.383</v>
       </c>
       <c r="U25" t="n">
-        <v>18.157</v>
+        <v>45.915</v>
       </c>
       <c r="V25" t="n">
-        <v>6.566</v>
+        <v>32.49</v>
       </c>
       <c r="W25" t="n">
-        <v>-24.265</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2376,55 +2524,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>31.91300386790401</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>8.623920580589118</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>19.31957507327515</v>
+        <v>-8.516992429863468</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>7.569461404868649</v>
       </c>
       <c r="L26" t="n">
-        <v>4.846554716272955</v>
+        <v>16.53177272942414</v>
       </c>
       <c r="M26" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>13.9</v>
+        <v>84.8</v>
       </c>
       <c r="O26" t="n">
-        <v>75</v>
+        <v>43.3</v>
       </c>
       <c r="P26" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>4.847</v>
+        <v>15.149</v>
       </c>
       <c r="T26" t="n">
-        <v>3.503</v>
+        <v>15.149</v>
       </c>
       <c r="U26" t="n">
-        <v>46.446</v>
+        <v>31.508</v>
       </c>
       <c r="V26" t="n">
-        <v>12.887</v>
+        <v>24.09</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.154</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="27">
@@ -2435,12 +2595,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T6_skor_momentum|E30|S5|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|Bvolatilite</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2453,239 +2613,73 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BRYAT.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BRYAT.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H27" t="n">
-        <v>11.62011748225586</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>5.314240480464827</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BRYAT.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>-5.014656161917919</v>
+        <v>-6.347935434616581</v>
       </c>
       <c r="K27" t="n">
-        <v>14.97783194397475</v>
+        <v>3.239577297814389</v>
       </c>
       <c r="L27" t="n">
-        <v>26.56377822016731</v>
+        <v>13.58292314070337</v>
       </c>
       <c r="M27" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>41.7</v>
+        <v>304.6</v>
       </c>
       <c r="O27" t="n">
-        <v>51.2</v>
+        <v>46.9</v>
       </c>
       <c r="P27" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>13.274</v>
+        <v>10.3</v>
       </c>
       <c r="T27" t="n">
-        <v>13.274</v>
+        <v>10.3</v>
       </c>
       <c r="U27" t="n">
-        <v>44.285</v>
+        <v>17.958</v>
       </c>
       <c r="V27" t="n">
-        <v>33.438</v>
+        <v>6.874</v>
       </c>
       <c r="W27" t="n">
-        <v>-22.085</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>9.056918277769066</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>-8.866327060107892</v>
-      </c>
-      <c r="K28" t="n">
-        <v>7.569460837479292</v>
-      </c>
-      <c r="L28" t="n">
-        <v>16.92815412482109</v>
-      </c>
-      <c r="M28" t="n">
-        <v>72.22222222222221</v>
-      </c>
-      <c r="N28" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>15.149</v>
-      </c>
-      <c r="T28" t="n">
-        <v>15.149</v>
-      </c>
-      <c r="U28" t="n">
-        <v>32.295</v>
-      </c>
-      <c r="V28" t="n">
-        <v>24.09</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-4.946</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>T1_genislik_skor|E30|S3|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>AKSA.IS, ALARK.IS, BSOKE.IS</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-12 | ALARK.IS: 2026-08-11 | BSOKE.IS: 2026-08-05</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>-12.73766062807727</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | ALARK.IS: -2.80% / +0.10% / -3.16% | BSOKE.IS: +2.29% / +4.50% / -2.02%</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>-24.54927299214288</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.619278208897891</v>
-      </c>
-      <c r="L29" t="n">
-        <v>44.44773885999038</v>
-      </c>
-      <c r="M29" t="n">
-        <v>100</v>
-      </c>
-      <c r="N29" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>17.278</v>
-      </c>
-      <c r="T29" t="n">
-        <v>13.054</v>
-      </c>
-      <c r="U29" t="n">
-        <v>26.029</v>
-      </c>
-      <c r="V29" t="n">
-        <v>23.445</v>
-      </c>
-      <c r="W29" t="n">
-        <v>-15.994</v>
+        <v>-8.095000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A16:W16"/>
     <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A17:W17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="2">
@@ -2701,10 +2695,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -2714,13 +2708,13 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -2854,37 +2848,79 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KAR_TOP3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ÖNCEKİ_ANALİZ_YOK</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>91.56479261353148</v>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>23.39595923130722</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-13.34044906797636</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20.6096939559789</v>
+      </c>
+      <c r="M3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N3" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="O3" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ÖNCEKİ_ANALİZ_YOK</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>28.897</v>
+      </c>
+      <c r="T3" t="n">
+        <v>28.897</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6.931</v>
+      </c>
+      <c r="V3" t="n">
+        <v>18.912</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-33.344</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2893,11 +2929,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2913,29 +2949,29 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>83.96669618870591</v>
+        <v>91.56479261353148</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>30.34851211040859</v>
+        <v>23.39595923130722</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-13.34044906797636</v>
       </c>
       <c r="L4" t="n">
-        <v>14.57984787268229</v>
+        <v>20.6096939559789</v>
       </c>
       <c r="M4" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>41.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>50.6</v>
+        <v>43.7</v>
       </c>
       <c r="P4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -2946,19 +2982,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>25.421</v>
+        <v>28.897</v>
       </c>
       <c r="T4" t="n">
-        <v>25.421</v>
+        <v>28.897</v>
       </c>
       <c r="U4" t="n">
-        <v>81.02800000000001</v>
+        <v>6.931</v>
       </c>
       <c r="V4" t="n">
-        <v>58.618</v>
+        <v>18.912</v>
       </c>
       <c r="W4" t="n">
-        <v>-18.089</v>
+        <v>-33.344</v>
       </c>
     </row>
     <row r="5">
@@ -2968,86 +3004,98 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>87.45314762918606</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>25.04605608184003</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-17.41592720282232</v>
+      </c>
+      <c r="L5" t="n">
+        <v>19.87241420107954</v>
+      </c>
+      <c r="M5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N5" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>83.96669618870591</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>30.34851211040859</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14.57984787268229</v>
-      </c>
-      <c r="M5" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="N5" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
-        <v>25.421</v>
+        <v>28.429</v>
       </c>
       <c r="T5" t="n">
-        <v>25.421</v>
+        <v>28.429</v>
       </c>
       <c r="U5" t="n">
-        <v>81.02800000000001</v>
+        <v>-5.959</v>
       </c>
       <c r="V5" t="n">
-        <v>58.618</v>
+        <v>2.872</v>
       </c>
       <c r="W5" t="n">
-        <v>-18.089</v>
+        <v>-36.628</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3063,29 +3111,29 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>70.31392713455024</v>
+        <v>73.75964826688029</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>23.71910970908662</v>
+        <v>32.17500090460663</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1.75900002341578e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>14.2080391548458</v>
+        <v>10.93171342838547</v>
       </c>
       <c r="M6" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="O6" t="n">
-        <v>49.6</v>
+        <v>52.4</v>
       </c>
       <c r="P6" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -3096,19 +3144,19 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>19.421</v>
+        <v>15.232</v>
       </c>
       <c r="T6" t="n">
-        <v>19.421</v>
+        <v>15.232</v>
       </c>
       <c r="U6" t="n">
-        <v>35.135</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>25.849</v>
+        <v>45.816</v>
       </c>
       <c r="W6" t="n">
-        <v>-32.57</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="7">
@@ -3118,11 +3166,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3138,29 +3186,29 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>83.96669618870591</v>
+        <v>73.75964826688029</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>30.34851211040859</v>
+        <v>32.17500090460663</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-1.75900002341578e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>14.57984787268229</v>
+        <v>10.93171342838547</v>
       </c>
       <c r="M7" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="O7" t="n">
-        <v>50.6</v>
+        <v>52.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -3171,19 +3219,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>25.421</v>
+        <v>15.232</v>
       </c>
       <c r="T7" t="n">
-        <v>25.421</v>
+        <v>15.232</v>
       </c>
       <c r="U7" t="n">
-        <v>81.02800000000001</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>58.618</v>
+        <v>45.816</v>
       </c>
       <c r="W7" t="n">
-        <v>-18.089</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="8">
@@ -3193,86 +3241,98 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>66.30149434982813</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>30.34761773567121</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-24.73397862399341</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14.51092595374885</v>
+      </c>
+      <c r="M8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>83.96669618870591</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>30.34851211040859</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>14.57984787268229</v>
-      </c>
-      <c r="M8" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="N8" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
-        <v>25.421</v>
+        <v>35.388</v>
       </c>
       <c r="T8" t="n">
-        <v>25.421</v>
+        <v>35.388</v>
       </c>
       <c r="U8" t="n">
-        <v>81.02800000000001</v>
+        <v>-8.849</v>
       </c>
       <c r="V8" t="n">
-        <v>58.618</v>
+        <v>-15.451</v>
       </c>
       <c r="W8" t="n">
-        <v>-18.089</v>
+        <v>-49.923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3285,55 +3345,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BSOKE.IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>56.03042053281114</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>41.94189944051843</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>28.15701356966698</v>
+        <v>19.29474557819859</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-3.804599201929793</v>
       </c>
       <c r="L9" t="n">
-        <v>9.385192872081106</v>
+        <v>5.815920071163994</v>
       </c>
       <c r="M9" t="n">
-        <v>77.77777777777779</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N9" t="n">
-        <v>118.6</v>
+        <v>32.2</v>
       </c>
       <c r="O9" t="n">
-        <v>52.7</v>
+        <v>56.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>11.325</v>
+        <v>11.941</v>
       </c>
       <c r="T9" t="n">
-        <v>11.325</v>
+        <v>11.941</v>
       </c>
       <c r="U9" t="n">
-        <v>81.36</v>
+        <v>-7.395</v>
       </c>
       <c r="V9" t="n">
-        <v>42.129</v>
+        <v>-9.042999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-9.914</v>
+        <v>-12.558</v>
       </c>
     </row>
     <row r="10">
@@ -3343,11 +3415,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|coklu_zarf</t>
+          <t>T2_rotasyon|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3360,55 +3432,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BSOKE.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>49.31250917020018</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>32.22665657857966</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +9.47% / +24.13% / -0.52%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
-        <v>24.57373716046218</v>
+        <v>15.87125250627721</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4087994352198754</v>
+        <v>-7.545565760942496</v>
       </c>
       <c r="L10" t="n">
-        <v>4.922945032023218</v>
+        <v>4.152173979569406</v>
       </c>
       <c r="M10" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N10" t="n">
-        <v>15.4</v>
+        <v>61</v>
       </c>
       <c r="O10" t="n">
-        <v>51.6</v>
+        <v>45.5</v>
       </c>
       <c r="P10" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>12.747</v>
+        <v>18.978</v>
       </c>
       <c r="T10" t="n">
-        <v>12.747</v>
+        <v>18.978</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.367</v>
+        <v>-14.062</v>
       </c>
       <c r="V10" t="n">
-        <v>-9.683</v>
+        <v>-16.873</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.392</v>
+        <v>-20.129</v>
       </c>
     </row>
     <row r="11">
@@ -3418,11 +3502,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|Bvolatilite</t>
+          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3435,81 +3519,69 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, BSOKE.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>33.82427078969281</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +9.47% / +24.13% / -0.52%</t>
-        </is>
-      </c>
+        <v>73.75964826688029</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>16.75244184166531</v>
+        <v>32.17500090460663</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.545392024480901</v>
+        <v>-1.75900002341578e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>4.152177865701379</v>
+        <v>10.93171342838547</v>
       </c>
       <c r="M11" t="n">
-        <v>33.33333333333333</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>59</v>
+        <v>41.7</v>
       </c>
       <c r="O11" t="n">
-        <v>42.9</v>
+        <v>52.4</v>
       </c>
       <c r="P11" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>18.978</v>
+        <v>15.232</v>
       </c>
       <c r="T11" t="n">
-        <v>18.978</v>
+        <v>15.232</v>
       </c>
       <c r="U11" t="n">
-        <v>-14.645</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-16.994</v>
+        <v>45.816</v>
       </c>
       <c r="W11" t="n">
-        <v>-19.993</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3525,29 +3597,29 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>41.56012474067232</v>
+        <v>8.326900458734364</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>23.05440645199586</v>
+        <v>-8.338698318262827</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>11.24844055823626</v>
       </c>
       <c r="L12" t="n">
-        <v>7.832157184647482</v>
+        <v>15.1193724336431</v>
       </c>
       <c r="M12" t="n">
-        <v>55.55555555555556</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N12" t="n">
-        <v>22.8</v>
+        <v>39.7</v>
       </c>
       <c r="O12" t="n">
-        <v>67.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3558,19 +3630,19 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>6.172</v>
+        <v>12.679</v>
       </c>
       <c r="T12" t="n">
-        <v>6.172</v>
+        <v>10.364</v>
       </c>
       <c r="U12" t="n">
-        <v>22.178</v>
+        <v>32.693</v>
       </c>
       <c r="V12" t="n">
-        <v>9.586</v>
+        <v>17.594</v>
       </c>
       <c r="W12" t="n">
-        <v>-8.037000000000001</v>
+        <v>-5.555</v>
       </c>
     </row>
     <row r="13">
@@ -3580,11 +3652,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3597,55 +3669,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AEFES.IS, BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AEFES.IS: 2026-08-12 | BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-12 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>14.82306397966822</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>12.66702235000581</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +0.32% / +1.94% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.89% / +4.22% / -2.40% | ECILC.IS: +9.62% / +9.86% / -1.57%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>-9.531327255112876</v>
+        <v>-8.680214783453089</v>
       </c>
       <c r="K13" t="n">
-        <v>11.24844230268829</v>
+        <v>6.806799949189068</v>
       </c>
       <c r="L13" t="n">
-        <v>14.15029836851692</v>
+        <v>26.13605890970743</v>
       </c>
       <c r="M13" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>56.1</v>
+        <v>175.1</v>
       </c>
       <c r="O13" t="n">
-        <v>48.7</v>
+        <v>43.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>17.392</v>
+        <v>21.464</v>
       </c>
       <c r="T13" t="n">
-        <v>17.392</v>
+        <v>21.464</v>
       </c>
       <c r="U13" t="n">
-        <v>43.969</v>
+        <v>27.564</v>
       </c>
       <c r="V13" t="n">
-        <v>21.325</v>
+        <v>17.35</v>
       </c>
       <c r="W13" t="n">
-        <v>-6.027</v>
+        <v>-7.578</v>
       </c>
     </row>
     <row r="14">
@@ -3655,11 +3739,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3672,315 +3756,349 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>AEFES.IS, BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>AEFES.IS: 2026-08-12 | BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-12 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>12.51721948350586</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +0.32% / +1.94% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.89% / +4.22% / -2.40% | ECILC.IS: +9.62% / +9.86% / -1.57%</t>
-        </is>
-      </c>
+        <v>0.1852998653190774</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-8.713031902113466</v>
+        <v>-22.00780799603813</v>
       </c>
       <c r="K14" t="n">
-        <v>6.807167723513485</v>
+        <v>4.971426232468645</v>
       </c>
       <c r="L14" t="n">
-        <v>26.1360558999528</v>
+        <v>50.19196082132959</v>
       </c>
       <c r="M14" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="N14" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>49</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12.186</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12.186</v>
+      </c>
+      <c r="U14" t="n">
+        <v>59.874</v>
+      </c>
+      <c r="V14" t="n">
+        <v>42.782</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-21.293</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>BENZERSIZ SECILEN SISTEMLER</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Grup</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Sira</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Etiket</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Karar_Tarihi</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Onceki_Karar_Tarihi</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Acik_Hisseler</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Pozisyon_Baslangiclari</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Secim_Donemi_CAGR_Pct</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Hisse_Bazli_Aktif_Kar_Pct</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Iki_Ay_Haric_CAGR_Pct</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Son_3_Ay_Getiri_Pct</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Secim_Donemi_Max_DD_Pct</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Aktif_Ay_Orani_Pct</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Yillik_Islem</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Kazanma_Pct</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Ort_Tutma_Bar</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Pozisyon_Durumu</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Acik_Pozisyon_Adedi</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Yillik_Max_DD_Pct</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>YTD_Max_DD_Pct</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Yillik_Kar_Pct</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>YTD_Kar_Pct</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Son_1Y_Tepeden_Suana_DD_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KAR_TOP3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>91.56479261353148</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>23.39595923130722</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-13.34044906797636</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.6096939559789</v>
+      </c>
+      <c r="M18" t="n">
         <v>100</v>
       </c>
-      <c r="N14" t="n">
-        <v>183</v>
-      </c>
-      <c r="O14" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>22.553</v>
-      </c>
-      <c r="T14" t="n">
-        <v>22.553</v>
-      </c>
-      <c r="U14" t="n">
-        <v>25.692</v>
-      </c>
-      <c r="V14" t="n">
-        <v>15.723</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-9.339</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="N18" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>28.897</v>
+      </c>
+      <c r="T18" t="n">
+        <v>28.897</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6.931</v>
+      </c>
+      <c r="V18" t="n">
+        <v>18.912</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-33.344</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KAR_TOP3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>49.91322755613019</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>7.600451148622889</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.971424769515997</v>
-      </c>
-      <c r="L15" t="n">
-        <v>19.53582128130424</v>
-      </c>
-      <c r="M15" t="n">
-        <v>100</v>
-      </c>
-      <c r="N15" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>18.867</v>
-      </c>
-      <c r="T15" t="n">
-        <v>18.867</v>
-      </c>
-      <c r="U15" t="n">
-        <v>78.093</v>
-      </c>
-      <c r="V15" t="n">
-        <v>40.341</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-24.086</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>BENZERSIZ SECILEN SISTEMLER</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Grup</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Sira</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Etiket</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Karar_Tarihi</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Onceki_Karar_Tarihi</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Acik_Hisseler</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Pozisyon_Baslangiclari</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Secim_Donemi_CAGR_Pct</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Hisse_Bazli_Aktif_Kar_Pct</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Iki_Ay_Haric_CAGR_Pct</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Son_3_Ay_Getiri_Pct</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>Secim_Donemi_Max_DD_Pct</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Aktif_Ay_Orani_Pct</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Yillik_Islem</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Kazanma_Pct</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Ort_Tutma_Bar</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Pozisyon_Durumu</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Acik_Pozisyon_Adedi</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>Yillik_Max_DD_Pct</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>YTD_Max_DD_Pct</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>Yillik_Kar_Pct</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>YTD_Kar_Pct</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>Son_1Y_Tepeden_Suana_DD_Pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ÖNCEKİ_ANALİZ_YOK</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>91.56479261353148</v>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>23.39595923130722</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-13.34044906797636</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.6096939559789</v>
+      </c>
+      <c r="M19" t="n">
+        <v>100</v>
+      </c>
+      <c r="N19" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.8</v>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ÖNCEKİ_ANALİZ_YOK</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>28.897</v>
+      </c>
+      <c r="T19" t="n">
+        <v>28.897</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6.931</v>
+      </c>
+      <c r="V19" t="n">
+        <v>18.912</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-33.344</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3993,71 +4111,83 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H20" t="n">
-        <v>83.96669618870591</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>87.45314762918606</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
-        <v>30.34851211040859</v>
+        <v>25.04605608184003</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-17.41592720282232</v>
       </c>
       <c r="L20" t="n">
-        <v>14.57984787268229</v>
+        <v>19.87241420107954</v>
       </c>
       <c r="M20" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>41.2</v>
+        <v>101.2</v>
       </c>
       <c r="O20" t="n">
-        <v>50.6</v>
+        <v>41.7</v>
       </c>
       <c r="P20" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>25.421</v>
+        <v>28.429</v>
       </c>
       <c r="T20" t="n">
-        <v>25.421</v>
+        <v>28.429</v>
       </c>
       <c r="U20" t="n">
-        <v>81.02800000000001</v>
+        <v>-5.959</v>
       </c>
       <c r="V20" t="n">
-        <v>58.618</v>
+        <v>2.872</v>
       </c>
       <c r="W20" t="n">
-        <v>-18.089</v>
+        <v>-36.628</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 | 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4073,29 +4203,29 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>83.96669618870591</v>
+        <v>73.75964826688029</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>30.34851211040859</v>
+        <v>32.17500090460663</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-1.75900002341578e-06</v>
       </c>
       <c r="L21" t="n">
-        <v>14.57984787268229</v>
+        <v>10.93171342838547</v>
       </c>
       <c r="M21" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="O21" t="n">
-        <v>50.6</v>
+        <v>52.4</v>
       </c>
       <c r="P21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -4106,35 +4236,35 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>25.421</v>
+        <v>15.232</v>
       </c>
       <c r="T21" t="n">
-        <v>25.421</v>
+        <v>15.232</v>
       </c>
       <c r="U21" t="n">
-        <v>81.02800000000001</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>58.618</v>
+        <v>45.816</v>
       </c>
       <c r="W21" t="n">
-        <v>-18.089</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4150,29 +4280,29 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>70.31392713455024</v>
+        <v>73.75964826688029</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>23.71910970908662</v>
+        <v>32.17500090460663</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-1.75900002341578e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>14.2080391548458</v>
+        <v>10.93171342838547</v>
       </c>
       <c r="M22" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="O22" t="n">
-        <v>49.6</v>
+        <v>52.4</v>
       </c>
       <c r="P22" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4183,19 +4313,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>19.421</v>
+        <v>15.232</v>
       </c>
       <c r="T22" t="n">
-        <v>19.421</v>
+        <v>15.232</v>
       </c>
       <c r="U22" t="n">
-        <v>35.135</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>25.849</v>
+        <v>45.816</v>
       </c>
       <c r="W22" t="n">
-        <v>-32.57</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="23">
@@ -4211,7 +4341,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4224,71 +4354,83 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>56.03042053281114</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>66.30149434982813</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>28.15701356966698</v>
+        <v>30.34761773567121</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-24.73397862399341</v>
       </c>
       <c r="L23" t="n">
-        <v>9.385192872081106</v>
+        <v>14.51092595374885</v>
       </c>
       <c r="M23" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>118.6</v>
+        <v>102.7</v>
       </c>
       <c r="O23" t="n">
-        <v>52.7</v>
+        <v>39.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>11.325</v>
+        <v>35.388</v>
       </c>
       <c r="T23" t="n">
-        <v>11.325</v>
+        <v>35.388</v>
       </c>
       <c r="U23" t="n">
-        <v>81.36</v>
+        <v>-8.849</v>
       </c>
       <c r="V23" t="n">
-        <v>42.129</v>
+        <v>-15.451</v>
       </c>
       <c r="W23" t="n">
-        <v>-9.914</v>
+        <v>-49.923</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4301,55 +4443,67 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BSOKE.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>49.91322755613019</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>41.94189944051843</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>7.600451148622889</v>
+        <v>19.29474557819859</v>
       </c>
       <c r="K24" t="n">
-        <v>4.971424769515997</v>
+        <v>-3.804599201929793</v>
       </c>
       <c r="L24" t="n">
-        <v>19.53582128130424</v>
+        <v>5.815920071163994</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N24" t="n">
-        <v>67.5</v>
+        <v>32.2</v>
       </c>
       <c r="O24" t="n">
-        <v>44.1</v>
+        <v>56.9</v>
       </c>
       <c r="P24" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>18.867</v>
+        <v>11.941</v>
       </c>
       <c r="T24" t="n">
-        <v>18.867</v>
+        <v>11.941</v>
       </c>
       <c r="U24" t="n">
-        <v>78.093</v>
+        <v>-7.395</v>
       </c>
       <c r="V24" t="n">
-        <v>40.341</v>
+        <v>-9.042999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>-24.086</v>
+        <v>-12.558</v>
       </c>
     </row>
     <row r="25">
@@ -4360,12 +4514,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|coklu_zarf</t>
+          <t>T2_rotasyon|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4378,71 +4532,83 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BSOKE.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>49.31250917020018</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>32.22665657857966</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +9.47% / +24.13% / -0.52%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>24.57373716046218</v>
+        <v>15.87125250627721</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4087994352198754</v>
+        <v>-7.545565760942496</v>
       </c>
       <c r="L25" t="n">
-        <v>4.922945032023218</v>
+        <v>4.152173979569406</v>
       </c>
       <c r="M25" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>15.4</v>
+        <v>61</v>
       </c>
       <c r="O25" t="n">
-        <v>51.6</v>
+        <v>45.5</v>
       </c>
       <c r="P25" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>12.747</v>
+        <v>18.978</v>
       </c>
       <c r="T25" t="n">
-        <v>12.747</v>
+        <v>18.978</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.367</v>
+        <v>-14.062</v>
       </c>
       <c r="V25" t="n">
-        <v>-9.683</v>
+        <v>-16.873</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.392</v>
+        <v>-20.129</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E70|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4455,71 +4621,83 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>AEFES.IS, BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>AEFES.IS: 2026-08-12 | BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-12 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>41.56012474067232</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>12.66702235000581</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +0.32% / +1.94% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.89% / +4.22% / -2.40% | ECILC.IS: +9.62% / +9.86% / -1.57%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>23.05440645199586</v>
+        <v>-8.680214783453089</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>6.806799949189068</v>
       </c>
       <c r="L26" t="n">
-        <v>7.832157184647482</v>
+        <v>26.13605890970743</v>
       </c>
       <c r="M26" t="n">
-        <v>55.55555555555556</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>22.8</v>
+        <v>175.1</v>
       </c>
       <c r="O26" t="n">
-        <v>67.40000000000001</v>
+        <v>43.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
-        <v>6.172</v>
+        <v>21.464</v>
       </c>
       <c r="T26" t="n">
-        <v>6.172</v>
+        <v>21.464</v>
       </c>
       <c r="U26" t="n">
-        <v>22.178</v>
+        <v>27.564</v>
       </c>
       <c r="V26" t="n">
-        <v>9.586</v>
+        <v>17.35</v>
       </c>
       <c r="W26" t="n">
-        <v>-8.037000000000001</v>
+        <v>-7.578</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|Bvolatilite</t>
+          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4532,67 +4710,55 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, BSOKE.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>33.82427078969281</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +9.47% / +24.13% / -0.52%</t>
-        </is>
-      </c>
+        <v>8.326900458734364</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>16.75244184166531</v>
+        <v>-8.338698318262827</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.545392024480901</v>
+        <v>11.24844055823626</v>
       </c>
       <c r="L27" t="n">
-        <v>4.152177865701379</v>
+        <v>15.1193724336431</v>
       </c>
       <c r="M27" t="n">
-        <v>33.33333333333333</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N27" t="n">
-        <v>59</v>
+        <v>39.7</v>
       </c>
       <c r="O27" t="n">
-        <v>42.9</v>
+        <v>45</v>
       </c>
       <c r="P27" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>18.978</v>
+        <v>12.679</v>
       </c>
       <c r="T27" t="n">
-        <v>18.978</v>
+        <v>10.364</v>
       </c>
       <c r="U27" t="n">
-        <v>-14.645</v>
+        <v>32.693</v>
       </c>
       <c r="V27" t="n">
-        <v>-16.994</v>
+        <v>17.594</v>
       </c>
       <c r="W27" t="n">
-        <v>-19.993</v>
+        <v>-5.555</v>
       </c>
     </row>
     <row r="28">
@@ -4603,12 +4769,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4624,29 +4790,29 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>14.82306397966822</v>
+        <v>0.1852998653190774</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>-9.531327255112876</v>
+        <v>-22.00780799603813</v>
       </c>
       <c r="K28" t="n">
-        <v>11.24844230268829</v>
+        <v>4.971426232468645</v>
       </c>
       <c r="L28" t="n">
-        <v>14.15029836851692</v>
+        <v>50.19196082132959</v>
       </c>
       <c r="M28" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N28" t="n">
-        <v>56.1</v>
+        <v>47.6</v>
       </c>
       <c r="O28" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="P28" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4657,114 +4823,25 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>17.392</v>
+        <v>12.186</v>
       </c>
       <c r="T28" t="n">
-        <v>17.392</v>
+        <v>12.186</v>
       </c>
       <c r="U28" t="n">
-        <v>43.969</v>
+        <v>59.874</v>
       </c>
       <c r="V28" t="n">
-        <v>21.325</v>
+        <v>42.782</v>
       </c>
       <c r="W28" t="n">
-        <v>-6.027</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>AEFES.IS, BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AEFES.IS: 2026-08-12 | BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-12 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>12.51721948350586</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +0.32% / +1.94% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.89% / +4.22% / -2.40% | ECILC.IS: +9.62% / +9.86% / -1.57%</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>-8.713031902113466</v>
-      </c>
-      <c r="K29" t="n">
-        <v>6.807167723513485</v>
-      </c>
-      <c r="L29" t="n">
-        <v>26.1360558999528</v>
-      </c>
-      <c r="M29" t="n">
-        <v>100</v>
-      </c>
-      <c r="N29" t="n">
-        <v>183</v>
-      </c>
-      <c r="O29" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="P29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>22.553</v>
-      </c>
-      <c r="T29" t="n">
-        <v>22.553</v>
-      </c>
-      <c r="U29" t="n">
-        <v>25.692</v>
-      </c>
-      <c r="V29" t="n">
-        <v>15.723</v>
-      </c>
-      <c r="W29" t="n">
-        <v>-9.339</v>
+        <v>-21.293</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A16:W16"/>
     <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A17:W17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="2">

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -742,34 +742,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CWENE.IS, TRMET.IS</t>
+          <t>AKSA.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
+          <t>AKSA.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>71.34932273384752</v>
+        <v>73.91462605481856</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.65% / -2.28%</t>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>28.90742434227913</v>
+        <v>29.3281854651174</v>
       </c>
       <c r="K3" t="n">
         <v>-16.69555354433906</v>
@@ -807,7 +807,7 @@
         <v>25.314</v>
       </c>
       <c r="V3" t="n">
-        <v>-15.653</v>
+        <v>-15.119</v>
       </c>
       <c r="W3" t="n">
         <v>-69.568</v>
@@ -824,68 +824,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>67.66470503641577</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>69.28710330559822</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J4" t="n">
-        <v>27.238264119624</v>
+        <v>29.61687177483288</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.063423217612653</v>
+        <v>-18.47919897889352</v>
       </c>
       <c r="L4" t="n">
-        <v>14.41049705545434</v>
+        <v>22.190831633245</v>
       </c>
       <c r="M4" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>53.1</v>
+        <v>111.6</v>
       </c>
       <c r="O4" t="n">
-        <v>51.4</v>
+        <v>39.6</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>23.105</v>
+        <v>27.762</v>
       </c>
       <c r="T4" t="n">
-        <v>23.105</v>
+        <v>27.762</v>
       </c>
       <c r="U4" t="n">
-        <v>8.699</v>
+        <v>37.084</v>
       </c>
       <c r="V4" t="n">
-        <v>2.761</v>
+        <v>20.736</v>
       </c>
       <c r="W4" t="n">
-        <v>-30.289</v>
+        <v>-46.446</v>
       </c>
     </row>
     <row r="5">
@@ -899,17 +911,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -919,10 +931,10 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>27.238264119624</v>
+        <v>25.31911840398602</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.063423217612653</v>
+        <v>-8.063423217612641</v>
       </c>
       <c r="L5" t="n">
         <v>14.41049705545434</v>
@@ -957,7 +969,7 @@
         <v>8.699</v>
       </c>
       <c r="V5" t="n">
-        <v>2.761</v>
+        <v>2.872</v>
       </c>
       <c r="W5" t="n">
         <v>-30.289</v>
@@ -974,80 +986,68 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CWENE.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>71.34932273384752</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.65% / -2.28%</t>
-        </is>
-      </c>
+        <v>61.9655453107135</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>28.90742434227913</v>
+        <v>32.08371516582042</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.69555354433906</v>
+        <v>1.621821921204969e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>17.11290382444416</v>
+        <v>13.78592482270004</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>162.7</v>
+        <v>24.3</v>
       </c>
       <c r="O6" t="n">
-        <v>43.3</v>
+        <v>63.3</v>
       </c>
       <c r="P6" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>36.941</v>
+        <v>8.218</v>
       </c>
       <c r="T6" t="n">
-        <v>36.941</v>
+        <v>4.976</v>
       </c>
       <c r="U6" t="n">
-        <v>25.314</v>
+        <v>83.73399999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-15.653</v>
+        <v>13.474</v>
       </c>
       <c r="W6" t="n">
-        <v>-69.568</v>
+        <v>-4.893</v>
       </c>
     </row>
     <row r="7">
@@ -1061,68 +1061,80 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>56.53775645557823</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>69.28710330559822</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J7" t="n">
-        <v>27.61399559485631</v>
+        <v>29.61687177483288</v>
       </c>
       <c r="K7" t="n">
-        <v>1.621821921204969e-06</v>
+        <v>-18.47919897889352</v>
       </c>
       <c r="L7" t="n">
-        <v>13.78592482270004</v>
+        <v>22.190831633245</v>
       </c>
       <c r="M7" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>24.3</v>
+        <v>111.6</v>
       </c>
       <c r="O7" t="n">
-        <v>63.3</v>
+        <v>39.6</v>
       </c>
       <c r="P7" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>8.218</v>
+        <v>27.762</v>
       </c>
       <c r="T7" t="n">
-        <v>4.976</v>
+        <v>27.762</v>
       </c>
       <c r="U7" t="n">
-        <v>83.73399999999999</v>
+        <v>37.084</v>
       </c>
       <c r="V7" t="n">
-        <v>13.056</v>
+        <v>20.736</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.893</v>
+        <v>-46.446</v>
       </c>
     </row>
     <row r="8">
@@ -1136,68 +1148,80 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AKSA.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AKSA.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>67.66470503641577</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>73.91462605481856</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
-        <v>27.238264119624</v>
+        <v>29.3281854651174</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.063423217612653</v>
+        <v>-16.69555354433906</v>
       </c>
       <c r="L8" t="n">
-        <v>14.41049705545434</v>
+        <v>17.11290382444416</v>
       </c>
       <c r="M8" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>53.1</v>
+        <v>162.7</v>
       </c>
       <c r="O8" t="n">
-        <v>51.4</v>
+        <v>43.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>23.105</v>
+        <v>36.941</v>
       </c>
       <c r="T8" t="n">
-        <v>23.105</v>
+        <v>36.941</v>
       </c>
       <c r="U8" t="n">
-        <v>8.699</v>
+        <v>25.314</v>
       </c>
       <c r="V8" t="n">
-        <v>2.761</v>
+        <v>-15.119</v>
       </c>
       <c r="W8" t="n">
-        <v>-30.289</v>
+        <v>-69.568</v>
       </c>
     </row>
     <row r="9">
@@ -1216,22 +1240,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>31.91300080326922</v>
+        <v>31.91300080326926</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>19.31957756950657</v>
+        <v>17.64340578198198</v>
       </c>
       <c r="K9" t="n">
         <v>2.302203561121985e-06</v>
@@ -1286,80 +1310,68 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, CWENE.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>44.1931793598139</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>47.7084504688879</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>20.60664105207755</v>
+        <v>25.69738108440036</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.39404112492812</v>
+        <v>-20.72609957575339</v>
       </c>
       <c r="L10" t="n">
-        <v>8.000657219756324</v>
+        <v>11.47600961545611</v>
       </c>
       <c r="M10" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>83.8</v>
+        <v>122.5</v>
       </c>
       <c r="O10" t="n">
-        <v>47.3</v>
+        <v>42.5</v>
       </c>
       <c r="P10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>17.037</v>
+        <v>26.084</v>
       </c>
       <c r="T10" t="n">
-        <v>17.037</v>
+        <v>26.084</v>
       </c>
       <c r="U10" t="n">
-        <v>18.157</v>
+        <v>5.211</v>
       </c>
       <c r="V10" t="n">
-        <v>6.566</v>
+        <v>-6.821</v>
       </c>
       <c r="W10" t="n">
-        <v>-24.265</v>
+        <v>-36.5</v>
       </c>
     </row>
     <row r="11">
@@ -1373,57 +1385,57 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGHOL.IS, CWENE.IS, KCHOL.IS, TKFEN.IS, TRMET.IS</t>
+          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-11 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>39.6760709590217</v>
+        <v>44.1931793598139</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +2.93% / +3.05% / -0.60% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.89% / +24.59% / -0.43%</t>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>20.68188468299766</v>
+        <v>17.47880176656278</v>
       </c>
       <c r="K11" t="n">
-        <v>-14.19875003210586</v>
+        <v>-12.38000262629327</v>
       </c>
       <c r="L11" t="n">
-        <v>8.721900452178899</v>
+        <v>8.000657219756324</v>
       </c>
       <c r="M11" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>156.3</v>
+        <v>83.8</v>
       </c>
       <c r="O11" t="n">
-        <v>45.7</v>
+        <v>47.3</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1431,22 +1443,22 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>20.179</v>
+        <v>17.024</v>
       </c>
       <c r="T11" t="n">
-        <v>20.179</v>
+        <v>17.024</v>
       </c>
       <c r="U11" t="n">
-        <v>3.177</v>
+        <v>18.176</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.691</v>
+        <v>6.63</v>
       </c>
       <c r="W11" t="n">
-        <v>-26.083</v>
+        <v>-24.246</v>
       </c>
     </row>
     <row r="12">
@@ -1465,12 +1477,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1488,14 +1500,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.63% / +3.12% / -1.79% | BRSAN.IS: +9.94% / +12.94% / 0.00% | BSOKE.IS: +6.66% / +8.97% / -0.29%</t>
+          <t>ARCLK.IS: -2.68% / +3.12% / -2.86% | BRSAN.IS: +10.55% / +13.72% / 0.00% | BSOKE.IS: +6.72% / +8.97% / -0.29%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5.100353757880249</v>
+        <v>0.5979844862621819</v>
       </c>
       <c r="K12" t="n">
-        <v>15.66519674594435</v>
+        <v>15.13867124891788</v>
       </c>
       <c r="L12" t="n">
         <v>14.82627592190883</v>
@@ -1527,13 +1539,13 @@
         <v>14.383</v>
       </c>
       <c r="U12" t="n">
-        <v>45.915</v>
+        <v>45.25</v>
       </c>
       <c r="V12" t="n">
-        <v>32.49</v>
+        <v>33.196</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.26</v>
+        <v>-13.924</v>
       </c>
     </row>
     <row r="13">
@@ -1552,37 +1564,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>8.623920580589118</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>8.623920580589095</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-8.516992429863468</v>
+        <v>-8.261163935788185</v>
       </c>
       <c r="K13" t="n">
-        <v>7.569461404868649</v>
+        <v>7.583805912323638</v>
       </c>
       <c r="L13" t="n">
         <v>16.53177272942414</v>
@@ -1591,21 +1591,21 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>84.8</v>
+        <v>84.3</v>
       </c>
       <c r="O13" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>15.149</v>
@@ -1614,13 +1614,13 @@
         <v>15.149</v>
       </c>
       <c r="U13" t="n">
-        <v>31.508</v>
+        <v>31.525</v>
       </c>
       <c r="V13" t="n">
-        <v>24.09</v>
+        <v>24.116</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.917</v>
+        <v>-4.899</v>
       </c>
     </row>
     <row r="14">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|Bvolatilite</t>
+          <t>T1_genislik_skor|E30|S5|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|Bvolatilite</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BRYAT.IS, TKFEN.IS</t>
+          <t>AKSA.IS, ALARK.IS, BSOKE.IS, CWENE.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BRYAT.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+          <t>AKSA.IS: 2026-08-13 | ALARK.IS: 2026-08-11 | BSOKE.IS: 2026-08-05 | CWENE.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.314240480464827</v>
+        <v>6.76395532820866</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BRYAT.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | ALARK.IS: -2.89% / +0.10% / -3.35% | BSOKE.IS: +2.34% / +4.50% / -2.02% | CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-6.347935434616581</v>
+        <v>-14.84944944967732</v>
       </c>
       <c r="K14" t="n">
-        <v>3.239577297814389</v>
+        <v>2.294090072135879</v>
       </c>
       <c r="L14" t="n">
-        <v>13.58292314070337</v>
+        <v>29.71908457756942</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>304.6</v>
+        <v>201.4</v>
       </c>
       <c r="O14" t="n">
-        <v>46.9</v>
+        <v>46.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>10.3</v>
+        <v>13.8</v>
       </c>
       <c r="T14" t="n">
-        <v>10.3</v>
+        <v>13.8</v>
       </c>
       <c r="U14" t="n">
-        <v>17.958</v>
+        <v>46.505</v>
       </c>
       <c r="V14" t="n">
-        <v>6.874</v>
+        <v>45.697</v>
       </c>
       <c r="W14" t="n">
-        <v>-8.095000000000001</v>
+        <v>-13.935</v>
       </c>
     </row>
     <row r="16">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 | 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1852,34 +1852,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CWENE.IS, TRMET.IS</t>
+          <t>AKSA.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-12 | TRMET.IS: 2026-08-11</t>
+          <t>AKSA.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>71.34932273384752</v>
+        <v>73.91462605481856</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.65% / -2.28%</t>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>28.90742434227913</v>
+        <v>29.3281854651174</v>
       </c>
       <c r="K18" t="n">
         <v>-16.69555354433906</v>
@@ -1917,7 +1917,7 @@
         <v>25.314</v>
       </c>
       <c r="V18" t="n">
-        <v>-15.653</v>
+        <v>-15.119</v>
       </c>
       <c r="W18" t="n">
         <v>-69.568</v>
@@ -1931,73 +1931,85 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 | 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H19" t="n">
-        <v>67.66470503641577</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>69.28710330559822</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J19" t="n">
-        <v>27.238264119624</v>
+        <v>29.61687177483288</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.063423217612653</v>
+        <v>-18.47919897889352</v>
       </c>
       <c r="L19" t="n">
-        <v>14.41049705545434</v>
+        <v>22.190831633245</v>
       </c>
       <c r="M19" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>53.1</v>
+        <v>111.6</v>
       </c>
       <c r="O19" t="n">
-        <v>51.4</v>
+        <v>39.6</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>23.105</v>
+        <v>27.762</v>
       </c>
       <c r="T19" t="n">
-        <v>23.105</v>
+        <v>27.762</v>
       </c>
       <c r="U19" t="n">
-        <v>8.699</v>
+        <v>37.084</v>
       </c>
       <c r="V19" t="n">
-        <v>2.761</v>
+        <v>20.736</v>
       </c>
       <c r="W19" t="n">
-        <v>-30.289</v>
+        <v>-46.446</v>
       </c>
     </row>
     <row r="20">
@@ -2013,17 +2025,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2033,10 +2045,10 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>27.238264119624</v>
+        <v>25.31911840398602</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.063423217612653</v>
+        <v>-8.063423217612641</v>
       </c>
       <c r="L20" t="n">
         <v>14.41049705545434</v>
@@ -2071,7 +2083,7 @@
         <v>8.699</v>
       </c>
       <c r="V20" t="n">
-        <v>2.761</v>
+        <v>2.872</v>
       </c>
       <c r="W20" t="n">
         <v>-30.289</v>
@@ -2085,7 +2097,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2095,22 +2107,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>56.53775645557823</v>
+        <v>61.9655453107135</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>27.61399559485631</v>
+        <v>32.08371516582042</v>
       </c>
       <c r="K21" t="n">
         <v>1.621821921204969e-06</v>
@@ -2148,7 +2160,7 @@
         <v>83.73399999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>13.056</v>
+        <v>13.474</v>
       </c>
       <c r="W21" t="n">
         <v>-4.893</v>
@@ -2167,80 +2179,68 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, CWENE.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>44.1931793598139</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>47.7084504688879</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>20.60664105207755</v>
+        <v>25.69738108440036</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.39404112492812</v>
+        <v>-20.72609957575339</v>
       </c>
       <c r="L22" t="n">
-        <v>8.000657219756324</v>
+        <v>11.47600961545611</v>
       </c>
       <c r="M22" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>83.8</v>
+        <v>122.5</v>
       </c>
       <c r="O22" t="n">
-        <v>47.3</v>
+        <v>42.5</v>
       </c>
       <c r="P22" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>17.037</v>
+        <v>26.084</v>
       </c>
       <c r="T22" t="n">
-        <v>17.037</v>
+        <v>26.084</v>
       </c>
       <c r="U22" t="n">
-        <v>18.157</v>
+        <v>5.211</v>
       </c>
       <c r="V22" t="n">
-        <v>6.566</v>
+        <v>-6.821</v>
       </c>
       <c r="W22" t="n">
-        <v>-24.265</v>
+        <v>-36.5</v>
       </c>
     </row>
     <row r="23">
@@ -2256,57 +2256,57 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite</t>
+          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AGHOL.IS, CWENE.IS, KCHOL.IS, TKFEN.IS, TRMET.IS</t>
+          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-12 | CWENE.IS: 2026-08-12 | KCHOL.IS: 2026-08-11 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>39.6760709590217</v>
+        <v>44.1931793598139</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | CWENE.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: +2.93% / +3.05% / -0.60% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.89% / +24.59% / -0.43%</t>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>20.68188468299766</v>
+        <v>17.47880176656278</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.19875003210586</v>
+        <v>-12.38000262629327</v>
       </c>
       <c r="L23" t="n">
-        <v>8.721900452178899</v>
+        <v>8.000657219756324</v>
       </c>
       <c r="M23" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>156.3</v>
+        <v>83.8</v>
       </c>
       <c r="O23" t="n">
-        <v>45.7</v>
+        <v>47.3</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2314,22 +2314,22 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
-        <v>20.179</v>
+        <v>17.024</v>
       </c>
       <c r="T23" t="n">
-        <v>20.179</v>
+        <v>17.024</v>
       </c>
       <c r="U23" t="n">
-        <v>3.177</v>
+        <v>18.176</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.691</v>
+        <v>6.63</v>
       </c>
       <c r="W23" t="n">
-        <v>-26.083</v>
+        <v>-24.246</v>
       </c>
     </row>
     <row r="24">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>31.91300080326922</v>
+        <v>31.91300080326926</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>19.31957756950657</v>
+        <v>17.64340578198198</v>
       </c>
       <c r="K24" t="n">
         <v>2.302203561121985e-06</v>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2450,14 +2450,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -0.63% / +3.12% / -1.79% | BRSAN.IS: +9.94% / +12.94% / 0.00% | BSOKE.IS: +6.66% / +8.97% / -0.29%</t>
+          <t>ARCLK.IS: -2.68% / +3.12% / -2.86% | BRSAN.IS: +10.55% / +13.72% / 0.00% | BSOKE.IS: +6.72% / +8.97% / -0.29%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>5.100353757880249</v>
+        <v>0.5979844862621819</v>
       </c>
       <c r="K25" t="n">
-        <v>15.66519674594435</v>
+        <v>15.13867124891788</v>
       </c>
       <c r="L25" t="n">
         <v>14.82627592190883</v>
@@ -2489,13 +2489,13 @@
         <v>14.383</v>
       </c>
       <c r="U25" t="n">
-        <v>45.915</v>
+        <v>45.25</v>
       </c>
       <c r="V25" t="n">
-        <v>32.49</v>
+        <v>33.196</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.26</v>
+        <v>-13.924</v>
       </c>
     </row>
     <row r="26">
@@ -2516,37 +2516,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>8.623920580589118</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>8.623920580589095</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>-8.516992429863468</v>
+        <v>-8.261163935788185</v>
       </c>
       <c r="K26" t="n">
-        <v>7.569461404868649</v>
+        <v>7.583805912323638</v>
       </c>
       <c r="L26" t="n">
         <v>16.53177272942414</v>
@@ -2555,21 +2543,21 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>84.8</v>
+        <v>84.3</v>
       </c>
       <c r="O26" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>15.149</v>
@@ -2578,13 +2566,13 @@
         <v>15.149</v>
       </c>
       <c r="U26" t="n">
-        <v>31.508</v>
+        <v>31.525</v>
       </c>
       <c r="V26" t="n">
-        <v>24.09</v>
+        <v>24.116</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.917</v>
+        <v>-4.899</v>
       </c>
     </row>
     <row r="27">
@@ -2600,57 +2588,57 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|Bvolatilite</t>
+          <t>T1_genislik_skor|E30|S5|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|Bvolatilite</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BRYAT.IS, TKFEN.IS</t>
+          <t>AKSA.IS, ALARK.IS, BSOKE.IS, CWENE.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BRYAT.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+          <t>AKSA.IS: 2026-08-13 | ALARK.IS: 2026-08-11 | BSOKE.IS: 2026-08-05 | CWENE.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.314240480464827</v>
+        <v>6.76395532820866</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRYAT.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | ALARK.IS: -2.89% / +0.10% / -3.35% | BSOKE.IS: +2.34% / +4.50% / -2.02% | CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-6.347935434616581</v>
+        <v>-14.84944944967732</v>
       </c>
       <c r="K27" t="n">
-        <v>3.239577297814389</v>
+        <v>2.294090072135879</v>
       </c>
       <c r="L27" t="n">
-        <v>13.58292314070337</v>
+        <v>29.71908457756942</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>304.6</v>
+        <v>201.4</v>
       </c>
       <c r="O27" t="n">
-        <v>46.9</v>
+        <v>46.1</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2658,22 +2646,22 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>10.3</v>
+        <v>13.8</v>
       </c>
       <c r="T27" t="n">
-        <v>10.3</v>
+        <v>13.8</v>
       </c>
       <c r="U27" t="n">
-        <v>17.958</v>
+        <v>46.505</v>
       </c>
       <c r="V27" t="n">
-        <v>6.874</v>
+        <v>45.697</v>
       </c>
       <c r="W27" t="n">
-        <v>-8.095000000000001</v>
+        <v>-13.935</v>
       </c>
     </row>
   </sheetData>
@@ -2858,68 +2846,80 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>91.56479261353148</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>95.17942072734355</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J3" t="n">
-        <v>23.39595923130722</v>
+        <v>32.50943475287353</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.34044906797636</v>
+        <v>-18.96868434006504</v>
       </c>
       <c r="L3" t="n">
-        <v>20.6096939559789</v>
+        <v>19.87241420107954</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>74.90000000000001</v>
+        <v>101.2</v>
       </c>
       <c r="O3" t="n">
-        <v>43.7</v>
+        <v>41.7</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>28.897</v>
+        <v>29.384</v>
       </c>
       <c r="T3" t="n">
-        <v>28.897</v>
+        <v>29.384</v>
       </c>
       <c r="U3" t="n">
-        <v>6.931</v>
+        <v>-7.727</v>
       </c>
       <c r="V3" t="n">
-        <v>18.912</v>
+        <v>-0.542</v>
       </c>
       <c r="W3" t="n">
-        <v>-33.344</v>
+        <v>-38.397</v>
       </c>
     </row>
     <row r="4">
@@ -2933,30 +2933,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>91.56479261353148</v>
+        <v>94.61905079674457</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>23.39595923130722</v>
+        <v>26.23454465636599</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.34044906797636</v>
+        <v>-13.34044906797633</v>
       </c>
       <c r="L4" t="n">
         <v>20.6096939559789</v>
@@ -2991,7 +2991,7 @@
         <v>6.931</v>
       </c>
       <c r="V4" t="n">
-        <v>18.912</v>
+        <v>18.369</v>
       </c>
       <c r="W4" t="n">
         <v>-33.344</v>
@@ -3008,80 +3008,68 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>87.45314762918606</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>94.61905079674457</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>25.04605608184003</v>
+        <v>26.23454465636599</v>
       </c>
       <c r="K5" t="n">
-        <v>-17.41592720282232</v>
+        <v>-13.34044906797633</v>
       </c>
       <c r="L5" t="n">
-        <v>19.87241420107954</v>
+        <v>20.6096939559789</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>101.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>41.7</v>
+        <v>43.7</v>
       </c>
       <c r="P5" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>28.429</v>
+        <v>28.897</v>
       </c>
       <c r="T5" t="n">
-        <v>28.429</v>
+        <v>28.897</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.959</v>
+        <v>6.931</v>
       </c>
       <c r="V5" t="n">
-        <v>2.872</v>
+        <v>18.369</v>
       </c>
       <c r="W5" t="n">
-        <v>-36.628</v>
+        <v>-33.344</v>
       </c>
     </row>
     <row r="6">
@@ -3095,68 +3083,80 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>73.75964826688029</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>70.53333624874938</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
-        <v>32.17500090460663</v>
+        <v>34.82253143286685</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.75900002341578e-06</v>
+        <v>-26.14753157146566</v>
       </c>
       <c r="L6" t="n">
-        <v>10.93171342838547</v>
+        <v>14.51092369816588</v>
       </c>
       <c r="M6" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>41.7</v>
+        <v>104.2</v>
       </c>
       <c r="O6" t="n">
-        <v>52.4</v>
+        <v>39.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>15.232</v>
+        <v>36.603</v>
       </c>
       <c r="T6" t="n">
-        <v>15.232</v>
+        <v>36.603</v>
       </c>
       <c r="U6" t="n">
-        <v>69.63200000000001</v>
+        <v>-10.563</v>
       </c>
       <c r="V6" t="n">
-        <v>45.816</v>
+        <v>-18.259</v>
       </c>
       <c r="W6" t="n">
-        <v>-16.27</v>
+        <v>-51.636</v>
       </c>
     </row>
     <row r="7">
@@ -3170,17 +3170,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>32.17500090460663</v>
+        <v>32.34918865075789</v>
       </c>
       <c r="K7" t="n">
         <v>-1.75900002341578e-06</v>
@@ -3228,7 +3228,7 @@
         <v>69.63200000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>45.816</v>
+        <v>46.229</v>
       </c>
       <c r="W7" t="n">
         <v>-16.27</v>
@@ -3245,80 +3245,68 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>66.30149434982813</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>73.75964826688029</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>30.34761773567121</v>
+        <v>32.34918865075789</v>
       </c>
       <c r="K8" t="n">
-        <v>-24.73397862399341</v>
+        <v>-1.75900002341578e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>14.51092595374885</v>
+        <v>10.93171342838547</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N8" t="n">
-        <v>102.7</v>
+        <v>41.7</v>
       </c>
       <c r="O8" t="n">
-        <v>39.6</v>
+        <v>52.4</v>
       </c>
       <c r="P8" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>35.388</v>
+        <v>15.232</v>
       </c>
       <c r="T8" t="n">
-        <v>35.388</v>
+        <v>15.232</v>
       </c>
       <c r="U8" t="n">
-        <v>-8.849</v>
+        <v>69.63200000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-15.451</v>
+        <v>46.229</v>
       </c>
       <c r="W8" t="n">
-        <v>-49.923</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="9">
@@ -3337,37 +3325,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BRSAN.IS, BSOKE.IS</t>
+          <t>AGHOL.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>41.94189944051843</v>
+        <v>41.94189944051841</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19.29474557819859</v>
+        <v>23.19304514092613</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.804599201929793</v>
+        <v>-5.90358254997626</v>
       </c>
       <c r="L9" t="n">
         <v>5.815920071163994</v>
@@ -3393,19 +3381,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>11.941</v>
+        <v>13.863</v>
       </c>
       <c r="T9" t="n">
-        <v>11.941</v>
+        <v>13.863</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.395</v>
+        <v>-9.416</v>
       </c>
       <c r="V9" t="n">
-        <v>-9.042999999999999</v>
+        <v>-11.028</v>
       </c>
       <c r="W9" t="n">
-        <v>-12.558</v>
+        <v>-14.579</v>
       </c>
     </row>
     <row r="10">
@@ -3419,80 +3407,68 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|Bvolatilite</t>
+          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, BSOKE.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>32.22665657857966</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +9.47% / +24.13% / -0.52%</t>
-        </is>
-      </c>
+        <v>38.08584121207757</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>15.87125250627721</v>
+        <v>14.85812229550152</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.545565760942496</v>
+        <v>-10.35969645108858</v>
       </c>
       <c r="L10" t="n">
-        <v>4.152173979569406</v>
+        <v>3.605272693289541</v>
       </c>
       <c r="M10" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N10" t="n">
-        <v>61</v>
+        <v>39.2</v>
       </c>
       <c r="O10" t="n">
-        <v>45.5</v>
+        <v>44.3</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>18.978</v>
+        <v>22.794</v>
       </c>
       <c r="T10" t="n">
-        <v>18.978</v>
+        <v>22.794</v>
       </c>
       <c r="U10" t="n">
-        <v>-14.062</v>
+        <v>-17.177</v>
       </c>
       <c r="V10" t="n">
-        <v>-16.873</v>
+        <v>-19.815</v>
       </c>
       <c r="W10" t="n">
-        <v>-20.129</v>
+        <v>-24.453</v>
       </c>
     </row>
     <row r="11">
@@ -3511,12 +3487,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3526,7 +3502,7 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>32.17500090460663</v>
+        <v>32.34918865075789</v>
       </c>
       <c r="K11" t="n">
         <v>-1.75900002341578e-06</v>
@@ -3564,7 +3540,7 @@
         <v>69.63200000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>45.816</v>
+        <v>46.229</v>
       </c>
       <c r="W11" t="n">
         <v>-16.27</v>
@@ -3586,22 +3562,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>8.326900458734364</v>
+        <v>8.326900458734343</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-8.338698318262827</v>
+        <v>-8.030096457283253</v>
       </c>
       <c r="K12" t="n">
         <v>11.24844055823626</v>
@@ -3639,7 +3615,7 @@
         <v>32.693</v>
       </c>
       <c r="V12" t="n">
-        <v>17.594</v>
+        <v>17.425</v>
       </c>
       <c r="W12" t="n">
         <v>-5.555</v>
@@ -3661,37 +3637,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEFES.IS, BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS</t>
+          <t>BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS, ENKAI.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AEFES.IS: 2026-08-12 | BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-12 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-13 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05 | ENKAI.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12.66702235000581</v>
+        <v>13.96656699373973</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +0.32% / +1.94% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.89% / +4.22% / -2.40% | ECILC.IS: +9.62% / +9.86% / -1.57%</t>
+          <t>BRSAN.IS: +0.84% / +3.73% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.91% / +4.22% / -2.40% | ECILC.IS: +11.67% / +13.93% / -1.57% | ENKAI.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-8.680214783453089</v>
+        <v>-7.503658754890596</v>
       </c>
       <c r="K13" t="n">
-        <v>6.806799949189068</v>
+        <v>6.799316168838421</v>
       </c>
       <c r="L13" t="n">
         <v>26.13605890970743</v>
@@ -3723,13 +3699,13 @@
         <v>21.464</v>
       </c>
       <c r="U13" t="n">
-        <v>27.564</v>
+        <v>27.556</v>
       </c>
       <c r="V13" t="n">
-        <v>17.35</v>
+        <v>17.534</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.578</v>
+        <v>-7.587</v>
       </c>
     </row>
     <row r="14">
@@ -3743,45 +3719,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1852998653190774</v>
+        <v>45.0589059523848</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-22.00780799603813</v>
+        <v>3.452723024503923</v>
       </c>
       <c r="K14" t="n">
-        <v>4.971426232468645</v>
+        <v>4.973709971745888</v>
       </c>
       <c r="L14" t="n">
-        <v>50.19196082132959</v>
+        <v>28.80374524525355</v>
       </c>
       <c r="M14" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>47.6</v>
+        <v>64.5</v>
       </c>
       <c r="O14" t="n">
-        <v>49</v>
+        <v>41.5</v>
       </c>
       <c r="P14" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3792,19 +3768,19 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>12.186</v>
+        <v>18.867</v>
       </c>
       <c r="T14" t="n">
-        <v>12.186</v>
+        <v>18.867</v>
       </c>
       <c r="U14" t="n">
-        <v>59.874</v>
+        <v>78.093</v>
       </c>
       <c r="V14" t="n">
-        <v>42.782</v>
+        <v>43.297</v>
       </c>
       <c r="W14" t="n">
-        <v>-21.293</v>
+        <v>-24.086</v>
       </c>
     </row>
     <row r="16">
@@ -3944,68 +3920,80 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H18" t="n">
-        <v>91.56479261353148</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>95.17942072734355</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J18" t="n">
-        <v>23.39595923130722</v>
+        <v>32.50943475287353</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.34044906797636</v>
+        <v>-18.96868434006504</v>
       </c>
       <c r="L18" t="n">
-        <v>20.6096939559789</v>
+        <v>19.87241420107954</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>74.90000000000001</v>
+        <v>101.2</v>
       </c>
       <c r="O18" t="n">
-        <v>43.7</v>
+        <v>41.7</v>
       </c>
       <c r="P18" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>28.897</v>
+        <v>29.384</v>
       </c>
       <c r="T18" t="n">
-        <v>28.897</v>
+        <v>29.384</v>
       </c>
       <c r="U18" t="n">
-        <v>6.931</v>
+        <v>-7.727</v>
       </c>
       <c r="V18" t="n">
-        <v>18.912</v>
+        <v>-0.542</v>
       </c>
       <c r="W18" t="n">
-        <v>-33.344</v>
+        <v>-38.397</v>
       </c>
     </row>
     <row r="19">
@@ -4021,30 +4009,30 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>91.56479261353148</v>
+        <v>94.61905079674457</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>23.39595923130722</v>
+        <v>26.23454465636599</v>
       </c>
       <c r="K19" t="n">
-        <v>-13.34044906797636</v>
+        <v>-13.34044906797633</v>
       </c>
       <c r="L19" t="n">
         <v>20.6096939559789</v>
@@ -4079,7 +4067,7 @@
         <v>6.931</v>
       </c>
       <c r="V19" t="n">
-        <v>18.912</v>
+        <v>18.369</v>
       </c>
       <c r="W19" t="n">
         <v>-33.344</v>
@@ -4098,80 +4086,68 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>87.45314762918606</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>94.61905079674457</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>25.04605608184003</v>
+        <v>26.23454465636599</v>
       </c>
       <c r="K20" t="n">
-        <v>-17.41592720282232</v>
+        <v>-13.34044906797633</v>
       </c>
       <c r="L20" t="n">
-        <v>19.87241420107954</v>
+        <v>20.6096939559789</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>101.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>41.7</v>
+        <v>43.7</v>
       </c>
       <c r="P20" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>28.429</v>
+        <v>28.897</v>
       </c>
       <c r="T20" t="n">
-        <v>28.429</v>
+        <v>28.897</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.959</v>
+        <v>6.931</v>
       </c>
       <c r="V20" t="n">
-        <v>2.872</v>
+        <v>18.369</v>
       </c>
       <c r="W20" t="n">
-        <v>-36.628</v>
+        <v>-33.344</v>
       </c>
     </row>
     <row r="21">
@@ -4182,7 +4158,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1 | 3</t>
+          <t>2 | 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4192,12 +4168,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4207,7 +4183,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>32.17500090460663</v>
+        <v>32.34918865075789</v>
       </c>
       <c r="K21" t="n">
         <v>-1.75900002341578e-06</v>
@@ -4245,7 +4221,7 @@
         <v>69.63200000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>45.816</v>
+        <v>46.229</v>
       </c>
       <c r="W21" t="n">
         <v>-16.27</v>
@@ -4259,7 +4235,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4269,12 +4245,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4284,7 +4260,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>32.17500090460663</v>
+        <v>32.34918865075789</v>
       </c>
       <c r="K22" t="n">
         <v>-1.75900002341578e-06</v>
@@ -4322,7 +4298,7 @@
         <v>69.63200000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>45.816</v>
+        <v>46.229</v>
       </c>
       <c r="W22" t="n">
         <v>-16.27</v>
@@ -4336,59 +4312,59 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>AGHOL.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-12</t>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>66.30149434982813</v>
+        <v>70.53333624874938</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>30.34761773567121</v>
+        <v>34.82253143286685</v>
       </c>
       <c r="K23" t="n">
-        <v>-24.73397862399341</v>
+        <v>-26.14753157146566</v>
       </c>
       <c r="L23" t="n">
-        <v>14.51092595374885</v>
+        <v>14.51092369816588</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>102.7</v>
+        <v>104.2</v>
       </c>
       <c r="O23" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="P23" t="n">
         <v>3.8</v>
@@ -4402,108 +4378,96 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>35.388</v>
+        <v>36.603</v>
       </c>
       <c r="T23" t="n">
-        <v>35.388</v>
+        <v>36.603</v>
       </c>
       <c r="U23" t="n">
-        <v>-8.849</v>
+        <v>-10.563</v>
       </c>
       <c r="V23" t="n">
-        <v>-15.451</v>
+        <v>-18.259</v>
       </c>
       <c r="W23" t="n">
-        <v>-49.923</v>
+        <v>-51.636</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, BSOKE.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>41.94189944051843</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>45.0589059523848</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>19.29474557819859</v>
+        <v>3.452723024503923</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.804599201929793</v>
+        <v>4.973709971745888</v>
       </c>
       <c r="L24" t="n">
-        <v>5.815920071163994</v>
+        <v>28.80374524525355</v>
       </c>
       <c r="M24" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>32.2</v>
+        <v>64.5</v>
       </c>
       <c r="O24" t="n">
-        <v>56.9</v>
+        <v>41.5</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>11.941</v>
+        <v>18.867</v>
       </c>
       <c r="T24" t="n">
-        <v>11.941</v>
+        <v>18.867</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.395</v>
+        <v>78.093</v>
       </c>
       <c r="V24" t="n">
-        <v>-9.042999999999999</v>
+        <v>43.297</v>
       </c>
       <c r="W24" t="n">
-        <v>-12.558</v>
+        <v>-24.086</v>
       </c>
     </row>
     <row r="25">
@@ -4514,62 +4478,62 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|Bvolatilite</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BRSAN.IS, BSOKE.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
+          <t>AGHOL.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | BSOKE.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>32.22665657857966</v>
+        <v>41.94189944051841</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +9.47% / +24.13% / -0.52%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>15.87125250627721</v>
+        <v>23.19304514092613</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.545565760942496</v>
+        <v>-5.90358254997626</v>
       </c>
       <c r="L25" t="n">
-        <v>4.152173979569406</v>
+        <v>5.815920071163994</v>
       </c>
       <c r="M25" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>61</v>
+        <v>32.2</v>
       </c>
       <c r="O25" t="n">
-        <v>45.5</v>
+        <v>56.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4577,28 +4541,28 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>18.978</v>
+        <v>13.863</v>
       </c>
       <c r="T25" t="n">
-        <v>18.978</v>
+        <v>13.863</v>
       </c>
       <c r="U25" t="n">
-        <v>-14.062</v>
+        <v>-9.416</v>
       </c>
       <c r="V25" t="n">
-        <v>-16.873</v>
+        <v>-11.028</v>
       </c>
       <c r="W25" t="n">
-        <v>-20.129</v>
+        <v>-14.579</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4608,80 +4572,68 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>AEFES.IS, BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>AEFES.IS: 2026-08-12 | BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-12 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>12.66702235000581</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>AEFES.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +0.32% / +1.94% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.89% / +4.22% / -2.40% | ECILC.IS: +9.62% / +9.86% / -1.57%</t>
-        </is>
-      </c>
+        <v>38.08584121207757</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>-8.680214783453089</v>
+        <v>14.85812229550152</v>
       </c>
       <c r="K26" t="n">
-        <v>6.806799949189068</v>
+        <v>-10.35969645108858</v>
       </c>
       <c r="L26" t="n">
-        <v>26.13605890970743</v>
+        <v>3.605272693289541</v>
       </c>
       <c r="M26" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N26" t="n">
-        <v>175.1</v>
+        <v>39.2</v>
       </c>
       <c r="O26" t="n">
-        <v>43.9</v>
+        <v>44.3</v>
       </c>
       <c r="P26" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>21.464</v>
+        <v>22.794</v>
       </c>
       <c r="T26" t="n">
-        <v>21.464</v>
+        <v>22.794</v>
       </c>
       <c r="U26" t="n">
-        <v>27.564</v>
+        <v>-17.177</v>
       </c>
       <c r="V26" t="n">
-        <v>17.35</v>
+        <v>-19.815</v>
       </c>
       <c r="W26" t="n">
-        <v>-7.578</v>
+        <v>-24.453</v>
       </c>
     </row>
     <row r="27">
@@ -4692,73 +4644,85 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS, ENKAI.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-13 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05 | ENKAI.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H27" t="n">
-        <v>8.326900458734364</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>13.96656699373973</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +0.84% / +3.73% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.91% / +4.22% / -2.40% | ECILC.IS: +11.67% / +13.93% / -1.57% | ENKAI.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>-8.338698318262827</v>
+        <v>-7.503658754890596</v>
       </c>
       <c r="K27" t="n">
-        <v>11.24844055823626</v>
+        <v>6.799316168838421</v>
       </c>
       <c r="L27" t="n">
-        <v>15.1193724336431</v>
+        <v>26.13605890970743</v>
       </c>
       <c r="M27" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>39.7</v>
+        <v>175.1</v>
       </c>
       <c r="O27" t="n">
-        <v>45</v>
+        <v>43.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>12.679</v>
+        <v>21.464</v>
       </c>
       <c r="T27" t="n">
-        <v>10.364</v>
+        <v>21.464</v>
       </c>
       <c r="U27" t="n">
-        <v>32.693</v>
+        <v>27.556</v>
       </c>
       <c r="V27" t="n">
-        <v>17.594</v>
+        <v>17.534</v>
       </c>
       <c r="W27" t="n">
-        <v>-5.555</v>
+        <v>-7.587</v>
       </c>
     </row>
     <row r="28">
@@ -4769,50 +4733,50 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|coklu_zarf</t>
+          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0.1852998653190774</v>
+        <v>8.326900458734343</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>-22.00780799603813</v>
+        <v>-8.030096457283253</v>
       </c>
       <c r="K28" t="n">
-        <v>4.971426232468645</v>
+        <v>11.24844055823626</v>
       </c>
       <c r="L28" t="n">
-        <v>50.19196082132959</v>
+        <v>15.1193724336431</v>
       </c>
       <c r="M28" t="n">
-        <v>83.33333333333334</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N28" t="n">
-        <v>47.6</v>
+        <v>39.7</v>
       </c>
       <c r="O28" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="P28" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4823,19 +4787,19 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>12.186</v>
+        <v>12.679</v>
       </c>
       <c r="T28" t="n">
-        <v>12.186</v>
+        <v>10.364</v>
       </c>
       <c r="U28" t="n">
-        <v>59.874</v>
+        <v>32.693</v>
       </c>
       <c r="V28" t="n">
-        <v>42.782</v>
+        <v>17.425</v>
       </c>
       <c r="W28" t="n">
-        <v>-21.293</v>
+        <v>-5.555</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W27" headerRowCount="1">
-  <autoFilter ref="A17:W27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W26" headerRowCount="1">
+  <autoFilter ref="A17:W26"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -254,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W28" headerRowCount="1">
-  <autoFilter ref="A17:W28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W26" headerRowCount="1">
+  <autoFilter ref="A17:W26"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -574,20 +574,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -750,67 +750,55 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AKSA.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>73.91462605481856</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
-        </is>
-      </c>
+        <v>71.7096707191417</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>29.3281854651174</v>
+        <v>10.52140217505859</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.69555354433906</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>17.11290382444416</v>
+        <v>25.61349479378329</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N3" t="n">
-        <v>162.7</v>
+        <v>49.6</v>
       </c>
       <c r="O3" t="n">
-        <v>43.3</v>
+        <v>42</v>
       </c>
       <c r="P3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>36.941</v>
+        <v>11.01</v>
       </c>
       <c r="T3" t="n">
-        <v>36.941</v>
+        <v>10.869</v>
       </c>
       <c r="U3" t="n">
-        <v>25.314</v>
+        <v>140.475</v>
       </c>
       <c r="V3" t="n">
-        <v>-15.119</v>
+        <v>68.77200000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>-69.568</v>
+        <v>-28.954</v>
       </c>
     </row>
     <row r="4">
@@ -824,7 +812,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -837,67 +825,55 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>69.28710330559822</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>71.14835325524578</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>29.61687177483288</v>
+        <v>37.83905010537829</v>
       </c>
       <c r="K4" t="n">
-        <v>-18.47919897889352</v>
+        <v>-2.929523572966308</v>
       </c>
       <c r="L4" t="n">
-        <v>22.190831633245</v>
+        <v>12.6166884158664</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N4" t="n">
-        <v>111.6</v>
+        <v>57.5</v>
       </c>
       <c r="O4" t="n">
-        <v>39.6</v>
+        <v>56.9</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>27.762</v>
+        <v>11.453</v>
       </c>
       <c r="T4" t="n">
-        <v>27.762</v>
+        <v>11.453</v>
       </c>
       <c r="U4" t="n">
-        <v>37.084</v>
+        <v>94.13200000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>20.736</v>
+        <v>12.087</v>
       </c>
       <c r="W4" t="n">
-        <v>-46.446</v>
+        <v>-20.494</v>
       </c>
     </row>
     <row r="5">
@@ -911,7 +887,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -924,55 +900,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, CWENE.IS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | CWENE.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>67.66470503641577</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>67.61086137129925</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.58% / +3.42% / -1.11% | CWENE.IS: -2.43% / +0.00% / -3.06%</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>25.31911840398602</v>
+        <v>23.38198980936981</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.063423217612641</v>
+        <v>-21.027470517574</v>
       </c>
       <c r="L5" t="n">
-        <v>14.41049705545434</v>
+        <v>17.05327546391042</v>
       </c>
       <c r="M5" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>53.1</v>
+        <v>136.4</v>
       </c>
       <c r="O5" t="n">
-        <v>51.4</v>
+        <v>48</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>23.105</v>
+        <v>30.946</v>
       </c>
       <c r="T5" t="n">
-        <v>23.105</v>
+        <v>30.946</v>
       </c>
       <c r="U5" t="n">
-        <v>8.699</v>
+        <v>48.388</v>
       </c>
       <c r="V5" t="n">
-        <v>2.872</v>
+        <v>8.683999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-30.289</v>
+        <v>-66.497</v>
       </c>
     </row>
     <row r="6">
@@ -986,7 +974,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
+          <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1002,29 +990,29 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>61.9655453107135</v>
+        <v>71.14835325524578</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>32.08371516582042</v>
+        <v>37.83905010537829</v>
       </c>
       <c r="K6" t="n">
-        <v>1.621821921204969e-06</v>
+        <v>-2.929523572966308</v>
       </c>
       <c r="L6" t="n">
-        <v>13.78592482270004</v>
+        <v>12.6166884158664</v>
       </c>
       <c r="M6" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>24.3</v>
+        <v>57.5</v>
       </c>
       <c r="O6" t="n">
-        <v>63.3</v>
+        <v>56.9</v>
       </c>
       <c r="P6" t="n">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1035,19 +1023,19 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>8.218</v>
+        <v>11.453</v>
       </c>
       <c r="T6" t="n">
-        <v>4.976</v>
+        <v>11.453</v>
       </c>
       <c r="U6" t="n">
-        <v>83.73399999999999</v>
+        <v>94.13200000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>13.474</v>
+        <v>12.087</v>
       </c>
       <c r="W6" t="n">
-        <v>-4.893</v>
+        <v>-20.494</v>
       </c>
     </row>
     <row r="7">
@@ -1061,7 +1049,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1074,67 +1062,55 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>69.28710330559822</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>60.15988621066983</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>29.61687177483288</v>
+        <v>29.41081527100167</v>
       </c>
       <c r="K7" t="n">
-        <v>-18.47919897889352</v>
+        <v>-0.4732772020725418</v>
       </c>
       <c r="L7" t="n">
-        <v>22.190831633245</v>
+        <v>12.39638337363852</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N7" t="n">
-        <v>111.6</v>
+        <v>21.3</v>
       </c>
       <c r="O7" t="n">
-        <v>39.6</v>
+        <v>55.8</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>27.762</v>
+        <v>12.717</v>
       </c>
       <c r="T7" t="n">
-        <v>27.762</v>
+        <v>12.717</v>
       </c>
       <c r="U7" t="n">
-        <v>37.084</v>
+        <v>78.098</v>
       </c>
       <c r="V7" t="n">
-        <v>20.736</v>
+        <v>7.375</v>
       </c>
       <c r="W7" t="n">
-        <v>-46.446</v>
+        <v>-21.589</v>
       </c>
     </row>
     <row r="8">
@@ -1148,7 +1124,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1163,42 +1139,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AKSA.IS, TRMET.IS</t>
+          <t>BRSAN.IS, CWENE.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AKSA.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
+          <t>BRSAN.IS: 2026-08-12 | CWENE.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>73.91462605481856</v>
+        <v>67.61086137129925</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
+          <t>BRSAN.IS: -0.58% / +3.42% / -1.11% | CWENE.IS: -2.43% / +0.00% / -3.06%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29.3281854651174</v>
+        <v>23.38198980936981</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.69555354433906</v>
+        <v>-21.027470517574</v>
       </c>
       <c r="L8" t="n">
-        <v>17.11290382444416</v>
+        <v>17.05327546391042</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>162.7</v>
+        <v>136.4</v>
       </c>
       <c r="O8" t="n">
-        <v>43.3</v>
+        <v>48</v>
       </c>
       <c r="P8" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1209,19 +1185,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>36.941</v>
+        <v>30.946</v>
       </c>
       <c r="T8" t="n">
-        <v>36.941</v>
+        <v>30.946</v>
       </c>
       <c r="U8" t="n">
-        <v>25.314</v>
+        <v>48.388</v>
       </c>
       <c r="V8" t="n">
-        <v>-15.119</v>
+        <v>8.683999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-69.568</v>
+        <v>-66.497</v>
       </c>
     </row>
     <row r="9">
@@ -1235,7 +1211,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
+          <t>T4_konsensus|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1251,29 +1227,29 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>31.91300080326926</v>
+        <v>66.49721870311937</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>17.64340578198198</v>
+        <v>34.09313051933771</v>
       </c>
       <c r="K9" t="n">
-        <v>2.302203561121985e-06</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4.846554569756845</v>
+        <v>10.66215926594336</v>
       </c>
       <c r="M9" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>13.9</v>
+        <v>47.6</v>
       </c>
       <c r="O9" t="n">
-        <v>75</v>
+        <v>59.4</v>
       </c>
       <c r="P9" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1284,19 +1260,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.847</v>
+        <v>6.103</v>
       </c>
       <c r="T9" t="n">
-        <v>3.503</v>
+        <v>6.103</v>
       </c>
       <c r="U9" t="n">
-        <v>46.446</v>
+        <v>102.166</v>
       </c>
       <c r="V9" t="n">
-        <v>12.887</v>
+        <v>16.518</v>
       </c>
       <c r="W9" t="n">
-        <v>-2.154</v>
+        <v>-12.844</v>
       </c>
     </row>
     <row r="10">
@@ -1310,7 +1286,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1323,55 +1299,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>47.7084504688879</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>36.78585504819178</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
-        <v>25.69738108440036</v>
+        <v>21.23845504164525</v>
       </c>
       <c r="K10" t="n">
-        <v>-20.72609957575339</v>
+        <v>-22.80856515541238</v>
       </c>
       <c r="L10" t="n">
-        <v>11.47600961545611</v>
+        <v>6.958481500131142</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>122.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>26.084</v>
+        <v>28.807</v>
       </c>
       <c r="T10" t="n">
-        <v>26.084</v>
+        <v>28.807</v>
       </c>
       <c r="U10" t="n">
-        <v>5.211</v>
+        <v>0.926</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.821</v>
+        <v>-12.051</v>
       </c>
       <c r="W10" t="n">
-        <v>-36.5</v>
+        <v>-40.838</v>
       </c>
     </row>
     <row r="11">
@@ -1385,7 +1373,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1398,67 +1386,55 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>44.1931793598139</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>60.15988621066983</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>17.47880176656278</v>
+        <v>29.41081527100167</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.38000262629327</v>
+        <v>-0.4732772020725418</v>
       </c>
       <c r="L11" t="n">
-        <v>8.000657219756324</v>
+        <v>12.39638337363852</v>
       </c>
       <c r="M11" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N11" t="n">
-        <v>83.8</v>
+        <v>21.3</v>
       </c>
       <c r="O11" t="n">
-        <v>47.3</v>
+        <v>55.8</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>17.024</v>
+        <v>12.717</v>
       </c>
       <c r="T11" t="n">
-        <v>17.024</v>
+        <v>12.717</v>
       </c>
       <c r="U11" t="n">
-        <v>18.176</v>
+        <v>78.098</v>
       </c>
       <c r="V11" t="n">
-        <v>6.63</v>
+        <v>7.375</v>
       </c>
       <c r="W11" t="n">
-        <v>-24.246</v>
+        <v>-21.589</v>
       </c>
     </row>
     <row r="12">
@@ -1472,7 +1448,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1487,42 +1463,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ARCLK.IS, BRSAN.IS, BSOKE.IS</t>
+          <t>ARCLK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: 2026-07-29 | BRSAN.IS: 2026-08-07 | BSOKE.IS: 2026-08-03</t>
+          <t>ARCLK.IS: 2026-07-17 | BRSAN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>24.12162912768729</v>
+        <v>15.69318443671461</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -2.68% / +3.12% / -2.86% | BRSAN.IS: +10.55% / +13.72% / 0.00% | BSOKE.IS: +6.72% / +8.97% / -0.29%</t>
+          <t>ARCLK.IS: -2.48% / +4.30% / -2.97% | BRSAN.IS: +8.20% / +12.54% / -2.42%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.5979844862621819</v>
+        <v>2.170155878001112</v>
       </c>
       <c r="K12" t="n">
-        <v>15.13867124891788</v>
+        <v>29.25303854891397</v>
       </c>
       <c r="L12" t="n">
-        <v>14.82627592190883</v>
+        <v>16.59988022061277</v>
       </c>
       <c r="M12" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N12" t="n">
-        <v>64</v>
+        <v>43.2</v>
       </c>
       <c r="O12" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
       <c r="P12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1530,22 +1506,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>14.383</v>
+        <v>11.893</v>
       </c>
       <c r="T12" t="n">
-        <v>14.383</v>
+        <v>11.893</v>
       </c>
       <c r="U12" t="n">
-        <v>45.25</v>
+        <v>58.763</v>
       </c>
       <c r="V12" t="n">
-        <v>33.196</v>
+        <v>47.144</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.924</v>
+        <v>-4.082</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1535,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1575,26 +1551,26 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>8.623920580589095</v>
+        <v>14.91975365488964</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-8.261163935788185</v>
+        <v>-6.722612060786748</v>
       </c>
       <c r="K13" t="n">
-        <v>7.583805912323638</v>
+        <v>9.530994557902584</v>
       </c>
       <c r="L13" t="n">
-        <v>16.53177272942414</v>
+        <v>25.87645235296805</v>
       </c>
       <c r="M13" t="n">
-        <v>72.22222222222221</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N13" t="n">
-        <v>84.3</v>
+        <v>85.3</v>
       </c>
       <c r="O13" t="n">
-        <v>43.5</v>
+        <v>46.5</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1608,19 +1584,19 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>15.149</v>
+        <v>14.11</v>
       </c>
       <c r="T13" t="n">
-        <v>15.149</v>
+        <v>14.11</v>
       </c>
       <c r="U13" t="n">
-        <v>31.525</v>
+        <v>70.47799999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>24.116</v>
+        <v>44.844</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.899</v>
+        <v>-28.005</v>
       </c>
     </row>
     <row r="14">
@@ -1634,7 +1610,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|Bvolatilite</t>
+          <t>T6_skor_momentum|E30|S5|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1649,42 +1625,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AKSA.IS, ALARK.IS, BSOKE.IS, CWENE.IS, TRMET.IS</t>
+          <t>TRALT.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AKSA.IS: 2026-08-13 | ALARK.IS: 2026-08-11 | BSOKE.IS: 2026-08-05 | CWENE.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
+          <t>TRALT.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6.76395532820866</v>
+        <v>19.66188721503979</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | ALARK.IS: -2.89% / +0.10% / -3.35% | BSOKE.IS: +2.34% / +4.50% / -2.02% | CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
+          <t>TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-14.84944944967732</v>
+        <v>2.869534524659589</v>
       </c>
       <c r="K14" t="n">
-        <v>2.294090072135879</v>
+        <v>4.029282486825658</v>
       </c>
       <c r="L14" t="n">
-        <v>29.71908457756942</v>
+        <v>9.611326813483668</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>201.4</v>
+        <v>163.2</v>
       </c>
       <c r="O14" t="n">
-        <v>46.1</v>
+        <v>48</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1692,22 +1668,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>13.8</v>
+        <v>9.945</v>
       </c>
       <c r="T14" t="n">
-        <v>13.8</v>
+        <v>9.945</v>
       </c>
       <c r="U14" t="n">
-        <v>46.505</v>
+        <v>27.499</v>
       </c>
       <c r="V14" t="n">
-        <v>45.697</v>
+        <v>22.644</v>
       </c>
       <c r="W14" t="n">
-        <v>-13.935</v>
+        <v>-4.876</v>
       </c>
     </row>
     <row r="16">
@@ -1837,17 +1813,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 | 3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1860,67 +1836,55 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>AKSA.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>73.91462605481856</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
-        </is>
-      </c>
+        <v>71.7096707191417</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>29.3281854651174</v>
+        <v>10.52140217505859</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.69555354433906</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>17.11290382444416</v>
+        <v>25.61349479378329</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>162.7</v>
+        <v>49.6</v>
       </c>
       <c r="O18" t="n">
-        <v>43.3</v>
+        <v>42</v>
       </c>
       <c r="P18" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>36.941</v>
+        <v>11.01</v>
       </c>
       <c r="T18" t="n">
-        <v>36.941</v>
+        <v>10.869</v>
       </c>
       <c r="U18" t="n">
-        <v>25.314</v>
+        <v>140.475</v>
       </c>
       <c r="V18" t="n">
-        <v>-15.119</v>
+        <v>68.77200000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>-69.568</v>
+        <v>-28.954</v>
       </c>
     </row>
     <row r="19">
@@ -1931,12 +1895,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 | 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1949,73 +1913,61 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>69.28710330559822</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>71.14835325524578</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>29.61687177483288</v>
+        <v>37.83905010537829</v>
       </c>
       <c r="K19" t="n">
-        <v>-18.47919897889352</v>
+        <v>-2.929523572966308</v>
       </c>
       <c r="L19" t="n">
-        <v>22.190831633245</v>
+        <v>12.6166884158664</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N19" t="n">
-        <v>111.6</v>
+        <v>57.5</v>
       </c>
       <c r="O19" t="n">
-        <v>39.6</v>
+        <v>56.9</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>27.762</v>
+        <v>11.453</v>
       </c>
       <c r="T19" t="n">
-        <v>27.762</v>
+        <v>11.453</v>
       </c>
       <c r="U19" t="n">
-        <v>37.084</v>
+        <v>94.13200000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>20.736</v>
+        <v>12.087</v>
       </c>
       <c r="W19" t="n">
-        <v>-46.446</v>
+        <v>-20.494</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2025,7 +1977,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2038,61 +1990,73 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, CWENE.IS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | CWENE.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H20" t="n">
-        <v>67.66470503641577</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>67.61086137129925</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.58% / +3.42% / -1.11% | CWENE.IS: -2.43% / +0.00% / -3.06%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
-        <v>25.31911840398602</v>
+        <v>23.38198980936981</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.063423217612641</v>
+        <v>-21.027470517574</v>
       </c>
       <c r="L20" t="n">
-        <v>14.41049705545434</v>
+        <v>17.05327546391042</v>
       </c>
       <c r="M20" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>53.1</v>
+        <v>136.4</v>
       </c>
       <c r="O20" t="n">
-        <v>51.4</v>
+        <v>48</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>23.105</v>
+        <v>30.946</v>
       </c>
       <c r="T20" t="n">
-        <v>23.105</v>
+        <v>30.946</v>
       </c>
       <c r="U20" t="n">
-        <v>8.699</v>
+        <v>48.388</v>
       </c>
       <c r="V20" t="n">
-        <v>2.872</v>
+        <v>8.683999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-30.289</v>
+        <v>-66.497</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2102,7 +2066,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
+          <t>T4_konsensus|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2118,29 +2082,29 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>61.9655453107135</v>
+        <v>66.49721870311937</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>32.08371516582042</v>
+        <v>34.09313051933771</v>
       </c>
       <c r="K21" t="n">
-        <v>1.621821921204969e-06</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>13.78592482270004</v>
+        <v>10.66215926594336</v>
       </c>
       <c r="M21" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N21" t="n">
-        <v>24.3</v>
+        <v>47.6</v>
       </c>
       <c r="O21" t="n">
-        <v>63.3</v>
+        <v>59.4</v>
       </c>
       <c r="P21" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2151,35 +2115,35 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>8.218</v>
+        <v>6.103</v>
       </c>
       <c r="T21" t="n">
-        <v>4.976</v>
+        <v>6.103</v>
       </c>
       <c r="U21" t="n">
-        <v>83.73399999999999</v>
+        <v>102.166</v>
       </c>
       <c r="V21" t="n">
-        <v>13.474</v>
+        <v>16.518</v>
       </c>
       <c r="W21" t="n">
-        <v>-4.893</v>
+        <v>-12.844</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 | 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2195,29 +2159,29 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>47.7084504688879</v>
+        <v>60.15988621066983</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>25.69738108440036</v>
+        <v>29.41081527100167</v>
       </c>
       <c r="K22" t="n">
-        <v>-20.72609957575339</v>
+        <v>-0.4732772020725418</v>
       </c>
       <c r="L22" t="n">
-        <v>11.47600961545611</v>
+        <v>12.39638337363852</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N22" t="n">
-        <v>122.5</v>
+        <v>21.3</v>
       </c>
       <c r="O22" t="n">
-        <v>42.5</v>
+        <v>55.8</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2228,19 +2192,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>26.084</v>
+        <v>12.717</v>
       </c>
       <c r="T22" t="n">
-        <v>26.084</v>
+        <v>12.717</v>
       </c>
       <c r="U22" t="n">
-        <v>5.211</v>
+        <v>78.098</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.821</v>
+        <v>7.375</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.5</v>
+        <v>-21.589</v>
       </c>
     </row>
     <row r="23">
@@ -2251,12 +2215,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2271,42 +2235,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AKSA.IS, BRSAN.IS, KCHOL.IS</t>
+          <t>BRSAN.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AKSA.IS: 2026-08-13 | BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
+          <t>BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>44.1931793598139</v>
+        <v>36.78585504819178</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>17.47880176656278</v>
+        <v>21.23845504164525</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.38000262629327</v>
+        <v>-22.80856515541238</v>
       </c>
       <c r="L23" t="n">
-        <v>8.000657219756324</v>
+        <v>6.958481500131142</v>
       </c>
       <c r="M23" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N23" t="n">
-        <v>83.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>47.3</v>
+        <v>43.5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2314,38 +2278,38 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>17.024</v>
+        <v>28.807</v>
       </c>
       <c r="T23" t="n">
-        <v>17.024</v>
+        <v>28.807</v>
       </c>
       <c r="U23" t="n">
-        <v>18.176</v>
+        <v>0.926</v>
       </c>
       <c r="V23" t="n">
-        <v>6.63</v>
+        <v>-12.051</v>
       </c>
       <c r="W23" t="n">
-        <v>-24.246</v>
+        <v>-40.838</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
+          <t>T6_skor_momentum|E30|S5|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2358,55 +2322,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>TRALT.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TRALT.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>31.91300080326926</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>19.66188721503979</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>17.64340578198198</v>
+        <v>2.869534524659589</v>
       </c>
       <c r="K24" t="n">
-        <v>2.302203561121985e-06</v>
+        <v>4.029282486825658</v>
       </c>
       <c r="L24" t="n">
-        <v>4.846554569756845</v>
+        <v>9.611326813483668</v>
       </c>
       <c r="M24" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>13.9</v>
+        <v>163.2</v>
       </c>
       <c r="O24" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="P24" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>4.847</v>
+        <v>9.945</v>
       </c>
       <c r="T24" t="n">
-        <v>3.503</v>
+        <v>9.945</v>
       </c>
       <c r="U24" t="n">
-        <v>46.446</v>
+        <v>27.499</v>
       </c>
       <c r="V24" t="n">
-        <v>12.887</v>
+        <v>22.644</v>
       </c>
       <c r="W24" t="n">
-        <v>-2.154</v>
+        <v>-4.876</v>
       </c>
     </row>
     <row r="25">
@@ -2422,7 +2398,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2437,42 +2413,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ARCLK.IS, BRSAN.IS, BSOKE.IS</t>
+          <t>ARCLK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ARCLK.IS: 2026-07-29 | BRSAN.IS: 2026-08-07 | BSOKE.IS: 2026-08-03</t>
+          <t>ARCLK.IS: 2026-07-17 | BRSAN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>24.12162912768729</v>
+        <v>15.69318443671461</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -2.68% / +3.12% / -2.86% | BRSAN.IS: +10.55% / +13.72% / 0.00% | BSOKE.IS: +6.72% / +8.97% / -0.29%</t>
+          <t>ARCLK.IS: -2.48% / +4.30% / -2.97% | BRSAN.IS: +8.20% / +12.54% / -2.42%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.5979844862621819</v>
+        <v>2.170155878001112</v>
       </c>
       <c r="K25" t="n">
-        <v>15.13867124891788</v>
+        <v>29.25303854891397</v>
       </c>
       <c r="L25" t="n">
-        <v>14.82627592190883</v>
+        <v>16.59988022061277</v>
       </c>
       <c r="M25" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N25" t="n">
-        <v>64</v>
+        <v>43.2</v>
       </c>
       <c r="O25" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
       <c r="P25" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2480,22 +2456,22 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>14.383</v>
+        <v>11.893</v>
       </c>
       <c r="T25" t="n">
-        <v>14.383</v>
+        <v>11.893</v>
       </c>
       <c r="U25" t="n">
-        <v>45.25</v>
+        <v>58.763</v>
       </c>
       <c r="V25" t="n">
-        <v>33.196</v>
+        <v>47.144</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.924</v>
+        <v>-4.082</v>
       </c>
     </row>
     <row r="26">
@@ -2511,7 +2487,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M30|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2527,26 +2503,26 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>8.623920580589095</v>
+        <v>14.91975365488964</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>-8.261163935788185</v>
+        <v>-6.722612060786748</v>
       </c>
       <c r="K26" t="n">
-        <v>7.583805912323638</v>
+        <v>9.530994557902584</v>
       </c>
       <c r="L26" t="n">
-        <v>16.53177272942414</v>
+        <v>25.87645235296805</v>
       </c>
       <c r="M26" t="n">
-        <v>72.22222222222221</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N26" t="n">
-        <v>84.3</v>
+        <v>85.3</v>
       </c>
       <c r="O26" t="n">
-        <v>43.5</v>
+        <v>46.5</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -2560,108 +2536,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>15.149</v>
+        <v>14.11</v>
       </c>
       <c r="T26" t="n">
-        <v>15.149</v>
+        <v>14.11</v>
       </c>
       <c r="U26" t="n">
-        <v>31.525</v>
+        <v>70.47799999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>24.116</v>
+        <v>44.844</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.899</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>T1_genislik_skor|E30|S5|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|Bvolatilite</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>AKSA.IS, ALARK.IS, BSOKE.IS, CWENE.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>AKSA.IS: 2026-08-13 | ALARK.IS: 2026-08-11 | BSOKE.IS: 2026-08-05 | CWENE.IS: 2026-08-13 | TRMET.IS: 2026-08-11</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>6.76395532820866</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>AKSA.IS: -0.02% / +0.00% / 0.00% | ALARK.IS: -2.89% / +0.10% / -3.35% | BSOKE.IS: +2.34% / +4.50% / -2.02% | CWENE.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +0.77% / +1.97% / -2.28%</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>-14.84944944967732</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.294090072135879</v>
-      </c>
-      <c r="L27" t="n">
-        <v>29.71908457756942</v>
-      </c>
-      <c r="M27" t="n">
-        <v>100</v>
-      </c>
-      <c r="N27" t="n">
-        <v>201.4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>46.505</v>
-      </c>
-      <c r="V27" t="n">
-        <v>45.697</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-13.935</v>
+        <v>-28.005</v>
       </c>
     </row>
   </sheetData>
@@ -2683,20 +2570,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2846,7 +2733,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2861,42 +2748,42 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS</t>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>95.17942072734355</v>
+        <v>73.55709251838034</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>32.50943475287353</v>
+        <v>24.91776733953206</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.96868434006504</v>
+        <v>-18.76800334617383</v>
       </c>
       <c r="L3" t="n">
-        <v>19.87241420107954</v>
+        <v>17.14344531576387</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>101.2</v>
+        <v>134.9</v>
       </c>
       <c r="O3" t="n">
-        <v>41.7</v>
+        <v>40.8</v>
       </c>
       <c r="P3" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -2904,22 +2791,22 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>29.384</v>
+        <v>30.582</v>
       </c>
       <c r="T3" t="n">
-        <v>29.384</v>
+        <v>30.582</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.727</v>
+        <v>13.295</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.542</v>
+        <v>4.469</v>
       </c>
       <c r="W3" t="n">
-        <v>-38.397</v>
+        <v>-49.911</v>
       </c>
     </row>
     <row r="4">
@@ -2933,7 +2820,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2946,55 +2833,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>94.61905079674457</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>73.55709251838034</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+        </is>
+      </c>
       <c r="J4" t="n">
-        <v>26.23454465636599</v>
+        <v>24.91776733953206</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.34044906797633</v>
+        <v>-18.76800334617383</v>
       </c>
       <c r="L4" t="n">
-        <v>20.6096939559789</v>
+        <v>17.14344531576387</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>74.90000000000001</v>
+        <v>134.9</v>
       </c>
       <c r="O4" t="n">
-        <v>43.7</v>
+        <v>40.8</v>
       </c>
       <c r="P4" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>28.897</v>
+        <v>30.582</v>
       </c>
       <c r="T4" t="n">
-        <v>28.897</v>
+        <v>30.582</v>
       </c>
       <c r="U4" t="n">
-        <v>6.931</v>
+        <v>13.295</v>
       </c>
       <c r="V4" t="n">
-        <v>18.369</v>
+        <v>4.469</v>
       </c>
       <c r="W4" t="n">
-        <v>-33.344</v>
+        <v>-49.911</v>
       </c>
     </row>
     <row r="5">
@@ -3008,7 +2907,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3021,55 +2920,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, ENJSA.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>94.61905079674457</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>69.61349897281856</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33% | TRMET.IS: +10.78% / +24.13% / -0.52%</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>26.23454465636599</v>
+        <v>43.30442621244415</v>
       </c>
       <c r="K5" t="n">
-        <v>-13.34044906797633</v>
+        <v>-20.22131847683636</v>
       </c>
       <c r="L5" t="n">
-        <v>20.6096939559789</v>
+        <v>9.921568402707182</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>74.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>43.7</v>
+        <v>50.6</v>
       </c>
       <c r="P5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>28.897</v>
+        <v>25.753</v>
       </c>
       <c r="T5" t="n">
-        <v>28.897</v>
+        <v>25.753</v>
       </c>
       <c r="U5" t="n">
-        <v>6.931</v>
+        <v>5.193</v>
       </c>
       <c r="V5" t="n">
-        <v>18.369</v>
+        <v>-7.549</v>
       </c>
       <c r="W5" t="n">
-        <v>-33.344</v>
+        <v>-36.487</v>
       </c>
     </row>
     <row r="6">
@@ -3083,7 +2994,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3098,42 +3009,42 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.53333624874938</v>
+        <v>69.61349897281856</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33% | TRMET.IS: +10.78% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>34.82253143286685</v>
+        <v>43.30442621244415</v>
       </c>
       <c r="K6" t="n">
-        <v>-26.14753157146566</v>
+        <v>-20.22131847683636</v>
       </c>
       <c r="L6" t="n">
-        <v>14.51092369816588</v>
+        <v>9.921568402707182</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>104.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>39.5</v>
+        <v>50.6</v>
       </c>
       <c r="P6" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -3141,22 +3052,22 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>36.603</v>
+        <v>25.753</v>
       </c>
       <c r="T6" t="n">
-        <v>36.603</v>
+        <v>25.753</v>
       </c>
       <c r="U6" t="n">
-        <v>-10.563</v>
+        <v>5.193</v>
       </c>
       <c r="V6" t="n">
-        <v>-18.259</v>
+        <v>-7.549</v>
       </c>
       <c r="W6" t="n">
-        <v>-51.636</v>
+        <v>-36.487</v>
       </c>
     </row>
     <row r="7">
@@ -3170,7 +3081,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3183,55 +3094,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>73.75964826688029</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>71.64484083015594</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+        </is>
+      </c>
       <c r="J7" t="n">
-        <v>32.34918865075789</v>
+        <v>34.63451047134283</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.75900002341578e-06</v>
+        <v>-13.94852559003611</v>
       </c>
       <c r="L7" t="n">
-        <v>10.93171342838547</v>
+        <v>15.76726292384321</v>
       </c>
       <c r="M7" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>41.7</v>
+        <v>136.4</v>
       </c>
       <c r="O7" t="n">
-        <v>52.4</v>
+        <v>40.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>15.232</v>
+        <v>25.176</v>
       </c>
       <c r="T7" t="n">
-        <v>15.232</v>
+        <v>25.176</v>
       </c>
       <c r="U7" t="n">
-        <v>69.63200000000001</v>
+        <v>17.64</v>
       </c>
       <c r="V7" t="n">
-        <v>46.229</v>
+        <v>-0.18</v>
       </c>
       <c r="W7" t="n">
-        <v>-16.27</v>
+        <v>-39.583</v>
       </c>
     </row>
     <row r="8">
@@ -3245,7 +3168,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3258,55 +3181,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>73.75964826688029</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>71.64484083015594</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
-        <v>32.34918865075789</v>
+        <v>34.63451047134283</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.75900002341578e-06</v>
+        <v>-13.94852559003611</v>
       </c>
       <c r="L8" t="n">
-        <v>10.93171342838547</v>
+        <v>15.76726292384321</v>
       </c>
       <c r="M8" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>41.7</v>
+        <v>136.4</v>
       </c>
       <c r="O8" t="n">
-        <v>52.4</v>
+        <v>40.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>15.232</v>
+        <v>25.176</v>
       </c>
       <c r="T8" t="n">
-        <v>15.232</v>
+        <v>25.176</v>
       </c>
       <c r="U8" t="n">
-        <v>69.63200000000001</v>
+        <v>17.64</v>
       </c>
       <c r="V8" t="n">
-        <v>46.229</v>
+        <v>-0.18</v>
       </c>
       <c r="W8" t="n">
-        <v>-16.27</v>
+        <v>-39.583</v>
       </c>
     </row>
     <row r="9">
@@ -3320,7 +3255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|coklu_zarf</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3335,42 +3270,42 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>41.94189944051841</v>
+        <v>69.61349897281856</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33% | TRMET.IS: +10.78% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>23.19304514092613</v>
+        <v>43.30442621244415</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.90358254997626</v>
+        <v>-20.22131847683636</v>
       </c>
       <c r="L9" t="n">
-        <v>5.815920071163994</v>
+        <v>9.921568402707182</v>
       </c>
       <c r="M9" t="n">
-        <v>33.33333333333333</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>32.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>56.9</v>
+        <v>50.6</v>
       </c>
       <c r="P9" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -3378,22 +3313,22 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>13.863</v>
+        <v>25.753</v>
       </c>
       <c r="T9" t="n">
-        <v>13.863</v>
+        <v>25.753</v>
       </c>
       <c r="U9" t="n">
-        <v>-9.416</v>
+        <v>5.193</v>
       </c>
       <c r="V9" t="n">
-        <v>-11.028</v>
+        <v>-7.549</v>
       </c>
       <c r="W9" t="n">
-        <v>-14.579</v>
+        <v>-36.487</v>
       </c>
     </row>
     <row r="10">
@@ -3407,7 +3342,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3423,29 +3358,29 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>38.08584121207757</v>
+        <v>31.1518364332128</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>14.85812229550152</v>
+        <v>14.46262836377386</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.35969645108858</v>
+        <v>-12.72549823041446</v>
       </c>
       <c r="L10" t="n">
-        <v>3.605272693289541</v>
+        <v>6.329963381531822</v>
       </c>
       <c r="M10" t="n">
-        <v>33.33333333333333</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>39.2</v>
+        <v>26.8</v>
       </c>
       <c r="O10" t="n">
-        <v>44.3</v>
+        <v>42.6</v>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -3456,19 +3391,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>22.794</v>
+        <v>30.482</v>
       </c>
       <c r="T10" t="n">
-        <v>22.794</v>
+        <v>25.928</v>
       </c>
       <c r="U10" t="n">
-        <v>-17.177</v>
+        <v>-23.452</v>
       </c>
       <c r="V10" t="n">
-        <v>-19.815</v>
+        <v>-25.928</v>
       </c>
       <c r="W10" t="n">
-        <v>-24.453</v>
+        <v>-33.565</v>
       </c>
     </row>
     <row r="11">
@@ -3482,7 +3417,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3495,55 +3430,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>73.75964826688029</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>71.64484083015594</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+        </is>
+      </c>
       <c r="J11" t="n">
-        <v>32.34918865075789</v>
+        <v>34.63451047134283</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.75900002341578e-06</v>
+        <v>-13.94852559003611</v>
       </c>
       <c r="L11" t="n">
-        <v>10.93171342838547</v>
+        <v>15.76726292384321</v>
       </c>
       <c r="M11" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>41.7</v>
+        <v>136.4</v>
       </c>
       <c r="O11" t="n">
-        <v>52.4</v>
+        <v>40.4</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>15.232</v>
+        <v>25.176</v>
       </c>
       <c r="T11" t="n">
-        <v>15.232</v>
+        <v>25.176</v>
       </c>
       <c r="U11" t="n">
-        <v>69.63200000000001</v>
+        <v>17.64</v>
       </c>
       <c r="V11" t="n">
-        <v>46.229</v>
+        <v>-0.18</v>
       </c>
       <c r="W11" t="n">
-        <v>-16.27</v>
+        <v>-39.583</v>
       </c>
     </row>
     <row r="12">
@@ -3557,7 +3504,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
+          <t>T3_kademeli_slot|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3573,29 +3520,29 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>8.326900458734343</v>
+        <v>27.77992254030131</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-8.030096457283253</v>
+        <v>-0.3947399939562279</v>
       </c>
       <c r="K12" t="n">
-        <v>11.24844055823626</v>
+        <v>7.725663662162252</v>
       </c>
       <c r="L12" t="n">
-        <v>15.1193724336431</v>
+        <v>23.0569407093583</v>
       </c>
       <c r="M12" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>39.7</v>
+        <v>136.9</v>
       </c>
       <c r="O12" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3606,19 +3553,19 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>12.679</v>
+        <v>14.102</v>
       </c>
       <c r="T12" t="n">
-        <v>10.364</v>
+        <v>14.102</v>
       </c>
       <c r="U12" t="n">
-        <v>32.693</v>
+        <v>53.388</v>
       </c>
       <c r="V12" t="n">
-        <v>17.425</v>
+        <v>43.828</v>
       </c>
       <c r="W12" t="n">
-        <v>-5.555</v>
+        <v>-19.852</v>
       </c>
     </row>
     <row r="13">
@@ -3632,7 +3579,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3647,42 +3594,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS, ENKAI.IS</t>
+          <t>CWENE.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-13 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05 | ENKAI.IS: 2026-08-13</t>
+          <t>CWENE.IS: 2026-08-12 | RALYH.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.96656699373973</v>
+        <v>-17.85349092315649</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +0.84% / +3.73% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.91% / +4.22% / -2.40% | ECILC.IS: +11.67% / +13.93% / -1.57% | ENKAI.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CWENE.IS: -2.47% / +0.00% / -3.11% | RALYH.IS: +2.91% / +2.93% / -0.99%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-7.503658754890596</v>
+        <v>-38.46787507721694</v>
       </c>
       <c r="K13" t="n">
-        <v>6.799316168838421</v>
+        <v>6.144711297826366</v>
       </c>
       <c r="L13" t="n">
-        <v>26.13605890970743</v>
+        <v>49.48136135333956</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>175.1</v>
+        <v>120</v>
       </c>
       <c r="O13" t="n">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
       <c r="P13" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3690,22 +3637,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>21.464</v>
+        <v>23.673</v>
       </c>
       <c r="T13" t="n">
-        <v>21.464</v>
+        <v>21.907</v>
       </c>
       <c r="U13" t="n">
-        <v>27.556</v>
+        <v>16.355</v>
       </c>
       <c r="V13" t="n">
-        <v>17.534</v>
+        <v>23.44</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.587</v>
+        <v>-19.255</v>
       </c>
     </row>
     <row r="14">
@@ -3719,7 +3666,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3732,55 +3679,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TRALT.IS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TRALT.IS: 2026-08-13</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>45.0589059523848</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>13.50616593082303</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>3.452723024503923</v>
+        <v>0.3486751900400487</v>
       </c>
       <c r="K14" t="n">
-        <v>4.973709971745888</v>
+        <v>5.455912207814473</v>
       </c>
       <c r="L14" t="n">
-        <v>28.80374524525355</v>
+        <v>11.73786427798399</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>64.5</v>
+        <v>129.5</v>
       </c>
       <c r="O14" t="n">
-        <v>41.5</v>
+        <v>47.5</v>
       </c>
       <c r="P14" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>18.867</v>
+        <v>13.751</v>
       </c>
       <c r="T14" t="n">
-        <v>18.867</v>
+        <v>13.751</v>
       </c>
       <c r="U14" t="n">
-        <v>78.093</v>
+        <v>35.855</v>
       </c>
       <c r="V14" t="n">
-        <v>43.297</v>
+        <v>26.771</v>
       </c>
       <c r="W14" t="n">
-        <v>-24.086</v>
+        <v>-4.752</v>
       </c>
     </row>
     <row r="16">
@@ -3920,7 +3879,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3935,42 +3894,42 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS</t>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>95.17942072734355</v>
+        <v>73.55709251838034</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>32.50943475287353</v>
+        <v>24.91776733953206</v>
       </c>
       <c r="K18" t="n">
-        <v>-18.96868434006504</v>
+        <v>-18.76800334617383</v>
       </c>
       <c r="L18" t="n">
-        <v>19.87241420107954</v>
+        <v>17.14344531576387</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>101.2</v>
+        <v>134.9</v>
       </c>
       <c r="O18" t="n">
-        <v>41.7</v>
+        <v>40.8</v>
       </c>
       <c r="P18" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3978,22 +3937,22 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.384</v>
+        <v>30.582</v>
       </c>
       <c r="T18" t="n">
-        <v>29.384</v>
+        <v>30.582</v>
       </c>
       <c r="U18" t="n">
-        <v>-7.727</v>
+        <v>13.295</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.542</v>
+        <v>4.469</v>
       </c>
       <c r="W18" t="n">
-        <v>-38.397</v>
+        <v>-49.911</v>
       </c>
     </row>
     <row r="19">
@@ -4009,7 +3968,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4022,71 +3981,83 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H19" t="n">
-        <v>94.61905079674457</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>73.55709251838034</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+        </is>
+      </c>
       <c r="J19" t="n">
-        <v>26.23454465636599</v>
+        <v>24.91776733953206</v>
       </c>
       <c r="K19" t="n">
-        <v>-13.34044906797633</v>
+        <v>-18.76800334617383</v>
       </c>
       <c r="L19" t="n">
-        <v>20.6096939559789</v>
+        <v>17.14344531576387</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>74.90000000000001</v>
+        <v>134.9</v>
       </c>
       <c r="O19" t="n">
-        <v>43.7</v>
+        <v>40.8</v>
       </c>
       <c r="P19" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>28.897</v>
+        <v>30.582</v>
       </c>
       <c r="T19" t="n">
-        <v>28.897</v>
+        <v>30.582</v>
       </c>
       <c r="U19" t="n">
-        <v>6.931</v>
+        <v>13.295</v>
       </c>
       <c r="V19" t="n">
-        <v>18.369</v>
+        <v>4.469</v>
       </c>
       <c r="W19" t="n">
-        <v>-33.344</v>
+        <v>-49.911</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2 | 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4099,71 +4070,83 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H20" t="n">
-        <v>94.61905079674457</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>71.64484083015594</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
-        <v>26.23454465636599</v>
+        <v>34.63451047134283</v>
       </c>
       <c r="K20" t="n">
-        <v>-13.34044906797633</v>
+        <v>-13.94852559003611</v>
       </c>
       <c r="L20" t="n">
-        <v>20.6096939559789</v>
+        <v>15.76726292384321</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>74.90000000000001</v>
+        <v>136.4</v>
       </c>
       <c r="O20" t="n">
-        <v>43.7</v>
+        <v>40.4</v>
       </c>
       <c r="P20" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>28.897</v>
+        <v>25.176</v>
       </c>
       <c r="T20" t="n">
-        <v>28.897</v>
+        <v>25.176</v>
       </c>
       <c r="U20" t="n">
-        <v>6.931</v>
+        <v>17.64</v>
       </c>
       <c r="V20" t="n">
-        <v>18.369</v>
+        <v>-0.18</v>
       </c>
       <c r="W20" t="n">
-        <v>-33.344</v>
+        <v>-39.583</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2 | 3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4176,71 +4159,83 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H21" t="n">
-        <v>73.75964826688029</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>71.64484083015594</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+        </is>
+      </c>
       <c r="J21" t="n">
-        <v>32.34918865075789</v>
+        <v>34.63451047134283</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.75900002341578e-06</v>
+        <v>-13.94852559003611</v>
       </c>
       <c r="L21" t="n">
-        <v>10.93171342838547</v>
+        <v>15.76726292384321</v>
       </c>
       <c r="M21" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>41.7</v>
+        <v>136.4</v>
       </c>
       <c r="O21" t="n">
-        <v>52.4</v>
+        <v>40.4</v>
       </c>
       <c r="P21" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>15.232</v>
+        <v>25.176</v>
       </c>
       <c r="T21" t="n">
-        <v>15.232</v>
+        <v>25.176</v>
       </c>
       <c r="U21" t="n">
-        <v>69.63200000000001</v>
+        <v>17.64</v>
       </c>
       <c r="V21" t="n">
-        <v>46.229</v>
+        <v>-0.18</v>
       </c>
       <c r="W21" t="n">
-        <v>-16.27</v>
+        <v>-39.583</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 | 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4253,71 +4248,83 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, ENJSA.IS, TRMET.IS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+        </is>
+      </c>
       <c r="H22" t="n">
-        <v>73.75964826688029</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>69.61349897281856</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33% | TRMET.IS: +10.78% / +24.13% / -0.52%</t>
+        </is>
+      </c>
       <c r="J22" t="n">
-        <v>32.34918865075789</v>
+        <v>43.30442621244415</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.75900002341578e-06</v>
+        <v>-20.22131847683636</v>
       </c>
       <c r="L22" t="n">
-        <v>10.93171342838547</v>
+        <v>9.921568402707182</v>
       </c>
       <c r="M22" t="n">
-        <v>77.77777777777779</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N22" t="n">
-        <v>41.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>52.4</v>
+        <v>50.6</v>
       </c>
       <c r="P22" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>15.232</v>
+        <v>25.753</v>
       </c>
       <c r="T22" t="n">
-        <v>15.232</v>
+        <v>25.753</v>
       </c>
       <c r="U22" t="n">
-        <v>69.63200000000001</v>
+        <v>5.193</v>
       </c>
       <c r="V22" t="n">
-        <v>46.229</v>
+        <v>-7.549</v>
       </c>
       <c r="W22" t="n">
-        <v>-16.27</v>
+        <v>-36.487</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4330,67 +4337,55 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, BRSAN.IS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>70.53333624874938</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>31.1518364332128</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>34.82253143286685</v>
+        <v>14.46262836377386</v>
       </c>
       <c r="K23" t="n">
-        <v>-26.14753157146566</v>
+        <v>-12.72549823041446</v>
       </c>
       <c r="L23" t="n">
-        <v>14.51092369816588</v>
+        <v>6.329963381531822</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>104.2</v>
+        <v>26.8</v>
       </c>
       <c r="O23" t="n">
-        <v>39.5</v>
+        <v>42.6</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>36.603</v>
+        <v>30.482</v>
       </c>
       <c r="T23" t="n">
-        <v>36.603</v>
+        <v>25.928</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.563</v>
+        <v>-23.452</v>
       </c>
       <c r="V23" t="n">
-        <v>-18.259</v>
+        <v>-25.928</v>
       </c>
       <c r="W23" t="n">
-        <v>-51.636</v>
+        <v>-33.565</v>
       </c>
     </row>
     <row r="24">
@@ -4401,12 +4396,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
+          <t>T3_kademeli_slot|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4422,29 +4417,29 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>45.0589059523848</v>
+        <v>27.77992254030131</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>3.452723024503923</v>
+        <v>-0.3947399939562279</v>
       </c>
       <c r="K24" t="n">
-        <v>4.973709971745888</v>
+        <v>7.725663662162252</v>
       </c>
       <c r="L24" t="n">
-        <v>28.80374524525355</v>
+        <v>23.0569407093583</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>64.5</v>
+        <v>136.9</v>
       </c>
       <c r="O24" t="n">
-        <v>41.5</v>
+        <v>47.5</v>
       </c>
       <c r="P24" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4455,35 +4450,35 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>18.867</v>
+        <v>14.102</v>
       </c>
       <c r="T24" t="n">
-        <v>18.867</v>
+        <v>14.102</v>
       </c>
       <c r="U24" t="n">
-        <v>78.093</v>
+        <v>53.388</v>
       </c>
       <c r="V24" t="n">
-        <v>43.297</v>
+        <v>43.828</v>
       </c>
       <c r="W24" t="n">
-        <v>-24.086</v>
+        <v>-19.852</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|coklu_zarf</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4498,42 +4493,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS</t>
+          <t>TRALT.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-13</t>
+          <t>TRALT.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>41.94189944051841</v>
+        <v>13.50616593082303</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>23.19304514092613</v>
+        <v>0.3486751900400487</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.90358254997626</v>
+        <v>5.455912207814473</v>
       </c>
       <c r="L25" t="n">
-        <v>5.815920071163994</v>
+        <v>11.73786427798399</v>
       </c>
       <c r="M25" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>32.2</v>
+        <v>129.5</v>
       </c>
       <c r="O25" t="n">
-        <v>56.9</v>
+        <v>47.5</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4541,28 +4536,28 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>13.863</v>
+        <v>13.751</v>
       </c>
       <c r="T25" t="n">
-        <v>13.863</v>
+        <v>13.751</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.416</v>
+        <v>35.855</v>
       </c>
       <c r="V25" t="n">
-        <v>-11.028</v>
+        <v>26.771</v>
       </c>
       <c r="W25" t="n">
-        <v>-14.579</v>
+        <v>-4.752</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4572,7 +4567,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4585,221 +4580,67 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CWENE.IS, RALYH.IS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CWENE.IS: 2026-08-12 | RALYH.IS: 2026-08-12</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>38.08584121207757</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>-17.85349092315649</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CWENE.IS: -2.47% / +0.00% / -3.11% | RALYH.IS: +2.91% / +2.93% / -0.99%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>14.85812229550152</v>
+        <v>-38.46787507721694</v>
       </c>
       <c r="K26" t="n">
-        <v>-10.35969645108858</v>
+        <v>6.144711297826366</v>
       </c>
       <c r="L26" t="n">
-        <v>3.605272693289541</v>
+        <v>49.48136135333956</v>
       </c>
       <c r="M26" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>39.2</v>
+        <v>120</v>
       </c>
       <c r="O26" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="P26" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>22.794</v>
+        <v>23.673</v>
       </c>
       <c r="T26" t="n">
-        <v>22.794</v>
+        <v>21.907</v>
       </c>
       <c r="U26" t="n">
-        <v>-17.177</v>
+        <v>16.355</v>
       </c>
       <c r="V26" t="n">
-        <v>-19.815</v>
+        <v>23.44</v>
       </c>
       <c r="W26" t="n">
-        <v>-24.453</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, BRYAT.IS, BSOKE.IS, ECILC.IS, ENKAI.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-11 | BRYAT.IS: 2026-08-13 | BSOKE.IS: 2026-08-05 | ECILC.IS: 2026-08-05 | ENKAI.IS: 2026-08-13</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>13.96656699373973</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +0.84% / +3.73% / -2.69% | BRYAT.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +1.91% / +4.22% / -2.40% | ECILC.IS: +11.67% / +13.93% / -1.57% | ENKAI.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>-7.503658754890596</v>
-      </c>
-      <c r="K27" t="n">
-        <v>6.799316168838421</v>
-      </c>
-      <c r="L27" t="n">
-        <v>26.13605890970743</v>
-      </c>
-      <c r="M27" t="n">
-        <v>100</v>
-      </c>
-      <c r="N27" t="n">
-        <v>175.1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>21.464</v>
-      </c>
-      <c r="T27" t="n">
-        <v>21.464</v>
-      </c>
-      <c r="U27" t="n">
-        <v>27.556</v>
-      </c>
-      <c r="V27" t="n">
-        <v>17.534</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-7.587</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>T4_konsensus|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>8.326900458734343</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>-8.030096457283253</v>
-      </c>
-      <c r="K28" t="n">
-        <v>11.24844055823626</v>
-      </c>
-      <c r="L28" t="n">
-        <v>15.1193724336431</v>
-      </c>
-      <c r="M28" t="n">
-        <v>72.22222222222221</v>
-      </c>
-      <c r="N28" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="O28" t="n">
-        <v>45</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>12.679</v>
-      </c>
-      <c r="T28" t="n">
-        <v>10.364</v>
-      </c>
-      <c r="U28" t="n">
-        <v>32.693</v>
-      </c>
-      <c r="V28" t="n">
-        <v>17.425</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-5.555</v>
+        <v>-19.255</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -587,7 +587,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -753,17 +753,17 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>71.7096707191417</v>
+        <v>71.70967223366058</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>10.52140217505859</v>
+        <v>10.52140120974327</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-1.210370781379311e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>25.61349479378329</v>
+        <v>25.6134921875</v>
       </c>
       <c r="M3" t="n">
         <v>83.33333333333334</v>
@@ -828,17 +828,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>71.14835325524578</v>
+        <v>71.1483564365692</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>37.83905010537829</v>
+        <v>37.83904503746869</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.929523572966308</v>
+        <v>-2.929522243797422</v>
       </c>
       <c r="L4" t="n">
-        <v>12.6166884158664</v>
+        <v>12.61668847159575</v>
       </c>
       <c r="M4" t="n">
         <v>83.33333333333334</v>
@@ -902,39 +902,39 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CWENE.IS</t>
+          <t>BRSAN.IS, OYAKC.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CWENE.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>67.61086137129925</v>
+        <v>67.61086897684163</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.58% / +3.42% / -1.11% | CWENE.IS: -2.43% / +0.00% / -3.06%</t>
+          <t>BRSAN.IS: -0.26% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23.38198980936981</v>
+        <v>23.38199081518826</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.027470517574</v>
+        <v>-21.55441490254855</v>
       </c>
       <c r="L5" t="n">
-        <v>17.05327546391042</v>
+        <v>17.053274561763</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>136.4</v>
+        <v>136.9</v>
       </c>
       <c r="O5" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="P5" t="n">
         <v>2.9</v>
@@ -948,19 +948,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.946</v>
+        <v>31.406</v>
       </c>
       <c r="T5" t="n">
-        <v>30.946</v>
+        <v>31.406</v>
       </c>
       <c r="U5" t="n">
-        <v>48.388</v>
+        <v>47.398</v>
       </c>
       <c r="V5" t="n">
-        <v>8.683999999999999</v>
+        <v>7.959</v>
       </c>
       <c r="W5" t="n">
-        <v>-66.497</v>
+        <v>-67.488</v>
       </c>
     </row>
     <row r="6">
@@ -990,17 +990,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>71.14835325524578</v>
+        <v>71.1483564365692</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>37.83905010537829</v>
+        <v>37.83904503746869</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.929523572966308</v>
+        <v>-2.929522243797422</v>
       </c>
       <c r="L6" t="n">
-        <v>12.6166884158664</v>
+        <v>12.61668847159575</v>
       </c>
       <c r="M6" t="n">
         <v>83.33333333333334</v>
@@ -1065,17 +1065,17 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>60.15988621066983</v>
+        <v>60.15988351316175</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>29.41081527100167</v>
+        <v>29.4108103819297</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4732772020725418</v>
+        <v>-0.4732783336371393</v>
       </c>
       <c r="L7" t="n">
-        <v>12.39638337363852</v>
+        <v>12.39638328010337</v>
       </c>
       <c r="M7" t="n">
         <v>72.22222222222221</v>
@@ -1139,39 +1139,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CWENE.IS</t>
+          <t>BRSAN.IS, OYAKC.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CWENE.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>67.61086137129925</v>
+        <v>67.61086897684163</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.58% / +3.42% / -1.11% | CWENE.IS: -2.43% / +0.00% / -3.06%</t>
+          <t>BRSAN.IS: -0.26% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>23.38198980936981</v>
+        <v>23.38199081518826</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.027470517574</v>
+        <v>-21.55441490254855</v>
       </c>
       <c r="L8" t="n">
-        <v>17.05327546391042</v>
+        <v>17.053274561763</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>136.4</v>
+        <v>136.9</v>
       </c>
       <c r="O8" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="P8" t="n">
         <v>2.9</v>
@@ -1185,19 +1185,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>30.946</v>
+        <v>31.406</v>
       </c>
       <c r="T8" t="n">
-        <v>30.946</v>
+        <v>31.406</v>
       </c>
       <c r="U8" t="n">
-        <v>48.388</v>
+        <v>47.398</v>
       </c>
       <c r="V8" t="n">
-        <v>8.683999999999999</v>
+        <v>7.959</v>
       </c>
       <c r="W8" t="n">
-        <v>-66.497</v>
+        <v>-67.488</v>
       </c>
     </row>
     <row r="9">
@@ -1227,17 +1227,17 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>66.49721870311937</v>
+        <v>66.49721725529525</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>34.09313051933771</v>
+        <v>34.09313515588226</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.193644082521985e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>10.66215926594336</v>
+        <v>10.6621618758353</v>
       </c>
       <c r="M9" t="n">
         <v>72.22222222222221</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>36.78585504819178</v>
+        <v>36.78585803744296</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1318,13 +1318,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>21.23845504164525</v>
+        <v>21.23845403639202</v>
       </c>
       <c r="K10" t="n">
-        <v>-22.80856515541238</v>
+        <v>-23.70303440323126</v>
       </c>
       <c r="L10" t="n">
-        <v>6.958481500131142</v>
+        <v>6.958484193025216</v>
       </c>
       <c r="M10" t="n">
         <v>72.22222222222221</v>
@@ -1347,19 +1347,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>28.807</v>
+        <v>29.632</v>
       </c>
       <c r="T10" t="n">
-        <v>28.807</v>
+        <v>29.632</v>
       </c>
       <c r="U10" t="n">
-        <v>0.926</v>
+        <v>-0.244</v>
       </c>
       <c r="V10" t="n">
-        <v>-12.051</v>
+        <v>-13.07</v>
       </c>
       <c r="W10" t="n">
-        <v>-40.838</v>
+        <v>-42.007</v>
       </c>
     </row>
     <row r="11">
@@ -1389,17 +1389,17 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>60.15988621066983</v>
+        <v>60.15988351316175</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>29.41081527100167</v>
+        <v>29.4108103819297</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4732772020725418</v>
+        <v>-0.4732783336371393</v>
       </c>
       <c r="L11" t="n">
-        <v>12.39638337363852</v>
+        <v>12.39638328010337</v>
       </c>
       <c r="M11" t="n">
         <v>72.22222222222221</v>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>15.69318443671461</v>
+        <v>15.69318442167043</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -2.48% / +4.30% / -2.97% | BRSAN.IS: +8.20% / +12.54% / -2.42%</t>
+          <t>ARCLK.IS: -2.73% / +4.30% / -2.97% | BRSAN.IS: +8.54% / +12.54% / -2.42%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2.170155878001112</v>
+        <v>2.170157264886741</v>
       </c>
       <c r="K12" t="n">
-        <v>29.25303854891397</v>
+        <v>29.30614661508311</v>
       </c>
       <c r="L12" t="n">
-        <v>16.59988022061277</v>
+        <v>16.59987690736074</v>
       </c>
       <c r="M12" t="n">
         <v>72.22222222222221</v>
@@ -1515,13 +1515,13 @@
         <v>11.893</v>
       </c>
       <c r="U12" t="n">
-        <v>58.763</v>
+        <v>58.829</v>
       </c>
       <c r="V12" t="n">
-        <v>47.144</v>
+        <v>47.204</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.082</v>
+        <v>-4.017</v>
       </c>
     </row>
     <row r="13">
@@ -1551,17 +1551,17 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>14.91975365488964</v>
+        <v>14.91975714093474</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-6.722612060786748</v>
+        <v>-6.722611259504041</v>
       </c>
       <c r="K13" t="n">
-        <v>9.530994557902584</v>
+        <v>9.530992240556714</v>
       </c>
       <c r="L13" t="n">
-        <v>25.87645235296805</v>
+        <v>25.876453125</v>
       </c>
       <c r="M13" t="n">
         <v>66.66666666666666</v>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19.66188721503979</v>
+        <v>19.66188612652675</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2.869534524659589</v>
+        <v>2.869524013514457</v>
       </c>
       <c r="K14" t="n">
-        <v>4.029282486825658</v>
+        <v>4.029249565700943</v>
       </c>
       <c r="L14" t="n">
-        <v>9.611326813483668</v>
+        <v>9.611322526719135</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -1839,17 +1839,17 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>71.7096707191417</v>
+        <v>71.70967223366058</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>10.52140217505859</v>
+        <v>10.52140120974327</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-1.210370781379311e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>25.61349479378329</v>
+        <v>25.6134921875</v>
       </c>
       <c r="M18" t="n">
         <v>83.33333333333334</v>
@@ -1916,17 +1916,17 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>71.14835325524578</v>
+        <v>71.1483564365692</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>37.83905010537829</v>
+        <v>37.83904503746869</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.929523572966308</v>
+        <v>-2.929522243797422</v>
       </c>
       <c r="L19" t="n">
-        <v>12.6166884158664</v>
+        <v>12.61668847159575</v>
       </c>
       <c r="M19" t="n">
         <v>83.33333333333334</v>
@@ -1992,39 +1992,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CWENE.IS</t>
+          <t>BRSAN.IS, OYAKC.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CWENE.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>67.61086137129925</v>
+        <v>67.61086897684163</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.58% / +3.42% / -1.11% | CWENE.IS: -2.43% / +0.00% / -3.06%</t>
+          <t>BRSAN.IS: -0.26% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>23.38198980936981</v>
+        <v>23.38199081518826</v>
       </c>
       <c r="K20" t="n">
-        <v>-21.027470517574</v>
+        <v>-21.55441490254855</v>
       </c>
       <c r="L20" t="n">
-        <v>17.05327546391042</v>
+        <v>17.053274561763</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>136.4</v>
+        <v>136.9</v>
       </c>
       <c r="O20" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="P20" t="n">
         <v>2.9</v>
@@ -2038,19 +2038,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>30.946</v>
+        <v>31.406</v>
       </c>
       <c r="T20" t="n">
-        <v>30.946</v>
+        <v>31.406</v>
       </c>
       <c r="U20" t="n">
-        <v>48.388</v>
+        <v>47.398</v>
       </c>
       <c r="V20" t="n">
-        <v>8.683999999999999</v>
+        <v>7.959</v>
       </c>
       <c r="W20" t="n">
-        <v>-66.497</v>
+        <v>-67.488</v>
       </c>
     </row>
     <row r="21">
@@ -2082,17 +2082,17 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>66.49721870311937</v>
+        <v>66.49721725529525</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>34.09313051933771</v>
+        <v>34.09313515588226</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3.193644082521985e-06</v>
       </c>
       <c r="L21" t="n">
-        <v>10.66215926594336</v>
+        <v>10.6621618758353</v>
       </c>
       <c r="M21" t="n">
         <v>72.22222222222221</v>
@@ -2159,17 +2159,17 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>60.15988621066983</v>
+        <v>60.15988351316175</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>29.41081527100167</v>
+        <v>29.4108103819297</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4732772020725418</v>
+        <v>-0.4732783336371393</v>
       </c>
       <c r="L22" t="n">
-        <v>12.39638337363852</v>
+        <v>12.39638328010337</v>
       </c>
       <c r="M22" t="n">
         <v>72.22222222222221</v>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>36.78585504819178</v>
+        <v>36.78585803744296</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>21.23845504164525</v>
+        <v>21.23845403639202</v>
       </c>
       <c r="K23" t="n">
-        <v>-22.80856515541238</v>
+        <v>-23.70303440323126</v>
       </c>
       <c r="L23" t="n">
-        <v>6.958481500131142</v>
+        <v>6.958484193025216</v>
       </c>
       <c r="M23" t="n">
         <v>72.22222222222221</v>
@@ -2281,19 +2281,19 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>28.807</v>
+        <v>29.632</v>
       </c>
       <c r="T23" t="n">
-        <v>28.807</v>
+        <v>29.632</v>
       </c>
       <c r="U23" t="n">
-        <v>0.926</v>
+        <v>-0.244</v>
       </c>
       <c r="V23" t="n">
-        <v>-12.051</v>
+        <v>-13.07</v>
       </c>
       <c r="W23" t="n">
-        <v>-40.838</v>
+        <v>-42.007</v>
       </c>
     </row>
     <row r="24">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>19.66188721503979</v>
+        <v>19.66188612652675</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2341,13 +2341,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2.869534524659589</v>
+        <v>2.869524013514457</v>
       </c>
       <c r="K24" t="n">
-        <v>4.029282486825658</v>
+        <v>4.029249565700943</v>
       </c>
       <c r="L24" t="n">
-        <v>9.611326813483668</v>
+        <v>9.611322526719135</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
@@ -2422,21 +2422,21 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>15.69318443671461</v>
+        <v>15.69318442167043</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -2.48% / +4.30% / -2.97% | BRSAN.IS: +8.20% / +12.54% / -2.42%</t>
+          <t>ARCLK.IS: -2.73% / +4.30% / -2.97% | BRSAN.IS: +8.54% / +12.54% / -2.42%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2.170155878001112</v>
+        <v>2.170157264886741</v>
       </c>
       <c r="K25" t="n">
-        <v>29.25303854891397</v>
+        <v>29.30614661508311</v>
       </c>
       <c r="L25" t="n">
-        <v>16.59988022061277</v>
+        <v>16.59987690736074</v>
       </c>
       <c r="M25" t="n">
         <v>72.22222222222221</v>
@@ -2465,13 +2465,13 @@
         <v>11.893</v>
       </c>
       <c r="U25" t="n">
-        <v>58.763</v>
+        <v>58.829</v>
       </c>
       <c r="V25" t="n">
-        <v>47.144</v>
+        <v>47.204</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.082</v>
+        <v>-4.017</v>
       </c>
     </row>
     <row r="26">
@@ -2503,17 +2503,17 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>14.91975365488964</v>
+        <v>14.91975714093474</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>-6.722612060786748</v>
+        <v>-6.722611259504041</v>
       </c>
       <c r="K26" t="n">
-        <v>9.530994557902584</v>
+        <v>9.530992240556714</v>
       </c>
       <c r="L26" t="n">
-        <v>25.87645235296805</v>
+        <v>25.876453125</v>
       </c>
       <c r="M26" t="n">
         <v>66.66666666666666</v>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>73.55709251838034</v>
+        <v>73.55709052781789</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>24.91776733953206</v>
+        <v>24.91776691656204</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.76800334617383</v>
+        <v>-18.6497321418215</v>
       </c>
       <c r="L3" t="n">
-        <v>17.14344531576387</v>
+        <v>17.14344300175863</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
@@ -2794,19 +2794,19 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>30.582</v>
+        <v>30.481</v>
       </c>
       <c r="T3" t="n">
-        <v>30.582</v>
+        <v>30.481</v>
       </c>
       <c r="U3" t="n">
-        <v>13.295</v>
+        <v>13.46</v>
       </c>
       <c r="V3" t="n">
-        <v>4.469</v>
+        <v>4.621</v>
       </c>
       <c r="W3" t="n">
-        <v>-49.911</v>
+        <v>-49.746</v>
       </c>
     </row>
     <row r="4">
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.55709251838034</v>
+        <v>73.55709052781789</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>24.91776733953206</v>
+        <v>24.91776691656204</v>
       </c>
       <c r="K4" t="n">
-        <v>-18.76800334617383</v>
+        <v>-18.6497321418215</v>
       </c>
       <c r="L4" t="n">
-        <v>17.14344531576387</v>
+        <v>17.14344300175863</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
@@ -2881,19 +2881,19 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>30.582</v>
+        <v>30.481</v>
       </c>
       <c r="T4" t="n">
-        <v>30.582</v>
+        <v>30.481</v>
       </c>
       <c r="U4" t="n">
-        <v>13.295</v>
+        <v>13.46</v>
       </c>
       <c r="V4" t="n">
-        <v>4.469</v>
+        <v>4.621</v>
       </c>
       <c r="W4" t="n">
-        <v>-49.911</v>
+        <v>-49.746</v>
       </c>
     </row>
     <row r="5">
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>69.61349897281856</v>
+        <v>69.61350586989693</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33% | TRMET.IS: +10.78% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +14.21% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>43.30442621244415</v>
+        <v>43.30443180651103</v>
       </c>
       <c r="K5" t="n">
-        <v>-20.22131847683636</v>
+        <v>-19.79059845634175</v>
       </c>
       <c r="L5" t="n">
-        <v>9.921568402707182</v>
+        <v>9.921570716242634</v>
       </c>
       <c r="M5" t="n">
         <v>83.33333333333334</v>
@@ -2968,19 +2968,19 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>25.753</v>
+        <v>25.352</v>
       </c>
       <c r="T5" t="n">
-        <v>25.753</v>
+        <v>25.352</v>
       </c>
       <c r="U5" t="n">
-        <v>5.193</v>
+        <v>5.761</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.549</v>
+        <v>-7.05</v>
       </c>
       <c r="W5" t="n">
-        <v>-36.487</v>
+        <v>-35.919</v>
       </c>
     </row>
     <row r="6">
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69.61349897281856</v>
+        <v>69.61350586989693</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33% | TRMET.IS: +10.78% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +14.21% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>43.30442621244415</v>
+        <v>43.30443180651103</v>
       </c>
       <c r="K6" t="n">
-        <v>-20.22131847683636</v>
+        <v>-19.79059845634175</v>
       </c>
       <c r="L6" t="n">
-        <v>9.921568402707182</v>
+        <v>9.921570716242634</v>
       </c>
       <c r="M6" t="n">
         <v>83.33333333333334</v>
@@ -3055,19 +3055,19 @@
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>25.753</v>
+        <v>25.352</v>
       </c>
       <c r="T6" t="n">
-        <v>25.753</v>
+        <v>25.352</v>
       </c>
       <c r="U6" t="n">
-        <v>5.193</v>
+        <v>5.761</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.549</v>
+        <v>-7.05</v>
       </c>
       <c r="W6" t="n">
-        <v>-36.487</v>
+        <v>-35.919</v>
       </c>
     </row>
     <row r="7">
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.64484083015594</v>
+        <v>71.64483370334607</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>34.63451047134283</v>
+        <v>34.63450038557985</v>
       </c>
       <c r="K7" t="n">
-        <v>-13.94852559003611</v>
+        <v>-13.82323922004988</v>
       </c>
       <c r="L7" t="n">
-        <v>15.76726292384321</v>
+        <v>15.76726005038759</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
@@ -3142,19 +3142,19 @@
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="T7" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="U7" t="n">
-        <v>17.64</v>
+        <v>17.811</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.18</v>
+        <v>-0.034</v>
       </c>
       <c r="W7" t="n">
-        <v>-39.583</v>
+        <v>-39.411</v>
       </c>
     </row>
     <row r="8">
@@ -3192,21 +3192,21 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>71.64484083015594</v>
+        <v>71.64483370334607</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>34.63451047134283</v>
+        <v>34.63450038557985</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.94852559003611</v>
+        <v>-13.82323922004988</v>
       </c>
       <c r="L8" t="n">
-        <v>15.76726292384321</v>
+        <v>15.76726005038759</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -3229,19 +3229,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="T8" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="U8" t="n">
-        <v>17.64</v>
+        <v>17.811</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.18</v>
+        <v>-0.034</v>
       </c>
       <c r="W8" t="n">
-        <v>-39.583</v>
+        <v>-39.411</v>
       </c>
     </row>
     <row r="9">
@@ -3279,21 +3279,21 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>69.61349897281856</v>
+        <v>69.61350586989693</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33% | TRMET.IS: +10.78% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +14.21% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>43.30442621244415</v>
+        <v>43.30443180651103</v>
       </c>
       <c r="K9" t="n">
-        <v>-20.22131847683636</v>
+        <v>-19.79059845634175</v>
       </c>
       <c r="L9" t="n">
-        <v>9.921568402707182</v>
+        <v>9.921570716242634</v>
       </c>
       <c r="M9" t="n">
         <v>83.33333333333334</v>
@@ -3316,19 +3316,19 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>25.753</v>
+        <v>25.352</v>
       </c>
       <c r="T9" t="n">
-        <v>25.753</v>
+        <v>25.352</v>
       </c>
       <c r="U9" t="n">
-        <v>5.193</v>
+        <v>5.761</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.549</v>
+        <v>-7.05</v>
       </c>
       <c r="W9" t="n">
-        <v>-36.487</v>
+        <v>-35.919</v>
       </c>
     </row>
     <row r="10">
@@ -3358,17 +3358,17 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>31.1518364332128</v>
+        <v>31.15183851699386</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>14.46262836377386</v>
+        <v>14.46263148924893</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.72549823041446</v>
+        <v>-12.53733793376361</v>
       </c>
       <c r="L10" t="n">
-        <v>6.329963381531822</v>
+        <v>6.329965794996994</v>
       </c>
       <c r="M10" t="n">
         <v>44.44444444444444</v>
@@ -3391,19 +3391,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>30.482</v>
+        <v>30.337</v>
       </c>
       <c r="T10" t="n">
-        <v>25.928</v>
+        <v>25.773</v>
       </c>
       <c r="U10" t="n">
-        <v>-23.452</v>
+        <v>-23.287</v>
       </c>
       <c r="V10" t="n">
-        <v>-25.928</v>
+        <v>-25.768</v>
       </c>
       <c r="W10" t="n">
-        <v>-33.565</v>
+        <v>-33.4</v>
       </c>
     </row>
     <row r="11">
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>71.64484083015594</v>
+        <v>71.64483370334607</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34.63451047134283</v>
+        <v>34.63450038557985</v>
       </c>
       <c r="K11" t="n">
-        <v>-13.94852559003611</v>
+        <v>-13.82323922004988</v>
       </c>
       <c r="L11" t="n">
-        <v>15.76726292384321</v>
+        <v>15.76726005038759</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
@@ -3478,19 +3478,19 @@
         <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="T11" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="U11" t="n">
-        <v>17.64</v>
+        <v>17.811</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.18</v>
+        <v>-0.034</v>
       </c>
       <c r="W11" t="n">
-        <v>-39.583</v>
+        <v>-39.411</v>
       </c>
     </row>
     <row r="12">
@@ -3520,17 +3520,17 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>27.77992254030131</v>
+        <v>27.77992134829283</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-0.3947399939562279</v>
+        <v>-0.3947387514697143</v>
       </c>
       <c r="K12" t="n">
-        <v>7.725663662162252</v>
+        <v>9.772255138930541</v>
       </c>
       <c r="L12" t="n">
-        <v>23.0569407093583</v>
+        <v>23.0569390189834</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
@@ -3559,13 +3559,13 @@
         <v>14.102</v>
       </c>
       <c r="U12" t="n">
-        <v>53.388</v>
+        <v>56.302</v>
       </c>
       <c r="V12" t="n">
-        <v>43.828</v>
+        <v>46.561</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.852</v>
+        <v>-16.938</v>
       </c>
     </row>
     <row r="13">
@@ -3599,34 +3599,34 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-12 | RALYH.IS: 2026-08-12</t>
+          <t>CWENE.IS: 2026-08-13 | RALYH.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-17.85349092315649</v>
+        <v>-17.85349196318069</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CWENE.IS: -2.47% / +0.00% / -3.11% | RALYH.IS: +2.91% / +2.93% / -0.99%</t>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +4.71% / +5.79% / -0.98%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-38.46787507721694</v>
+        <v>-38.46787682799764</v>
       </c>
       <c r="K13" t="n">
-        <v>6.144711297826366</v>
+        <v>6.2585456346961</v>
       </c>
       <c r="L13" t="n">
-        <v>49.48136135333956</v>
+        <v>49.48136038965337</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="O13" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
@@ -3646,13 +3646,13 @@
         <v>21.907</v>
       </c>
       <c r="U13" t="n">
-        <v>16.355</v>
+        <v>16.48</v>
       </c>
       <c r="V13" t="n">
-        <v>23.44</v>
+        <v>23.572</v>
       </c>
       <c r="W13" t="n">
-        <v>-19.255</v>
+        <v>-19.13</v>
       </c>
     </row>
     <row r="14">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13.50616593082303</v>
+        <v>13.50616295266203</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3698,13 +3698,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.3486751900400487</v>
+        <v>0.3486754611526699</v>
       </c>
       <c r="K14" t="n">
-        <v>5.455912207814473</v>
+        <v>6.202674078687576</v>
       </c>
       <c r="L14" t="n">
-        <v>11.73786427798399</v>
+        <v>11.73786047909323</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -3733,13 +3733,13 @@
         <v>13.751</v>
       </c>
       <c r="U14" t="n">
-        <v>35.855</v>
+        <v>36.817</v>
       </c>
       <c r="V14" t="n">
-        <v>26.771</v>
+        <v>27.669</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.752</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="16">
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>73.55709251838034</v>
+        <v>73.55709052781789</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>24.91776733953206</v>
+        <v>24.91776691656204</v>
       </c>
       <c r="K18" t="n">
-        <v>-18.76800334617383</v>
+        <v>-18.6497321418215</v>
       </c>
       <c r="L18" t="n">
-        <v>17.14344531576387</v>
+        <v>17.14344300175863</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
@@ -3940,19 +3940,19 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>30.582</v>
+        <v>30.481</v>
       </c>
       <c r="T18" t="n">
-        <v>30.582</v>
+        <v>30.481</v>
       </c>
       <c r="U18" t="n">
-        <v>13.295</v>
+        <v>13.46</v>
       </c>
       <c r="V18" t="n">
-        <v>4.469</v>
+        <v>4.621</v>
       </c>
       <c r="W18" t="n">
-        <v>-49.911</v>
+        <v>-49.746</v>
       </c>
     </row>
     <row r="19">
@@ -3992,21 +3992,21 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>73.55709251838034</v>
+        <v>73.55709052781789</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>24.91776733953206</v>
+        <v>24.91776691656204</v>
       </c>
       <c r="K19" t="n">
-        <v>-18.76800334617383</v>
+        <v>-18.6497321418215</v>
       </c>
       <c r="L19" t="n">
-        <v>17.14344531576387</v>
+        <v>17.14344300175863</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
@@ -4029,19 +4029,19 @@
         <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.582</v>
+        <v>30.481</v>
       </c>
       <c r="T19" t="n">
-        <v>30.582</v>
+        <v>30.481</v>
       </c>
       <c r="U19" t="n">
-        <v>13.295</v>
+        <v>13.46</v>
       </c>
       <c r="V19" t="n">
-        <v>4.469</v>
+        <v>4.621</v>
       </c>
       <c r="W19" t="n">
-        <v>-49.911</v>
+        <v>-49.746</v>
       </c>
     </row>
     <row r="20">
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>71.64484083015594</v>
+        <v>71.64483370334607</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>34.63451047134283</v>
+        <v>34.63450038557985</v>
       </c>
       <c r="K20" t="n">
-        <v>-13.94852559003611</v>
+        <v>-13.82323922004988</v>
       </c>
       <c r="L20" t="n">
-        <v>15.76726292384321</v>
+        <v>15.76726005038759</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
@@ -4118,19 +4118,19 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="T20" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="U20" t="n">
-        <v>17.64</v>
+        <v>17.811</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.18</v>
+        <v>-0.034</v>
       </c>
       <c r="W20" t="n">
-        <v>-39.583</v>
+        <v>-39.411</v>
       </c>
     </row>
     <row r="21">
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>71.64484083015594</v>
+        <v>71.64483370334607</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>34.63451047134283</v>
+        <v>34.63450038557985</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.94852559003611</v>
+        <v>-13.82323922004988</v>
       </c>
       <c r="L21" t="n">
-        <v>15.76726292384321</v>
+        <v>15.76726005038759</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -4207,19 +4207,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="T21" t="n">
-        <v>25.176</v>
+        <v>25.067</v>
       </c>
       <c r="U21" t="n">
-        <v>17.64</v>
+        <v>17.811</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.18</v>
+        <v>-0.034</v>
       </c>
       <c r="W21" t="n">
-        <v>-39.583</v>
+        <v>-39.411</v>
       </c>
     </row>
     <row r="22">
@@ -4259,21 +4259,21 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>69.61349897281856</v>
+        <v>69.61350586989693</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.63% / +3.37% / -1.16% | ENJSA.IS: +0.21% / +1.82% / -0.33% | TRMET.IS: +10.78% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +14.21% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>43.30442621244415</v>
+        <v>43.30443180651103</v>
       </c>
       <c r="K22" t="n">
-        <v>-20.22131847683636</v>
+        <v>-19.79059845634175</v>
       </c>
       <c r="L22" t="n">
-        <v>9.921568402707182</v>
+        <v>9.921570716242634</v>
       </c>
       <c r="M22" t="n">
         <v>83.33333333333334</v>
@@ -4296,19 +4296,19 @@
         <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>25.753</v>
+        <v>25.352</v>
       </c>
       <c r="T22" t="n">
-        <v>25.753</v>
+        <v>25.352</v>
       </c>
       <c r="U22" t="n">
-        <v>5.193</v>
+        <v>5.761</v>
       </c>
       <c r="V22" t="n">
-        <v>-7.549</v>
+        <v>-7.05</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.487</v>
+        <v>-35.919</v>
       </c>
     </row>
     <row r="23">
@@ -4340,17 +4340,17 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>31.1518364332128</v>
+        <v>31.15183851699386</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>14.46262836377386</v>
+        <v>14.46263148924893</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.72549823041446</v>
+        <v>-12.53733793376361</v>
       </c>
       <c r="L23" t="n">
-        <v>6.329963381531822</v>
+        <v>6.329965794996994</v>
       </c>
       <c r="M23" t="n">
         <v>44.44444444444444</v>
@@ -4373,19 +4373,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>30.482</v>
+        <v>30.337</v>
       </c>
       <c r="T23" t="n">
-        <v>25.928</v>
+        <v>25.773</v>
       </c>
       <c r="U23" t="n">
-        <v>-23.452</v>
+        <v>-23.287</v>
       </c>
       <c r="V23" t="n">
-        <v>-25.928</v>
+        <v>-25.768</v>
       </c>
       <c r="W23" t="n">
-        <v>-33.565</v>
+        <v>-33.4</v>
       </c>
     </row>
     <row r="24">
@@ -4417,17 +4417,17 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>27.77992254030131</v>
+        <v>27.77992134829283</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-0.3947399939562279</v>
+        <v>-0.3947387514697143</v>
       </c>
       <c r="K24" t="n">
-        <v>7.725663662162252</v>
+        <v>9.772255138930541</v>
       </c>
       <c r="L24" t="n">
-        <v>23.0569407093583</v>
+        <v>23.0569390189834</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
@@ -4456,13 +4456,13 @@
         <v>14.102</v>
       </c>
       <c r="U24" t="n">
-        <v>53.388</v>
+        <v>56.302</v>
       </c>
       <c r="V24" t="n">
-        <v>43.828</v>
+        <v>46.561</v>
       </c>
       <c r="W24" t="n">
-        <v>-19.852</v>
+        <v>-16.938</v>
       </c>
     </row>
     <row r="25">
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.50616593082303</v>
+        <v>13.50616295266203</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4510,13 +4510,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.3486751900400487</v>
+        <v>0.3486754611526699</v>
       </c>
       <c r="K25" t="n">
-        <v>5.455912207814473</v>
+        <v>6.202674078687576</v>
       </c>
       <c r="L25" t="n">
-        <v>11.73786427798399</v>
+        <v>11.73786047909323</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
@@ -4545,13 +4545,13 @@
         <v>13.751</v>
       </c>
       <c r="U25" t="n">
-        <v>35.855</v>
+        <v>36.817</v>
       </c>
       <c r="V25" t="n">
-        <v>26.771</v>
+        <v>27.669</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.752</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="26">
@@ -4587,34 +4587,34 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-12 | RALYH.IS: 2026-08-12</t>
+          <t>CWENE.IS: 2026-08-13 | RALYH.IS: 2026-08-12</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-17.85349092315649</v>
+        <v>-17.85349196318069</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CWENE.IS: -2.47% / +0.00% / -3.11% | RALYH.IS: +2.91% / +2.93% / -0.99%</t>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +4.71% / +5.79% / -0.98%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-38.46787507721694</v>
+        <v>-38.46787682799764</v>
       </c>
       <c r="K26" t="n">
-        <v>6.144711297826366</v>
+        <v>6.2585456346961</v>
       </c>
       <c r="L26" t="n">
-        <v>49.48136135333956</v>
+        <v>49.48136038965337</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="O26" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
@@ -4634,13 +4634,13 @@
         <v>21.907</v>
       </c>
       <c r="U26" t="n">
-        <v>16.355</v>
+        <v>16.48</v>
       </c>
       <c r="V26" t="n">
-        <v>23.44</v>
+        <v>23.572</v>
       </c>
       <c r="W26" t="n">
-        <v>-19.255</v>
+        <v>-19.13</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -915,14 +915,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.26% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.18% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>23.38199081518826</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.55441490254855</v>
+        <v>-21.5225547760162</v>
       </c>
       <c r="L5" t="n">
         <v>17.053274561763</v>
@@ -948,19 +948,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>31.406</v>
+        <v>31.378</v>
       </c>
       <c r="T5" t="n">
-        <v>31.406</v>
+        <v>31.378</v>
       </c>
       <c r="U5" t="n">
-        <v>47.398</v>
+        <v>47.458</v>
       </c>
       <c r="V5" t="n">
-        <v>7.959</v>
+        <v>8.002000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-67.488</v>
+        <v>-67.428</v>
       </c>
     </row>
     <row r="6">
@@ -1152,14 +1152,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.26% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.18% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>23.38199081518826</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.55441490254855</v>
+        <v>-21.5225547760162</v>
       </c>
       <c r="L8" t="n">
         <v>17.053274561763</v>
@@ -1185,19 +1185,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.406</v>
+        <v>31.378</v>
       </c>
       <c r="T8" t="n">
-        <v>31.406</v>
+        <v>31.378</v>
       </c>
       <c r="U8" t="n">
-        <v>47.398</v>
+        <v>47.458</v>
       </c>
       <c r="V8" t="n">
-        <v>7.959</v>
+        <v>8.002000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>-67.488</v>
+        <v>-67.428</v>
       </c>
     </row>
     <row r="9">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -2.73% / +4.30% / -2.97% | BRSAN.IS: +8.54% / +12.54% / -2.42%</t>
+          <t>ARCLK.IS: -3.04% / +4.30% / -3.02% | BRSAN.IS: +8.63% / +12.54% / -2.42%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2.170157264886741</v>
       </c>
       <c r="K12" t="n">
-        <v>29.30614661508311</v>
+        <v>29.1651175531009</v>
       </c>
       <c r="L12" t="n">
         <v>16.59987690736074</v>
@@ -1515,13 +1515,13 @@
         <v>11.893</v>
       </c>
       <c r="U12" t="n">
-        <v>58.829</v>
+        <v>58.655</v>
       </c>
       <c r="V12" t="n">
-        <v>47.204</v>
+        <v>47.043</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.017</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="13">
@@ -1645,7 +1645,7 @@
         <v>2.869524013514457</v>
       </c>
       <c r="K14" t="n">
-        <v>4.029249565700943</v>
+        <v>4.029262319275073</v>
       </c>
       <c r="L14" t="n">
         <v>9.611322526719135</v>
@@ -2005,14 +2005,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.26% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.18% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>23.38199081518826</v>
       </c>
       <c r="K20" t="n">
-        <v>-21.55441490254855</v>
+        <v>-21.5225547760162</v>
       </c>
       <c r="L20" t="n">
         <v>17.053274561763</v>
@@ -2038,19 +2038,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>31.406</v>
+        <v>31.378</v>
       </c>
       <c r="T20" t="n">
-        <v>31.406</v>
+        <v>31.378</v>
       </c>
       <c r="U20" t="n">
-        <v>47.398</v>
+        <v>47.458</v>
       </c>
       <c r="V20" t="n">
-        <v>7.959</v>
+        <v>8.002000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-67.488</v>
+        <v>-67.428</v>
       </c>
     </row>
     <row r="21">
@@ -2344,7 +2344,7 @@
         <v>2.869524013514457</v>
       </c>
       <c r="K24" t="n">
-        <v>4.029249565700943</v>
+        <v>4.029262319275073</v>
       </c>
       <c r="L24" t="n">
         <v>9.611322526719135</v>
@@ -2426,14 +2426,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -2.73% / +4.30% / -2.97% | BRSAN.IS: +8.54% / +12.54% / -2.42%</t>
+          <t>ARCLK.IS: -3.04% / +4.30% / -3.02% | BRSAN.IS: +8.63% / +12.54% / -2.42%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>2.170157264886741</v>
       </c>
       <c r="K25" t="n">
-        <v>29.30614661508311</v>
+        <v>29.1651175531009</v>
       </c>
       <c r="L25" t="n">
         <v>16.59987690736074</v>
@@ -2465,13 +2465,13 @@
         <v>11.893</v>
       </c>
       <c r="U25" t="n">
-        <v>58.829</v>
+        <v>58.655</v>
       </c>
       <c r="V25" t="n">
-        <v>47.204</v>
+        <v>47.043</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.017</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="26">
@@ -2761,14 +2761,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>24.91776691656204</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.6497321418215</v>
+        <v>-18.62685445263705</v>
       </c>
       <c r="L3" t="n">
         <v>17.14344300175863</v>
@@ -2794,19 +2794,19 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>30.481</v>
+        <v>30.461</v>
       </c>
       <c r="T3" t="n">
-        <v>30.481</v>
+        <v>30.461</v>
       </c>
       <c r="U3" t="n">
-        <v>13.46</v>
+        <v>13.492</v>
       </c>
       <c r="V3" t="n">
-        <v>4.621</v>
+        <v>4.65</v>
       </c>
       <c r="W3" t="n">
-        <v>-49.746</v>
+        <v>-49.714</v>
       </c>
     </row>
     <row r="4">
@@ -2848,14 +2848,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>24.91776691656204</v>
       </c>
       <c r="K4" t="n">
-        <v>-18.6497321418215</v>
+        <v>-18.62685445263705</v>
       </c>
       <c r="L4" t="n">
         <v>17.14344300175863</v>
@@ -2881,19 +2881,19 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>30.481</v>
+        <v>30.461</v>
       </c>
       <c r="T4" t="n">
-        <v>30.481</v>
+        <v>30.461</v>
       </c>
       <c r="U4" t="n">
-        <v>13.46</v>
+        <v>13.492</v>
       </c>
       <c r="V4" t="n">
-        <v>4.621</v>
+        <v>4.65</v>
       </c>
       <c r="W4" t="n">
-        <v>-49.746</v>
+        <v>-49.714</v>
       </c>
     </row>
     <row r="5">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +14.21% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +12.59% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>43.30443180651103</v>
       </c>
       <c r="K5" t="n">
-        <v>-19.79059845634175</v>
+        <v>-19.93655816936733</v>
       </c>
       <c r="L5" t="n">
         <v>9.921570716242634</v>
@@ -2968,19 +2968,19 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>25.352</v>
+        <v>25.488</v>
       </c>
       <c r="T5" t="n">
-        <v>25.352</v>
+        <v>25.488</v>
       </c>
       <c r="U5" t="n">
-        <v>5.761</v>
+        <v>5.568</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.05</v>
+        <v>-7.219</v>
       </c>
       <c r="W5" t="n">
-        <v>-35.919</v>
+        <v>-36.111</v>
       </c>
     </row>
     <row r="6">
@@ -3022,14 +3022,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +14.21% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +12.59% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>43.30443180651103</v>
       </c>
       <c r="K6" t="n">
-        <v>-19.79059845634175</v>
+        <v>-19.93655816936733</v>
       </c>
       <c r="L6" t="n">
         <v>9.921570716242634</v>
@@ -3055,19 +3055,19 @@
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>25.352</v>
+        <v>25.488</v>
       </c>
       <c r="T6" t="n">
-        <v>25.352</v>
+        <v>25.488</v>
       </c>
       <c r="U6" t="n">
-        <v>5.761</v>
+        <v>5.568</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.05</v>
+        <v>-7.219</v>
       </c>
       <c r="W6" t="n">
-        <v>-35.919</v>
+        <v>-36.111</v>
       </c>
     </row>
     <row r="7">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K7" t="n">
-        <v>-13.82323922004988</v>
+        <v>-13.79900420276039</v>
       </c>
       <c r="L7" t="n">
         <v>15.76726005038759</v>
@@ -3142,19 +3142,19 @@
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="T7" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="U7" t="n">
-        <v>17.811</v>
+        <v>17.844</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.034</v>
+        <v>-0.006</v>
       </c>
       <c r="W7" t="n">
-        <v>-39.411</v>
+        <v>-39.378</v>
       </c>
     </row>
     <row r="8">
@@ -3196,14 +3196,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.82323922004988</v>
+        <v>-13.79900420276039</v>
       </c>
       <c r="L8" t="n">
         <v>15.76726005038759</v>
@@ -3229,19 +3229,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="T8" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="U8" t="n">
-        <v>17.811</v>
+        <v>17.844</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.034</v>
+        <v>-0.006</v>
       </c>
       <c r="W8" t="n">
-        <v>-39.411</v>
+        <v>-39.378</v>
       </c>
     </row>
     <row r="9">
@@ -3283,14 +3283,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +14.21% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +12.59% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>43.30443180651103</v>
       </c>
       <c r="K9" t="n">
-        <v>-19.79059845634175</v>
+        <v>-19.93655816936733</v>
       </c>
       <c r="L9" t="n">
         <v>9.921570716242634</v>
@@ -3316,19 +3316,19 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>25.352</v>
+        <v>25.488</v>
       </c>
       <c r="T9" t="n">
-        <v>25.352</v>
+        <v>25.488</v>
       </c>
       <c r="U9" t="n">
-        <v>5.761</v>
+        <v>5.568</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.05</v>
+        <v>-7.219</v>
       </c>
       <c r="W9" t="n">
-        <v>-35.919</v>
+        <v>-36.111</v>
       </c>
     </row>
     <row r="10">
@@ -3365,7 +3365,7 @@
         <v>14.46263148924893</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.53733793376361</v>
+        <v>-12.50094272570126</v>
       </c>
       <c r="L10" t="n">
         <v>6.329965794996994</v>
@@ -3397,13 +3397,13 @@
         <v>25.773</v>
       </c>
       <c r="U10" t="n">
-        <v>-23.287</v>
+        <v>-23.255</v>
       </c>
       <c r="V10" t="n">
-        <v>-25.768</v>
+        <v>-25.737</v>
       </c>
       <c r="W10" t="n">
-        <v>-33.4</v>
+        <v>-33.368</v>
       </c>
     </row>
     <row r="11">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K11" t="n">
-        <v>-13.82323922004988</v>
+        <v>-13.79900420276039</v>
       </c>
       <c r="L11" t="n">
         <v>15.76726005038759</v>
@@ -3478,19 +3478,19 @@
         <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="T11" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="U11" t="n">
-        <v>17.811</v>
+        <v>17.844</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.034</v>
+        <v>-0.006</v>
       </c>
       <c r="W11" t="n">
-        <v>-39.411</v>
+        <v>-39.378</v>
       </c>
     </row>
     <row r="12">
@@ -3527,7 +3527,7 @@
         <v>-0.3947387514697143</v>
       </c>
       <c r="K12" t="n">
-        <v>9.772255138930541</v>
+        <v>9.994834947859355</v>
       </c>
       <c r="L12" t="n">
         <v>23.0569390189834</v>
@@ -3559,13 +3559,13 @@
         <v>14.102</v>
       </c>
       <c r="U12" t="n">
-        <v>56.302</v>
+        <v>56.619</v>
       </c>
       <c r="V12" t="n">
-        <v>46.561</v>
+        <v>46.858</v>
       </c>
       <c r="W12" t="n">
-        <v>-16.938</v>
+        <v>-16.621</v>
       </c>
     </row>
     <row r="13">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-13 | RALYH.IS: 2026-08-12</t>
+          <t>CWENE.IS: 2026-08-13 | RALYH.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3607,14 +3607,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +4.71% / +5.79% / -0.98%</t>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-38.46787682799764</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2585456346961</v>
+        <v>7.138866265320409</v>
       </c>
       <c r="L13" t="n">
         <v>49.48136038965337</v>
@@ -3623,10 +3623,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>120.5</v>
+        <v>121</v>
       </c>
       <c r="O13" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
@@ -3646,13 +3646,13 @@
         <v>21.907</v>
       </c>
       <c r="U13" t="n">
-        <v>16.48</v>
+        <v>17.445</v>
       </c>
       <c r="V13" t="n">
-        <v>23.572</v>
+        <v>24.596</v>
       </c>
       <c r="W13" t="n">
-        <v>-19.13</v>
+        <v>-18.165</v>
       </c>
     </row>
     <row r="14">
@@ -3701,7 +3701,7 @@
         <v>0.3486754611526699</v>
       </c>
       <c r="K14" t="n">
-        <v>6.202674078687576</v>
+        <v>5.752084971784233</v>
       </c>
       <c r="L14" t="n">
         <v>11.73786047909323</v>
@@ -3733,13 +3733,13 @@
         <v>13.751</v>
       </c>
       <c r="U14" t="n">
-        <v>36.817</v>
+        <v>36.237</v>
       </c>
       <c r="V14" t="n">
-        <v>27.669</v>
+        <v>27.127</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.79</v>
+        <v>-4.371</v>
       </c>
     </row>
     <row r="16">
@@ -3907,14 +3907,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>24.91776691656204</v>
       </c>
       <c r="K18" t="n">
-        <v>-18.6497321418215</v>
+        <v>-18.62685445263705</v>
       </c>
       <c r="L18" t="n">
         <v>17.14344300175863</v>
@@ -3940,19 +3940,19 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>30.481</v>
+        <v>30.461</v>
       </c>
       <c r="T18" t="n">
-        <v>30.481</v>
+        <v>30.461</v>
       </c>
       <c r="U18" t="n">
-        <v>13.46</v>
+        <v>13.492</v>
       </c>
       <c r="V18" t="n">
-        <v>4.621</v>
+        <v>4.65</v>
       </c>
       <c r="W18" t="n">
-        <v>-49.746</v>
+        <v>-49.714</v>
       </c>
     </row>
     <row r="19">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>24.91776691656204</v>
       </c>
       <c r="K19" t="n">
-        <v>-18.6497321418215</v>
+        <v>-18.62685445263705</v>
       </c>
       <c r="L19" t="n">
         <v>17.14344300175863</v>
@@ -4029,19 +4029,19 @@
         <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.481</v>
+        <v>30.461</v>
       </c>
       <c r="T19" t="n">
-        <v>30.481</v>
+        <v>30.461</v>
       </c>
       <c r="U19" t="n">
-        <v>13.46</v>
+        <v>13.492</v>
       </c>
       <c r="V19" t="n">
-        <v>4.621</v>
+        <v>4.65</v>
       </c>
       <c r="W19" t="n">
-        <v>-49.746</v>
+        <v>-49.714</v>
       </c>
     </row>
     <row r="20">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K20" t="n">
-        <v>-13.82323922004988</v>
+        <v>-13.79900420276039</v>
       </c>
       <c r="L20" t="n">
         <v>15.76726005038759</v>
@@ -4118,19 +4118,19 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="T20" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="U20" t="n">
-        <v>17.811</v>
+        <v>17.844</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.034</v>
+        <v>-0.006</v>
       </c>
       <c r="W20" t="n">
-        <v>-39.411</v>
+        <v>-39.378</v>
       </c>
     </row>
     <row r="21">
@@ -4174,14 +4174,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.82323922004988</v>
+        <v>-13.79900420276039</v>
       </c>
       <c r="L21" t="n">
         <v>15.76726005038759</v>
@@ -4207,19 +4207,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="T21" t="n">
-        <v>25.067</v>
+        <v>25.046</v>
       </c>
       <c r="U21" t="n">
-        <v>17.811</v>
+        <v>17.844</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.034</v>
+        <v>-0.006</v>
       </c>
       <c r="W21" t="n">
-        <v>-39.411</v>
+        <v>-39.378</v>
       </c>
     </row>
     <row r="22">
@@ -4263,14 +4263,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.30% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +14.21% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +12.59% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>43.30443180651103</v>
       </c>
       <c r="K22" t="n">
-        <v>-19.79059845634175</v>
+        <v>-19.93655816936733</v>
       </c>
       <c r="L22" t="n">
         <v>9.921570716242634</v>
@@ -4296,19 +4296,19 @@
         <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>25.352</v>
+        <v>25.488</v>
       </c>
       <c r="T22" t="n">
-        <v>25.352</v>
+        <v>25.488</v>
       </c>
       <c r="U22" t="n">
-        <v>5.761</v>
+        <v>5.568</v>
       </c>
       <c r="V22" t="n">
-        <v>-7.05</v>
+        <v>-7.219</v>
       </c>
       <c r="W22" t="n">
-        <v>-35.919</v>
+        <v>-36.111</v>
       </c>
     </row>
     <row r="23">
@@ -4347,7 +4347,7 @@
         <v>14.46263148924893</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.53733793376361</v>
+        <v>-12.50094272570126</v>
       </c>
       <c r="L23" t="n">
         <v>6.329965794996994</v>
@@ -4379,13 +4379,13 @@
         <v>25.773</v>
       </c>
       <c r="U23" t="n">
-        <v>-23.287</v>
+        <v>-23.255</v>
       </c>
       <c r="V23" t="n">
-        <v>-25.768</v>
+        <v>-25.737</v>
       </c>
       <c r="W23" t="n">
-        <v>-33.4</v>
+        <v>-33.368</v>
       </c>
     </row>
     <row r="24">
@@ -4424,7 +4424,7 @@
         <v>-0.3947387514697143</v>
       </c>
       <c r="K24" t="n">
-        <v>9.772255138930541</v>
+        <v>9.994834947859355</v>
       </c>
       <c r="L24" t="n">
         <v>23.0569390189834</v>
@@ -4456,13 +4456,13 @@
         <v>14.102</v>
       </c>
       <c r="U24" t="n">
-        <v>56.302</v>
+        <v>56.619</v>
       </c>
       <c r="V24" t="n">
-        <v>46.561</v>
+        <v>46.858</v>
       </c>
       <c r="W24" t="n">
-        <v>-16.938</v>
+        <v>-16.621</v>
       </c>
     </row>
     <row r="25">
@@ -4513,7 +4513,7 @@
         <v>0.3486754611526699</v>
       </c>
       <c r="K25" t="n">
-        <v>6.202674078687576</v>
+        <v>5.752084971784233</v>
       </c>
       <c r="L25" t="n">
         <v>11.73786047909323</v>
@@ -4545,13 +4545,13 @@
         <v>13.751</v>
       </c>
       <c r="U25" t="n">
-        <v>36.817</v>
+        <v>36.237</v>
       </c>
       <c r="V25" t="n">
-        <v>27.669</v>
+        <v>27.127</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.79</v>
+        <v>-4.371</v>
       </c>
     </row>
     <row r="26">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-13 | RALYH.IS: 2026-08-12</t>
+          <t>CWENE.IS: 2026-08-13 | RALYH.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4595,14 +4595,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +4.71% / +5.79% / -0.98%</t>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-38.46787682799764</v>
       </c>
       <c r="K26" t="n">
-        <v>6.2585456346961</v>
+        <v>7.138866265320409</v>
       </c>
       <c r="L26" t="n">
         <v>49.48136038965337</v>
@@ -4611,10 +4611,10 @@
         <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>120.5</v>
+        <v>121</v>
       </c>
       <c r="O26" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
@@ -4634,13 +4634,13 @@
         <v>21.907</v>
       </c>
       <c r="U26" t="n">
-        <v>16.48</v>
+        <v>17.445</v>
       </c>
       <c r="V26" t="n">
-        <v>23.572</v>
+        <v>24.596</v>
       </c>
       <c r="W26" t="n">
-        <v>-19.13</v>
+        <v>-18.165</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -742,12 +742,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -769,7 +769,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N3" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="O3" t="n">
         <v>42</v>
@@ -792,13 +792,13 @@
         <v>10.869</v>
       </c>
       <c r="U3" t="n">
-        <v>140.475</v>
+        <v>147.854</v>
       </c>
       <c r="V3" t="n">
         <v>68.77200000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>-28.954</v>
+        <v>-29.842</v>
       </c>
     </row>
     <row r="4">
@@ -817,12 +817,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -844,7 +844,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N4" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="O4" t="n">
         <v>56.9</v>
@@ -867,13 +867,13 @@
         <v>11.453</v>
       </c>
       <c r="U4" t="n">
-        <v>94.13200000000001</v>
+        <v>102.534</v>
       </c>
       <c r="V4" t="n">
         <v>12.087</v>
       </c>
       <c r="W4" t="n">
-        <v>-20.494</v>
+        <v>-21.381</v>
       </c>
     </row>
     <row r="5">
@@ -892,37 +892,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, OYAKC.IS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>67.61086897684163</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.18% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>23.38199081518826</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.5225547760162</v>
+        <v>-20.65382212853851</v>
       </c>
       <c r="L5" t="n">
         <v>17.053274561763</v>
@@ -931,36 +919,36 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>136.9</v>
+        <v>136.6</v>
       </c>
       <c r="O5" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.9</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>31.378</v>
+        <v>31.365</v>
       </c>
       <c r="T5" t="n">
-        <v>31.378</v>
+        <v>31.365</v>
       </c>
       <c r="U5" t="n">
-        <v>47.458</v>
+        <v>53.749</v>
       </c>
       <c r="V5" t="n">
-        <v>8.002000000000001</v>
+        <v>9.198</v>
       </c>
       <c r="W5" t="n">
-        <v>-67.428</v>
+        <v>-67.852</v>
       </c>
     </row>
     <row r="6">
@@ -979,12 +967,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1006,7 +994,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="O6" t="n">
         <v>56.9</v>
@@ -1029,13 +1017,13 @@
         <v>11.453</v>
       </c>
       <c r="U6" t="n">
-        <v>94.13200000000001</v>
+        <v>102.534</v>
       </c>
       <c r="V6" t="n">
         <v>12.087</v>
       </c>
       <c r="W6" t="n">
-        <v>-20.494</v>
+        <v>-21.381</v>
       </c>
     </row>
     <row r="7">
@@ -1054,12 +1042,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1104,13 +1092,13 @@
         <v>12.717</v>
       </c>
       <c r="U7" t="n">
-        <v>78.098</v>
+        <v>84.405</v>
       </c>
       <c r="V7" t="n">
         <v>7.375</v>
       </c>
       <c r="W7" t="n">
-        <v>-21.589</v>
+        <v>-22.353</v>
       </c>
     </row>
     <row r="8">
@@ -1129,37 +1117,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, OYAKC.IS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>67.61086897684163</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.18% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>23.38199081518826</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.5225547760162</v>
+        <v>-20.65382212853851</v>
       </c>
       <c r="L8" t="n">
         <v>17.053274561763</v>
@@ -1168,36 +1144,36 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>136.9</v>
+        <v>136.6</v>
       </c>
       <c r="O8" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="P8" t="n">
         <v>2.9</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>31.378</v>
+        <v>31.365</v>
       </c>
       <c r="T8" t="n">
-        <v>31.378</v>
+        <v>31.365</v>
       </c>
       <c r="U8" t="n">
-        <v>47.458</v>
+        <v>53.749</v>
       </c>
       <c r="V8" t="n">
-        <v>8.002000000000001</v>
+        <v>9.198</v>
       </c>
       <c r="W8" t="n">
-        <v>-67.428</v>
+        <v>-67.852</v>
       </c>
     </row>
     <row r="9">
@@ -1216,12 +1192,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1243,7 +1219,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="O9" t="n">
         <v>59.4</v>
@@ -1266,13 +1242,13 @@
         <v>6.103</v>
       </c>
       <c r="U9" t="n">
-        <v>102.166</v>
+        <v>110.915</v>
       </c>
       <c r="V9" t="n">
         <v>16.518</v>
       </c>
       <c r="W9" t="n">
-        <v>-12.844</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="10">
@@ -1291,37 +1267,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>36.78585803744296</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>21.23845403639202</v>
       </c>
       <c r="K10" t="n">
-        <v>-23.70303440323126</v>
+        <v>-22.57590564039316</v>
       </c>
       <c r="L10" t="n">
         <v>6.958484193025216</v>
@@ -1330,36 +1294,36 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="O10" t="n">
-        <v>43.5</v>
+        <v>44.7</v>
       </c>
       <c r="P10" t="n">
         <v>4.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>29.632</v>
+        <v>29.618</v>
       </c>
       <c r="T10" t="n">
-        <v>29.632</v>
+        <v>29.618</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.244</v>
+        <v>2.96</v>
       </c>
       <c r="V10" t="n">
-        <v>-13.07</v>
+        <v>-11.786</v>
       </c>
       <c r="W10" t="n">
-        <v>-42.007</v>
+        <v>-41.226</v>
       </c>
     </row>
     <row r="11">
@@ -1378,12 +1342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1428,13 +1392,13 @@
         <v>12.717</v>
       </c>
       <c r="U11" t="n">
-        <v>78.098</v>
+        <v>84.405</v>
       </c>
       <c r="V11" t="n">
         <v>7.375</v>
       </c>
       <c r="W11" t="n">
-        <v>-21.589</v>
+        <v>-22.353</v>
       </c>
     </row>
     <row r="12">
@@ -1453,12 +1417,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1476,14 +1440,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -3.04% / +4.30% / -3.02% | BRSAN.IS: +8.63% / +12.54% / -2.42%</t>
+          <t>ARCLK.IS: -3.25% / +4.30% / -3.23% | BRSAN.IS: +11.57% / +14.10% / -2.42%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2.170157264886741</v>
       </c>
       <c r="K12" t="n">
-        <v>29.1651175531009</v>
+        <v>30.86729577709186</v>
       </c>
       <c r="L12" t="n">
         <v>16.59987690736074</v>
@@ -1492,7 +1456,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N12" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="O12" t="n">
         <v>56.3</v>
@@ -1515,13 +1479,13 @@
         <v>11.893</v>
       </c>
       <c r="U12" t="n">
-        <v>58.655</v>
+        <v>64.986</v>
       </c>
       <c r="V12" t="n">
-        <v>47.043</v>
+        <v>48.981</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.19</v>
+        <v>-2.155</v>
       </c>
     </row>
     <row r="13">
@@ -1540,12 +1504,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1567,7 +1531,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N13" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="O13" t="n">
         <v>46.5</v>
@@ -1590,13 +1554,13 @@
         <v>14.11</v>
       </c>
       <c r="U13" t="n">
-        <v>70.47799999999999</v>
+        <v>73.982</v>
       </c>
       <c r="V13" t="n">
         <v>44.844</v>
       </c>
       <c r="W13" t="n">
-        <v>-28.005</v>
+        <v>-28.581</v>
       </c>
     </row>
     <row r="14">
@@ -1615,22 +1579,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRALT.IS</t>
+          <t>TKFEN.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TRALT.IS: 2026-08-13</t>
+          <t>TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1638,14 +1602,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.69% / +0.00% / -1.29%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2.869524013514457</v>
       </c>
       <c r="K14" t="n">
-        <v>4.029262319275073</v>
+        <v>3.893442696263727</v>
       </c>
       <c r="L14" t="n">
         <v>9.611322526719135</v>
@@ -1654,10 +1618,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>163.2</v>
+        <v>163.4</v>
       </c>
       <c r="O14" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="P14" t="n">
         <v>1.9</v>
@@ -1668,7 +1632,7 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>9.945</v>
@@ -1677,13 +1641,13 @@
         <v>9.945</v>
       </c>
       <c r="U14" t="n">
-        <v>27.499</v>
+        <v>28.26</v>
       </c>
       <c r="V14" t="n">
-        <v>22.644</v>
+        <v>22.484</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.876</v>
+        <v>-5.079</v>
       </c>
     </row>
     <row r="16">
@@ -1828,12 +1792,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1855,7 +1819,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="O18" t="n">
         <v>42</v>
@@ -1878,13 +1842,13 @@
         <v>10.869</v>
       </c>
       <c r="U18" t="n">
-        <v>140.475</v>
+        <v>147.854</v>
       </c>
       <c r="V18" t="n">
         <v>68.77200000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>-28.954</v>
+        <v>-29.842</v>
       </c>
     </row>
     <row r="19">
@@ -1905,12 +1869,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1932,7 +1896,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N19" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="O19" t="n">
         <v>56.9</v>
@@ -1955,13 +1919,13 @@
         <v>11.453</v>
       </c>
       <c r="U19" t="n">
-        <v>94.13200000000001</v>
+        <v>102.534</v>
       </c>
       <c r="V19" t="n">
         <v>12.087</v>
       </c>
       <c r="W19" t="n">
-        <v>-20.494</v>
+        <v>-21.381</v>
       </c>
     </row>
     <row r="20">
@@ -1982,37 +1946,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, OYAKC.IS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>67.61086897684163</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.18% / +3.42% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>23.38199081518826</v>
       </c>
       <c r="K20" t="n">
-        <v>-21.5225547760162</v>
+        <v>-20.65382212853851</v>
       </c>
       <c r="L20" t="n">
         <v>17.053274561763</v>
@@ -2021,36 +1973,36 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>136.9</v>
+        <v>136.6</v>
       </c>
       <c r="O20" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="P20" t="n">
         <v>2.9</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>31.378</v>
+        <v>31.365</v>
       </c>
       <c r="T20" t="n">
-        <v>31.378</v>
+        <v>31.365</v>
       </c>
       <c r="U20" t="n">
-        <v>47.458</v>
+        <v>53.749</v>
       </c>
       <c r="V20" t="n">
-        <v>8.002000000000001</v>
+        <v>9.198</v>
       </c>
       <c r="W20" t="n">
-        <v>-67.428</v>
+        <v>-67.852</v>
       </c>
     </row>
     <row r="21">
@@ -2071,12 +2023,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2098,7 +2050,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N21" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="O21" t="n">
         <v>59.4</v>
@@ -2121,13 +2073,13 @@
         <v>6.103</v>
       </c>
       <c r="U21" t="n">
-        <v>102.166</v>
+        <v>110.915</v>
       </c>
       <c r="V21" t="n">
         <v>16.518</v>
       </c>
       <c r="W21" t="n">
-        <v>-12.844</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="22">
@@ -2148,12 +2100,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2198,13 +2150,13 @@
         <v>12.717</v>
       </c>
       <c r="U22" t="n">
-        <v>78.098</v>
+        <v>84.405</v>
       </c>
       <c r="V22" t="n">
         <v>7.375</v>
       </c>
       <c r="W22" t="n">
-        <v>-21.589</v>
+        <v>-22.353</v>
       </c>
     </row>
     <row r="23">
@@ -2225,37 +2177,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-13 | KCHOL.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>36.78585803744296</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>21.23845403639202</v>
       </c>
       <c r="K23" t="n">
-        <v>-23.70303440323126</v>
+        <v>-22.57590564039316</v>
       </c>
       <c r="L23" t="n">
         <v>6.958484193025216</v>
@@ -2264,36 +2204,36 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N23" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="O23" t="n">
-        <v>43.5</v>
+        <v>44.7</v>
       </c>
       <c r="P23" t="n">
         <v>4.3</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>29.632</v>
+        <v>29.618</v>
       </c>
       <c r="T23" t="n">
-        <v>29.632</v>
+        <v>29.618</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.244</v>
+        <v>2.96</v>
       </c>
       <c r="V23" t="n">
-        <v>-13.07</v>
+        <v>-11.786</v>
       </c>
       <c r="W23" t="n">
-        <v>-42.007</v>
+        <v>-41.226</v>
       </c>
     </row>
     <row r="24">
@@ -2314,22 +2254,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRALT.IS</t>
+          <t>TKFEN.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TRALT.IS: 2026-08-13</t>
+          <t>TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2337,14 +2277,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.69% / +0.00% / -1.29%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>2.869524013514457</v>
       </c>
       <c r="K24" t="n">
-        <v>4.029262319275073</v>
+        <v>3.893442696263727</v>
       </c>
       <c r="L24" t="n">
         <v>9.611322526719135</v>
@@ -2353,10 +2293,10 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>163.2</v>
+        <v>163.4</v>
       </c>
       <c r="O24" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="P24" t="n">
         <v>1.9</v>
@@ -2367,7 +2307,7 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
         <v>9.945</v>
@@ -2376,13 +2316,13 @@
         <v>9.945</v>
       </c>
       <c r="U24" t="n">
-        <v>27.499</v>
+        <v>28.26</v>
       </c>
       <c r="V24" t="n">
-        <v>22.644</v>
+        <v>22.484</v>
       </c>
       <c r="W24" t="n">
-        <v>-4.876</v>
+        <v>-5.079</v>
       </c>
     </row>
     <row r="25">
@@ -2403,12 +2343,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2426,14 +2366,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -3.04% / +4.30% / -3.02% | BRSAN.IS: +8.63% / +12.54% / -2.42%</t>
+          <t>ARCLK.IS: -3.25% / +4.30% / -3.23% | BRSAN.IS: +11.57% / +14.10% / -2.42%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>2.170157264886741</v>
       </c>
       <c r="K25" t="n">
-        <v>29.1651175531009</v>
+        <v>30.86729577709186</v>
       </c>
       <c r="L25" t="n">
         <v>16.59987690736074</v>
@@ -2442,7 +2382,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N25" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="O25" t="n">
         <v>56.3</v>
@@ -2465,13 +2405,13 @@
         <v>11.893</v>
       </c>
       <c r="U25" t="n">
-        <v>58.655</v>
+        <v>64.986</v>
       </c>
       <c r="V25" t="n">
-        <v>47.043</v>
+        <v>48.981</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.19</v>
+        <v>-2.155</v>
       </c>
     </row>
     <row r="26">
@@ -2492,12 +2432,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2519,7 +2459,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N26" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="O26" t="n">
         <v>46.5</v>
@@ -2542,13 +2482,13 @@
         <v>14.11</v>
       </c>
       <c r="U26" t="n">
-        <v>70.47799999999999</v>
+        <v>73.982</v>
       </c>
       <c r="V26" t="n">
         <v>44.844</v>
       </c>
       <c r="W26" t="n">
-        <v>-28.005</v>
+        <v>-28.581</v>
       </c>
     </row>
   </sheetData>
@@ -2578,7 +2518,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -2738,12 +2678,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2761,14 +2701,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>24.91776691656204</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.62685445263705</v>
+        <v>-17.71549271538467</v>
       </c>
       <c r="L3" t="n">
         <v>17.14344300175863</v>
@@ -2777,13 +2717,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>134.9</v>
+        <v>134.7</v>
       </c>
       <c r="O3" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="P3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -2794,19 +2734,19 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>30.461</v>
+        <v>30.437</v>
       </c>
       <c r="T3" t="n">
-        <v>30.461</v>
+        <v>30.437</v>
       </c>
       <c r="U3" t="n">
-        <v>13.492</v>
+        <v>13.67</v>
       </c>
       <c r="V3" t="n">
-        <v>4.65</v>
+        <v>5.823</v>
       </c>
       <c r="W3" t="n">
-        <v>-49.714</v>
+        <v>-47.982</v>
       </c>
     </row>
     <row r="4">
@@ -2825,12 +2765,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2848,14 +2788,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>24.91776691656204</v>
       </c>
       <c r="K4" t="n">
-        <v>-18.62685445263705</v>
+        <v>-17.71549271538467</v>
       </c>
       <c r="L4" t="n">
         <v>17.14344300175863</v>
@@ -2864,13 +2804,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>134.9</v>
+        <v>134.7</v>
       </c>
       <c r="O4" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -2881,19 +2821,19 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>30.461</v>
+        <v>30.437</v>
       </c>
       <c r="T4" t="n">
-        <v>30.461</v>
+        <v>30.437</v>
       </c>
       <c r="U4" t="n">
-        <v>13.492</v>
+        <v>13.67</v>
       </c>
       <c r="V4" t="n">
-        <v>4.65</v>
+        <v>5.823</v>
       </c>
       <c r="W4" t="n">
-        <v>-49.714</v>
+        <v>-47.982</v>
       </c>
     </row>
     <row r="5">
@@ -2912,22 +2852,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BRSAN.IS, ENJSA.IS, TRMET.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2935,14 +2875,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +12.59% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.28% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>43.30443180651103</v>
       </c>
       <c r="K5" t="n">
-        <v>-19.93655816936733</v>
+        <v>-19.57965489967173</v>
       </c>
       <c r="L5" t="n">
         <v>9.921570716242634</v>
@@ -2951,10 +2891,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="O5" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="P5" t="n">
         <v>5.1</v>
@@ -2965,22 +2905,22 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>25.488</v>
+        <v>25.467</v>
       </c>
       <c r="T5" t="n">
-        <v>25.488</v>
+        <v>25.467</v>
       </c>
       <c r="U5" t="n">
-        <v>5.568</v>
+        <v>6.921</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.219</v>
+        <v>-6.805</v>
       </c>
       <c r="W5" t="n">
-        <v>-36.111</v>
+        <v>-35.937</v>
       </c>
     </row>
     <row r="6">
@@ -2999,22 +2939,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BRSAN.IS, ENJSA.IS, TRMET.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3022,14 +2962,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +12.59% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.28% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>43.30443180651103</v>
       </c>
       <c r="K6" t="n">
-        <v>-19.93655816936733</v>
+        <v>-19.57965489967173</v>
       </c>
       <c r="L6" t="n">
         <v>9.921570716242634</v>
@@ -3038,10 +2978,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="O6" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="P6" t="n">
         <v>5.1</v>
@@ -3052,22 +2992,22 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>25.488</v>
+        <v>25.467</v>
       </c>
       <c r="T6" t="n">
-        <v>25.488</v>
+        <v>25.467</v>
       </c>
       <c r="U6" t="n">
-        <v>5.568</v>
+        <v>6.921</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.219</v>
+        <v>-6.805</v>
       </c>
       <c r="W6" t="n">
-        <v>-36.111</v>
+        <v>-35.937</v>
       </c>
     </row>
     <row r="7">
@@ -3086,12 +3026,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3109,14 +3049,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K7" t="n">
-        <v>-13.79900420276039</v>
+        <v>-12.8335715805579</v>
       </c>
       <c r="L7" t="n">
         <v>15.76726005038759</v>
@@ -3125,10 +3065,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>136.4</v>
+        <v>136.1</v>
       </c>
       <c r="O7" t="n">
-        <v>40.4</v>
+        <v>41.1</v>
       </c>
       <c r="P7" t="n">
         <v>4.4</v>
@@ -3142,19 +3082,19 @@
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="T7" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="U7" t="n">
-        <v>17.844</v>
+        <v>18.734</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.006</v>
+        <v>1.114</v>
       </c>
       <c r="W7" t="n">
-        <v>-39.378</v>
+        <v>-37.921</v>
       </c>
     </row>
     <row r="8">
@@ -3173,12 +3113,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3196,14 +3136,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.79900420276039</v>
+        <v>-12.8335715805579</v>
       </c>
       <c r="L8" t="n">
         <v>15.76726005038759</v>
@@ -3212,10 +3152,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>136.4</v>
+        <v>136.1</v>
       </c>
       <c r="O8" t="n">
-        <v>40.4</v>
+        <v>41.1</v>
       </c>
       <c r="P8" t="n">
         <v>4.4</v>
@@ -3229,19 +3169,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="T8" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="U8" t="n">
-        <v>17.844</v>
+        <v>18.734</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.006</v>
+        <v>1.114</v>
       </c>
       <c r="W8" t="n">
-        <v>-39.378</v>
+        <v>-37.921</v>
       </c>
     </row>
     <row r="9">
@@ -3260,22 +3200,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BRSAN.IS, ENJSA.IS, TRMET.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -3283,14 +3223,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +12.59% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.28% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>43.30443180651103</v>
       </c>
       <c r="K9" t="n">
-        <v>-19.93655816936733</v>
+        <v>-19.57965489967173</v>
       </c>
       <c r="L9" t="n">
         <v>9.921570716242634</v>
@@ -3299,10 +3239,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="O9" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="P9" t="n">
         <v>5.1</v>
@@ -3313,22 +3253,22 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>25.488</v>
+        <v>25.467</v>
       </c>
       <c r="T9" t="n">
-        <v>25.488</v>
+        <v>25.467</v>
       </c>
       <c r="U9" t="n">
-        <v>5.568</v>
+        <v>6.921</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.219</v>
+        <v>-6.805</v>
       </c>
       <c r="W9" t="n">
-        <v>-36.111</v>
+        <v>-35.937</v>
       </c>
     </row>
     <row r="10">
@@ -3347,12 +3287,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3365,7 +3305,7 @@
         <v>14.46263148924893</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.50094272570126</v>
+        <v>-12.48115478119579</v>
       </c>
       <c r="L10" t="n">
         <v>6.329965794996994</v>
@@ -3374,7 +3314,7 @@
         <v>44.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="O10" t="n">
         <v>42.6</v>
@@ -3397,13 +3337,13 @@
         <v>25.773</v>
       </c>
       <c r="U10" t="n">
-        <v>-23.255</v>
+        <v>-23.576</v>
       </c>
       <c r="V10" t="n">
-        <v>-25.737</v>
+        <v>-25.721</v>
       </c>
       <c r="W10" t="n">
-        <v>-33.368</v>
+        <v>-33.203</v>
       </c>
     </row>
     <row r="11">
@@ -3422,12 +3362,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3445,14 +3385,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K11" t="n">
-        <v>-13.79900420276039</v>
+        <v>-12.8335715805579</v>
       </c>
       <c r="L11" t="n">
         <v>15.76726005038759</v>
@@ -3461,10 +3401,10 @@
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>136.4</v>
+        <v>136.1</v>
       </c>
       <c r="O11" t="n">
-        <v>40.4</v>
+        <v>41.1</v>
       </c>
       <c r="P11" t="n">
         <v>4.4</v>
@@ -3478,19 +3418,19 @@
         <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="T11" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="U11" t="n">
-        <v>17.844</v>
+        <v>18.734</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.006</v>
+        <v>1.114</v>
       </c>
       <c r="W11" t="n">
-        <v>-39.378</v>
+        <v>-37.921</v>
       </c>
     </row>
     <row r="12">
@@ -3509,12 +3449,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -3527,7 +3467,7 @@
         <v>-0.3947387514697143</v>
       </c>
       <c r="K12" t="n">
-        <v>9.994834947859355</v>
+        <v>10.01971019808436</v>
       </c>
       <c r="L12" t="n">
         <v>23.0569390189834</v>
@@ -3536,7 +3476,7 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>136.9</v>
+        <v>136.6</v>
       </c>
       <c r="O12" t="n">
         <v>47.5</v>
@@ -3559,13 +3499,13 @@
         <v>14.102</v>
       </c>
       <c r="U12" t="n">
-        <v>56.619</v>
+        <v>58.16</v>
       </c>
       <c r="V12" t="n">
-        <v>46.858</v>
+        <v>46.891</v>
       </c>
       <c r="W12" t="n">
-        <v>-16.621</v>
+        <v>-16.745</v>
       </c>
     </row>
     <row r="13">
@@ -3584,12 +3524,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3607,14 +3547,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CWENE.IS: +0.14% / +2.26% / -3.25% | RALYH.IS: +0.92% / +1.54% / -0.98%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-38.46787682799764</v>
       </c>
       <c r="K13" t="n">
-        <v>7.138866265320409</v>
+        <v>7.739333417787675</v>
       </c>
       <c r="L13" t="n">
         <v>49.48136038965337</v>
@@ -3623,10 +3563,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>121</v>
+        <v>120.8</v>
       </c>
       <c r="O13" t="n">
-        <v>43.9</v>
+        <v>44.7</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
@@ -3646,13 +3586,13 @@
         <v>21.907</v>
       </c>
       <c r="U13" t="n">
-        <v>17.445</v>
+        <v>19.904</v>
       </c>
       <c r="V13" t="n">
-        <v>24.596</v>
+        <v>25.294</v>
       </c>
       <c r="W13" t="n">
-        <v>-18.165</v>
+        <v>-17.773</v>
       </c>
     </row>
     <row r="14">
@@ -3671,22 +3611,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRALT.IS</t>
+          <t>SASA.IS, TKFEN.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TRALT.IS: 2026-08-13</t>
+          <t>SASA.IS: 2026-08-14 | TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3694,14 +3634,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.94% / +0.00% / -1.55%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>0.3486754611526699</v>
       </c>
       <c r="K14" t="n">
-        <v>5.752084971784233</v>
+        <v>5.40669718472091</v>
       </c>
       <c r="L14" t="n">
         <v>11.73786047909323</v>
@@ -3710,10 +3650,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>129.5</v>
+        <v>130.2</v>
       </c>
       <c r="O14" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
       <c r="P14" t="n">
         <v>1.7</v>
@@ -3724,7 +3664,7 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
         <v>13.751</v>
@@ -3733,13 +3673,13 @@
         <v>13.751</v>
       </c>
       <c r="U14" t="n">
-        <v>36.237</v>
+        <v>37.706</v>
       </c>
       <c r="V14" t="n">
-        <v>27.127</v>
+        <v>26.712</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.371</v>
+        <v>-4.884</v>
       </c>
     </row>
     <row r="16">
@@ -3884,12 +3824,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3907,14 +3847,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>24.91776691656204</v>
       </c>
       <c r="K18" t="n">
-        <v>-18.62685445263705</v>
+        <v>-17.71549271538467</v>
       </c>
       <c r="L18" t="n">
         <v>17.14344300175863</v>
@@ -3923,13 +3863,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>134.9</v>
+        <v>134.7</v>
       </c>
       <c r="O18" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="P18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3940,19 +3880,19 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>30.461</v>
+        <v>30.437</v>
       </c>
       <c r="T18" t="n">
-        <v>30.461</v>
+        <v>30.437</v>
       </c>
       <c r="U18" t="n">
-        <v>13.492</v>
+        <v>13.67</v>
       </c>
       <c r="V18" t="n">
-        <v>4.65</v>
+        <v>5.823</v>
       </c>
       <c r="W18" t="n">
-        <v>-49.714</v>
+        <v>-47.982</v>
       </c>
     </row>
     <row r="19">
@@ -3973,12 +3913,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3996,14 +3936,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>24.91776691656204</v>
       </c>
       <c r="K19" t="n">
-        <v>-18.62685445263705</v>
+        <v>-17.71549271538467</v>
       </c>
       <c r="L19" t="n">
         <v>17.14344300175863</v>
@@ -4012,13 +3952,13 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>134.9</v>
+        <v>134.7</v>
       </c>
       <c r="O19" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="P19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -4029,19 +3969,19 @@
         <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.461</v>
+        <v>30.437</v>
       </c>
       <c r="T19" t="n">
-        <v>30.461</v>
+        <v>30.437</v>
       </c>
       <c r="U19" t="n">
-        <v>13.492</v>
+        <v>13.67</v>
       </c>
       <c r="V19" t="n">
-        <v>4.65</v>
+        <v>5.823</v>
       </c>
       <c r="W19" t="n">
-        <v>-49.714</v>
+        <v>-47.982</v>
       </c>
     </row>
     <row r="20">
@@ -4062,12 +4002,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4085,14 +4025,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K20" t="n">
-        <v>-13.79900420276039</v>
+        <v>-12.8335715805579</v>
       </c>
       <c r="L20" t="n">
         <v>15.76726005038759</v>
@@ -4101,10 +4041,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>136.4</v>
+        <v>136.1</v>
       </c>
       <c r="O20" t="n">
-        <v>40.4</v>
+        <v>41.1</v>
       </c>
       <c r="P20" t="n">
         <v>4.4</v>
@@ -4118,19 +4058,19 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="T20" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="U20" t="n">
-        <v>17.844</v>
+        <v>18.734</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.006</v>
+        <v>1.114</v>
       </c>
       <c r="W20" t="n">
-        <v>-39.378</v>
+        <v>-37.921</v>
       </c>
     </row>
     <row r="21">
@@ -4151,12 +4091,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4174,14 +4114,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69%</t>
+          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>34.63450038557985</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.79900420276039</v>
+        <v>-12.8335715805579</v>
       </c>
       <c r="L21" t="n">
         <v>15.76726005038759</v>
@@ -4190,10 +4130,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>136.4</v>
+        <v>136.1</v>
       </c>
       <c r="O21" t="n">
-        <v>40.4</v>
+        <v>41.1</v>
       </c>
       <c r="P21" t="n">
         <v>4.4</v>
@@ -4207,19 +4147,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="T21" t="n">
-        <v>25.046</v>
+        <v>25.02</v>
       </c>
       <c r="U21" t="n">
-        <v>17.844</v>
+        <v>18.734</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.006</v>
+        <v>1.114</v>
       </c>
       <c r="W21" t="n">
-        <v>-39.378</v>
+        <v>-37.921</v>
       </c>
     </row>
     <row r="22">
@@ -4240,22 +4180,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BRSAN.IS, ENJSA.IS, TRMET.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TRMET.IS: 2026-07-20</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14 | TRMET.IS: 2026-07-20</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4263,14 +4203,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.22% / +3.38% / -1.15% | ENJSA.IS: +0.31% / +1.83% / -0.69% | TRMET.IS: +12.59% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.28% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>43.30443180651103</v>
       </c>
       <c r="K22" t="n">
-        <v>-19.93655816936733</v>
+        <v>-19.57965489967173</v>
       </c>
       <c r="L22" t="n">
         <v>9.921570716242634</v>
@@ -4279,10 +4219,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N22" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="O22" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="P22" t="n">
         <v>5.1</v>
@@ -4293,22 +4233,22 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>25.488</v>
+        <v>25.467</v>
       </c>
       <c r="T22" t="n">
-        <v>25.488</v>
+        <v>25.467</v>
       </c>
       <c r="U22" t="n">
-        <v>5.568</v>
+        <v>6.921</v>
       </c>
       <c r="V22" t="n">
-        <v>-7.219</v>
+        <v>-6.805</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.111</v>
+        <v>-35.937</v>
       </c>
     </row>
     <row r="23">
@@ -4329,12 +4269,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4347,7 +4287,7 @@
         <v>14.46263148924893</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.50094272570126</v>
+        <v>-12.48115478119579</v>
       </c>
       <c r="L23" t="n">
         <v>6.329965794996994</v>
@@ -4356,7 +4296,7 @@
         <v>44.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="O23" t="n">
         <v>42.6</v>
@@ -4379,13 +4319,13 @@
         <v>25.773</v>
       </c>
       <c r="U23" t="n">
-        <v>-23.255</v>
+        <v>-23.576</v>
       </c>
       <c r="V23" t="n">
-        <v>-25.737</v>
+        <v>-25.721</v>
       </c>
       <c r="W23" t="n">
-        <v>-33.368</v>
+        <v>-33.203</v>
       </c>
     </row>
     <row r="24">
@@ -4406,12 +4346,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4424,7 +4364,7 @@
         <v>-0.3947387514697143</v>
       </c>
       <c r="K24" t="n">
-        <v>9.994834947859355</v>
+        <v>10.01971019808436</v>
       </c>
       <c r="L24" t="n">
         <v>23.0569390189834</v>
@@ -4433,7 +4373,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>136.9</v>
+        <v>136.6</v>
       </c>
       <c r="O24" t="n">
         <v>47.5</v>
@@ -4456,13 +4396,13 @@
         <v>14.102</v>
       </c>
       <c r="U24" t="n">
-        <v>56.619</v>
+        <v>58.16</v>
       </c>
       <c r="V24" t="n">
-        <v>46.858</v>
+        <v>46.891</v>
       </c>
       <c r="W24" t="n">
-        <v>-16.621</v>
+        <v>-16.745</v>
       </c>
     </row>
     <row r="25">
@@ -4483,22 +4423,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRALT.IS</t>
+          <t>SASA.IS, TKFEN.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TRALT.IS: 2026-08-13</t>
+          <t>SASA.IS: 2026-08-14 | TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -4506,14 +4446,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.94% / +0.00% / -1.55%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>0.3486754611526699</v>
       </c>
       <c r="K25" t="n">
-        <v>5.752084971784233</v>
+        <v>5.40669718472091</v>
       </c>
       <c r="L25" t="n">
         <v>11.73786047909323</v>
@@ -4522,10 +4462,10 @@
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>129.5</v>
+        <v>130.2</v>
       </c>
       <c r="O25" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
       <c r="P25" t="n">
         <v>1.7</v>
@@ -4536,7 +4476,7 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
         <v>13.751</v>
@@ -4545,13 +4485,13 @@
         <v>13.751</v>
       </c>
       <c r="U25" t="n">
-        <v>36.237</v>
+        <v>37.706</v>
       </c>
       <c r="V25" t="n">
-        <v>27.127</v>
+        <v>26.712</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.371</v>
+        <v>-4.884</v>
       </c>
     </row>
     <row r="26">
@@ -4572,12 +4512,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4595,14 +4535,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CWENE.IS: +0.14% / +2.26% / -3.25% | RALYH.IS: +0.92% / +1.54% / -0.98%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-38.46787682799764</v>
       </c>
       <c r="K26" t="n">
-        <v>7.138866265320409</v>
+        <v>7.739333417787675</v>
       </c>
       <c r="L26" t="n">
         <v>49.48136038965337</v>
@@ -4611,10 +4551,10 @@
         <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>121</v>
+        <v>120.8</v>
       </c>
       <c r="O26" t="n">
-        <v>43.9</v>
+        <v>44.7</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
@@ -4634,13 +4574,13 @@
         <v>21.907</v>
       </c>
       <c r="U26" t="n">
-        <v>17.445</v>
+        <v>19.904</v>
       </c>
       <c r="V26" t="n">
-        <v>24.596</v>
+        <v>25.294</v>
       </c>
       <c r="W26" t="n">
-        <v>-18.165</v>
+        <v>-17.773</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W26" headerRowCount="1">
-  <autoFilter ref="A17:W26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W25" headerRowCount="1">
+  <autoFilter ref="A17:W25"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -254,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W26" headerRowCount="1">
-  <autoFilter ref="A17:W26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W25" headerRowCount="1">
+  <autoFilter ref="A17:W25"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -574,20 +574,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -753,29 +753,29 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>71.70967223366058</v>
+        <v>76.05364743555474</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>10.52140120974327</v>
+        <v>42.73534444389067</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.210370781379311e-06</v>
+        <v>-2.929522243797422</v>
       </c>
       <c r="L3" t="n">
-        <v>25.6134921875</v>
+        <v>12.61668847159575</v>
       </c>
       <c r="M3" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N3" t="n">
-        <v>49.5</v>
+        <v>57.5</v>
       </c>
       <c r="O3" t="n">
-        <v>42</v>
+        <v>56.9</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -786,19 +786,19 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>11.01</v>
+        <v>11.453</v>
       </c>
       <c r="T3" t="n">
-        <v>10.869</v>
+        <v>11.453</v>
       </c>
       <c r="U3" t="n">
-        <v>147.854</v>
+        <v>94.13200000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>68.77200000000001</v>
+        <v>12.359</v>
       </c>
       <c r="W3" t="n">
-        <v>-29.842</v>
+        <v>-20.494</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -825,55 +825,67 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, KCHOL.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-14 | KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>71.1483564365692</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>73.33744768345549</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.31% / +2.55% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J4" t="n">
-        <v>37.83904503746869</v>
+        <v>8.066976193836894</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.929522243797422</v>
+        <v>-25.93261415219912</v>
       </c>
       <c r="L4" t="n">
-        <v>12.61668847159575</v>
+        <v>16.97824457163605</v>
       </c>
       <c r="M4" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>57.4</v>
+        <v>156.3</v>
       </c>
       <c r="O4" t="n">
-        <v>56.9</v>
+        <v>39</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>11.453</v>
+        <v>37.087</v>
       </c>
       <c r="T4" t="n">
-        <v>11.453</v>
+        <v>37.087</v>
       </c>
       <c r="U4" t="n">
-        <v>102.534</v>
+        <v>2.688</v>
       </c>
       <c r="V4" t="n">
-        <v>12.087</v>
+        <v>0.044</v>
       </c>
       <c r="W4" t="n">
-        <v>-21.381</v>
+        <v>-60.535</v>
       </c>
     </row>
     <row r="5">
@@ -900,17 +912,29 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, OYAKC.IS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>67.61086897684163</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>72.46555718063254</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +2.36% / +4.85% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>23.38199081518826</v>
+        <v>25.51016247674216</v>
       </c>
       <c r="K5" t="n">
-        <v>-20.65382212853851</v>
+        <v>-20.80834283091162</v>
       </c>
       <c r="L5" t="n">
         <v>17.053274561763</v>
@@ -919,7 +943,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>136.6</v>
+        <v>136.9</v>
       </c>
       <c r="O5" t="n">
         <v>48.2</v>
@@ -929,26 +953,26 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>31.365</v>
+        <v>30.754</v>
       </c>
       <c r="T5" t="n">
-        <v>31.365</v>
+        <v>30.754</v>
       </c>
       <c r="U5" t="n">
-        <v>53.749</v>
+        <v>48.8</v>
       </c>
       <c r="V5" t="n">
-        <v>9.198</v>
+        <v>9.231999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-67.852</v>
+        <v>-66.086</v>
       </c>
     </row>
     <row r="6">
@@ -978,11 +1002,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>71.1483564365692</v>
+        <v>76.05364743555474</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>37.83904503746869</v>
+        <v>42.73534444389067</v>
       </c>
       <c r="K6" t="n">
         <v>-2.929522243797422</v>
@@ -994,7 +1018,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="O6" t="n">
         <v>56.9</v>
@@ -1017,13 +1041,13 @@
         <v>11.453</v>
       </c>
       <c r="U6" t="n">
-        <v>102.534</v>
+        <v>94.13200000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>12.087</v>
+        <v>12.359</v>
       </c>
       <c r="W6" t="n">
-        <v>-21.381</v>
+        <v>-20.494</v>
       </c>
     </row>
     <row r="7">
@@ -1053,11 +1077,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>60.15988351316175</v>
+        <v>65.42678320466875</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>29.4108103819297</v>
+        <v>34.44264306823472</v>
       </c>
       <c r="K7" t="n">
         <v>-0.4732783336371393</v>
@@ -1092,13 +1116,13 @@
         <v>12.717</v>
       </c>
       <c r="U7" t="n">
-        <v>84.405</v>
+        <v>78.098</v>
       </c>
       <c r="V7" t="n">
-        <v>7.375</v>
+        <v>5.863</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.353</v>
+        <v>-21.589</v>
       </c>
     </row>
     <row r="8">
@@ -1125,17 +1149,29 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, OYAKC.IS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>67.61086897684163</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>72.46555718063254</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +2.36% / +4.85% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
-        <v>23.38199081518826</v>
+        <v>25.51016247674216</v>
       </c>
       <c r="K8" t="n">
-        <v>-20.65382212853851</v>
+        <v>-20.80834283091162</v>
       </c>
       <c r="L8" t="n">
         <v>17.053274561763</v>
@@ -1144,7 +1180,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>136.6</v>
+        <v>136.9</v>
       </c>
       <c r="O8" t="n">
         <v>48.2</v>
@@ -1154,26 +1190,26 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.365</v>
+        <v>30.754</v>
       </c>
       <c r="T8" t="n">
-        <v>31.365</v>
+        <v>30.754</v>
       </c>
       <c r="U8" t="n">
-        <v>53.749</v>
+        <v>48.8</v>
       </c>
       <c r="V8" t="n">
-        <v>9.198</v>
+        <v>9.231999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-67.852</v>
+        <v>-66.086</v>
       </c>
     </row>
     <row r="9">
@@ -1187,7 +1223,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T4_konsensus|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1200,55 +1236,67 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-14 | TKFEN.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>66.49721725529525</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>40.06047860324801</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>34.09313515588226</v>
+        <v>23.81201687014565</v>
       </c>
       <c r="K9" t="n">
-        <v>3.193644082521985e-06</v>
+        <v>-23.9092632533063</v>
       </c>
       <c r="L9" t="n">
-        <v>10.6621618758353</v>
+        <v>6.958484193025216</v>
       </c>
       <c r="M9" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>47.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>59.4</v>
+        <v>43.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>6.103</v>
+        <v>29.822</v>
       </c>
       <c r="T9" t="n">
-        <v>6.103</v>
+        <v>29.822</v>
       </c>
       <c r="U9" t="n">
-        <v>110.915</v>
+        <v>-0.513</v>
       </c>
       <c r="V9" t="n">
-        <v>16.518</v>
+        <v>-13.662</v>
       </c>
       <c r="W9" t="n">
-        <v>-13.4</v>
+        <v>-42.277</v>
       </c>
     </row>
     <row r="10">
@@ -1262,7 +1310,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1278,29 +1326,29 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>36.78585803744296</v>
+        <v>76.05364743555474</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>21.23845403639202</v>
+        <v>42.73534444389067</v>
       </c>
       <c r="K10" t="n">
-        <v>-22.57590564039316</v>
+        <v>-2.929522243797422</v>
       </c>
       <c r="L10" t="n">
-        <v>6.958484193025216</v>
+        <v>12.61668847159575</v>
       </c>
       <c r="M10" t="n">
-        <v>72.22222222222221</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>79.7</v>
+        <v>57.5</v>
       </c>
       <c r="O10" t="n">
-        <v>44.7</v>
+        <v>56.9</v>
       </c>
       <c r="P10" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1311,19 +1359,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>29.618</v>
+        <v>11.453</v>
       </c>
       <c r="T10" t="n">
-        <v>29.618</v>
+        <v>11.453</v>
       </c>
       <c r="U10" t="n">
-        <v>2.96</v>
+        <v>94.13200000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-11.786</v>
+        <v>12.359</v>
       </c>
       <c r="W10" t="n">
-        <v>-41.226</v>
+        <v>-20.494</v>
       </c>
     </row>
     <row r="11">
@@ -1353,11 +1401,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>60.15988351316175</v>
+        <v>65.42678320466875</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>29.4108103819297</v>
+        <v>34.44264306823472</v>
       </c>
       <c r="K11" t="n">
         <v>-0.4732783336371393</v>
@@ -1392,13 +1440,13 @@
         <v>12.717</v>
       </c>
       <c r="U11" t="n">
-        <v>84.405</v>
+        <v>78.098</v>
       </c>
       <c r="V11" t="n">
-        <v>7.375</v>
+        <v>5.863</v>
       </c>
       <c r="W11" t="n">
-        <v>-22.353</v>
+        <v>-21.589</v>
       </c>
     </row>
     <row r="12">
@@ -1436,18 +1484,18 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>15.69318442167043</v>
+        <v>17.86582823895642</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARCLK.IS: -3.25% / +4.30% / -3.23% | BRSAN.IS: +11.57% / +14.10% / -2.42%</t>
+          <t>ARCLK.IS: -3.04% / +4.30% / -3.23% | BRSAN.IS: +11.40% / +14.10% / -2.42%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2.170157264886741</v>
+        <v>3.794219766359896</v>
       </c>
       <c r="K12" t="n">
-        <v>30.86729577709186</v>
+        <v>30.88947200900061</v>
       </c>
       <c r="L12" t="n">
         <v>16.59987690736074</v>
@@ -1456,7 +1504,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N12" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="O12" t="n">
         <v>56.3</v>
@@ -1479,13 +1527,13 @@
         <v>11.893</v>
       </c>
       <c r="U12" t="n">
-        <v>64.986</v>
+        <v>60.773</v>
       </c>
       <c r="V12" t="n">
-        <v>48.981</v>
+        <v>48.753</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.155</v>
+        <v>-2.072</v>
       </c>
     </row>
     <row r="13">
@@ -1515,11 +1563,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>14.91975714093474</v>
+        <v>15.39934170704613</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-6.722611259504041</v>
+        <v>-7.076686406535327</v>
       </c>
       <c r="K13" t="n">
         <v>9.530992240556714</v>
@@ -1531,7 +1579,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="N13" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="O13" t="n">
         <v>46.5</v>
@@ -1554,13 +1602,13 @@
         <v>14.11</v>
       </c>
       <c r="U13" t="n">
-        <v>73.982</v>
+        <v>70.47799999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>44.844</v>
+        <v>46.712</v>
       </c>
       <c r="W13" t="n">
-        <v>-28.581</v>
+        <v>-28.005</v>
       </c>
     </row>
     <row r="14">
@@ -1594,22 +1642,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-13</t>
+          <t>TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19.66188612652675</v>
+        <v>19.05950372123677</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.69% / +0.00% / -1.29%</t>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2.869524013514457</v>
+        <v>2.288788066639036</v>
       </c>
       <c r="K14" t="n">
-        <v>3.893442696263727</v>
+        <v>3.800523305866488</v>
       </c>
       <c r="L14" t="n">
         <v>9.611322526719135</v>
@@ -1618,7 +1666,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>163.4</v>
+        <v>163.7</v>
       </c>
       <c r="O14" t="n">
         <v>47.9</v>
@@ -1641,13 +1689,13 @@
         <v>9.945</v>
       </c>
       <c r="U14" t="n">
-        <v>28.26</v>
+        <v>27.227</v>
       </c>
       <c r="V14" t="n">
-        <v>22.484</v>
+        <v>22.499</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.079</v>
+        <v>-5.149</v>
       </c>
     </row>
     <row r="16">
@@ -1777,17 +1825,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 | 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1803,29 +1851,29 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>71.70967223366058</v>
+        <v>76.05364743555474</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>10.52140120974327</v>
+        <v>42.73534444389067</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.210370781379311e-06</v>
+        <v>-2.929522243797422</v>
       </c>
       <c r="L18" t="n">
-        <v>25.6134921875</v>
+        <v>12.61668847159575</v>
       </c>
       <c r="M18" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>49.5</v>
+        <v>57.5</v>
       </c>
       <c r="O18" t="n">
-        <v>42</v>
+        <v>56.9</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1836,35 +1884,35 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>11.01</v>
+        <v>11.453</v>
       </c>
       <c r="T18" t="n">
-        <v>10.869</v>
+        <v>11.453</v>
       </c>
       <c r="U18" t="n">
-        <v>147.854</v>
+        <v>94.13200000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>68.77200000000001</v>
+        <v>12.359</v>
       </c>
       <c r="W18" t="n">
-        <v>-29.842</v>
+        <v>-20.494</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 | 1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1877,55 +1925,67 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, KCHOL.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-14 | KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H19" t="n">
-        <v>71.1483564365692</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>73.33744768345549</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.31% / +2.55% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J19" t="n">
-        <v>37.83904503746869</v>
+        <v>8.066976193836894</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.929522243797422</v>
+        <v>-25.93261415219912</v>
       </c>
       <c r="L19" t="n">
-        <v>12.61668847159575</v>
+        <v>16.97824457163605</v>
       </c>
       <c r="M19" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>57.4</v>
+        <v>156.3</v>
       </c>
       <c r="O19" t="n">
-        <v>56.9</v>
+        <v>39</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>11.453</v>
+        <v>37.087</v>
       </c>
       <c r="T19" t="n">
-        <v>11.453</v>
+        <v>37.087</v>
       </c>
       <c r="U19" t="n">
-        <v>102.534</v>
+        <v>2.688</v>
       </c>
       <c r="V19" t="n">
-        <v>12.087</v>
+        <v>0.044</v>
       </c>
       <c r="W19" t="n">
-        <v>-21.381</v>
+        <v>-60.535</v>
       </c>
     </row>
     <row r="20">
@@ -1954,17 +2014,29 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, OYAKC.IS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H20" t="n">
-        <v>67.61086897684163</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>72.46555718063254</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +2.36% / +4.85% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
-        <v>23.38199081518826</v>
+        <v>25.51016247674216</v>
       </c>
       <c r="K20" t="n">
-        <v>-20.65382212853851</v>
+        <v>-20.80834283091162</v>
       </c>
       <c r="L20" t="n">
         <v>17.053274561763</v>
@@ -1973,7 +2045,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>136.6</v>
+        <v>136.9</v>
       </c>
       <c r="O20" t="n">
         <v>48.2</v>
@@ -1983,42 +2055,42 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>31.365</v>
+        <v>30.754</v>
       </c>
       <c r="T20" t="n">
-        <v>31.365</v>
+        <v>30.754</v>
       </c>
       <c r="U20" t="n">
-        <v>53.749</v>
+        <v>48.8</v>
       </c>
       <c r="V20" t="n">
-        <v>9.198</v>
+        <v>9.231999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-67.852</v>
+        <v>-66.086</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 | 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T4_konsensus|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2034,29 +2106,29 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>66.49721725529525</v>
+        <v>65.42678320466875</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>34.09313515588226</v>
+        <v>34.44264306823472</v>
       </c>
       <c r="K21" t="n">
-        <v>3.193644082521985e-06</v>
+        <v>-0.4732783336371393</v>
       </c>
       <c r="L21" t="n">
-        <v>10.6621618758353</v>
+        <v>12.39638328010337</v>
       </c>
       <c r="M21" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N21" t="n">
-        <v>47.5</v>
+        <v>21.3</v>
       </c>
       <c r="O21" t="n">
-        <v>59.4</v>
+        <v>55.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2067,35 +2139,35 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6.103</v>
+        <v>12.717</v>
       </c>
       <c r="T21" t="n">
-        <v>6.103</v>
+        <v>12.717</v>
       </c>
       <c r="U21" t="n">
-        <v>110.915</v>
+        <v>78.098</v>
       </c>
       <c r="V21" t="n">
-        <v>16.518</v>
+        <v>5.863</v>
       </c>
       <c r="W21" t="n">
-        <v>-13.4</v>
+        <v>-21.589</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2 | 3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2108,71 +2180,83 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-14 | TKFEN.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H22" t="n">
-        <v>60.15988351316175</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>40.06047860324801</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J22" t="n">
-        <v>29.4108103819297</v>
+        <v>23.81201687014565</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4732783336371393</v>
+        <v>-23.9092632533063</v>
       </c>
       <c r="L22" t="n">
-        <v>12.39638328010337</v>
+        <v>6.958484193025216</v>
       </c>
       <c r="M22" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N22" t="n">
-        <v>21.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>55.8</v>
+        <v>43.5</v>
       </c>
       <c r="P22" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>12.717</v>
+        <v>29.822</v>
       </c>
       <c r="T22" t="n">
-        <v>12.717</v>
+        <v>29.822</v>
       </c>
       <c r="U22" t="n">
-        <v>84.405</v>
+        <v>-0.513</v>
       </c>
       <c r="V22" t="n">
-        <v>7.375</v>
+        <v>-13.662</v>
       </c>
       <c r="W22" t="n">
-        <v>-22.353</v>
+        <v>-42.277</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T6_skor_momentum|E30|S5|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2185,55 +2269,67 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>TKFEN.IS, TRALT.IS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>36.78585803744296</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>19.05950372123677</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>21.23845403639202</v>
+        <v>2.288788066639036</v>
       </c>
       <c r="K23" t="n">
-        <v>-22.57590564039316</v>
+        <v>3.800523305866488</v>
       </c>
       <c r="L23" t="n">
-        <v>6.958484193025216</v>
+        <v>9.611322526719135</v>
       </c>
       <c r="M23" t="n">
-        <v>72.22222222222221</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>79.7</v>
+        <v>163.7</v>
       </c>
       <c r="O23" t="n">
-        <v>44.7</v>
+        <v>47.9</v>
       </c>
       <c r="P23" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>29.618</v>
+        <v>9.945</v>
       </c>
       <c r="T23" t="n">
-        <v>29.618</v>
+        <v>9.945</v>
       </c>
       <c r="U23" t="n">
-        <v>2.96</v>
+        <v>27.227</v>
       </c>
       <c r="V23" t="n">
-        <v>-11.786</v>
+        <v>22.499</v>
       </c>
       <c r="W23" t="n">
-        <v>-41.226</v>
+        <v>-5.149</v>
       </c>
     </row>
     <row r="24">
@@ -2244,12 +2340,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2264,42 +2360,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TKFEN.IS, TRALT.IS</t>
+          <t>ARCLK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-13</t>
+          <t>ARCLK.IS: 2026-07-17 | BRSAN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>19.66188612652675</v>
+        <v>17.86582823895642</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.69% / +0.00% / -1.29%</t>
+          <t>ARCLK.IS: -3.04% / +4.30% / -3.23% | BRSAN.IS: +11.40% / +14.10% / -2.42%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2.869524013514457</v>
+        <v>3.794219766359896</v>
       </c>
       <c r="K24" t="n">
-        <v>3.893442696263727</v>
+        <v>30.88947200900061</v>
       </c>
       <c r="L24" t="n">
-        <v>9.611322526719135</v>
+        <v>16.59987690736074</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N24" t="n">
-        <v>163.4</v>
+        <v>43.2</v>
       </c>
       <c r="O24" t="n">
-        <v>47.9</v>
+        <v>56.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2310,19 +2406,19 @@
         <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>9.945</v>
+        <v>11.893</v>
       </c>
       <c r="T24" t="n">
-        <v>9.945</v>
+        <v>11.893</v>
       </c>
       <c r="U24" t="n">
-        <v>28.26</v>
+        <v>60.773</v>
       </c>
       <c r="V24" t="n">
-        <v>22.484</v>
+        <v>48.753</v>
       </c>
       <c r="W24" t="n">
-        <v>-5.079</v>
+        <v>-2.072</v>
       </c>
     </row>
     <row r="25">
@@ -2333,12 +2429,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2351,144 +2447,55 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ARCLK.IS, BRSAN.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARCLK.IS: 2026-07-17 | BRSAN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>15.69318442167043</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ARCLK.IS: -3.25% / +4.30% / -3.23% | BRSAN.IS: +11.57% / +14.10% / -2.42%</t>
-        </is>
-      </c>
+        <v>15.39934170704613</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>2.170157264886741</v>
+        <v>-7.076686406535327</v>
       </c>
       <c r="K25" t="n">
-        <v>30.86729577709186</v>
+        <v>9.530992240556714</v>
       </c>
       <c r="L25" t="n">
-        <v>16.59987690736074</v>
+        <v>25.876453125</v>
       </c>
       <c r="M25" t="n">
-        <v>72.22222222222221</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N25" t="n">
-        <v>43.1</v>
+        <v>85.3</v>
       </c>
       <c r="O25" t="n">
-        <v>56.3</v>
+        <v>46.5</v>
       </c>
       <c r="P25" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>11.893</v>
+        <v>14.11</v>
       </c>
       <c r="T25" t="n">
-        <v>11.893</v>
+        <v>14.11</v>
       </c>
       <c r="U25" t="n">
-        <v>64.986</v>
+        <v>70.47799999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>48.981</v>
+        <v>46.712</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.155</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>14.91975714093474</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>-6.722611259504041</v>
-      </c>
-      <c r="K26" t="n">
-        <v>9.530992240556714</v>
-      </c>
-      <c r="L26" t="n">
-        <v>25.876453125</v>
-      </c>
-      <c r="M26" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="N26" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="T26" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="U26" t="n">
-        <v>73.982</v>
-      </c>
-      <c r="V26" t="n">
-        <v>44.844</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-28.581</v>
+        <v>-28.005</v>
       </c>
     </row>
   </sheetData>
@@ -2510,7 +2517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2688,27 +2695,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>73.55709052781789</v>
+        <v>83.68283999170649</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>24.91776691656204</v>
+        <v>28.373662392288</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.71549271538467</v>
+        <v>-18.02705376434217</v>
       </c>
       <c r="L3" t="n">
         <v>17.14344300175863</v>
@@ -2717,13 +2724,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>134.7</v>
+        <v>134.9</v>
       </c>
       <c r="O3" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -2734,19 +2741,19 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>30.437</v>
+        <v>29.949</v>
       </c>
       <c r="T3" t="n">
-        <v>30.437</v>
+        <v>29.949</v>
       </c>
       <c r="U3" t="n">
-        <v>13.67</v>
+        <v>14.328</v>
       </c>
       <c r="V3" t="n">
-        <v>5.823</v>
+        <v>5.38</v>
       </c>
       <c r="W3" t="n">
-        <v>-47.982</v>
+        <v>-48.878</v>
       </c>
     </row>
     <row r="4">
@@ -2775,27 +2782,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.55709052781789</v>
+        <v>83.68283999170649</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>24.91776691656204</v>
+        <v>28.373662392288</v>
       </c>
       <c r="K4" t="n">
-        <v>-17.71549271538467</v>
+        <v>-18.02705376434217</v>
       </c>
       <c r="L4" t="n">
         <v>17.14344300175863</v>
@@ -2804,13 +2811,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>134.7</v>
+        <v>134.9</v>
       </c>
       <c r="O4" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="P4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -2821,19 +2828,19 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>30.437</v>
+        <v>29.949</v>
       </c>
       <c r="T4" t="n">
-        <v>30.437</v>
+        <v>29.949</v>
       </c>
       <c r="U4" t="n">
-        <v>13.67</v>
+        <v>14.328</v>
       </c>
       <c r="V4" t="n">
-        <v>5.823</v>
+        <v>5.38</v>
       </c>
       <c r="W4" t="n">
-        <v>-47.982</v>
+        <v>-48.878</v>
       </c>
     </row>
     <row r="5">
@@ -2871,18 +2878,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>69.61350586989693</v>
+        <v>69.61350586989698</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.28% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.19% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>43.30443180651103</v>
+        <v>43.10920851715343</v>
       </c>
       <c r="K5" t="n">
-        <v>-19.57965489967173</v>
+        <v>-19.74574732903608</v>
       </c>
       <c r="L5" t="n">
         <v>9.921570716242634</v>
@@ -2891,7 +2898,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>50.9</v>
@@ -2908,19 +2915,19 @@
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>25.467</v>
+        <v>25.31</v>
       </c>
       <c r="T5" t="n">
-        <v>25.467</v>
+        <v>25.31</v>
       </c>
       <c r="U5" t="n">
-        <v>6.921</v>
+        <v>5.82</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.805</v>
+        <v>-7.047</v>
       </c>
       <c r="W5" t="n">
-        <v>-35.937</v>
+        <v>-35.859</v>
       </c>
     </row>
     <row r="6">
@@ -2958,18 +2965,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69.61350586989693</v>
+        <v>69.61350586989698</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.28% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.19% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>43.30443180651103</v>
+        <v>43.10920851715343</v>
       </c>
       <c r="K6" t="n">
-        <v>-19.57965489967173</v>
+        <v>-19.74574732903608</v>
       </c>
       <c r="L6" t="n">
         <v>9.921570716242634</v>
@@ -2978,7 +2985,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>50.9</v>
@@ -2995,19 +3002,19 @@
         <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>25.467</v>
+        <v>25.31</v>
       </c>
       <c r="T6" t="n">
-        <v>25.467</v>
+        <v>25.31</v>
       </c>
       <c r="U6" t="n">
-        <v>6.921</v>
+        <v>5.82</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.805</v>
+        <v>-7.047</v>
       </c>
       <c r="W6" t="n">
-        <v>-35.937</v>
+        <v>-35.859</v>
       </c>
     </row>
     <row r="7">
@@ -3036,27 +3043,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.64483370334607</v>
+        <v>79.44046302924768</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>34.63450038557985</v>
+        <v>39.06030755509926</v>
       </c>
       <c r="K7" t="n">
-        <v>-12.8335715805579</v>
+        <v>-13.16361747581136</v>
       </c>
       <c r="L7" t="n">
         <v>15.76726005038759</v>
@@ -3065,10 +3072,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>136.1</v>
+        <v>136.4</v>
       </c>
       <c r="O7" t="n">
-        <v>41.1</v>
+        <v>40.7</v>
       </c>
       <c r="P7" t="n">
         <v>4.4</v>
@@ -3082,19 +3089,19 @@
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="T7" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="U7" t="n">
-        <v>18.734</v>
+        <v>18.713</v>
       </c>
       <c r="V7" t="n">
-        <v>1.114</v>
+        <v>-0.28</v>
       </c>
       <c r="W7" t="n">
-        <v>-37.921</v>
+        <v>-38.51</v>
       </c>
     </row>
     <row r="8">
@@ -3123,27 +3130,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>71.64483370334607</v>
+        <v>79.44046302924768</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>34.63450038557985</v>
+        <v>39.06030755509926</v>
       </c>
       <c r="K8" t="n">
-        <v>-12.8335715805579</v>
+        <v>-13.16361747581136</v>
       </c>
       <c r="L8" t="n">
         <v>15.76726005038759</v>
@@ -3152,10 +3159,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>136.1</v>
+        <v>136.4</v>
       </c>
       <c r="O8" t="n">
-        <v>41.1</v>
+        <v>40.7</v>
       </c>
       <c r="P8" t="n">
         <v>4.4</v>
@@ -3169,19 +3176,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="T8" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="U8" t="n">
-        <v>18.734</v>
+        <v>18.713</v>
       </c>
       <c r="V8" t="n">
-        <v>1.114</v>
+        <v>-0.28</v>
       </c>
       <c r="W8" t="n">
-        <v>-37.921</v>
+        <v>-38.51</v>
       </c>
     </row>
     <row r="9">
@@ -3219,18 +3226,18 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>69.61350586989693</v>
+        <v>69.61350586989698</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.28% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.19% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>43.30443180651103</v>
+        <v>43.10920851715343</v>
       </c>
       <c r="K9" t="n">
-        <v>-19.57965489967173</v>
+        <v>-19.74574732903608</v>
       </c>
       <c r="L9" t="n">
         <v>9.921570716242634</v>
@@ -3239,7 +3246,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>50.9</v>
@@ -3256,19 +3263,19 @@
         <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>25.467</v>
+        <v>25.31</v>
       </c>
       <c r="T9" t="n">
-        <v>25.467</v>
+        <v>25.31</v>
       </c>
       <c r="U9" t="n">
-        <v>6.921</v>
+        <v>5.82</v>
       </c>
       <c r="V9" t="n">
-        <v>-6.805</v>
+        <v>-7.047</v>
       </c>
       <c r="W9" t="n">
-        <v>-35.937</v>
+        <v>-35.859</v>
       </c>
     </row>
     <row r="10">
@@ -3282,7 +3289,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|coklu_zarf</t>
+          <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3295,55 +3302,67 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>31.15183851699386</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>79.44046302924768</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
-        <v>14.46263148924893</v>
+        <v>39.06030755509926</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.48115478119579</v>
+        <v>-13.16361747581136</v>
       </c>
       <c r="L10" t="n">
-        <v>6.329965794996994</v>
+        <v>15.76726005038759</v>
       </c>
       <c r="M10" t="n">
-        <v>44.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>26.7</v>
+        <v>136.4</v>
       </c>
       <c r="O10" t="n">
-        <v>42.6</v>
+        <v>40.7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>30.337</v>
+        <v>24.494</v>
       </c>
       <c r="T10" t="n">
-        <v>25.773</v>
+        <v>24.494</v>
       </c>
       <c r="U10" t="n">
-        <v>-23.576</v>
+        <v>18.713</v>
       </c>
       <c r="V10" t="n">
-        <v>-25.721</v>
+        <v>-0.28</v>
       </c>
       <c r="W10" t="n">
-        <v>-33.203</v>
+        <v>-38.51</v>
       </c>
     </row>
     <row r="11">
@@ -3357,7 +3376,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3372,27 +3391,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>71.64483370334607</v>
+        <v>79.44046302924768</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34.63450038557985</v>
+        <v>39.06030755509926</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.8335715805579</v>
+        <v>-13.16361747581136</v>
       </c>
       <c r="L11" t="n">
         <v>15.76726005038759</v>
@@ -3401,10 +3420,10 @@
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>136.1</v>
+        <v>136.4</v>
       </c>
       <c r="O11" t="n">
-        <v>41.1</v>
+        <v>40.7</v>
       </c>
       <c r="P11" t="n">
         <v>4.4</v>
@@ -3418,19 +3437,19 @@
         <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="T11" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="U11" t="n">
-        <v>18.734</v>
+        <v>18.713</v>
       </c>
       <c r="V11" t="n">
-        <v>1.114</v>
+        <v>-0.28</v>
       </c>
       <c r="W11" t="n">
-        <v>-37.921</v>
+        <v>-38.51</v>
       </c>
     </row>
     <row r="12">
@@ -3460,14 +3479,14 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>27.77992134829283</v>
+        <v>27.44212969659623</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-0.3947387514697143</v>
+        <v>-1.325508829134781</v>
       </c>
       <c r="K12" t="n">
-        <v>10.01971019808436</v>
+        <v>9.807845239497247</v>
       </c>
       <c r="L12" t="n">
         <v>23.0569390189834</v>
@@ -3476,7 +3495,7 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>136.6</v>
+        <v>136.9</v>
       </c>
       <c r="O12" t="n">
         <v>47.5</v>
@@ -3499,13 +3518,13 @@
         <v>14.102</v>
       </c>
       <c r="U12" t="n">
-        <v>58.16</v>
+        <v>56.349</v>
       </c>
       <c r="V12" t="n">
-        <v>46.891</v>
+        <v>46.317</v>
       </c>
       <c r="W12" t="n">
-        <v>-16.745</v>
+        <v>-16.891</v>
       </c>
     </row>
     <row r="13">
@@ -3539,22 +3558,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CWENE.IS: 2026-08-13 | RALYH.IS: 2026-08-13</t>
+          <t>CWENE.IS: 2026-08-14 | RALYH.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-17.85349196318069</v>
+        <v>-18.12728286424745</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CWENE.IS: +0.14% / +2.26% / -3.25% | RALYH.IS: +0.92% / +1.54% / -0.98%</t>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-38.46787682799764</v>
+        <v>-39.30005974862217</v>
       </c>
       <c r="K13" t="n">
-        <v>7.739333417787675</v>
+        <v>7.253780702616264</v>
       </c>
       <c r="L13" t="n">
         <v>49.48136038965337</v>
@@ -3563,10 +3582,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>120.8</v>
+        <v>121</v>
       </c>
       <c r="O13" t="n">
-        <v>44.7</v>
+        <v>43.9</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
@@ -3586,13 +3605,13 @@
         <v>21.907</v>
       </c>
       <c r="U13" t="n">
-        <v>19.904</v>
+        <v>17.569</v>
       </c>
       <c r="V13" t="n">
-        <v>25.294</v>
+        <v>24.723</v>
       </c>
       <c r="W13" t="n">
-        <v>-17.773</v>
+        <v>-18.041</v>
       </c>
     </row>
     <row r="14">
@@ -3606,7 +3625,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3619,67 +3638,55 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SASA.IS, TKFEN.IS, TRALT.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SASA.IS: 2026-08-14 | TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-13</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>13.50616295266203</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.94% / +0.00% / -1.55%</t>
-        </is>
-      </c>
+        <v>-7.609034621162936</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.3486754611526699</v>
+        <v>-18.83545908828166</v>
       </c>
       <c r="K14" t="n">
-        <v>5.40669718472091</v>
+        <v>4.779352275141924</v>
       </c>
       <c r="L14" t="n">
-        <v>11.73786047909323</v>
+        <v>34.76409501205259</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>130.2</v>
+        <v>43.2</v>
       </c>
       <c r="O14" t="n">
-        <v>47.1</v>
+        <v>43.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>13.751</v>
+        <v>11.176</v>
       </c>
       <c r="T14" t="n">
-        <v>13.751</v>
+        <v>11.176</v>
       </c>
       <c r="U14" t="n">
-        <v>37.706</v>
+        <v>30.95</v>
       </c>
       <c r="V14" t="n">
-        <v>26.712</v>
+        <v>25.214</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.884</v>
+        <v>-3.614</v>
       </c>
     </row>
     <row r="16">
@@ -3834,27 +3841,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>73.55709052781789</v>
+        <v>83.68283999170649</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>24.91776691656204</v>
+        <v>28.373662392288</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.71549271538467</v>
+        <v>-18.02705376434217</v>
       </c>
       <c r="L18" t="n">
         <v>17.14344300175863</v>
@@ -3863,13 +3870,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>134.7</v>
+        <v>134.9</v>
       </c>
       <c r="O18" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="P18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3880,19 +3887,19 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>30.437</v>
+        <v>29.949</v>
       </c>
       <c r="T18" t="n">
-        <v>30.437</v>
+        <v>29.949</v>
       </c>
       <c r="U18" t="n">
-        <v>13.67</v>
+        <v>14.328</v>
       </c>
       <c r="V18" t="n">
-        <v>5.823</v>
+        <v>5.38</v>
       </c>
       <c r="W18" t="n">
-        <v>-47.982</v>
+        <v>-48.878</v>
       </c>
     </row>
     <row r="19">
@@ -3923,27 +3930,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>73.55709052781789</v>
+        <v>83.68283999170649</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>24.91776691656204</v>
+        <v>28.373662392288</v>
       </c>
       <c r="K19" t="n">
-        <v>-17.71549271538467</v>
+        <v>-18.02705376434217</v>
       </c>
       <c r="L19" t="n">
         <v>17.14344300175863</v>
@@ -3952,13 +3959,13 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>134.7</v>
+        <v>134.9</v>
       </c>
       <c r="O19" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="P19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3969,19 +3976,19 @@
         <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.437</v>
+        <v>29.949</v>
       </c>
       <c r="T19" t="n">
-        <v>30.437</v>
+        <v>29.949</v>
       </c>
       <c r="U19" t="n">
-        <v>13.67</v>
+        <v>14.328</v>
       </c>
       <c r="V19" t="n">
-        <v>5.823</v>
+        <v>5.38</v>
       </c>
       <c r="W19" t="n">
-        <v>-47.982</v>
+        <v>-48.878</v>
       </c>
     </row>
     <row r="20">
@@ -3992,7 +3999,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2 | 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4012,27 +4019,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>71.64483370334607</v>
+        <v>79.44046302924768</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>34.63450038557985</v>
+        <v>39.06030755509926</v>
       </c>
       <c r="K20" t="n">
-        <v>-12.8335715805579</v>
+        <v>-13.16361747581136</v>
       </c>
       <c r="L20" t="n">
         <v>15.76726005038759</v>
@@ -4041,10 +4048,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>136.1</v>
+        <v>136.4</v>
       </c>
       <c r="O20" t="n">
-        <v>41.1</v>
+        <v>40.7</v>
       </c>
       <c r="P20" t="n">
         <v>4.4</v>
@@ -4058,25 +4065,25 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="T20" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="U20" t="n">
-        <v>18.734</v>
+        <v>18.713</v>
       </c>
       <c r="V20" t="n">
-        <v>1.114</v>
+        <v>-0.28</v>
       </c>
       <c r="W20" t="n">
-        <v>-37.921</v>
+        <v>-38.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4101,27 +4108,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AGHOL.IS, BRSAN.IS, ENJSA.IS</t>
+          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-08-13 | BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12</t>
+          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>71.64483370334607</v>
+        <v>79.44046302924768</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +0.34% / +2.80% / 0.00% | BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>34.63450038557985</v>
+        <v>39.06030755509926</v>
       </c>
       <c r="K21" t="n">
-        <v>-12.8335715805579</v>
+        <v>-13.16361747581136</v>
       </c>
       <c r="L21" t="n">
         <v>15.76726005038759</v>
@@ -4130,10 +4137,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>136.1</v>
+        <v>136.4</v>
       </c>
       <c r="O21" t="n">
-        <v>41.1</v>
+        <v>40.7</v>
       </c>
       <c r="P21" t="n">
         <v>4.4</v>
@@ -4147,19 +4154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="T21" t="n">
-        <v>25.02</v>
+        <v>24.494</v>
       </c>
       <c r="U21" t="n">
-        <v>18.734</v>
+        <v>18.713</v>
       </c>
       <c r="V21" t="n">
-        <v>1.114</v>
+        <v>-0.28</v>
       </c>
       <c r="W21" t="n">
-        <v>-37.921</v>
+        <v>-38.51</v>
       </c>
     </row>
     <row r="22">
@@ -4199,18 +4206,18 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>69.61350586989693</v>
+        <v>69.61350586989698</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +2.24% / +4.56% / -1.13% | ENJSA.IS: +0.82% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.28% / +24.13% / -0.52%</t>
+          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.19% / +24.13% / -0.52%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>43.30443180651103</v>
+        <v>43.10920851715343</v>
       </c>
       <c r="K22" t="n">
-        <v>-19.57965489967173</v>
+        <v>-19.74574732903608</v>
       </c>
       <c r="L22" t="n">
         <v>9.921570716242634</v>
@@ -4219,7 +4226,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N22" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>50.9</v>
@@ -4236,35 +4243,35 @@
         <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>25.467</v>
+        <v>25.31</v>
       </c>
       <c r="T22" t="n">
-        <v>25.467</v>
+        <v>25.31</v>
       </c>
       <c r="U22" t="n">
-        <v>6.921</v>
+        <v>5.82</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.805</v>
+        <v>-7.047</v>
       </c>
       <c r="W22" t="n">
-        <v>-35.937</v>
+        <v>-35.859</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|coklu_zarf</t>
+          <t>T3_kademeli_slot|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4280,29 +4287,29 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>31.15183851699386</v>
+        <v>27.44212969659623</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>14.46263148924893</v>
+        <v>-1.325508829134781</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.48115478119579</v>
+        <v>9.807845239497247</v>
       </c>
       <c r="L23" t="n">
-        <v>6.329965794996994</v>
+        <v>23.0569390189834</v>
       </c>
       <c r="M23" t="n">
-        <v>44.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>26.7</v>
+        <v>136.9</v>
       </c>
       <c r="O23" t="n">
-        <v>42.6</v>
+        <v>47.5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -4313,19 +4320,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>30.337</v>
+        <v>14.102</v>
       </c>
       <c r="T23" t="n">
-        <v>25.773</v>
+        <v>14.102</v>
       </c>
       <c r="U23" t="n">
-        <v>-23.576</v>
+        <v>56.349</v>
       </c>
       <c r="V23" t="n">
-        <v>-25.721</v>
+        <v>46.317</v>
       </c>
       <c r="W23" t="n">
-        <v>-33.203</v>
+        <v>-16.891</v>
       </c>
     </row>
     <row r="24">
@@ -4336,12 +4343,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T1_genislik_skor|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4357,29 +4364,29 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>27.77992134829283</v>
+        <v>-7.609034621162936</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-0.3947387514697143</v>
+        <v>-18.83545908828166</v>
       </c>
       <c r="K24" t="n">
-        <v>10.01971019808436</v>
+        <v>4.779352275141924</v>
       </c>
       <c r="L24" t="n">
-        <v>23.0569390189834</v>
+        <v>34.76409501205259</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N24" t="n">
-        <v>136.6</v>
+        <v>43.2</v>
       </c>
       <c r="O24" t="n">
-        <v>47.5</v>
+        <v>43.7</v>
       </c>
       <c r="P24" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4390,19 +4397,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>14.102</v>
+        <v>11.176</v>
       </c>
       <c r="T24" t="n">
-        <v>14.102</v>
+        <v>11.176</v>
       </c>
       <c r="U24" t="n">
-        <v>58.16</v>
+        <v>30.95</v>
       </c>
       <c r="V24" t="n">
-        <v>46.891</v>
+        <v>25.214</v>
       </c>
       <c r="W24" t="n">
-        <v>-16.745</v>
+        <v>-3.614</v>
       </c>
     </row>
     <row r="25">
@@ -4413,12 +4420,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4433,42 +4440,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SASA.IS, TKFEN.IS, TRALT.IS</t>
+          <t>CWENE.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SASA.IS: 2026-08-14 | TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-13</t>
+          <t>CWENE.IS: 2026-08-14 | RALYH.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.50616295266203</v>
+        <v>-18.12728286424745</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SASA.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.94% / +0.00% / -1.55%</t>
+          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.3486754611526699</v>
+        <v>-39.30005974862217</v>
       </c>
       <c r="K25" t="n">
-        <v>5.40669718472091</v>
+        <v>7.253780702616264</v>
       </c>
       <c r="L25" t="n">
-        <v>11.73786047909323</v>
+        <v>49.48136038965337</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>130.2</v>
+        <v>121</v>
       </c>
       <c r="O25" t="n">
-        <v>47.1</v>
+        <v>43.9</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4476,111 +4483,22 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>13.751</v>
+        <v>23.673</v>
       </c>
       <c r="T25" t="n">
-        <v>13.751</v>
+        <v>21.907</v>
       </c>
       <c r="U25" t="n">
-        <v>37.706</v>
+        <v>17.569</v>
       </c>
       <c r="V25" t="n">
-        <v>26.712</v>
+        <v>24.723</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.884</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LAST_3_TOP3</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>CWENE.IS, RALYH.IS</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>CWENE.IS: 2026-08-13 | RALYH.IS: 2026-08-13</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>-17.85349196318069</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>CWENE.IS: +0.14% / +2.26% / -3.25% | RALYH.IS: +0.92% / +1.54% / -0.98%</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>-38.46787682799764</v>
-      </c>
-      <c r="K26" t="n">
-        <v>7.739333417787675</v>
-      </c>
-      <c r="L26" t="n">
-        <v>49.48136038965337</v>
-      </c>
-      <c r="M26" t="n">
-        <v>100</v>
-      </c>
-      <c r="N26" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>23.673</v>
-      </c>
-      <c r="T26" t="n">
-        <v>21.907</v>
-      </c>
-      <c r="U26" t="n">
-        <v>19.904</v>
-      </c>
-      <c r="V26" t="n">
-        <v>25.294</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-17.773</v>
+        <v>-18.041</v>
       </c>
     </row>
   </sheetData>

--- a/ATL.xlsx
+++ b/ATL.xlsx
@@ -582,10 +582,10 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -740,16 +740,8 @@
           <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
@@ -815,34 +807,14 @@
           <t>T2_rotasyon|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, KCHOL.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-14 | KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>73.33744768345549</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.31% / +2.55% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>8.066976193836894</v>
       </c>
@@ -866,11 +838,11 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>37.087</v>
@@ -902,34 +874,14 @@
           <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, OYAKC.IS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>72.46555718063254</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.36% / +4.85% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>25.51016247674216</v>
       </c>
@@ -953,11 +905,11 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>30.754</v>
@@ -989,16 +941,8 @@
           <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
@@ -1064,16 +1008,8 @@
           <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
@@ -1139,34 +1075,14 @@
           <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, OYAKC.IS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>72.46555718063254</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.36% / +4.85% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>25.51016247674216</v>
       </c>
@@ -1190,11 +1106,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>30.754</v>
@@ -1226,34 +1142,14 @@
           <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-14 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>40.06047860324801</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>23.81201687014565</v>
       </c>
@@ -1277,11 +1173,11 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>29.822</v>
@@ -1313,16 +1209,8 @@
           <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
@@ -1388,16 +1276,8 @@
           <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
@@ -1463,34 +1343,14 @@
           <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ARCLK.IS, BRSAN.IS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ARCLK.IS: 2026-07-17 | BRSAN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>17.86582823895642</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ARCLK.IS: -3.04% / +4.30% / -3.23% | BRSAN.IS: +11.40% / +14.10% / -2.42%</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>3.794219766359896</v>
       </c>
@@ -1514,11 +1374,11 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>11.893</v>
@@ -1550,16 +1410,8 @@
           <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
@@ -1625,34 +1477,14 @@
           <t>T6_skor_momentum|E30|S5|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TRALT.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>19.05950372123677</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>2.288788066639036</v>
       </c>
@@ -1676,11 +1508,11 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>9.945</v>
@@ -1838,16 +1670,8 @@
           <t>T4_konsensus|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
@@ -1915,34 +1739,14 @@
           <t>T2_rotasyon|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, KCHOL.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-14 | KCHOL.IS: 2026-08-10 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>73.33744768345549</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | KCHOL.IS: -0.31% / +2.55% / -3.48% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>8.066976193836894</v>
       </c>
@@ -1966,11 +1770,11 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>37.087</v>
@@ -2004,34 +1808,14 @@
           <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, OYAKC.IS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | OYAKC.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>72.46555718063254</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.36% / +4.85% / -1.11% | OYAKC.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>25.51016247674216</v>
       </c>
@@ -2055,11 +1839,11 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>30.754</v>
@@ -2093,16 +1877,8 @@
           <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|hacim_kirilim</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
@@ -2170,34 +1946,14 @@
           <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-14 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>40.06047860324801</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>23.81201687014565</v>
       </c>
@@ -2221,11 +1977,11 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>29.822</v>
@@ -2259,34 +2015,14 @@
           <t>T6_skor_momentum|E30|S5|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|Bvolatilite</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>TKFEN.IS, TRALT.IS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: 2026-08-14 | TRALT.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>19.05950372123677</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>TKFEN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>2.288788066639036</v>
       </c>
@@ -2310,11 +2046,11 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>9.945</v>
@@ -2348,34 +2084,14 @@
           <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ARCLK.IS, BRSAN.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARCLK.IS: 2026-07-17 | BRSAN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>17.86582823895642</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ARCLK.IS: -3.04% / +4.30% / -3.23% | BRSAN.IS: +11.40% / +14.10% / -2.42%</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>3.794219766359896</v>
       </c>
@@ -2399,11 +2115,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>11.893</v>
@@ -2437,16 +2153,8 @@
           <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
@@ -2525,10 +2233,10 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -2683,34 +2391,14 @@
           <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>83.68283999170649</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>28.373662392288</v>
       </c>
@@ -2734,11 +2422,11 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>29.949</v>
@@ -2770,34 +2458,14 @@
           <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>83.68283999170649</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>28.373662392288</v>
       </c>
@@ -2821,11 +2489,11 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>29.949</v>
@@ -2857,34 +2525,14 @@
           <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14 | TRMET.IS: 2026-07-20</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>69.61350586989698</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.19% / +24.13% / -0.52%</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>43.10920851715343</v>
       </c>
@@ -2908,11 +2556,11 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>25.31</v>
@@ -2944,34 +2592,14 @@
           <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14 | TRMET.IS: 2026-07-20</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>69.61350586989698</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.19% / +24.13% / -0.52%</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>43.10920851715343</v>
       </c>
@@ -2995,11 +2623,11 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>25.31</v>
@@ -3031,34 +2659,14 @@
           <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>79.44046302924768</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>39.06030755509926</v>
       </c>
@@ -3082,11 +2690,11 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>24.494</v>
@@ -3118,34 +2726,14 @@
           <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>79.44046302924768</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>39.06030755509926</v>
       </c>
@@ -3169,11 +2757,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>24.494</v>
@@ -3205,34 +2793,14 @@
           <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14 | TRMET.IS: 2026-07-20</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>69.61350586989698</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.19% / +24.13% / -0.52%</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>43.10920851715343</v>
       </c>
@@ -3256,11 +2824,11 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>25.31</v>
@@ -3292,34 +2860,14 @@
           <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>79.44046302924768</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>39.06030755509926</v>
       </c>
@@ -3343,11 +2891,11 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>24.494</v>
@@ -3379,34 +2927,14 @@
           <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>79.44046302924768</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>39.06030755509926</v>
       </c>
@@ -3430,11 +2958,11 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>24.494</v>
@@ -3466,16 +2994,8 @@
           <t>T3_kademeli_slot|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
@@ -3541,34 +3061,14 @@
           <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CWENE.IS, RALYH.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CWENE.IS: 2026-08-14 | RALYH.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>-18.12728286424745</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>-39.30005974862217</v>
       </c>
@@ -3592,11 +3092,11 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>23.673</v>
@@ -3628,16 +3128,8 @@
           <t>T1_genislik_skor|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
@@ -3829,34 +3321,14 @@
           <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>83.68283999170649</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>28.373662392288</v>
       </c>
@@ -3880,11 +3352,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>29.949</v>
@@ -3918,34 +3390,14 @@
           <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>83.68283999170649</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>28.373662392288</v>
       </c>
@@ -3969,11 +3421,11 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>29.949</v>
@@ -4007,34 +3459,14 @@
           <t>T1_genislik_skor|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>79.44046302924768</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>39.06030755509926</v>
       </c>
@@ -4058,11 +3490,11 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>24.494</v>
@@ -4096,34 +3528,14 @@
           <t>T5_tek_sistem|E30|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>79.44046302924768</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>39.06030755509926</v>
       </c>
@@ -4147,11 +3559,11 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>24.494</v>
@@ -4185,34 +3597,14 @@
           <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, ENJSA.IS, TKFEN.IS, TRMET.IS</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | ENJSA.IS: 2026-08-12 | TKFEN.IS: 2026-08-14 | TRMET.IS: 2026-07-20</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>69.61350586989698</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +2.08% / +4.56% / -1.13% | ENJSA.IS: +1.48% / +1.85% / -0.67% | TKFEN.IS: -0.02% / +0.00% / 0.00% | TRMET.IS: +10.19% / +24.13% / -0.52%</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>43.10920851715343</v>
       </c>
@@ -4236,11 +3628,11 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>25.31</v>
@@ -4274,16 +3666,8 @@
           <t>T3_kademeli_slot|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
@@ -4351,16 +3735,8 @@
           <t>T1_genislik_skor|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
@@ -4428,34 +3804,14 @@
           <t>T5_tek_sistem|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>CWENE.IS, RALYH.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>CWENE.IS: 2026-08-14 | RALYH.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>-18.12728286424745</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>CWENE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>-39.30005974862217</v>
       </c>
@@ -4479,11 +3835,11 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>23.673</v>
